--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="383">
   <si>
     <r>
       <rPr>
@@ -3778,9 +3778,24 @@
     <t xml:space="preserve">備註</t>
   </si>
   <si>
+    <t xml:space="preserve">2330</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台積電</t>
+  </si>
+  <si>
+    <t xml:space="preserve">半導體業</t>
+  </si>
+  <si>
     <t xml:space="preserve">核心</t>
   </si>
   <si>
+    <t xml:space="preserve">2408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南亞科</t>
+  </si>
+  <si>
     <t xml:space="preserve">觀察</t>
   </si>
   <si>
@@ -3825,6 +3840,15 @@
       </rPr>
       <t xml:space="preserve">N/M</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">5289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宜鼎</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電腦及週邊設備業</t>
   </si>
   <si>
     <r>
@@ -6042,13 +6066,13 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0;[RED]\-0.0"/>
-    <numFmt numFmtId="170" formatCode="#,##0;[RED]\-#,##0"/>
-    <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0;[RED]\-0.0"/>
+    <numFmt numFmtId="169" formatCode="#,##0;[RED]\-#,##0"/>
+    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="171" formatCode="General"/>
     <numFmt numFmtId="172" formatCode="0"/>
     <numFmt numFmtId="173" formatCode="#,##0"/>
   </numFmts>
@@ -6478,6 +6502,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6494,19 +6522,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6518,7 +6542,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6542,7 +6566,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6550,7 +6574,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6558,7 +6582,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6566,15 +6598,7 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6586,7 +6610,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6610,19 +6634,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6634,19 +6658,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6658,7 +6682,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6670,7 +6694,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6682,11 +6706,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6694,11 +6718,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6714,7 +6738,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6726,7 +6750,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6734,7 +6758,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6750,7 +6774,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="34" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7588,61 +7612,61 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="76" t="n">
-        <v>2330</v>
+      <c r="A2" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D2" s="78"/>
       <c r="E2" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="76" t="n">
-        <v>2408</v>
+      <c r="A3" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="80" t="n">
         <v>518</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D3" s="78"/>
       <c r="E3" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="76" t="n">
-        <v>5289</v>
+      <c r="A4" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
   </sheetData>
@@ -7710,16 +7734,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -7728,13 +7752,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -7743,7 +7767,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -7752,16 +7776,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -7770,16 +7794,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -7788,7 +7812,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -7797,7 +7821,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -7806,7 +7830,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -7818,29 +7842,29 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="16" t="str">
         <f aca="false">IF(Tickers!A2="","",Tickers!A2)</f>
         <v>2330</v>
       </c>
-      <c r="B2" s="66" t="n">
+      <c r="B2" s="66" t="str">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A2,Tickers!$A$2:$A$100,0)),""))</f>
-        <v>0</v>
+        <v>台積電</v>
       </c>
       <c r="C2" s="66" t="str">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A2,Tickers!$A$2:$A$100,0)),""))</f>
@@ -7848,7 +7872,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -7864,7 +7888,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>130.696847561644</v>
+        <v>130.79132890411</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -7872,15 +7896,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>28.2800185442745</v>
+        <v>27.6425591098748</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>25.1464808273027</v>
+        <v>24.5796544152119</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.6691572560628</v>
+        <v>18.2351538132056</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -7888,11 +7912,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>0.531347295371403</v>
+        <v>0.519370204697048</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.5827378144898</v>
+        <v>0.569190860318125</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -7900,7 +7924,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.0090164345</v>
+        <v>0.0092243606624738</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -7992,7 +8016,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8016,13 +8040,13 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="16" t="str">
         <f aca="false">IF(Tickers!A3="","",Tickers!A3)</f>
         <v>2408</v>
       </c>
-      <c r="B3" s="66" t="n">
+      <c r="B3" s="66" t="str">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A3,Tickers!$A$2:$A$100,0)),""))</f>
-        <v>0</v>
+        <v>南亞科</v>
       </c>
       <c r="C3" s="66" t="str">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A3,Tickers!$A$2:$A$100,0)),""))</f>
@@ -8046,7 +8070,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>85.55499</v>
+        <v>85.63905</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8062,7 +8086,7 @@
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>6.05458547771439</v>
+        <v>6.04864252931344</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8074,7 +8098,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.128354690197599</v>
+        <v>0.128228702166929</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8174,7 +8198,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8198,13 +8222,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="16" t="str">
         <f aca="false">IF(Tickers!A4="","",Tickers!A4)</f>
         <v>5289</v>
       </c>
-      <c r="B4" s="66" t="n">
+      <c r="B4" s="66" t="str">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A4,Tickers!$A$2:$A$100,0)),""))</f>
-        <v>0</v>
+        <v>宜鼎</v>
       </c>
       <c r="C4" s="66" t="str">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A4,Tickers!$A$2:$A$100,0)),""))</f>
@@ -8212,7 +8236,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8228,7 +8252,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>223.23662739726</v>
+        <v>246.897867534247</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8236,23 +8260,23 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>7.94302930703917</v>
+        <v>7.77869076965215</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>5.27867778222724</v>
+        <v>5.16946375914668</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>6.49534987562617</v>
+        <v>5.75136599672347</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>-0.512857668531057</v>
+        <v>-0.44842611440624</v>
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.00497017258734989</v>
+        <v>0.00486734143037023</v>
       </c>
       <c r="O4" s="51" t="str">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
@@ -8264,7 +8288,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00646706051034483</v>
+        <v>0.00660368854929578</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8332,7 +8356,7 @@
       </c>
       <c r="AH4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(AD4&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/AD4),"N/M"))</f>
-        <v>1.40566766680559</v>
+        <v>1.46159230182731</v>
       </c>
       <c r="AI4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,0),""))</f>
@@ -8348,7 +8372,7 @@
       </c>
       <c r="AL4" s="47" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A4,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -8356,7 +8380,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -11475,7 +11499,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -11504,78 +11528,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -11741,13 +11765,13 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="16" t="str">
         <f aca="false">IF(Calc!$A$2="","",Calc!A$2)</f>
         <v>2330</v>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="16" t="str">
         <f aca="false">IF(Calc!$A$2="","",Calc!B$2)</f>
-        <v>0</v>
+        <v>台積電</v>
       </c>
       <c r="C3" s="16" t="str">
         <f aca="false">IF(Calc!$A$2="","",Calc!C$2)</f>
@@ -11755,27 +11779,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>28.2800185442745</v>
+        <v>27.6425591098748</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.6691572560628</v>
+        <v>18.2351538132056</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>0.531347295371403</v>
+        <v>0.519370204697048</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.5827378144898</v>
+        <v>0.569190860318125</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.0090164345</v>
+        <v>0.0092243606624738</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -11859,13 +11883,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="16" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!A$3)</f>
         <v>2408</v>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="16" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!B$3)</f>
-        <v>0</v>
+        <v>南亞科</v>
       </c>
       <c r="C4" s="16" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!C$3)</f>
@@ -11881,7 +11905,7 @@
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>6.05458547771439</v>
+        <v>6.04864252931344</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -11889,7 +11913,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.128354690197599</v>
+        <v>0.128228702166929</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -11977,13 +12001,13 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="16" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!A$4)</f>
         <v>5289</v>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="16" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!B$4)</f>
-        <v>0</v>
+        <v>宜鼎</v>
       </c>
       <c r="C5" s="16" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!C$4)</f>
@@ -11991,19 +12015,19 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>1450</v>
+        <v>1420</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>7.94302930703917</v>
+        <v>7.77869076965215</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>6.49534987562617</v>
+        <v>5.75136599672347</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.00497017258734989</v>
+        <v>0.00486734143037023</v>
       </c>
       <c r="H5" s="17" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
@@ -12011,7 +12035,7 @@
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00646706051034483</v>
+        <v>0.00660368854929578</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12075,7 +12099,7 @@
       </c>
       <c r="Y5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AH$4)</f>
-        <v>1.40566766680559</v>
+        <v>1.46159230182731</v>
       </c>
       <c r="Z5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AI$4)</f>
@@ -16499,7 +16523,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2F93C2CF-31DD-479B-9724-836DF980E089}</x14:id>
+          <x14:id>{C0625DDC-5729-4C6C-8821-3F1BB92CD42E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16630,7 +16654,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2F93C2CF-31DD-479B-9724-836DF980E089}">
+          <x14:cfRule type="dataBar" id="{C0625DDC-5729-4C6C-8821-3F1BB92CD42E}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16703,7 +16727,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="16" t="str">
         <f aca="false">IF(Calc!$A$2="","",Calc!$A$2)</f>
         <v>2330</v>
       </c>
@@ -16733,11 +16757,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46266</v>
+        <v>-46267</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="J4" s="72" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -16745,7 +16769,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="16" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!$A$3)</f>
         <v>2408</v>
       </c>
@@ -16775,11 +16799,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46266</v>
+        <v>-46267</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="J5" s="72" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -16787,7 +16811,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="16" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!$A$4)</f>
         <v>5289</v>
       </c>
@@ -16817,11 +16841,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46266</v>
+        <v>-46267</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="J6" s="72" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -17615,13 +17639,17 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="73" t="n">
-        <v>2330</v>
-      </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
+      <c r="A2" s="73" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="74" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" s="74" t="s">
+        <v>169</v>
+      </c>
       <c r="D2" s="74" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E2" s="73"/>
       <c r="F2" s="75" t="n">
@@ -17630,32 +17658,40 @@
       <c r="G2" s="73"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="73" t="n">
-        <v>2408</v>
-      </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
+      <c r="A3" s="73" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="74" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>169</v>
+      </c>
       <c r="D3" s="74" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E3" s="73" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F3" s="75" t="n">
         <v>46264</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="73" t="n">
-        <v>5289</v>
-      </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
+      <c r="A4" s="73" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>178</v>
+      </c>
       <c r="D4" s="74" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E4" s="73"/>
       <c r="F4" s="75" t="n">
@@ -17818,7 +17854,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -17861,66 +17897,66 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="76" t="n">
-        <v>2330</v>
+      <c r="A2" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C2" s="77" t="n">
         <v>2026</v>
@@ -17932,13 +17968,13 @@
         <v>46295</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I2" s="79"/>
       <c r="J2" s="79"/>
@@ -17955,15 +17991,15 @@
         <v>0</v>
       </c>
       <c r="S2" s="66" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="76" t="n">
-        <v>2330</v>
+      <c r="A3" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C3" s="77" t="n">
         <v>2026</v>
@@ -17975,13 +18011,13 @@
         <v>46203</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G3" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H3" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I3" s="79" t="n">
         <v>1270380.25</v>
@@ -18014,15 +18050,15 @@
         <v>1</v>
       </c>
       <c r="S3" s="66" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="76" t="n">
-        <v>2330</v>
+      <c r="A4" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C4" s="77" t="n">
         <v>2026</v>
@@ -18034,13 +18070,13 @@
         <v>46112</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H4" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I4" s="79" t="n">
         <v>1134103.44</v>
@@ -18073,15 +18109,15 @@
         <v>2</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="76" t="n">
-        <v>2330</v>
+      <c r="A5" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C5" s="77" t="n">
         <v>2025</v>
@@ -18093,13 +18129,13 @@
         <v>46022</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G5" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H5" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I5" s="79" t="n">
         <v>1046090.421</v>
@@ -18132,15 +18168,15 @@
         <v>3</v>
       </c>
       <c r="S5" s="66" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="76" t="n">
-        <v>2330</v>
+      <c r="A6" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C6" s="77" t="n">
         <v>2025</v>
@@ -18152,13 +18188,13 @@
         <v>45930</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G6" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H6" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I6" s="79" t="n">
         <v>989918.318</v>
@@ -18191,15 +18227,15 @@
         <v>4</v>
       </c>
       <c r="S6" s="66" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="76" t="n">
-        <v>2330</v>
+      <c r="A7" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C7" s="77" t="n">
         <v>2025</v>
@@ -18211,13 +18247,13 @@
         <v>45838</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G7" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I7" s="79" t="n">
         <v>933791.869</v>
@@ -18250,15 +18286,15 @@
         <v>5</v>
       </c>
       <c r="S7" s="66" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="76" t="n">
-        <v>2330</v>
+      <c r="A8" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C8" s="77" t="n">
         <v>2025</v>
@@ -18270,13 +18306,13 @@
         <v>45747</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G8" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H8" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I8" s="79" t="n">
         <v>839253.664</v>
@@ -18309,15 +18345,15 @@
         <v>6</v>
       </c>
       <c r="S8" s="66" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="76" t="n">
-        <v>2330</v>
+      <c r="A9" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C9" s="77" t="n">
         <v>2024</v>
@@ -18329,13 +18365,13 @@
         <v>45657</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G9" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H9" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I9" s="79" t="n">
         <v>868461.178</v>
@@ -18368,15 +18404,15 @@
         <v>7</v>
       </c>
       <c r="S9" s="66" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="76" t="n">
-        <v>2330</v>
+      <c r="A10" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C10" s="77" t="n">
         <v>2024</v>
@@ -18388,13 +18424,13 @@
         <v>45565</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G10" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H10" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I10" s="79" t="n">
         <v>759692.143</v>
@@ -18427,15 +18463,15 @@
         <v>8</v>
       </c>
       <c r="S10" s="66" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="76" t="n">
-        <v>2330</v>
+      <c r="A11" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C11" s="77" t="n">
         <v>2024</v>
@@ -18447,13 +18483,13 @@
         <v>45473</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G11" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H11" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I11" s="79" t="n">
         <v>673510.177</v>
@@ -18486,15 +18522,15 @@
         <v>9</v>
       </c>
       <c r="S11" s="66" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="76" t="n">
-        <v>2330</v>
+      <c r="A12" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C12" s="77" t="n">
         <v>2024</v>
@@ -18506,13 +18542,13 @@
         <v>45382</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G12" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H12" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I12" s="79" t="n">
         <v>592644.201</v>
@@ -18545,15 +18581,15 @@
         <v>10</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="76" t="n">
-        <v>2330</v>
+      <c r="A13" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C13" s="77" t="n">
         <v>2023</v>
@@ -18565,13 +18601,13 @@
         <v>45291</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G13" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H13" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I13" s="79" t="n">
         <v>625528.856</v>
@@ -18604,15 +18640,15 @@
         <v>11</v>
       </c>
       <c r="S13" s="66" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="76" t="n">
-        <v>2330</v>
+      <c r="A14" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C14" s="77" t="n">
         <v>2023</v>
@@ -18624,13 +18660,13 @@
         <v>45199</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G14" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H14" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I14" s="79" t="n">
         <v>546732.758</v>
@@ -18663,15 +18699,15 @@
         <v>12</v>
       </c>
       <c r="S14" s="66" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="76" t="n">
-        <v>2330</v>
+      <c r="A15" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C15" s="77" t="n">
         <v>2023</v>
@@ -18683,13 +18719,13 @@
         <v>45107</v>
       </c>
       <c r="F15" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G15" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H15" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I15" s="79" t="n">
         <v>480841.254</v>
@@ -18722,15 +18758,15 @@
         <v>13</v>
       </c>
       <c r="S15" s="66" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="76" t="n">
-        <v>2330</v>
+      <c r="A16" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C16" s="77" t="n">
         <v>2023</v>
@@ -18742,13 +18778,13 @@
         <v>45016</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G16" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H16" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I16" s="79" t="n">
         <v>508632.973</v>
@@ -18781,15 +18817,15 @@
         <v>14</v>
       </c>
       <c r="S16" s="66" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="76" t="n">
-        <v>2330</v>
+      <c r="A17" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C17" s="77" t="n">
         <v>2022</v>
@@ -18801,13 +18837,13 @@
         <v>44926</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G17" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H17" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I17" s="79" t="n">
         <v>625531.868</v>
@@ -18840,15 +18876,15 @@
         <v>15</v>
       </c>
       <c r="S17" s="66" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="76" t="n">
-        <v>2330</v>
+      <c r="A18" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C18" s="77" t="n">
         <v>2022</v>
@@ -18860,13 +18896,13 @@
         <v>44834</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G18" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H18" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I18" s="79" t="n">
         <v>613142.743</v>
@@ -18899,15 +18935,15 @@
         <v>16</v>
       </c>
       <c r="S18" s="66" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="76" t="n">
-        <v>2330</v>
+      <c r="A19" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C19" s="77" t="n">
         <v>2022</v>
@@ -18919,13 +18955,13 @@
         <v>44742</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G19" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H19" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I19" s="79" t="n">
         <v>534140.808</v>
@@ -18958,15 +18994,15 @@
         <v>17</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="76" t="n">
-        <v>2330</v>
+      <c r="A20" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C20" s="77" t="n">
         <v>2022</v>
@@ -18978,13 +19014,13 @@
         <v>44651</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G20" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H20" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I20" s="79" t="n">
         <v>491075.873</v>
@@ -19017,15 +19053,15 @@
         <v>18</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="76" t="n">
-        <v>2330</v>
+      <c r="A21" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C21" s="77" t="n">
         <v>2021</v>
@@ -19037,13 +19073,13 @@
         <v>44561</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G21" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H21" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I21" s="79" t="n">
         <v>438189.306</v>
@@ -19076,15 +19112,15 @@
         <v>19</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="76" t="n">
-        <v>2330</v>
+      <c r="A22" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C22" s="77" t="n">
         <v>2021</v>
@@ -19096,13 +19132,13 @@
         <v>44469</v>
       </c>
       <c r="F22" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G22" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H22" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I22" s="79" t="n">
         <v>414670.379</v>
@@ -19135,15 +19171,15 @@
         <v>20</v>
       </c>
       <c r="S22" s="66" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="76" t="n">
-        <v>2330</v>
+      <c r="A23" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C23" s="77" t="n">
         <v>2021</v>
@@ -19155,13 +19191,13 @@
         <v>44377</v>
       </c>
       <c r="F23" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G23" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H23" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I23" s="79" t="n">
         <v>372145.122</v>
@@ -19194,15 +19230,15 @@
         <v>21</v>
       </c>
       <c r="S23" s="66" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="76" t="n">
-        <v>2330</v>
+      <c r="A24" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B24" s="76" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C24" s="77" t="n">
         <v>2021</v>
@@ -19214,13 +19250,13 @@
         <v>44286</v>
       </c>
       <c r="F24" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G24" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H24" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I24" s="79" t="n">
         <v>362410.23</v>
@@ -19253,15 +19289,15 @@
         <v>22</v>
       </c>
       <c r="S24" s="66" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="76" t="n">
-        <v>2330</v>
+      <c r="A25" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C25" s="77" t="n">
         <v>2020</v>
@@ -19273,13 +19309,13 @@
         <v>44196</v>
       </c>
       <c r="F25" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G25" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H25" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I25" s="79" t="n">
         <v>361533.057</v>
@@ -19312,15 +19348,15 @@
         <v>23</v>
       </c>
       <c r="S25" s="66" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="76" t="n">
-        <v>2330</v>
+      <c r="A26" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B26" s="76" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C26" s="77" t="n">
         <v>2020</v>
@@ -19332,13 +19368,13 @@
         <v>44104</v>
       </c>
       <c r="F26" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G26" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H26" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I26" s="79" t="n">
         <v>356426.204</v>
@@ -19369,15 +19405,15 @@
         <v>24</v>
       </c>
       <c r="S26" s="66" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="76" t="n">
-        <v>2408</v>
+      <c r="A27" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B27" s="76" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C27" s="77" t="n">
         <v>2026</v>
@@ -19389,13 +19425,13 @@
         <v>46295</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G27" s="76" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H27" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I27" s="79"/>
       <c r="J27" s="79"/>
@@ -19412,15 +19448,15 @@
         <v>0</v>
       </c>
       <c r="S27" s="66" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="76" t="n">
-        <v>2408</v>
+      <c r="A28" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C28" s="77" t="n">
         <v>2026</v>
@@ -19432,13 +19468,13 @@
         <v>46203</v>
       </c>
       <c r="F28" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G28" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H28" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I28" s="79" t="n">
         <v>82549.073</v>
@@ -19471,15 +19507,15 @@
         <v>1</v>
       </c>
       <c r="S28" s="66" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="76" t="n">
-        <v>2408</v>
+      <c r="A29" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B29" s="76" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C29" s="77" t="n">
         <v>2026</v>
@@ -19491,13 +19527,13 @@
         <v>46112</v>
       </c>
       <c r="F29" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G29" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H29" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I29" s="79" t="n">
         <v>49086.932</v>
@@ -19530,15 +19566,15 @@
         <v>2</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="76" t="n">
-        <v>2408</v>
+      <c r="A30" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C30" s="77" t="n">
         <v>2025</v>
@@ -19550,13 +19586,13 @@
         <v>46022</v>
       </c>
       <c r="F30" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G30" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H30" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I30" s="79" t="n">
         <v>30093.618</v>
@@ -19589,15 +19625,15 @@
         <v>3</v>
       </c>
       <c r="S30" s="66" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="76" t="n">
-        <v>2408</v>
+      <c r="A31" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C31" s="77" t="n">
         <v>2025</v>
@@ -19609,13 +19645,13 @@
         <v>45930</v>
       </c>
       <c r="F31" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G31" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H31" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I31" s="79" t="n">
         <v>18778.868</v>
@@ -19648,15 +19684,15 @@
         <v>4</v>
       </c>
       <c r="S31" s="66" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="76" t="n">
-        <v>2408</v>
+      <c r="A32" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C32" s="77" t="n">
         <v>2025</v>
@@ -19668,13 +19704,13 @@
         <v>45838</v>
       </c>
       <c r="F32" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G32" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H32" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I32" s="79" t="n">
         <v>10526.094</v>
@@ -19707,15 +19743,15 @@
         <v>5</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="76" t="n">
-        <v>2408</v>
+      <c r="A33" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B33" s="76" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C33" s="77" t="n">
         <v>2025</v>
@@ -19727,13 +19763,13 @@
         <v>45747</v>
       </c>
       <c r="F33" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G33" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H33" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I33" s="79" t="n">
         <v>7187.94</v>
@@ -19766,15 +19802,15 @@
         <v>6</v>
       </c>
       <c r="S33" s="66" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="76" t="n">
-        <v>2408</v>
+      <c r="A34" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B34" s="76" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C34" s="77" t="n">
         <v>2024</v>
@@ -19786,13 +19822,13 @@
         <v>45657</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G34" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H34" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I34" s="79" t="n">
         <v>6575.094</v>
@@ -19825,15 +19861,15 @@
         <v>7</v>
       </c>
       <c r="S34" s="66" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="76" t="n">
-        <v>2408</v>
+      <c r="A35" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B35" s="76" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C35" s="77" t="n">
         <v>2024</v>
@@ -19845,13 +19881,13 @@
         <v>45565</v>
       </c>
       <c r="F35" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G35" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H35" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I35" s="79" t="n">
         <v>8132.593</v>
@@ -19884,15 +19920,15 @@
         <v>8</v>
       </c>
       <c r="S35" s="66" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="76" t="n">
-        <v>2408</v>
+      <c r="A36" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B36" s="76" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C36" s="77" t="n">
         <v>2024</v>
@@ -19904,13 +19940,13 @@
         <v>45473</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G36" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H36" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I36" s="79" t="n">
         <v>9921.043</v>
@@ -19937,15 +19973,15 @@
         <v>9</v>
       </c>
       <c r="S36" s="66" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="76" t="n">
-        <v>2408</v>
+      <c r="A37" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C37" s="77" t="n">
         <v>2024</v>
@@ -19957,13 +19993,13 @@
         <v>45382</v>
       </c>
       <c r="F37" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G37" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H37" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I37" s="79" t="n">
         <v>9502.937</v>
@@ -19996,15 +20032,15 @@
         <v>10</v>
       </c>
       <c r="S37" s="66" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="76" t="n">
-        <v>2408</v>
+      <c r="A38" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C38" s="77" t="n">
         <v>2023</v>
@@ -20016,13 +20052,13 @@
         <v>45291</v>
       </c>
       <c r="F38" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G38" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H38" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I38" s="79" t="n">
         <v>8703.978</v>
@@ -20055,15 +20091,15 @@
         <v>11</v>
       </c>
       <c r="S38" s="66" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="76" t="n">
-        <v>2408</v>
+      <c r="A39" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C39" s="77" t="n">
         <v>2023</v>
@@ -20075,13 +20111,13 @@
         <v>45199</v>
       </c>
       <c r="F39" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G39" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H39" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I39" s="79" t="n">
         <v>7736.374</v>
@@ -20114,15 +20150,15 @@
         <v>12</v>
       </c>
       <c r="S39" s="66" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="76" t="n">
-        <v>2408</v>
+      <c r="A40" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C40" s="77" t="n">
         <v>2023</v>
@@ -20134,13 +20170,13 @@
         <v>45107</v>
       </c>
       <c r="F40" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G40" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H40" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I40" s="79" t="n">
         <v>7027.071</v>
@@ -20173,15 +20209,15 @@
         <v>13</v>
       </c>
       <c r="S40" s="66" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="76" t="n">
-        <v>2408</v>
+      <c r="A41" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B41" s="76" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C41" s="77" t="n">
         <v>2023</v>
@@ -20193,13 +20229,13 @@
         <v>45016</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G41" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H41" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I41" s="79" t="n">
         <v>6424.883</v>
@@ -20232,15 +20268,15 @@
         <v>14</v>
       </c>
       <c r="S41" s="66" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="76" t="n">
-        <v>2408</v>
+      <c r="A42" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C42" s="77" t="n">
         <v>2022</v>
@@ -20252,13 +20288,13 @@
         <v>44926</v>
       </c>
       <c r="F42" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G42" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H42" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I42" s="79" t="n">
         <v>7953.553</v>
@@ -20291,15 +20327,15 @@
         <v>15</v>
       </c>
       <c r="S42" s="66" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="76" t="n">
-        <v>2408</v>
+      <c r="A43" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B43" s="76" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C43" s="77" t="n">
         <v>2022</v>
@@ -20311,13 +20347,13 @@
         <v>44834</v>
       </c>
       <c r="F43" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G43" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H43" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I43" s="79" t="n">
         <v>11021.725</v>
@@ -20350,15 +20386,15 @@
         <v>16</v>
       </c>
       <c r="S43" s="66" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="76" t="n">
-        <v>2408</v>
+      <c r="A44" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B44" s="76" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C44" s="77" t="n">
         <v>2022</v>
@@ -20370,13 +20406,13 @@
         <v>44742</v>
       </c>
       <c r="F44" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G44" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H44" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I44" s="79" t="n">
         <v>18030.672</v>
@@ -20409,15 +20445,15 @@
         <v>17</v>
       </c>
       <c r="S44" s="66" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="76" t="n">
-        <v>2408</v>
+      <c r="A45" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B45" s="76" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C45" s="77" t="n">
         <v>2022</v>
@@ -20429,13 +20465,13 @@
         <v>44651</v>
       </c>
       <c r="F45" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G45" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H45" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I45" s="79" t="n">
         <v>19946.325</v>
@@ -20468,15 +20504,15 @@
         <v>18</v>
       </c>
       <c r="S45" s="66" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="76" t="n">
-        <v>2408</v>
+      <c r="A46" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B46" s="76" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C46" s="77" t="n">
         <v>2021</v>
@@ -20488,13 +20524,13 @@
         <v>44561</v>
       </c>
       <c r="F46" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G46" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H46" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I46" s="79" t="n">
         <v>21398.949</v>
@@ -20527,15 +20563,15 @@
         <v>19</v>
       </c>
       <c r="S46" s="66" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="76" t="n">
-        <v>2408</v>
+      <c r="A47" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C47" s="77" t="n">
         <v>2021</v>
@@ -20547,13 +20583,13 @@
         <v>44469</v>
       </c>
       <c r="F47" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G47" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H47" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I47" s="79" t="n">
         <v>23837.128</v>
@@ -20586,15 +20622,15 @@
         <v>20</v>
       </c>
       <c r="S47" s="66" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="76" t="n">
-        <v>2408</v>
+      <c r="A48" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B48" s="76" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C48" s="77" t="n">
         <v>2021</v>
@@ -20606,13 +20642,13 @@
         <v>44377</v>
       </c>
       <c r="F48" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G48" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H48" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I48" s="79" t="n">
         <v>22637.468</v>
@@ -20645,15 +20681,15 @@
         <v>21</v>
       </c>
       <c r="S48" s="66" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="76" t="n">
-        <v>2408</v>
+      <c r="A49" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B49" s="76" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C49" s="77" t="n">
         <v>2021</v>
@@ -20665,13 +20701,13 @@
         <v>44286</v>
       </c>
       <c r="F49" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G49" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H49" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I49" s="79" t="n">
         <v>17730.613</v>
@@ -20704,15 +20740,15 @@
         <v>22</v>
       </c>
       <c r="S49" s="66" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="76" t="n">
-        <v>2408</v>
+      <c r="A50" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B50" s="76" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C50" s="77" t="n">
         <v>2020</v>
@@ -20724,13 +20760,13 @@
         <v>44196</v>
       </c>
       <c r="F50" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G50" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H50" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I50" s="79" t="n">
         <v>14773.42</v>
@@ -20763,15 +20799,15 @@
         <v>23</v>
       </c>
       <c r="S50" s="66" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="76" t="n">
-        <v>2408</v>
+      <c r="A51" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B51" s="76" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C51" s="77" t="n">
         <v>2020</v>
@@ -20783,13 +20819,13 @@
         <v>44104</v>
       </c>
       <c r="F51" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G51" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H51" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I51" s="79" t="n">
         <v>15323.867</v>
@@ -20820,15 +20856,15 @@
         <v>24</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="76" t="n">
-        <v>5289</v>
+      <c r="A52" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B52" s="76" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="C52" s="77" t="n">
         <v>2026</v>
@@ -20840,13 +20876,13 @@
         <v>46295</v>
       </c>
       <c r="F52" s="76" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G52" s="76" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="H52" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
@@ -20863,15 +20899,15 @@
         <v>0</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="76" t="n">
-        <v>5289</v>
+      <c r="A53" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B53" s="76" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C53" s="77" t="n">
         <v>2026</v>
@@ -20883,13 +20919,13 @@
         <v>46203</v>
       </c>
       <c r="F53" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G53" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H53" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I53" s="79" t="n">
         <v>22443.411</v>
@@ -20922,15 +20958,15 @@
         <v>1</v>
       </c>
       <c r="S53" s="66" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="76" t="n">
-        <v>5289</v>
+      <c r="A54" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B54" s="76" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C54" s="77" t="n">
         <v>2026</v>
@@ -20942,13 +20978,13 @@
         <v>46112</v>
       </c>
       <c r="F54" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G54" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H54" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I54" s="79" t="n">
         <v>13182.608</v>
@@ -20981,15 +21017,15 @@
         <v>2</v>
       </c>
       <c r="S54" s="66" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="76" t="n">
-        <v>5289</v>
+      <c r="A55" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C55" s="77" t="n">
         <v>2025</v>
@@ -21001,13 +21037,13 @@
         <v>46022</v>
       </c>
       <c r="F55" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G55" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H55" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I55" s="79" t="n">
         <v>4806.69</v>
@@ -21040,15 +21076,15 @@
         <v>3</v>
       </c>
       <c r="S55" s="66" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="76" t="n">
-        <v>5289</v>
+      <c r="A56" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="C56" s="77" t="n">
         <v>2025</v>
@@ -21060,13 +21096,13 @@
         <v>45930</v>
       </c>
       <c r="F56" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G56" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H56" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I56" s="79" t="n">
         <v>3807.401</v>
@@ -21099,15 +21135,15 @@
         <v>4</v>
       </c>
       <c r="S56" s="66" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="76" t="n">
-        <v>5289</v>
+      <c r="A57" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C57" s="77" t="n">
         <v>2025</v>
@@ -21119,13 +21155,13 @@
         <v>45838</v>
       </c>
       <c r="F57" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G57" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H57" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I57" s="79" t="n">
         <v>3028.429</v>
@@ -21158,15 +21194,15 @@
         <v>5</v>
       </c>
       <c r="S57" s="66" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="76" t="n">
-        <v>5289</v>
+      <c r="A58" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C58" s="77" t="n">
         <v>2025</v>
@@ -21178,13 +21214,13 @@
         <v>45747</v>
       </c>
       <c r="F58" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G58" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H58" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I58" s="79" t="n">
         <v>2618.742</v>
@@ -21217,15 +21253,15 @@
         <v>6</v>
       </c>
       <c r="S58" s="66" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="76" t="n">
-        <v>5289</v>
+      <c r="A59" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C59" s="77" t="n">
         <v>2024</v>
@@ -21237,13 +21273,13 @@
         <v>45657</v>
       </c>
       <c r="F59" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G59" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H59" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I59" s="79" t="n">
         <v>2228.005</v>
@@ -21276,15 +21312,15 @@
         <v>7</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="76" t="n">
-        <v>5289</v>
+      <c r="A60" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="C60" s="77" t="n">
         <v>2024</v>
@@ -21296,13 +21332,13 @@
         <v>45565</v>
       </c>
       <c r="F60" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G60" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H60" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I60" s="79" t="n">
         <v>2321.419</v>
@@ -21335,15 +21371,15 @@
         <v>8</v>
       </c>
       <c r="S60" s="66" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="76" t="n">
-        <v>5289</v>
+      <c r="A61" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C61" s="77" t="n">
         <v>2024</v>
@@ -21355,13 +21391,13 @@
         <v>45473</v>
       </c>
       <c r="F61" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G61" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H61" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I61" s="79" t="n">
         <v>2190.229</v>
@@ -21394,15 +21430,15 @@
         <v>9</v>
       </c>
       <c r="S61" s="66" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="76" t="n">
-        <v>5289</v>
+      <c r="A62" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C62" s="77" t="n">
         <v>2024</v>
@@ -21414,13 +21450,13 @@
         <v>45382</v>
       </c>
       <c r="F62" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G62" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H62" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I62" s="79" t="n">
         <v>2175.989</v>
@@ -21453,15 +21489,15 @@
         <v>10</v>
       </c>
       <c r="S62" s="66" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="76" t="n">
-        <v>5289</v>
+      <c r="A63" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B63" s="76" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C63" s="77" t="n">
         <v>2023</v>
@@ -21473,13 +21509,13 @@
         <v>45291</v>
       </c>
       <c r="F63" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G63" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H63" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I63" s="79" t="n">
         <v>2130.049</v>
@@ -21512,15 +21548,15 @@
         <v>11</v>
       </c>
       <c r="S63" s="66" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="76" t="n">
-        <v>5289</v>
+      <c r="A64" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B64" s="76" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="C64" s="77" t="n">
         <v>2023</v>
@@ -21532,13 +21568,13 @@
         <v>45199</v>
       </c>
       <c r="F64" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G64" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H64" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I64" s="79" t="n">
         <v>1993.007</v>
@@ -21571,15 +21607,15 @@
         <v>12</v>
       </c>
       <c r="S64" s="66" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="76" t="n">
-        <v>5289</v>
+      <c r="A65" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B65" s="76" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C65" s="77" t="n">
         <v>2023</v>
@@ -21591,13 +21627,13 @@
         <v>45107</v>
       </c>
       <c r="F65" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G65" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H65" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I65" s="79" t="n">
         <v>1930.516</v>
@@ -21630,15 +21666,15 @@
         <v>13</v>
       </c>
       <c r="S65" s="66" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="76" t="n">
-        <v>5289</v>
+      <c r="A66" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B66" s="76" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C66" s="77" t="n">
         <v>2023</v>
@@ -21650,13 +21686,13 @@
         <v>45016</v>
       </c>
       <c r="F66" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G66" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H66" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I66" s="79" t="n">
         <v>2260.206</v>
@@ -21689,15 +21725,15 @@
         <v>14</v>
       </c>
       <c r="S66" s="66" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="76" t="n">
-        <v>5289</v>
+      <c r="A67" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B67" s="76" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="C67" s="77" t="n">
         <v>2022</v>
@@ -21709,13 +21745,13 @@
         <v>44926</v>
       </c>
       <c r="F67" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G67" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H67" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I67" s="79" t="n">
         <v>2286.572</v>
@@ -21748,15 +21784,15 @@
         <v>15</v>
       </c>
       <c r="S67" s="66" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="76" t="n">
-        <v>5289</v>
+      <c r="A68" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C68" s="77" t="n">
         <v>2022</v>
@@ -21768,13 +21804,13 @@
         <v>44834</v>
       </c>
       <c r="F68" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G68" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H68" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I68" s="79" t="n">
         <v>2560.341</v>
@@ -21807,15 +21843,15 @@
         <v>16</v>
       </c>
       <c r="S68" s="66" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="76" t="n">
-        <v>5289</v>
+      <c r="A69" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B69" s="76" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C69" s="77" t="n">
         <v>2022</v>
@@ -21827,13 +21863,13 @@
         <v>44742</v>
       </c>
       <c r="F69" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G69" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H69" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I69" s="79" t="n">
         <v>2866.579</v>
@@ -21866,15 +21902,15 @@
         <v>17</v>
       </c>
       <c r="S69" s="66" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="76" t="n">
-        <v>5289</v>
+      <c r="A70" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B70" s="76" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C70" s="77" t="n">
         <v>2022</v>
@@ -21886,13 +21922,13 @@
         <v>44651</v>
       </c>
       <c r="F70" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G70" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H70" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I70" s="79" t="n">
         <v>2589.737</v>
@@ -21925,15 +21961,15 @@
         <v>18</v>
       </c>
       <c r="S70" s="66" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="76" t="n">
-        <v>5289</v>
+      <c r="A71" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B71" s="76" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C71" s="77" t="n">
         <v>2021</v>
@@ -21945,13 +21981,13 @@
         <v>44561</v>
       </c>
       <c r="F71" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G71" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H71" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I71" s="79" t="n">
         <v>2396.847</v>
@@ -21984,15 +22020,15 @@
         <v>19</v>
       </c>
       <c r="S71" s="66" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="76" t="n">
-        <v>5289</v>
+      <c r="A72" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B72" s="76" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C72" s="77" t="n">
         <v>2021</v>
@@ -22004,13 +22040,13 @@
         <v>44469</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G72" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H72" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I72" s="79" t="n">
         <v>2973.845</v>
@@ -22043,15 +22079,15 @@
         <v>20</v>
       </c>
       <c r="S72" s="66" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="76" t="n">
-        <v>5289</v>
+      <c r="A73" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B73" s="76" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C73" s="77" t="n">
         <v>2021</v>
@@ -22063,13 +22099,13 @@
         <v>44377</v>
       </c>
       <c r="F73" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G73" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H73" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I73" s="79" t="n">
         <v>2885.046</v>
@@ -22102,15 +22138,15 @@
         <v>21</v>
       </c>
       <c r="S73" s="66" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="76" t="n">
-        <v>5289</v>
+      <c r="A74" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B74" s="76" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C74" s="77" t="n">
         <v>2021</v>
@@ -22122,13 +22158,13 @@
         <v>44286</v>
       </c>
       <c r="F74" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G74" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H74" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I74" s="79" t="n">
         <v>1939.92</v>
@@ -22161,15 +22197,15 @@
         <v>22</v>
       </c>
       <c r="S74" s="66" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="76" t="n">
-        <v>5289</v>
+      <c r="A75" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B75" s="76" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C75" s="77" t="n">
         <v>2020</v>
@@ -22181,13 +22217,13 @@
         <v>44196</v>
       </c>
       <c r="F75" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G75" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H75" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I75" s="79" t="n">
         <v>1575.49</v>
@@ -22220,15 +22256,15 @@
         <v>23</v>
       </c>
       <c r="S75" s="66" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="76" t="n">
-        <v>5289</v>
+      <c r="A76" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B76" s="76" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C76" s="77" t="n">
         <v>2020</v>
@@ -22240,13 +22276,13 @@
         <v>44104</v>
       </c>
       <c r="F76" s="76" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G76" s="76" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="H76" s="76" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I76" s="79" t="n">
         <v>1627.205</v>
@@ -22277,142 +22313,142 @@
         <v>24</v>
       </c>
       <c r="S76" s="66" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="81" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="42" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="82" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="82" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="82" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="82" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="82" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="82" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C85" s="24" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="82" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="82" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="C87" s="25" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="82" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="82" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C89" s="24" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="82" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="82" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="C91" s="25" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="82" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="82" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C93" s="24" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="82" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C94" s="25" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="82" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C95" s="24" t="s">
         <v>47</v>
@@ -22420,15 +22456,15 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="82" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="24" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -22464,24 +22500,24 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="76" t="n">
-        <v>2330</v>
+      <c r="A2" s="76" t="s">
+        <v>167</v>
       </c>
       <c r="B2" s="80" t="n">
         <v>107.6434</v>
@@ -22496,12 +22532,12 @@
         <v>23</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="76" t="n">
-        <v>2408</v>
+      <c r="A3" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="80" t="n">
         <v>65.04435</v>
@@ -22516,32 +22552,32 @@
         <v>6</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="76" t="n">
-        <v>5289</v>
+      <c r="A4" s="76" t="s">
+        <v>176</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>339.7</v>
+        <v>353.215</v>
       </c>
       <c r="C4" s="80" t="n">
-        <v>165.48225</v>
+        <v>194.82417</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46387</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dashboard!$A$2:$AC$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$76</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$101</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="412">
   <si>
     <r>
       <rPr>
@@ -3851,6 +3851,18 @@
     <t xml:space="preserve">電腦及週邊設備業</t>
   </si>
   <si>
+    <t xml:space="preserve">2455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通信網路業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">池子</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4362,6 +4374,81 @@
   </si>
   <si>
     <t xml:space="preserve">2408|24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2455|24</t>
   </si>
   <si>
     <t xml:space="preserve">5289|0</t>
@@ -6787,11 +6874,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="33">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F3864"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F2F2"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6846,7 +6941,23 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF69C180"/>
+          <fgColor rgb="FFC1E5CA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF68C07F"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE6F5EA"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6871,6 +6982,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8696B"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCFEFD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6910,7 +7029,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF9FDFA"/>
+          <fgColor rgb="FFE2F3E7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F6EB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7597,7 +7724,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -7612,16 +7739,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7656,16 +7783,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>1420</v>
+        <v>542</v>
       </c>
       <c r="C4" s="78" t="n">
         <v>46267</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="80" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C5" s="78" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78" t="n">
         <v>46267</v>
       </c>
     </row>
@@ -7734,16 +7876,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -7752,13 +7894,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -7767,7 +7909,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -7776,16 +7918,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -7794,16 +7936,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -7812,7 +7954,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -7821,7 +7963,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -7830,7 +7972,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -7842,19 +7984,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8406,183 +8548,183 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="str">
         <f aca="false">IF(Tickers!A5="","",Tickers!A5)</f>
-        <v/>
+        <v>2455</v>
       </c>
       <c r="B5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A5,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>全新</v>
       </c>
       <c r="C5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A5,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D5" s="51" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E5" s="48" t="str">
+        <v>542</v>
+      </c>
+      <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="F5" s="51" t="str">
+        <v>3797.076</v>
+      </c>
+      <c r="F5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="G5" s="51" t="str">
+        <v>4.12</v>
+      </c>
+      <c r="G5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=0",Raw_Q!$R$2:$R$600,"&lt;=3"),""))</f>
-        <v/>
-      </c>
-      <c r="H5" s="51" t="str">
+        <v>4.69429</v>
+      </c>
+      <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v/>
-      </c>
-      <c r="I5" s="49" t="str">
+        <v>7.64497863013699</v>
+      </c>
+      <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
-        <v/>
-      </c>
-      <c r="J5" s="52" t="str">
+        <v>0.615686274509804</v>
+      </c>
+      <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="K5" s="52" t="str">
+        <v>131.553398058252</v>
+      </c>
+      <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="L5" s="52" t="str">
+        <v>115.459419848369</v>
+      </c>
+      <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="M5" s="49" t="str">
+        <v>70.8962086386222</v>
+      </c>
+      <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v/>
-      </c>
-      <c r="N5" s="51" t="str">
+        <v>0.65497812753633</v>
+      </c>
+      <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="O5" s="51" t="str">
+        <v>2.13669531878053</v>
+      </c>
+      <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="P5" s="51" t="str">
+        <v>1.08242101007701</v>
+      </c>
+      <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="Q5" s="49" t="str">
+        <v>2.62055653</v>
+      </c>
+      <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v/>
-      </c>
-      <c r="R5" s="49" t="str">
+        <v>0.00483497514760148</v>
+      </c>
+      <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
-        <v/>
-      </c>
-      <c r="S5" s="49" t="str">
+        <v>-0.18555809814312</v>
+      </c>
+      <c r="S5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="T5" s="49" t="str">
+        <v>0.351898298106533</v>
+      </c>
+      <c r="T5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,2)-1,""))</f>
-        <v/>
-      </c>
-      <c r="U5" s="49" t="str">
+        <v>0.00632016762047738</v>
+      </c>
+      <c r="U5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,3)-1,""))</f>
-        <v/>
-      </c>
-      <c r="V5" s="68" t="str">
+        <v>-0.000290749477120045</v>
+      </c>
+      <c r="V5" s="68" t="n">
         <f aca="false">IF($A5="","",IFERROR((T5-U5)*100,""))</f>
-        <v/>
+        <v>0.661091709759742</v>
       </c>
       <c r="W5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(IF(NOT(ISNUMBER(T5)),"",IF(T5&gt;0,IF(V5&gt;0,"成長且加速","成長但減速"),IF(V5&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
-        <v/>
-      </c>
-      <c r="X5" s="68" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="X5" s="68" t="n">
         <f aca="false">IF($A5="","",IFERROR((T5-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,6)-1))*100,""))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="49" t="str">
+        <v>10.6584385556805</v>
+      </c>
+      <c r="Y5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="Z5" s="49" t="str">
+        <v>4.75</v>
+      </c>
+      <c r="Z5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/E5,""))</f>
-        <v/>
-      </c>
-      <c r="AA5" s="49" t="str">
+        <v>0.367558352795678</v>
+      </c>
+      <c r="AA5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v/>
-      </c>
-      <c r="AB5" s="50" t="str">
+        <v>0.394732998966364</v>
+      </c>
+      <c r="AB5" s="50" t="n">
         <f aca="false">IF($A5="","",IFERROR((Z5-AA5)*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AC5" s="50" t="str">
+        <v>-271.746461706861</v>
+      </c>
+      <c r="AC5" s="50" t="n">
         <f aca="false">IF($A5="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="51" t="str">
+        <v>422.159438801699</v>
+      </c>
+      <c r="AD5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
-      </c>
-      <c r="AE5" s="48" t="str">
+        <v>19.9729105453098</v>
+      </c>
+      <c r="AE5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600),""))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="49" t="str">
+        <v>761.812308</v>
+      </c>
+      <c r="AF5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"N/M",AE5/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="49" t="str">
+        <v>0.233486293705565</v>
+      </c>
+      <c r="AG5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(AVERAGE(AO5:AS5),""))</f>
-        <v/>
-      </c>
-      <c r="AH5" s="49" t="str">
+        <v>0.19780000115247</v>
+      </c>
+      <c r="AH5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(AD5&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/AD5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AI5" s="51" t="str">
+        <v>0.265876622636104</v>
+      </c>
+      <c r="AI5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,0),""))</f>
-        <v/>
+        <v>1.43429</v>
       </c>
       <c r="AJ5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A5&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AK5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A5&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AL5" s="47" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AL5" s="47" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A5,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AM5" s="67" t="str">
+        <v>7</v>
+      </c>
+      <c r="AM5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AN5" s="67" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AO5" s="49" t="str">
+        <v>46267</v>
+      </c>
+      <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AP5" s="49" t="str">
+        <v>0.233486293705565</v>
+      </c>
+      <c r="AP5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=5)*(Raw_Q!$R$2:$R$600&lt;=8)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="49" t="str">
+        <v>0.160138774358236</v>
+      </c>
+      <c r="AQ5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=9)*(Raw_Q!$R$2:$R$600&lt;=12)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AR5" s="49" t="str">
+        <v>0.248589526969674</v>
+      </c>
+      <c r="AR5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=13)*(Raw_Q!$R$2:$R$600&lt;=16)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AS5" s="49" t="str">
+        <v>0.0905857987513444</v>
+      </c>
+      <c r="AS5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=17)*(Raw_Q!$R$2:$R$600&lt;=20)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,21))/2)),""))</f>
-        <v/>
+        <v>0.256199611977532</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11499,7 +11641,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -11528,78 +11670,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>381</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -12121,119 +12263,119 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!A$5)</f>
-        <v/>
+        <v>2455</v>
       </c>
       <c r="B6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!B$5)</f>
-        <v/>
+        <v>全新</v>
       </c>
       <c r="C6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!C$5)</f>
-        <v/>
-      </c>
-      <c r="D6" s="17" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v/>
-      </c>
-      <c r="E6" s="18" t="str">
+        <v>542</v>
+      </c>
+      <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="18" t="str">
+        <v>131.553398058252</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="17" t="str">
+        <v>70.8962086386222</v>
+      </c>
+      <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v/>
-      </c>
-      <c r="H6" s="17" t="str">
+        <v>2.13669531878053</v>
+      </c>
+      <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v/>
-      </c>
-      <c r="I6" s="19" t="str">
+        <v>1.08242101007701</v>
+      </c>
+      <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v/>
-      </c>
-      <c r="J6" s="19" t="str">
+        <v>0.00483497514760148</v>
+      </c>
+      <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
-        <v/>
-      </c>
-      <c r="K6" s="19" t="str">
+        <v>-0.18555809814312</v>
+      </c>
+      <c r="K6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!T$5)</f>
-        <v/>
-      </c>
-      <c r="L6" s="19" t="str">
+        <v>0.00632016762047738</v>
+      </c>
+      <c r="L6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!U$5)</f>
-        <v/>
-      </c>
-      <c r="M6" s="20" t="str">
+        <v>-0.000290749477120045</v>
+      </c>
+      <c r="M6" s="20" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!V$5)</f>
-        <v/>
+        <v>0.661091709759742</v>
       </c>
       <c r="N6" s="21" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!W$5)</f>
-        <v/>
-      </c>
-      <c r="O6" s="20" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="O6" s="20" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!X$5)</f>
-        <v/>
-      </c>
-      <c r="P6" s="19" t="str">
+        <v>10.6584385556805</v>
+      </c>
+      <c r="P6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!S$5)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="19" t="str">
+        <v>0.351898298106533</v>
+      </c>
+      <c r="Q6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Y$5)</f>
-        <v/>
-      </c>
-      <c r="R6" s="19" t="str">
+        <v>4.75</v>
+      </c>
+      <c r="R6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!I$5)</f>
-        <v/>
-      </c>
-      <c r="S6" s="19" t="str">
+        <v>0.615686274509804</v>
+      </c>
+      <c r="S6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Z$5)</f>
-        <v/>
-      </c>
-      <c r="T6" s="19" t="str">
+        <v>0.367558352795678</v>
+      </c>
+      <c r="T6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AA$5)</f>
-        <v/>
-      </c>
-      <c r="U6" s="22" t="str">
+        <v>0.394732998966364</v>
+      </c>
+      <c r="U6" s="22" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AB$5)</f>
-        <v/>
-      </c>
-      <c r="V6" s="22" t="str">
+        <v>-271.746461706861</v>
+      </c>
+      <c r="V6" s="22" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AC$5)</f>
-        <v/>
-      </c>
-      <c r="W6" s="19" t="str">
+        <v>422.159438801699</v>
+      </c>
+      <c r="W6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AF$5)</f>
-        <v/>
-      </c>
-      <c r="X6" s="19" t="str">
+        <v>0.233486293705565</v>
+      </c>
+      <c r="X6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AG$5)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="19" t="str">
+        <v>0.19780000115247</v>
+      </c>
+      <c r="Y6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AH$5)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="17" t="str">
+        <v>0.265876622636104</v>
+      </c>
+      <c r="Z6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AI$5)</f>
-        <v/>
+        <v>1.43429</v>
       </c>
       <c r="AA6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!AJ$5)</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AB6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!AK$5)</f>
-        <v/>
-      </c>
-      <c r="AC6" s="23" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AC6" s="23" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AM$5)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14237,36 +14379,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16523,7 +16665,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C0625DDC-5729-4C6C-8821-3F1BB92CD42E}</x14:id>
+          <x14:id>{19B8701F-5341-4828-A4F0-A79BF3ABB556}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16539,16 +16681,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16589,47 +16731,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16654,7 +16796,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C0625DDC-5729-4C6C-8821-3F1BB92CD42E}">
+          <x14:cfRule type="dataBar" id="{19B8701F-5341-4828-A4F0-A79BF3ABB556}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16855,43 +16997,43 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!$A$5)</f>
-        <v/>
-      </c>
-      <c r="B7" s="47" t="str">
+        <v>2455</v>
+      </c>
+      <c r="B7" s="47" t="n">
         <f aca="false">IF($A7="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A7,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v/>
-      </c>
-      <c r="C7" s="47" t="str">
+        <v>24</v>
+      </c>
+      <c r="C7" s="47" t="n">
         <f aca="false">IF($A7="","",Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="67" t="str">
+        <v>24</v>
+      </c>
+      <c r="D7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,$B7),""))</f>
-        <v/>
-      </c>
-      <c r="E7" s="67" t="str">
+        <v>44104</v>
+      </c>
+      <c r="E7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="F7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A7&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G7" s="67" t="str">
+        <v>FY2026Q3E</v>
+      </c>
+      <c r="G7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H7" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v/>
-      </c>
-      <c r="I7" s="67" t="str">
+        <v>-46267</v>
+      </c>
+      <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="J7" s="72" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
-        <v/>
+        <v>待更新財報</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17573,18 +17715,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17700,12 +17842,22 @@
       <c r="G4" s="73"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="73"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="A5" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>182</v>
+      </c>
       <c r="E5" s="73"/>
-      <c r="F5" s="75"/>
+      <c r="F5" s="75" t="n">
+        <v>46267</v>
+      </c>
       <c r="G5" s="73"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17854,7 +18006,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -17873,7 +18025,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S123"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -17897,58 +18049,58 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17956,7 +18108,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C2" s="77" t="n">
         <v>2026</v>
@@ -17968,13 +18120,13 @@
         <v>46295</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I2" s="79"/>
       <c r="J2" s="79"/>
@@ -17991,7 +18143,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="66" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17999,7 +18151,7 @@
         <v>167</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C3" s="77" t="n">
         <v>2026</v>
@@ -18011,13 +18163,13 @@
         <v>46203</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G3" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H3" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I3" s="79" t="n">
         <v>1270380.25</v>
@@ -18050,7 +18202,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="66" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18058,7 +18210,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C4" s="77" t="n">
         <v>2026</v>
@@ -18070,13 +18222,13 @@
         <v>46112</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G4" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H4" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H4" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I4" s="79" t="n">
         <v>1134103.44</v>
@@ -18109,7 +18261,7 @@
         <v>2</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18117,7 +18269,7 @@
         <v>167</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C5" s="77" t="n">
         <v>2025</v>
@@ -18129,13 +18281,13 @@
         <v>46022</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G5" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H5" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H5" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I5" s="79" t="n">
         <v>1046090.421</v>
@@ -18168,7 +18320,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="66" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18176,7 +18328,7 @@
         <v>167</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C6" s="77" t="n">
         <v>2025</v>
@@ -18188,13 +18340,13 @@
         <v>45930</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G6" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H6" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H6" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I6" s="79" t="n">
         <v>989918.318</v>
@@ -18227,7 +18379,7 @@
         <v>4</v>
       </c>
       <c r="S6" s="66" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18235,7 +18387,7 @@
         <v>167</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C7" s="77" t="n">
         <v>2025</v>
@@ -18247,13 +18399,13 @@
         <v>45838</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G7" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H7" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H7" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I7" s="79" t="n">
         <v>933791.869</v>
@@ -18286,7 +18438,7 @@
         <v>5</v>
       </c>
       <c r="S7" s="66" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18294,7 +18446,7 @@
         <v>167</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C8" s="77" t="n">
         <v>2025</v>
@@ -18306,13 +18458,13 @@
         <v>45747</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G8" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H8" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I8" s="79" t="n">
         <v>839253.664</v>
@@ -18345,7 +18497,7 @@
         <v>6</v>
       </c>
       <c r="S8" s="66" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18353,7 +18505,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C9" s="77" t="n">
         <v>2024</v>
@@ -18365,13 +18517,13 @@
         <v>45657</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G9" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H9" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H9" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I9" s="79" t="n">
         <v>868461.178</v>
@@ -18404,7 +18556,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="66" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18412,7 +18564,7 @@
         <v>167</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C10" s="77" t="n">
         <v>2024</v>
@@ -18424,13 +18576,13 @@
         <v>45565</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G10" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H10" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H10" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I10" s="79" t="n">
         <v>759692.143</v>
@@ -18463,7 +18615,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="66" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18471,7 +18623,7 @@
         <v>167</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C11" s="77" t="n">
         <v>2024</v>
@@ -18483,13 +18635,13 @@
         <v>45473</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G11" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H11" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I11" s="79" t="n">
         <v>673510.177</v>
@@ -18522,7 +18674,7 @@
         <v>9</v>
       </c>
       <c r="S11" s="66" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18530,7 +18682,7 @@
         <v>167</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C12" s="77" t="n">
         <v>2024</v>
@@ -18542,13 +18694,13 @@
         <v>45382</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G12" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H12" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H12" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I12" s="79" t="n">
         <v>592644.201</v>
@@ -18581,7 +18733,7 @@
         <v>10</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18589,7 +18741,7 @@
         <v>167</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C13" s="77" t="n">
         <v>2023</v>
@@ -18601,13 +18753,13 @@
         <v>45291</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G13" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H13" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H13" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I13" s="79" t="n">
         <v>625528.856</v>
@@ -18640,7 +18792,7 @@
         <v>11</v>
       </c>
       <c r="S13" s="66" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18648,7 +18800,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C14" s="77" t="n">
         <v>2023</v>
@@ -18660,13 +18812,13 @@
         <v>45199</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G14" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H14" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H14" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I14" s="79" t="n">
         <v>546732.758</v>
@@ -18699,7 +18851,7 @@
         <v>12</v>
       </c>
       <c r="S14" s="66" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18707,7 +18859,7 @@
         <v>167</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C15" s="77" t="n">
         <v>2023</v>
@@ -18719,13 +18871,13 @@
         <v>45107</v>
       </c>
       <c r="F15" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G15" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H15" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H15" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I15" s="79" t="n">
         <v>480841.254</v>
@@ -18758,7 +18910,7 @@
         <v>13</v>
       </c>
       <c r="S15" s="66" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18766,7 +18918,7 @@
         <v>167</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C16" s="77" t="n">
         <v>2023</v>
@@ -18778,13 +18930,13 @@
         <v>45016</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G16" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H16" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H16" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I16" s="79" t="n">
         <v>508632.973</v>
@@ -18817,7 +18969,7 @@
         <v>14</v>
       </c>
       <c r="S16" s="66" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18825,7 +18977,7 @@
         <v>167</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C17" s="77" t="n">
         <v>2022</v>
@@ -18837,13 +18989,13 @@
         <v>44926</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G17" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H17" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H17" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I17" s="79" t="n">
         <v>625531.868</v>
@@ -18876,7 +19028,7 @@
         <v>15</v>
       </c>
       <c r="S17" s="66" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18884,7 +19036,7 @@
         <v>167</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C18" s="77" t="n">
         <v>2022</v>
@@ -18896,13 +19048,13 @@
         <v>44834</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G18" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H18" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H18" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I18" s="79" t="n">
         <v>613142.743</v>
@@ -18935,7 +19087,7 @@
         <v>16</v>
       </c>
       <c r="S18" s="66" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18943,7 +19095,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C19" s="77" t="n">
         <v>2022</v>
@@ -18955,13 +19107,13 @@
         <v>44742</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G19" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H19" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H19" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I19" s="79" t="n">
         <v>534140.808</v>
@@ -18994,7 +19146,7 @@
         <v>17</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19002,7 +19154,7 @@
         <v>167</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C20" s="77" t="n">
         <v>2022</v>
@@ -19014,13 +19166,13 @@
         <v>44651</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G20" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H20" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H20" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I20" s="79" t="n">
         <v>491075.873</v>
@@ -19053,7 +19205,7 @@
         <v>18</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19061,7 +19213,7 @@
         <v>167</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C21" s="77" t="n">
         <v>2021</v>
@@ -19073,13 +19225,13 @@
         <v>44561</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G21" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H21" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H21" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I21" s="79" t="n">
         <v>438189.306</v>
@@ -19112,7 +19264,7 @@
         <v>19</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19120,7 +19272,7 @@
         <v>167</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C22" s="77" t="n">
         <v>2021</v>
@@ -19132,13 +19284,13 @@
         <v>44469</v>
       </c>
       <c r="F22" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G22" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H22" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H22" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I22" s="79" t="n">
         <v>414670.379</v>
@@ -19171,7 +19323,7 @@
         <v>20</v>
       </c>
       <c r="S22" s="66" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19179,7 +19331,7 @@
         <v>167</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C23" s="77" t="n">
         <v>2021</v>
@@ -19191,13 +19343,13 @@
         <v>44377</v>
       </c>
       <c r="F23" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G23" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H23" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H23" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I23" s="79" t="n">
         <v>372145.122</v>
@@ -19230,7 +19382,7 @@
         <v>21</v>
       </c>
       <c r="S23" s="66" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19238,7 +19390,7 @@
         <v>167</v>
       </c>
       <c r="B24" s="76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C24" s="77" t="n">
         <v>2021</v>
@@ -19250,13 +19402,13 @@
         <v>44286</v>
       </c>
       <c r="F24" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G24" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H24" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H24" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I24" s="79" t="n">
         <v>362410.23</v>
@@ -19289,7 +19441,7 @@
         <v>22</v>
       </c>
       <c r="S24" s="66" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19297,7 +19449,7 @@
         <v>167</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C25" s="77" t="n">
         <v>2020</v>
@@ -19309,13 +19461,13 @@
         <v>44196</v>
       </c>
       <c r="F25" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G25" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H25" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I25" s="79" t="n">
         <v>361533.057</v>
@@ -19348,7 +19500,7 @@
         <v>23</v>
       </c>
       <c r="S25" s="66" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19356,7 +19508,7 @@
         <v>167</v>
       </c>
       <c r="B26" s="76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C26" s="77" t="n">
         <v>2020</v>
@@ -19368,13 +19520,13 @@
         <v>44104</v>
       </c>
       <c r="F26" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G26" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H26" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H26" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I26" s="79" t="n">
         <v>356426.204</v>
@@ -19405,7 +19557,7 @@
         <v>24</v>
       </c>
       <c r="S26" s="66" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19413,7 +19565,7 @@
         <v>171</v>
       </c>
       <c r="B27" s="76" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C27" s="77" t="n">
         <v>2026</v>
@@ -19425,13 +19577,13 @@
         <v>46295</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G27" s="76" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H27" s="76" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I27" s="79"/>
       <c r="J27" s="79"/>
@@ -19448,7 +19600,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="66" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19456,7 +19608,7 @@
         <v>171</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C28" s="77" t="n">
         <v>2026</v>
@@ -19468,13 +19620,13 @@
         <v>46203</v>
       </c>
       <c r="F28" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G28" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H28" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H28" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I28" s="79" t="n">
         <v>82549.073</v>
@@ -19507,7 +19659,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="66" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19515,7 +19667,7 @@
         <v>171</v>
       </c>
       <c r="B29" s="76" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C29" s="77" t="n">
         <v>2026</v>
@@ -19527,13 +19679,13 @@
         <v>46112</v>
       </c>
       <c r="F29" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G29" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H29" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H29" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I29" s="79" t="n">
         <v>49086.932</v>
@@ -19566,7 +19718,7 @@
         <v>2</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19574,7 +19726,7 @@
         <v>171</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C30" s="77" t="n">
         <v>2025</v>
@@ -19586,13 +19738,13 @@
         <v>46022</v>
       </c>
       <c r="F30" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G30" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H30" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H30" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I30" s="79" t="n">
         <v>30093.618</v>
@@ -19625,7 +19777,7 @@
         <v>3</v>
       </c>
       <c r="S30" s="66" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19633,7 +19785,7 @@
         <v>171</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C31" s="77" t="n">
         <v>2025</v>
@@ -19645,13 +19797,13 @@
         <v>45930</v>
       </c>
       <c r="F31" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G31" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H31" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H31" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I31" s="79" t="n">
         <v>18778.868</v>
@@ -19684,7 +19836,7 @@
         <v>4</v>
       </c>
       <c r="S31" s="66" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19692,7 +19844,7 @@
         <v>171</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C32" s="77" t="n">
         <v>2025</v>
@@ -19704,13 +19856,13 @@
         <v>45838</v>
       </c>
       <c r="F32" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G32" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H32" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H32" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I32" s="79" t="n">
         <v>10526.094</v>
@@ -19743,7 +19895,7 @@
         <v>5</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19751,7 +19903,7 @@
         <v>171</v>
       </c>
       <c r="B33" s="76" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C33" s="77" t="n">
         <v>2025</v>
@@ -19763,13 +19915,13 @@
         <v>45747</v>
       </c>
       <c r="F33" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G33" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H33" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H33" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I33" s="79" t="n">
         <v>7187.94</v>
@@ -19802,7 +19954,7 @@
         <v>6</v>
       </c>
       <c r="S33" s="66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19810,7 +19962,7 @@
         <v>171</v>
       </c>
       <c r="B34" s="76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C34" s="77" t="n">
         <v>2024</v>
@@ -19822,13 +19974,13 @@
         <v>45657</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G34" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H34" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H34" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I34" s="79" t="n">
         <v>6575.094</v>
@@ -19861,7 +20013,7 @@
         <v>7</v>
       </c>
       <c r="S34" s="66" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19869,7 +20021,7 @@
         <v>171</v>
       </c>
       <c r="B35" s="76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C35" s="77" t="n">
         <v>2024</v>
@@ -19881,13 +20033,13 @@
         <v>45565</v>
       </c>
       <c r="F35" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G35" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H35" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H35" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I35" s="79" t="n">
         <v>8132.593</v>
@@ -19920,7 +20072,7 @@
         <v>8</v>
       </c>
       <c r="S35" s="66" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19928,7 +20080,7 @@
         <v>171</v>
       </c>
       <c r="B36" s="76" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C36" s="77" t="n">
         <v>2024</v>
@@ -19940,13 +20092,13 @@
         <v>45473</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G36" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H36" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H36" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I36" s="79" t="n">
         <v>9921.043</v>
@@ -19973,7 +20125,7 @@
         <v>9</v>
       </c>
       <c r="S36" s="66" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19981,7 +20133,7 @@
         <v>171</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C37" s="77" t="n">
         <v>2024</v>
@@ -19993,13 +20145,13 @@
         <v>45382</v>
       </c>
       <c r="F37" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G37" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H37" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H37" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I37" s="79" t="n">
         <v>9502.937</v>
@@ -20032,7 +20184,7 @@
         <v>10</v>
       </c>
       <c r="S37" s="66" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20040,7 +20192,7 @@
         <v>171</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C38" s="77" t="n">
         <v>2023</v>
@@ -20052,13 +20204,13 @@
         <v>45291</v>
       </c>
       <c r="F38" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G38" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H38" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H38" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I38" s="79" t="n">
         <v>8703.978</v>
@@ -20091,7 +20243,7 @@
         <v>11</v>
       </c>
       <c r="S38" s="66" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20099,7 +20251,7 @@
         <v>171</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C39" s="77" t="n">
         <v>2023</v>
@@ -20111,13 +20263,13 @@
         <v>45199</v>
       </c>
       <c r="F39" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G39" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H39" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H39" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I39" s="79" t="n">
         <v>7736.374</v>
@@ -20150,7 +20302,7 @@
         <v>12</v>
       </c>
       <c r="S39" s="66" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20158,7 +20310,7 @@
         <v>171</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C40" s="77" t="n">
         <v>2023</v>
@@ -20170,13 +20322,13 @@
         <v>45107</v>
       </c>
       <c r="F40" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G40" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H40" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H40" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I40" s="79" t="n">
         <v>7027.071</v>
@@ -20209,7 +20361,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="66" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20217,7 +20369,7 @@
         <v>171</v>
       </c>
       <c r="B41" s="76" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C41" s="77" t="n">
         <v>2023</v>
@@ -20229,13 +20381,13 @@
         <v>45016</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G41" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H41" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H41" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I41" s="79" t="n">
         <v>6424.883</v>
@@ -20268,7 +20420,7 @@
         <v>14</v>
       </c>
       <c r="S41" s="66" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20276,7 +20428,7 @@
         <v>171</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C42" s="77" t="n">
         <v>2022</v>
@@ -20288,13 +20440,13 @@
         <v>44926</v>
       </c>
       <c r="F42" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G42" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H42" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H42" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I42" s="79" t="n">
         <v>7953.553</v>
@@ -20327,7 +20479,7 @@
         <v>15</v>
       </c>
       <c r="S42" s="66" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20335,7 +20487,7 @@
         <v>171</v>
       </c>
       <c r="B43" s="76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C43" s="77" t="n">
         <v>2022</v>
@@ -20347,13 +20499,13 @@
         <v>44834</v>
       </c>
       <c r="F43" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G43" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H43" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H43" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I43" s="79" t="n">
         <v>11021.725</v>
@@ -20386,7 +20538,7 @@
         <v>16</v>
       </c>
       <c r="S43" s="66" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20394,7 +20546,7 @@
         <v>171</v>
       </c>
       <c r="B44" s="76" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C44" s="77" t="n">
         <v>2022</v>
@@ -20406,13 +20558,13 @@
         <v>44742</v>
       </c>
       <c r="F44" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G44" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H44" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H44" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I44" s="79" t="n">
         <v>18030.672</v>
@@ -20445,7 +20597,7 @@
         <v>17</v>
       </c>
       <c r="S44" s="66" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20453,7 +20605,7 @@
         <v>171</v>
       </c>
       <c r="B45" s="76" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C45" s="77" t="n">
         <v>2022</v>
@@ -20465,13 +20617,13 @@
         <v>44651</v>
       </c>
       <c r="F45" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G45" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H45" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H45" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I45" s="79" t="n">
         <v>19946.325</v>
@@ -20504,7 +20656,7 @@
         <v>18</v>
       </c>
       <c r="S45" s="66" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20512,7 +20664,7 @@
         <v>171</v>
       </c>
       <c r="B46" s="76" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C46" s="77" t="n">
         <v>2021</v>
@@ -20524,13 +20676,13 @@
         <v>44561</v>
       </c>
       <c r="F46" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G46" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H46" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H46" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I46" s="79" t="n">
         <v>21398.949</v>
@@ -20563,7 +20715,7 @@
         <v>19</v>
       </c>
       <c r="S46" s="66" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20571,7 +20723,7 @@
         <v>171</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C47" s="77" t="n">
         <v>2021</v>
@@ -20583,13 +20735,13 @@
         <v>44469</v>
       </c>
       <c r="F47" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G47" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H47" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H47" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I47" s="79" t="n">
         <v>23837.128</v>
@@ -20622,7 +20774,7 @@
         <v>20</v>
       </c>
       <c r="S47" s="66" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20630,7 +20782,7 @@
         <v>171</v>
       </c>
       <c r="B48" s="76" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C48" s="77" t="n">
         <v>2021</v>
@@ -20642,13 +20794,13 @@
         <v>44377</v>
       </c>
       <c r="F48" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G48" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H48" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H48" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I48" s="79" t="n">
         <v>22637.468</v>
@@ -20681,7 +20833,7 @@
         <v>21</v>
       </c>
       <c r="S48" s="66" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20689,7 +20841,7 @@
         <v>171</v>
       </c>
       <c r="B49" s="76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C49" s="77" t="n">
         <v>2021</v>
@@ -20701,13 +20853,13 @@
         <v>44286</v>
       </c>
       <c r="F49" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G49" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H49" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H49" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I49" s="79" t="n">
         <v>17730.613</v>
@@ -20740,7 +20892,7 @@
         <v>22</v>
       </c>
       <c r="S49" s="66" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20748,7 +20900,7 @@
         <v>171</v>
       </c>
       <c r="B50" s="76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C50" s="77" t="n">
         <v>2020</v>
@@ -20760,13 +20912,13 @@
         <v>44196</v>
       </c>
       <c r="F50" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G50" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H50" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H50" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I50" s="79" t="n">
         <v>14773.42</v>
@@ -20799,7 +20951,7 @@
         <v>23</v>
       </c>
       <c r="S50" s="66" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20807,7 +20959,7 @@
         <v>171</v>
       </c>
       <c r="B51" s="76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C51" s="77" t="n">
         <v>2020</v>
@@ -20819,13 +20971,13 @@
         <v>44104</v>
       </c>
       <c r="F51" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G51" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H51" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H51" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I51" s="79" t="n">
         <v>15323.867</v>
@@ -20856,15 +21008,15 @@
         <v>24</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B52" s="76" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C52" s="77" t="n">
         <v>2026</v>
@@ -20876,19 +21028,19 @@
         <v>46295</v>
       </c>
       <c r="F52" s="76" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G52" s="76" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H52" s="76" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
       <c r="K52" s="79"/>
       <c r="L52" s="80" t="n">
-        <v>99.01</v>
+        <v>1.43429</v>
       </c>
       <c r="M52" s="79"/>
       <c r="N52" s="79"/>
@@ -20899,15 +21051,15 @@
         <v>0</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B53" s="76" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C53" s="77" t="n">
         <v>2026</v>
@@ -20919,54 +21071,54 @@
         <v>46203</v>
       </c>
       <c r="F53" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G53" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H53" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H53" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I53" s="79" t="n">
-        <v>22443.411</v>
+        <v>965.373</v>
       </c>
       <c r="J53" s="79" t="n">
-        <v>14589.612</v>
+        <v>372.706</v>
       </c>
       <c r="K53" s="79" t="n">
-        <v>10368072000</v>
+        <v>213588000</v>
       </c>
       <c r="L53" s="80" t="n">
-        <v>108.93</v>
+        <v>1.15</v>
       </c>
       <c r="M53" s="79" t="n">
-        <v>96.3654</v>
+        <v>184.9059</v>
       </c>
       <c r="N53" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="79" t="n">
-        <v>23288.098</v>
+        <v>3693.109</v>
       </c>
       <c r="P53" s="80" t="n">
-        <v>0</v>
+        <v>2.62055653</v>
       </c>
       <c r="Q53" s="80" t="n">
-        <v>1615</v>
+        <v>347</v>
       </c>
       <c r="R53" s="47" t="n">
         <v>1</v>
       </c>
       <c r="S53" s="66" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B54" s="76" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C54" s="77" t="n">
         <v>2026</v>
@@ -20978,54 +21130,54 @@
         <v>46112</v>
       </c>
       <c r="F54" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G54" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H54" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H54" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I54" s="79" t="n">
-        <v>13182.608</v>
+        <v>959.31</v>
       </c>
       <c r="J54" s="79" t="n">
-        <v>7791.357</v>
+        <v>365.431</v>
       </c>
       <c r="K54" s="79" t="n">
-        <v>5466357000</v>
+        <v>195085000</v>
       </c>
       <c r="L54" s="80" t="n">
-        <v>57.49</v>
+        <v>1.06</v>
       </c>
       <c r="M54" s="79" t="n">
-        <v>96.3552</v>
+        <v>184.9059</v>
       </c>
       <c r="N54" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="79" t="n">
-        <v>14500.386</v>
+        <v>3667.225</v>
       </c>
       <c r="P54" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="80" t="n">
-        <v>847</v>
+        <v>246.5</v>
       </c>
       <c r="R54" s="47" t="n">
         <v>2</v>
       </c>
       <c r="S54" s="66" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C55" s="77" t="n">
         <v>2025</v>
@@ -21037,54 +21189,54 @@
         <v>46022</v>
       </c>
       <c r="F55" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G55" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H55" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H55" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I55" s="79" t="n">
-        <v>4806.69</v>
+        <v>959.589</v>
       </c>
       <c r="J55" s="79" t="n">
-        <v>1597.288</v>
+        <v>357.593</v>
       </c>
       <c r="K55" s="79" t="n">
-        <v>870716000</v>
+        <v>193882000</v>
       </c>
       <c r="L55" s="80" t="n">
-        <v>9.26</v>
+        <v>1.05</v>
       </c>
       <c r="M55" s="79" t="n">
-        <v>96.0407</v>
+        <v>184.9059</v>
       </c>
       <c r="N55" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O55" s="79" t="n">
-        <v>8940.787</v>
+        <v>3294.696</v>
       </c>
       <c r="P55" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="80" t="n">
-        <v>576</v>
+        <v>151.5</v>
       </c>
       <c r="R55" s="47" t="n">
         <v>3</v>
       </c>
       <c r="S55" s="66" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C56" s="77" t="n">
         <v>2025</v>
@@ -21096,54 +21248,54 @@
         <v>45930</v>
       </c>
       <c r="F56" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G56" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H56" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I56" s="79" t="n">
-        <v>3807.401</v>
+        <v>912.804</v>
       </c>
       <c r="J56" s="79" t="n">
-        <v>1248.818</v>
+        <v>299.917</v>
       </c>
       <c r="K56" s="79" t="n">
-        <v>643038000</v>
+        <v>160464000</v>
       </c>
       <c r="L56" s="80" t="n">
-        <v>6.87</v>
+        <v>0.86</v>
       </c>
       <c r="M56" s="79" t="n">
-        <v>95.3452</v>
+        <v>184.9059</v>
       </c>
       <c r="N56" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="79" t="n">
-        <v>7932.37</v>
+        <v>3104.723</v>
       </c>
       <c r="P56" s="80" t="n">
-        <v>9.37723774</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="80" t="n">
-        <v>329.5</v>
+        <v>161</v>
       </c>
       <c r="R56" s="47" t="n">
         <v>4</v>
       </c>
       <c r="S56" s="66" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C57" s="77" t="n">
         <v>2025</v>
@@ -21155,54 +21307,54 @@
         <v>45838</v>
       </c>
       <c r="F57" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G57" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H57" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H57" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I57" s="79" t="n">
-        <v>3028.429</v>
+        <v>714.087</v>
       </c>
       <c r="J57" s="79" t="n">
-        <v>785.089</v>
+        <v>245.545</v>
       </c>
       <c r="K57" s="79" t="n">
-        <v>185349000</v>
+        <v>36309000</v>
       </c>
       <c r="L57" s="80" t="n">
-        <v>2.02</v>
+        <v>0.2</v>
       </c>
       <c r="M57" s="79" t="n">
-        <v>91.6411</v>
+        <v>184.9059</v>
       </c>
       <c r="N57" s="79" t="n">
-        <v>0</v>
+        <v>1012000</v>
       </c>
       <c r="O57" s="79" t="n">
-        <v>7184.405</v>
+        <v>2832.433</v>
       </c>
       <c r="P57" s="80" t="n">
-        <v>0</v>
+        <v>3.21761015</v>
       </c>
       <c r="Q57" s="80" t="n">
-        <v>237</v>
+        <v>125</v>
       </c>
       <c r="R57" s="47" t="n">
         <v>5</v>
       </c>
       <c r="S57" s="66" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C58" s="77" t="n">
         <v>2025</v>
@@ -21214,54 +21366,54 @@
         <v>45747</v>
       </c>
       <c r="F58" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G58" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H58" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H58" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I58" s="79" t="n">
-        <v>2618.742</v>
+        <v>793.663</v>
       </c>
       <c r="J58" s="79" t="n">
-        <v>800.733</v>
+        <v>316.671</v>
       </c>
       <c r="K58" s="79" t="n">
-        <v>336540000</v>
+        <v>157287000</v>
       </c>
       <c r="L58" s="80" t="n">
-        <v>3.68</v>
+        <v>0.85</v>
       </c>
       <c r="M58" s="79" t="n">
-        <v>91.5746</v>
+        <v>184.9059</v>
       </c>
       <c r="N58" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O58" s="79" t="n">
-        <v>7854.351</v>
+        <v>3486.629</v>
       </c>
       <c r="P58" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="80" t="n">
-        <v>250.5</v>
+        <v>113.5</v>
       </c>
       <c r="R58" s="47" t="n">
         <v>6</v>
       </c>
       <c r="S58" s="66" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C59" s="77" t="n">
         <v>2024</v>
@@ -21273,54 +21425,54 @@
         <v>45657</v>
       </c>
       <c r="F59" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G59" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H59" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H59" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I59" s="79" t="n">
-        <v>2228.005</v>
+        <v>722.474</v>
       </c>
       <c r="J59" s="79" t="n">
-        <v>648.956</v>
+        <v>260.149</v>
       </c>
       <c r="K59" s="79" t="n">
-        <v>271532000</v>
+        <v>132861000</v>
       </c>
       <c r="L59" s="80" t="n">
-        <v>2.97</v>
+        <v>0.72</v>
       </c>
       <c r="M59" s="79" t="n">
-        <v>91.4561</v>
+        <v>184.9059</v>
       </c>
       <c r="N59" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O59" s="79" t="n">
-        <v>7491.143</v>
+        <v>3329.342</v>
       </c>
       <c r="P59" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="80" t="n">
-        <v>218</v>
+        <v>166.5</v>
       </c>
       <c r="R59" s="47" t="n">
         <v>7</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C60" s="77" t="n">
         <v>2024</v>
@@ -21332,54 +21484,54 @@
         <v>45565</v>
       </c>
       <c r="F60" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G60" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H60" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H60" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I60" s="79" t="n">
-        <v>2321.419</v>
+        <v>805.747</v>
       </c>
       <c r="J60" s="79" t="n">
-        <v>658.433</v>
+        <v>330.538</v>
       </c>
       <c r="K60" s="79" t="n">
-        <v>188620000</v>
+        <v>144407000</v>
       </c>
       <c r="L60" s="80" t="n">
-        <v>2.08</v>
+        <v>0.78</v>
       </c>
       <c r="M60" s="79" t="n">
-        <v>91.3372</v>
+        <v>184.9059</v>
       </c>
       <c r="N60" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O60" s="79" t="n">
-        <v>7196.228</v>
+        <v>3200.742</v>
       </c>
       <c r="P60" s="80" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="80" t="n">
-        <v>282</v>
+        <v>166</v>
       </c>
       <c r="R60" s="47" t="n">
         <v>8</v>
       </c>
       <c r="S60" s="66" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C61" s="77" t="n">
         <v>2024</v>
@@ -21391,54 +21543,54 @@
         <v>45473</v>
       </c>
       <c r="F61" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G61" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H61" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H61" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I61" s="79" t="n">
-        <v>2190.229</v>
+        <v>875.601</v>
       </c>
       <c r="J61" s="79" t="n">
-        <v>759.289</v>
+        <v>346.96</v>
       </c>
       <c r="K61" s="79" t="n">
-        <v>294050000</v>
+        <v>200826000</v>
       </c>
       <c r="L61" s="80" t="n">
-        <v>3.26</v>
+        <v>1.09</v>
       </c>
       <c r="M61" s="79" t="n">
-        <v>88.3977</v>
+        <v>184.9059</v>
       </c>
       <c r="N61" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O61" s="79" t="n">
-        <v>6803.334</v>
+        <v>3056.335</v>
       </c>
       <c r="P61" s="80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q61" s="80" t="n">
-        <v>302</v>
+        <v>165</v>
       </c>
       <c r="R61" s="47" t="n">
         <v>9</v>
       </c>
       <c r="S61" s="66" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C62" s="77" t="n">
         <v>2024</v>
@@ -21450,54 +21602,54 @@
         <v>45382</v>
       </c>
       <c r="F62" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G62" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H62" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H62" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I62" s="79" t="n">
-        <v>2175.989</v>
+        <v>837.395</v>
       </c>
       <c r="J62" s="79" t="n">
-        <v>758.571</v>
+        <v>341.317</v>
       </c>
       <c r="K62" s="79" t="n">
-        <v>351970000</v>
+        <v>192961000</v>
       </c>
       <c r="L62" s="80" t="n">
-        <v>3.98</v>
+        <v>1.04</v>
       </c>
       <c r="M62" s="79" t="n">
-        <v>88.3977</v>
+        <v>184.9059</v>
       </c>
       <c r="N62" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O62" s="79" t="n">
-        <v>7398.652</v>
+        <v>3262.302</v>
       </c>
       <c r="P62" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="80" t="n">
-        <v>305.5</v>
+        <v>169.5</v>
       </c>
       <c r="R62" s="47" t="n">
         <v>10</v>
       </c>
       <c r="S62" s="66" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B63" s="76" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C63" s="77" t="n">
         <v>2023</v>
@@ -21509,54 +21661,54 @@
         <v>45291</v>
       </c>
       <c r="F63" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G63" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H63" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H63" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I63" s="79" t="n">
-        <v>2130.049</v>
+        <v>936.937</v>
       </c>
       <c r="J63" s="79" t="n">
-        <v>707.384</v>
+        <v>411.959</v>
       </c>
       <c r="K63" s="79" t="n">
-        <v>262238000</v>
+        <v>188378000</v>
       </c>
       <c r="L63" s="80" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="M63" s="79" t="n">
-        <v>88.3977</v>
+        <v>184.9059</v>
       </c>
       <c r="N63" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O63" s="79" t="n">
-        <v>7036.917</v>
+        <v>3069.341</v>
       </c>
       <c r="P63" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="80" t="n">
-        <v>312</v>
+        <v>160.5</v>
       </c>
       <c r="R63" s="47" t="n">
         <v>11</v>
       </c>
       <c r="S63" s="66" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B64" s="76" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C64" s="77" t="n">
         <v>2023</v>
@@ -21568,54 +21720,54 @@
         <v>45199</v>
       </c>
       <c r="F64" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G64" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H64" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H64" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I64" s="79" t="n">
-        <v>1993.007</v>
+        <v>768.427</v>
       </c>
       <c r="J64" s="79" t="n">
-        <v>687.513</v>
+        <v>307.139</v>
       </c>
       <c r="K64" s="79" t="n">
-        <v>306457000</v>
+        <v>143945000</v>
       </c>
       <c r="L64" s="80" t="n">
-        <v>3.47</v>
+        <v>0.78</v>
       </c>
       <c r="M64" s="79" t="n">
-        <v>88.3977</v>
+        <v>184.9059</v>
       </c>
       <c r="N64" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="79" t="n">
-        <v>6756.961</v>
+        <v>2919.16</v>
       </c>
       <c r="P64" s="80" t="n">
-        <v>13.78192729</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="80" t="n">
-        <v>296.5</v>
+        <v>148</v>
       </c>
       <c r="R64" s="47" t="n">
         <v>12</v>
       </c>
       <c r="S64" s="66" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B65" s="76" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C65" s="77" t="n">
         <v>2023</v>
@@ -21627,54 +21779,54 @@
         <v>45107</v>
       </c>
       <c r="F65" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G65" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H65" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H65" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I65" s="79" t="n">
-        <v>1930.516</v>
+        <v>594.323</v>
       </c>
       <c r="J65" s="79" t="n">
-        <v>636.105</v>
+        <v>235.781</v>
       </c>
       <c r="K65" s="79" t="n">
-        <v>230718000</v>
+        <v>106159000</v>
       </c>
       <c r="L65" s="80" t="n">
-        <v>2.66</v>
+        <v>0.57</v>
       </c>
       <c r="M65" s="79" t="n">
-        <v>86.6666</v>
+        <v>184.9059</v>
       </c>
       <c r="N65" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O65" s="79" t="n">
-        <v>6433.521</v>
+        <v>2775.215</v>
       </c>
       <c r="P65" s="80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q65" s="80" t="n">
-        <v>324</v>
+        <v>116.5</v>
       </c>
       <c r="R65" s="47" t="n">
         <v>13</v>
       </c>
       <c r="S65" s="66" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B66" s="76" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C66" s="77" t="n">
         <v>2023</v>
@@ -21686,54 +21838,54 @@
         <v>45016</v>
       </c>
       <c r="F66" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G66" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H66" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I66" s="79" t="n">
-        <v>2260.206</v>
+        <v>394.417</v>
       </c>
       <c r="J66" s="79" t="n">
-        <v>814.91</v>
+        <v>154.035</v>
       </c>
       <c r="K66" s="79" t="n">
-        <v>348203000</v>
+        <v>11750000</v>
       </c>
       <c r="L66" s="80" t="n">
-        <v>4.02</v>
+        <v>0.06</v>
       </c>
       <c r="M66" s="79" t="n">
-        <v>86.6666</v>
+        <v>184.9059</v>
       </c>
       <c r="N66" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="79" t="n">
-        <v>7382.85</v>
+        <v>3094.34</v>
       </c>
       <c r="P66" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="80" t="n">
-        <v>314</v>
+        <v>92.3</v>
       </c>
       <c r="R66" s="47" t="n">
         <v>14</v>
       </c>
       <c r="S66" s="66" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B67" s="76" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C67" s="77" t="n">
         <v>2022</v>
@@ -21745,54 +21897,54 @@
         <v>44926</v>
       </c>
       <c r="F67" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G67" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H67" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H67" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I67" s="79" t="n">
-        <v>2286.572</v>
+        <v>506.067</v>
       </c>
       <c r="J67" s="79" t="n">
-        <v>860.807</v>
+        <v>201.013</v>
       </c>
       <c r="K67" s="79" t="n">
-        <v>385061000</v>
+        <v>37033000</v>
       </c>
       <c r="L67" s="80" t="n">
-        <v>4.44</v>
+        <v>0.2</v>
       </c>
       <c r="M67" s="79" t="n">
-        <v>86.5531</v>
+        <v>184.9059</v>
       </c>
       <c r="N67" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="79" t="n">
-        <v>7012.867</v>
+        <v>3082.59</v>
       </c>
       <c r="P67" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="80" t="n">
-        <v>185.5</v>
+        <v>69</v>
       </c>
       <c r="R67" s="47" t="n">
         <v>15</v>
       </c>
       <c r="S67" s="66" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C68" s="77" t="n">
         <v>2022</v>
@@ -21804,54 +21956,54 @@
         <v>44834</v>
       </c>
       <c r="F68" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G68" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H68" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H68" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I68" s="79" t="n">
-        <v>2560.341</v>
+        <v>522.089</v>
       </c>
       <c r="J68" s="79" t="n">
-        <v>914.902</v>
+        <v>221.557</v>
       </c>
       <c r="K68" s="79" t="n">
-        <v>542661000</v>
+        <v>105773000</v>
       </c>
       <c r="L68" s="80" t="n">
-        <v>6.28</v>
+        <v>0.57</v>
       </c>
       <c r="M68" s="79" t="n">
-        <v>86.4706</v>
+        <v>184.9059</v>
       </c>
       <c r="N68" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="79" t="n">
-        <v>6611.975</v>
+        <v>3045.985</v>
       </c>
       <c r="P68" s="80" t="n">
-        <v>11.5240749</v>
+        <v>0</v>
       </c>
       <c r="Q68" s="80" t="n">
-        <v>161.5</v>
+        <v>56.6</v>
       </c>
       <c r="R68" s="47" t="n">
         <v>16</v>
       </c>
       <c r="S68" s="66" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B69" s="76" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C69" s="77" t="n">
         <v>2022</v>
@@ -21863,54 +22015,54 @@
         <v>44742</v>
       </c>
       <c r="F69" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G69" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H69" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H69" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I69" s="79" t="n">
-        <v>2866.579</v>
+        <v>736.276</v>
       </c>
       <c r="J69" s="79" t="n">
-        <v>947.502</v>
+        <v>303.299</v>
       </c>
       <c r="K69" s="79" t="n">
-        <v>536500000</v>
+        <v>184441000</v>
       </c>
       <c r="L69" s="80" t="n">
-        <v>6.41</v>
+        <v>1</v>
       </c>
       <c r="M69" s="79" t="n">
-        <v>83.895</v>
+        <v>184.9059</v>
       </c>
       <c r="N69" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="79" t="n">
-        <v>6043.861</v>
+        <v>2940.212</v>
       </c>
       <c r="P69" s="80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q69" s="80" t="n">
-        <v>162.5</v>
+        <v>72</v>
       </c>
       <c r="R69" s="47" t="n">
         <v>17</v>
       </c>
       <c r="S69" s="66" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B70" s="76" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C70" s="77" t="n">
         <v>2022</v>
@@ -21922,54 +22074,54 @@
         <v>44651</v>
       </c>
       <c r="F70" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G70" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H70" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H70" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I70" s="79" t="n">
-        <v>2589.737</v>
+        <v>839.197</v>
       </c>
       <c r="J70" s="79" t="n">
-        <v>735.407</v>
+        <v>363.138</v>
       </c>
       <c r="K70" s="79" t="n">
-        <v>385967000</v>
+        <v>217481000</v>
       </c>
       <c r="L70" s="80" t="n">
-        <v>4.64</v>
+        <v>1.18</v>
       </c>
       <c r="M70" s="79" t="n">
-        <v>83.7225</v>
+        <v>184.9059</v>
       </c>
       <c r="N70" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="79" t="n">
-        <v>6458.201</v>
+        <v>3495.395</v>
       </c>
       <c r="P70" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="80" t="n">
-        <v>215</v>
+        <v>113.5</v>
       </c>
       <c r="R70" s="47" t="n">
         <v>18</v>
       </c>
       <c r="S70" s="66" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B71" s="76" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C71" s="77" t="n">
         <v>2021</v>
@@ -21981,54 +22133,54 @@
         <v>44561</v>
       </c>
       <c r="F71" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G71" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H71" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H71" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I71" s="79" t="n">
-        <v>2396.847</v>
+        <v>875.843</v>
       </c>
       <c r="J71" s="79" t="n">
-        <v>677.529</v>
+        <v>347.262</v>
       </c>
       <c r="K71" s="79" t="n">
-        <v>290253000</v>
+        <v>191791000</v>
       </c>
       <c r="L71" s="80" t="n">
-        <v>3.51</v>
+        <v>1.03</v>
       </c>
       <c r="M71" s="79" t="n">
-        <v>82.668</v>
+        <v>184.9059</v>
       </c>
       <c r="N71" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="79" t="n">
-        <v>5960.989</v>
+        <v>3277.914</v>
       </c>
       <c r="P71" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="80" t="n">
-        <v>204</v>
+        <v>144</v>
       </c>
       <c r="R71" s="47" t="n">
         <v>19</v>
       </c>
       <c r="S71" s="66" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B72" s="76" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C72" s="77" t="n">
         <v>2021</v>
@@ -22040,54 +22192,54 @@
         <v>44469</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G72" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H72" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H72" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I72" s="79" t="n">
-        <v>2973.845</v>
+        <v>947.399</v>
       </c>
       <c r="J72" s="79" t="n">
-        <v>975.336</v>
+        <v>402.279</v>
       </c>
       <c r="K72" s="79" t="n">
-        <v>533714000</v>
+        <v>211771000</v>
       </c>
       <c r="L72" s="80" t="n">
-        <v>6.46</v>
+        <v>1.15</v>
       </c>
       <c r="M72" s="79" t="n">
-        <v>82.628</v>
+        <v>184.9059</v>
       </c>
       <c r="N72" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O72" s="79" t="n">
-        <v>5663.586</v>
+        <v>3086.103</v>
       </c>
       <c r="P72" s="80" t="n">
-        <v>6.69560253</v>
+        <v>2.59</v>
       </c>
       <c r="Q72" s="80" t="n">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="R72" s="47" t="n">
         <v>20</v>
       </c>
       <c r="S72" s="66" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B73" s="76" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C73" s="77" t="n">
         <v>2021</v>
@@ -22099,54 +22251,54 @@
         <v>44377</v>
       </c>
       <c r="F73" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G73" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H73" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H73" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I73" s="79" t="n">
-        <v>2885.046</v>
+        <v>896.062</v>
       </c>
       <c r="J73" s="79" t="n">
-        <v>888.15</v>
+        <v>390.922</v>
       </c>
       <c r="K73" s="79" t="n">
-        <v>477358000</v>
+        <v>226778000</v>
       </c>
       <c r="L73" s="80" t="n">
-        <v>5.79</v>
+        <v>1.23</v>
       </c>
       <c r="M73" s="79" t="n">
-        <v>82.516</v>
+        <v>184.9059</v>
       </c>
       <c r="N73" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="79" t="n">
-        <v>5668.615</v>
+        <v>3353.238</v>
       </c>
       <c r="P73" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="80" t="n">
-        <v>190.5</v>
+        <v>134</v>
       </c>
       <c r="R73" s="47" t="n">
         <v>21</v>
       </c>
       <c r="S73" s="66" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B74" s="76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C74" s="77" t="n">
         <v>2021</v>
@@ -22158,54 +22310,54 @@
         <v>44286</v>
       </c>
       <c r="F74" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G74" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H74" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H74" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I74" s="79" t="n">
-        <v>1939.92</v>
+        <v>889.217</v>
       </c>
       <c r="J74" s="79" t="n">
-        <v>551.203</v>
+        <v>379.25</v>
       </c>
       <c r="K74" s="79" t="n">
-        <v>259563000</v>
+        <v>224741000</v>
       </c>
       <c r="L74" s="80" t="n">
-        <v>3.17</v>
+        <v>1.22</v>
       </c>
       <c r="M74" s="79" t="n">
-        <v>82.459</v>
+        <v>184.9059</v>
       </c>
       <c r="N74" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O74" s="79" t="n">
-        <v>5182.897</v>
+        <v>3126.46</v>
       </c>
       <c r="P74" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="80" t="n">
-        <v>170</v>
+        <v>118.5</v>
       </c>
       <c r="R74" s="47" t="n">
         <v>22</v>
       </c>
       <c r="S74" s="66" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B75" s="76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C75" s="77" t="n">
         <v>2020</v>
@@ -22217,54 +22369,54 @@
         <v>44196</v>
       </c>
       <c r="F75" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G75" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H75" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H75" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I75" s="79" t="n">
-        <v>1575.49</v>
+        <v>757.232</v>
       </c>
       <c r="J75" s="79" t="n">
-        <v>458.968</v>
+        <v>315.349</v>
       </c>
       <c r="K75" s="79" t="n">
-        <v>175456000</v>
+        <v>145795000</v>
       </c>
       <c r="L75" s="80" t="n">
-        <v>2.16</v>
+        <v>0.79</v>
       </c>
       <c r="M75" s="79" t="n">
-        <v>81.324</v>
+        <v>184.9059</v>
       </c>
       <c r="N75" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O75" s="79" t="n">
-        <v>4816.246</v>
+        <v>2901.719</v>
       </c>
       <c r="P75" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="80" t="n">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="R75" s="47" t="n">
         <v>23</v>
       </c>
       <c r="S75" s="66" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B76" s="76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C76" s="77" t="n">
         <v>2020</v>
@@ -22276,199 +22428,1656 @@
         <v>44104</v>
       </c>
       <c r="F76" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G76" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H76" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H76" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I76" s="79" t="n">
-        <v>1627.205</v>
+        <v>644.391</v>
       </c>
       <c r="J76" s="79" t="n">
-        <v>493.122</v>
+        <v>270.365</v>
       </c>
       <c r="K76" s="79" t="n">
-        <v>194271000</v>
+        <v>112847000</v>
       </c>
       <c r="L76" s="80" t="n">
-        <v>2.39</v>
+        <v>0.61</v>
       </c>
       <c r="M76" s="79" t="n">
-        <v>81.324</v>
+        <v>184.9059</v>
       </c>
       <c r="N76" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O76" s="79" t="n">
-        <v>4634.348</v>
+        <v>2755.453</v>
       </c>
       <c r="P76" s="80"/>
       <c r="Q76" s="80" t="n">
-        <v>158.5</v>
+        <v>78.5</v>
       </c>
       <c r="R76" s="47" t="n">
         <v>24</v>
       </c>
       <c r="S76" s="66" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" s="76" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D77" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="78" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F77" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="G77" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="H77" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I77" s="79"/>
+      <c r="J77" s="79"/>
+      <c r="K77" s="79"/>
+      <c r="L77" s="80" t="n">
+        <v>99.01</v>
+      </c>
+      <c r="M77" s="79"/>
+      <c r="N77" s="79"/>
+      <c r="O77" s="79"/>
+      <c r="P77" s="80"/>
+      <c r="Q77" s="80"/>
+      <c r="R77" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="66" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C78" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D78" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="78" t="n">
+        <v>46203</v>
+      </c>
+      <c r="F78" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G78" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H78" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I78" s="79" t="n">
+        <v>22443.411</v>
+      </c>
+      <c r="J78" s="79" t="n">
+        <v>14589.612</v>
+      </c>
+      <c r="K78" s="79" t="n">
+        <v>10368072000</v>
+      </c>
+      <c r="L78" s="80" t="n">
+        <v>108.93</v>
+      </c>
+      <c r="M78" s="79" t="n">
+        <v>96.3654</v>
+      </c>
+      <c r="N78" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="79" t="n">
+        <v>23288.098</v>
+      </c>
+      <c r="P78" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="80" t="n">
+        <v>1615</v>
+      </c>
+      <c r="R78" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" s="66" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="C79" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D79" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="78" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F79" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G79" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I79" s="79" t="n">
+        <v>13182.608</v>
+      </c>
+      <c r="J79" s="79" t="n">
+        <v>7791.357</v>
+      </c>
+      <c r="K79" s="79" t="n">
+        <v>5466357000</v>
+      </c>
+      <c r="L79" s="80" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="M79" s="79" t="n">
+        <v>96.3552</v>
+      </c>
+      <c r="N79" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="79" t="n">
+        <v>14500.386</v>
+      </c>
+      <c r="P79" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="80" t="n">
+        <v>847</v>
+      </c>
+      <c r="R79" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" s="66" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D80" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="78" t="n">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G80" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H80" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I80" s="79" t="n">
+        <v>4806.69</v>
+      </c>
+      <c r="J80" s="79" t="n">
+        <v>1597.288</v>
+      </c>
+      <c r="K80" s="79" t="n">
+        <v>870716000</v>
+      </c>
+      <c r="L80" s="80" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M80" s="79" t="n">
+        <v>96.0407</v>
+      </c>
+      <c r="N80" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="79" t="n">
+        <v>8940.787</v>
+      </c>
+      <c r="P80" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="80" t="n">
+        <v>576</v>
+      </c>
+      <c r="R80" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" s="66" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D81" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" s="78" t="n">
+        <v>45930</v>
+      </c>
+      <c r="F81" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G81" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H81" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I81" s="79" t="n">
+        <v>3807.401</v>
+      </c>
+      <c r="J81" s="79" t="n">
+        <v>1248.818</v>
+      </c>
+      <c r="K81" s="79" t="n">
+        <v>643038000</v>
+      </c>
+      <c r="L81" s="80" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M81" s="79" t="n">
+        <v>95.3452</v>
+      </c>
+      <c r="N81" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="79" t="n">
+        <v>7932.37</v>
+      </c>
+      <c r="P81" s="80" t="n">
+        <v>9.37723774</v>
+      </c>
+      <c r="Q81" s="80" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="R81" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S81" s="66" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B82" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D82" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="78" t="n">
+        <v>45838</v>
+      </c>
+      <c r="F82" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G82" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H82" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I82" s="79" t="n">
+        <v>3028.429</v>
+      </c>
+      <c r="J82" s="79" t="n">
+        <v>785.089</v>
+      </c>
+      <c r="K82" s="79" t="n">
+        <v>185349000</v>
+      </c>
+      <c r="L82" s="80" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M82" s="79" t="n">
+        <v>91.6411</v>
+      </c>
+      <c r="N82" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="79" t="n">
+        <v>7184.405</v>
+      </c>
+      <c r="P82" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="80" t="n">
+        <v>237</v>
+      </c>
+      <c r="R82" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" s="66" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="C83" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D83" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="78" t="n">
+        <v>45747</v>
+      </c>
+      <c r="F83" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G83" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H83" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I83" s="79" t="n">
+        <v>2618.742</v>
+      </c>
+      <c r="J83" s="79" t="n">
+        <v>800.733</v>
+      </c>
+      <c r="K83" s="79" t="n">
+        <v>336540000</v>
+      </c>
+      <c r="L83" s="80" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M83" s="79" t="n">
+        <v>91.5746</v>
+      </c>
+      <c r="N83" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="79" t="n">
+        <v>7854.351</v>
+      </c>
+      <c r="P83" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="80" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="R83" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S83" s="66" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="C84" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D84" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="78" t="n">
+        <v>45657</v>
+      </c>
+      <c r="F84" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G84" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H84" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I84" s="79" t="n">
+        <v>2228.005</v>
+      </c>
+      <c r="J84" s="79" t="n">
+        <v>648.956</v>
+      </c>
+      <c r="K84" s="79" t="n">
+        <v>271532000</v>
+      </c>
+      <c r="L84" s="80" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M84" s="79" t="n">
+        <v>91.4561</v>
+      </c>
+      <c r="N84" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="79" t="n">
+        <v>7491.143</v>
+      </c>
+      <c r="P84" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="80" t="n">
+        <v>218</v>
+      </c>
+      <c r="R84" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="S84" s="66" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85" s="76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D85" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" s="78" t="n">
+        <v>45565</v>
+      </c>
+      <c r="F85" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G85" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H85" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I85" s="79" t="n">
+        <v>2321.419</v>
+      </c>
+      <c r="J85" s="79" t="n">
+        <v>658.433</v>
+      </c>
+      <c r="K85" s="79" t="n">
+        <v>188620000</v>
+      </c>
+      <c r="L85" s="80" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M85" s="79" t="n">
+        <v>91.3372</v>
+      </c>
+      <c r="N85" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="79" t="n">
+        <v>7196.228</v>
+      </c>
+      <c r="P85" s="80" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q85" s="80" t="n">
+        <v>282</v>
+      </c>
+      <c r="R85" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="S85" s="66" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C86" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D86" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="78" t="n">
+        <v>45473</v>
+      </c>
+      <c r="F86" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G86" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H86" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I86" s="79" t="n">
+        <v>2190.229</v>
+      </c>
+      <c r="J86" s="79" t="n">
+        <v>759.289</v>
+      </c>
+      <c r="K86" s="79" t="n">
+        <v>294050000</v>
+      </c>
+      <c r="L86" s="80" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M86" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N86" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="79" t="n">
+        <v>6803.334</v>
+      </c>
+      <c r="P86" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="80" t="n">
         <v>302</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="81" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="42" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="82" t="s">
-        <v>305</v>
-      </c>
-      <c r="C80" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="82" t="s">
-        <v>307</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="82" t="s">
-        <v>308</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="82" t="s">
-        <v>309</v>
-      </c>
-      <c r="C83" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="82" t="s">
-        <v>310</v>
-      </c>
-      <c r="C84" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="82" t="s">
-        <v>311</v>
-      </c>
-      <c r="C85" s="24" t="s">
+      <c r="R86" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="S86" s="66" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D87" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="78" t="n">
+        <v>45382</v>
+      </c>
+      <c r="F87" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G87" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H87" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I87" s="79" t="n">
+        <v>2175.989</v>
+      </c>
+      <c r="J87" s="79" t="n">
+        <v>758.571</v>
+      </c>
+      <c r="K87" s="79" t="n">
+        <v>351970000</v>
+      </c>
+      <c r="L87" s="80" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M87" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N87" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="79" t="n">
+        <v>7398.652</v>
+      </c>
+      <c r="P87" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="80" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="R87" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S87" s="66" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D88" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="78" t="n">
+        <v>45291</v>
+      </c>
+      <c r="F88" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G88" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H88" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I88" s="79" t="n">
+        <v>2130.049</v>
+      </c>
+      <c r="J88" s="79" t="n">
+        <v>707.384</v>
+      </c>
+      <c r="K88" s="79" t="n">
+        <v>262238000</v>
+      </c>
+      <c r="L88" s="80" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M88" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N88" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="79" t="n">
+        <v>7036.917</v>
+      </c>
+      <c r="P88" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="80" t="n">
         <v>312</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="82" t="s">
-        <v>313</v>
-      </c>
-      <c r="C86" s="24" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="82" t="s">
+      <c r="R88" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="S88" s="66" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D89" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="78" t="n">
+        <v>45199</v>
+      </c>
+      <c r="F89" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G89" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H89" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I89" s="79" t="n">
+        <v>1993.007</v>
+      </c>
+      <c r="J89" s="79" t="n">
+        <v>687.513</v>
+      </c>
+      <c r="K89" s="79" t="n">
+        <v>306457000</v>
+      </c>
+      <c r="L89" s="80" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M89" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N89" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="79" t="n">
+        <v>6756.961</v>
+      </c>
+      <c r="P89" s="80" t="n">
+        <v>13.78192729</v>
+      </c>
+      <c r="Q89" s="80" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="R89" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="S89" s="66" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C90" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D90" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="78" t="n">
+        <v>45107</v>
+      </c>
+      <c r="F90" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G90" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I90" s="79" t="n">
+        <v>1930.516</v>
+      </c>
+      <c r="J90" s="79" t="n">
+        <v>636.105</v>
+      </c>
+      <c r="K90" s="79" t="n">
+        <v>230718000</v>
+      </c>
+      <c r="L90" s="80" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M90" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N90" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="79" t="n">
+        <v>6433.521</v>
+      </c>
+      <c r="P90" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="80" t="n">
+        <v>324</v>
+      </c>
+      <c r="R90" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="S90" s="66" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B91" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D91" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="78" t="n">
+        <v>45016</v>
+      </c>
+      <c r="F91" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G91" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H91" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I91" s="79" t="n">
+        <v>2260.206</v>
+      </c>
+      <c r="J91" s="79" t="n">
+        <v>814.91</v>
+      </c>
+      <c r="K91" s="79" t="n">
+        <v>348203000</v>
+      </c>
+      <c r="L91" s="80" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M91" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N91" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="79" t="n">
+        <v>7382.85</v>
+      </c>
+      <c r="P91" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="80" t="n">
         <v>314</v>
       </c>
-      <c r="C87" s="25" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="82" t="s">
-        <v>316</v>
-      </c>
-      <c r="C88" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="82" t="s">
-        <v>318</v>
-      </c>
-      <c r="C89" s="24" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="82" t="s">
-        <v>320</v>
-      </c>
-      <c r="C90" s="25" t="s">
+      <c r="R91" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="S91" s="66" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="82" t="s">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B92" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D92" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" s="78" t="n">
+        <v>44926</v>
+      </c>
+      <c r="F92" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G92" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H92" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I92" s="79" t="n">
+        <v>2286.572</v>
+      </c>
+      <c r="J92" s="79" t="n">
+        <v>860.807</v>
+      </c>
+      <c r="K92" s="79" t="n">
+        <v>385061000</v>
+      </c>
+      <c r="L92" s="80" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="M92" s="79" t="n">
+        <v>86.5531</v>
+      </c>
+      <c r="N92" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="79" t="n">
+        <v>7012.867</v>
+      </c>
+      <c r="P92" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="80" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R92" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="S92" s="66" t="s">
         <v>322</v>
       </c>
-      <c r="C91" s="25" t="s">
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D93" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="78" t="n">
+        <v>44834</v>
+      </c>
+      <c r="F93" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G93" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H93" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I93" s="79" t="n">
+        <v>2560.341</v>
+      </c>
+      <c r="J93" s="79" t="n">
+        <v>914.902</v>
+      </c>
+      <c r="K93" s="79" t="n">
+        <v>542661000</v>
+      </c>
+      <c r="L93" s="80" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M93" s="79" t="n">
+        <v>86.4706</v>
+      </c>
+      <c r="N93" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="79" t="n">
+        <v>6611.975</v>
+      </c>
+      <c r="P93" s="80" t="n">
+        <v>11.5240749</v>
+      </c>
+      <c r="Q93" s="80" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="R93" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="S93" s="66" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="82" t="s">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C94" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D94" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="78" t="n">
+        <v>44742</v>
+      </c>
+      <c r="F94" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G94" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H94" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I94" s="79" t="n">
+        <v>2866.579</v>
+      </c>
+      <c r="J94" s="79" t="n">
+        <v>947.502</v>
+      </c>
+      <c r="K94" s="79" t="n">
+        <v>536500000</v>
+      </c>
+      <c r="L94" s="80" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M94" s="79" t="n">
+        <v>83.895</v>
+      </c>
+      <c r="N94" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="79" t="n">
+        <v>6043.861</v>
+      </c>
+      <c r="P94" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="80" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="R94" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="S94" s="66" t="s">
         <v>324</v>
       </c>
-      <c r="C92" s="24" t="s">
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="C95" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D95" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="78" t="n">
+        <v>44651</v>
+      </c>
+      <c r="F95" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G95" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H95" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I95" s="79" t="n">
+        <v>2589.737</v>
+      </c>
+      <c r="J95" s="79" t="n">
+        <v>735.407</v>
+      </c>
+      <c r="K95" s="79" t="n">
+        <v>385967000</v>
+      </c>
+      <c r="L95" s="80" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M95" s="79" t="n">
+        <v>83.7225</v>
+      </c>
+      <c r="N95" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="79" t="n">
+        <v>6458.201</v>
+      </c>
+      <c r="P95" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="80" t="n">
+        <v>215</v>
+      </c>
+      <c r="R95" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="S95" s="66" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="82" t="s">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B96" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="C96" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D96" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" s="78" t="n">
+        <v>44561</v>
+      </c>
+      <c r="F96" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G96" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H96" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I96" s="79" t="n">
+        <v>2396.847</v>
+      </c>
+      <c r="J96" s="79" t="n">
+        <v>677.529</v>
+      </c>
+      <c r="K96" s="79" t="n">
+        <v>290253000</v>
+      </c>
+      <c r="L96" s="80" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M96" s="79" t="n">
+        <v>82.668</v>
+      </c>
+      <c r="N96" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="79" t="n">
+        <v>5960.989</v>
+      </c>
+      <c r="P96" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="80" t="n">
+        <v>204</v>
+      </c>
+      <c r="R96" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="S96" s="66" t="s">
         <v>326</v>
       </c>
-      <c r="C93" s="24" t="s">
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B97" s="76" t="s">
+        <v>247</v>
+      </c>
+      <c r="C97" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D97" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="78" t="n">
+        <v>44469</v>
+      </c>
+      <c r="F97" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G97" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H97" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I97" s="79" t="n">
+        <v>2973.845</v>
+      </c>
+      <c r="J97" s="79" t="n">
+        <v>975.336</v>
+      </c>
+      <c r="K97" s="79" t="n">
+        <v>533714000</v>
+      </c>
+      <c r="L97" s="80" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M97" s="79" t="n">
+        <v>82.628</v>
+      </c>
+      <c r="N97" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="79" t="n">
+        <v>5663.586</v>
+      </c>
+      <c r="P97" s="80" t="n">
+        <v>6.69560253</v>
+      </c>
+      <c r="Q97" s="80" t="n">
+        <v>182</v>
+      </c>
+      <c r="R97" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="S97" s="66" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="82" t="s">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="C98" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D98" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="78" t="n">
+        <v>44377</v>
+      </c>
+      <c r="F98" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G98" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H98" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I98" s="79" t="n">
+        <v>2885.046</v>
+      </c>
+      <c r="J98" s="79" t="n">
+        <v>888.15</v>
+      </c>
+      <c r="K98" s="79" t="n">
+        <v>477358000</v>
+      </c>
+      <c r="L98" s="80" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="M98" s="79" t="n">
+        <v>82.516</v>
+      </c>
+      <c r="N98" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="79" t="n">
+        <v>5668.615</v>
+      </c>
+      <c r="P98" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="80" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="R98" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="S98" s="66" t="s">
         <v>328</v>
       </c>
-      <c r="C94" s="25" t="s">
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" s="76" t="s">
+        <v>251</v>
+      </c>
+      <c r="C99" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D99" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="78" t="n">
+        <v>44286</v>
+      </c>
+      <c r="F99" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G99" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H99" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I99" s="79" t="n">
+        <v>1939.92</v>
+      </c>
+      <c r="J99" s="79" t="n">
+        <v>551.203</v>
+      </c>
+      <c r="K99" s="79" t="n">
+        <v>259563000</v>
+      </c>
+      <c r="L99" s="80" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M99" s="79" t="n">
+        <v>82.459</v>
+      </c>
+      <c r="N99" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="79" t="n">
+        <v>5182.897</v>
+      </c>
+      <c r="P99" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="80" t="n">
+        <v>170</v>
+      </c>
+      <c r="R99" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="S99" s="66" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="82" t="s">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B100" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="C100" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D100" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" s="78" t="n">
+        <v>44196</v>
+      </c>
+      <c r="F100" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G100" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H100" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I100" s="79" t="n">
+        <v>1575.49</v>
+      </c>
+      <c r="J100" s="79" t="n">
+        <v>458.968</v>
+      </c>
+      <c r="K100" s="79" t="n">
+        <v>175456000</v>
+      </c>
+      <c r="L100" s="80" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M100" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N100" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="79" t="n">
+        <v>4816.246</v>
+      </c>
+      <c r="P100" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="80" t="n">
+        <v>166</v>
+      </c>
+      <c r="R100" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="S100" s="66" t="s">
         <v>330</v>
       </c>
-      <c r="C95" s="24" t="s">
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="C101" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D101" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" s="78" t="n">
+        <v>44104</v>
+      </c>
+      <c r="F101" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G101" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H101" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I101" s="79" t="n">
+        <v>1627.205</v>
+      </c>
+      <c r="J101" s="79" t="n">
+        <v>493.122</v>
+      </c>
+      <c r="K101" s="79" t="n">
+        <v>194271000</v>
+      </c>
+      <c r="L101" s="80" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M101" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N101" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="79" t="n">
+        <v>4634.348</v>
+      </c>
+      <c r="P101" s="80"/>
+      <c r="Q101" s="80" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="R101" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="S101" s="66" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="81" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="42" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="82" t="s">
+        <v>334</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="82" t="s">
+        <v>336</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="82" t="s">
+        <v>337</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="82" t="s">
+        <v>338</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="82" t="s">
+        <v>339</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="82" t="s">
+        <v>340</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="82" t="s">
+        <v>342</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="82" t="s">
+        <v>343</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="82" t="s">
+        <v>345</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="82" t="s">
+        <v>347</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="82" t="s">
+        <v>349</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="82" t="s">
+        <v>351</v>
+      </c>
+      <c r="C116" s="25" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="82" t="s">
+        <v>353</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="82" t="s">
+        <v>355</v>
+      </c>
+      <c r="C118" s="24" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="82" t="s">
+        <v>357</v>
+      </c>
+      <c r="C119" s="25" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="82" t="s">
+        <v>359</v>
+      </c>
+      <c r="C120" s="24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="82" t="s">
-        <v>331</v>
-      </c>
-      <c r="C96" s="24" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="24" t="s">
-        <v>333</v>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="82" t="s">
+        <v>360</v>
+      </c>
+      <c r="C121" s="24" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="24" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S76"/>
+  <autoFilter ref="A1:S101"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -22485,7 +24094,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -22500,19 +24109,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22557,27 +24166,47 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>353.215</v>
+        <v>5.31033</v>
       </c>
       <c r="C4" s="80" t="n">
-        <v>194.82417</v>
+        <v>8.78848</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46387</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4" s="78" t="n">
         <v>46267</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>339</v>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="80" t="n">
+        <v>353.215</v>
+      </c>
+      <c r="C5" s="80" t="n">
+        <v>194.82417</v>
+      </c>
+      <c r="D5" s="78" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E5" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="78" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dashboard!$A$2:$AC$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$76</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$101</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="412">
   <si>
     <r>
       <rPr>
@@ -3851,6 +3851,18 @@
     <t xml:space="preserve">電腦及週邊設備業</t>
   </si>
   <si>
+    <t xml:space="preserve">3037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欣興</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電子工業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">池子</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4362,6 +4374,81 @@
   </si>
   <si>
     <t xml:space="preserve">2408|24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3037|24</t>
   </si>
   <si>
     <t xml:space="preserve">5289|0</t>
@@ -6787,11 +6874,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="34">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F3864"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF2F2F2"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6846,7 +6941,31 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF99D5A9"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF69C180"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF9FDFA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDDF1E2"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6894,6 +7013,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF7ECA92"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF1F9F3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -6910,7 +7037,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF9FDFA"/>
+          <fgColor rgb="FFE2F3E6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE7F5EB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7597,7 +7732,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -7612,16 +7747,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7656,16 +7791,31 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>1420</v>
+        <v>973</v>
       </c>
       <c r="C4" s="78" t="n">
         <v>46267</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="80" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C5" s="78" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78" t="n">
         <v>46267</v>
       </c>
     </row>
@@ -7734,16 +7884,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -7752,13 +7902,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -7767,7 +7917,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -7776,16 +7926,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>354</v>
+        <v>383</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -7794,16 +7944,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>356</v>
+        <v>385</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>358</v>
+        <v>387</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -7812,7 +7962,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>359</v>
+        <v>388</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -7821,7 +7971,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -7830,7 +7980,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>361</v>
+        <v>390</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -7842,19 +7992,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>362</v>
+        <v>391</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>365</v>
+        <v>394</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8406,183 +8556,183 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="str">
         <f aca="false">IF(Tickers!A5="","",Tickers!A5)</f>
-        <v/>
+        <v>3037</v>
       </c>
       <c r="B5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A5,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>欣興</v>
       </c>
       <c r="C5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A5,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D5" s="51" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E5" s="48" t="str">
+        <v>973</v>
+      </c>
+      <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="F5" s="51" t="str">
+        <v>149021.578</v>
+      </c>
+      <c r="F5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="G5" s="51" t="str">
+        <v>15.49</v>
+      </c>
+      <c r="G5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=0",Raw_Q!$R$2:$R$600,"&lt;=3"),""))</f>
-        <v/>
-      </c>
-      <c r="H5" s="51" t="str">
+        <v>17.86022</v>
+      </c>
+      <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v/>
-      </c>
-      <c r="I5" s="49" t="str">
+        <v>31.8584038356164</v>
+      </c>
+      <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
-        <v/>
-      </c>
-      <c r="J5" s="52" t="str">
+        <v>10.7348484848485</v>
+      </c>
+      <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="K5" s="52" t="str">
+        <v>62.8147191736604</v>
+      </c>
+      <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="L5" s="52" t="str">
+        <v>54.4786122455379</v>
+      </c>
+      <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="M5" s="49" t="str">
+        <v>30.5413919988115</v>
+      </c>
+      <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v/>
-      </c>
-      <c r="N5" s="51" t="str">
+        <v>0.868959365068322</v>
+      </c>
+      <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="O5" s="51" t="str">
+        <v>0.0585147701547155</v>
+      </c>
+      <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="P5" s="51" t="str">
+        <v>0.351470888358631</v>
+      </c>
+      <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="Q5" s="49" t="str">
+        <v>1.50004559</v>
+      </c>
+      <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v/>
-      </c>
-      <c r="R5" s="49" t="str">
+        <v>0.00154167069886948</v>
+      </c>
+      <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
-        <v/>
-      </c>
-      <c r="S5" s="49" t="str">
+        <v>-0.499985130009715</v>
+      </c>
+      <c r="S5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="T5" s="49" t="str">
+        <v>0.32106691775977</v>
+      </c>
+      <c r="T5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,2)-1,""))</f>
-        <v/>
-      </c>
-      <c r="U5" s="49" t="str">
+        <v>0.145363906943928</v>
+      </c>
+      <c r="U5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,3)-1,""))</f>
-        <v/>
-      </c>
-      <c r="V5" s="68" t="str">
+        <v>0.0794320733117051</v>
+      </c>
+      <c r="V5" s="68" t="n">
         <f aca="false">IF($A5="","",IFERROR((T5-U5)*100,""))</f>
-        <v/>
+        <v>6.59318336322232</v>
       </c>
       <c r="W5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(IF(NOT(ISNUMBER(T5)),"",IF(T5&gt;0,IF(V5&gt;0,"成長且加速","成長但減速"),IF(V5&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
-        <v/>
-      </c>
-      <c r="X5" s="68" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="X5" s="68" t="n">
         <f aca="false">IF($A5="","",IFERROR((T5-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,6)-1))*100,""))</f>
-        <v/>
-      </c>
-      <c r="Y5" s="49" t="str">
+        <v>6.63825189981138</v>
+      </c>
+      <c r="Y5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="Z5" s="49" t="str">
+        <v>421.5</v>
+      </c>
+      <c r="Z5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/E5,""))</f>
-        <v/>
-      </c>
-      <c r="AA5" s="49" t="str">
+        <v>0.183764179439839</v>
+      </c>
+      <c r="AA5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v/>
-      </c>
-      <c r="AB5" s="50" t="str">
+        <v>0.218926277697247</v>
+      </c>
+      <c r="AB5" s="50" t="n">
         <f aca="false">IF($A5="","",IFERROR((Z5-AA5)*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AC5" s="50" t="str">
+        <v>-351.620982574077</v>
+      </c>
+      <c r="AC5" s="50" t="n">
         <f aca="false">IF($A5="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="51" t="str">
+        <v>1172.66230031105</v>
+      </c>
+      <c r="AD5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
-      </c>
-      <c r="AE5" s="48" t="str">
+        <v>77.8511415598572</v>
+      </c>
+      <c r="AE5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600),""))</f>
-        <v/>
-      </c>
-      <c r="AF5" s="49" t="str">
+        <v>24410.793402</v>
+      </c>
+      <c r="AF5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"N/M",AE5/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AG5" s="49" t="str">
+        <v>0.230582339460269</v>
+      </c>
+      <c r="AG5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(AVERAGE(AO5:AS5),""))</f>
-        <v/>
-      </c>
-      <c r="AH5" s="49" t="str">
+        <v>0.205177462976033</v>
+      </c>
+      <c r="AH5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(AD5&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/AD5),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AI5" s="51" t="str">
+        <v>0.258465702580982</v>
+      </c>
+      <c r="AI5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,0),""))</f>
-        <v/>
+        <v>3.81022</v>
       </c>
       <c r="AJ5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A5&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AK5" s="66" t="str">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A5&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AL5" s="47" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AL5" s="47" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A5,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AM5" s="67" t="str">
+        <v>14</v>
+      </c>
+      <c r="AM5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AN5" s="67" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AO5" s="49" t="str">
+        <v>46267</v>
+      </c>
+      <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AP5" s="49" t="str">
+        <v>0.230582339460269</v>
+      </c>
+      <c r="AP5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=5)*(Raw_Q!$R$2:$R$600&lt;=8)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AQ5" s="49" t="str">
+        <v>0.0224224135601822</v>
+      </c>
+      <c r="AQ5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=9)*(Raw_Q!$R$2:$R$600&lt;=12)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,9)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AR5" s="49" t="str">
+        <v>0.107845687985598</v>
+      </c>
+      <c r="AR5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=13)*(Raw_Q!$R$2:$R$600&lt;=16)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,13)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AS5" s="49" t="str">
+        <v>0.290336370786566</v>
+      </c>
+      <c r="AS5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=17)*(Raw_Q!$R$2:$R$600&lt;=20)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,17)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,21))/2)),""))</f>
-        <v/>
+        <v>0.374700503087549</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11499,7 +11649,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -11528,78 +11678,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>370</v>
+        <v>399</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>371</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>373</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>374</v>
+        <v>403</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>375</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>377</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>378</v>
+        <v>407</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>379</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>381</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>382</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -12121,119 +12271,119 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!A$5)</f>
-        <v/>
+        <v>3037</v>
       </c>
       <c r="B6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!B$5)</f>
-        <v/>
+        <v>欣興</v>
       </c>
       <c r="C6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!C$5)</f>
-        <v/>
-      </c>
-      <c r="D6" s="17" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v/>
-      </c>
-      <c r="E6" s="18" t="str">
+        <v>973</v>
+      </c>
+      <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v/>
-      </c>
-      <c r="F6" s="18" t="str">
+        <v>62.8147191736604</v>
+      </c>
+      <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v/>
-      </c>
-      <c r="G6" s="17" t="str">
+        <v>30.5413919988115</v>
+      </c>
+      <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v/>
-      </c>
-      <c r="H6" s="17" t="str">
+        <v>0.0585147701547155</v>
+      </c>
+      <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v/>
-      </c>
-      <c r="I6" s="19" t="str">
+        <v>0.351470888358631</v>
+      </c>
+      <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v/>
-      </c>
-      <c r="J6" s="19" t="str">
+        <v>0.00154167069886948</v>
+      </c>
+      <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
-        <v/>
-      </c>
-      <c r="K6" s="19" t="str">
+        <v>-0.499985130009715</v>
+      </c>
+      <c r="K6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!T$5)</f>
-        <v/>
-      </c>
-      <c r="L6" s="19" t="str">
+        <v>0.145363906943928</v>
+      </c>
+      <c r="L6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!U$5)</f>
-        <v/>
-      </c>
-      <c r="M6" s="20" t="str">
+        <v>0.0794320733117051</v>
+      </c>
+      <c r="M6" s="20" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!V$5)</f>
-        <v/>
+        <v>6.59318336322232</v>
       </c>
       <c r="N6" s="21" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!W$5)</f>
-        <v/>
-      </c>
-      <c r="O6" s="20" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="O6" s="20" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!X$5)</f>
-        <v/>
-      </c>
-      <c r="P6" s="19" t="str">
+        <v>6.63825189981138</v>
+      </c>
+      <c r="P6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!S$5)</f>
-        <v/>
-      </c>
-      <c r="Q6" s="19" t="str">
+        <v>0.32106691775977</v>
+      </c>
+      <c r="Q6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Y$5)</f>
-        <v/>
-      </c>
-      <c r="R6" s="19" t="str">
+        <v>421.5</v>
+      </c>
+      <c r="R6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!I$5)</f>
-        <v/>
-      </c>
-      <c r="S6" s="19" t="str">
+        <v>10.7348484848485</v>
+      </c>
+      <c r="S6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Z$5)</f>
-        <v/>
-      </c>
-      <c r="T6" s="19" t="str">
+        <v>0.183764179439839</v>
+      </c>
+      <c r="T6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AA$5)</f>
-        <v/>
-      </c>
-      <c r="U6" s="22" t="str">
+        <v>0.218926277697247</v>
+      </c>
+      <c r="U6" s="22" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AB$5)</f>
-        <v/>
-      </c>
-      <c r="V6" s="22" t="str">
+        <v>-351.620982574077</v>
+      </c>
+      <c r="V6" s="22" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AC$5)</f>
-        <v/>
-      </c>
-      <c r="W6" s="19" t="str">
+        <v>1172.66230031105</v>
+      </c>
+      <c r="W6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AF$5)</f>
-        <v/>
-      </c>
-      <c r="X6" s="19" t="str">
+        <v>0.230582339460269</v>
+      </c>
+      <c r="X6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AG$5)</f>
-        <v/>
-      </c>
-      <c r="Y6" s="19" t="str">
+        <v>0.205177462976033</v>
+      </c>
+      <c r="Y6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AH$5)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="17" t="str">
+        <v>0.258465702580982</v>
+      </c>
+      <c r="Z6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AI$5)</f>
-        <v/>
+        <v>3.81022</v>
       </c>
       <c r="AA6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!AJ$5)</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AB6" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!AK$5)</f>
-        <v/>
-      </c>
-      <c r="AC6" s="23" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AC6" s="23" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AM$5)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14237,36 +14387,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16523,7 +16673,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C0625DDC-5729-4C6C-8821-3F1BB92CD42E}</x14:id>
+          <x14:id>{6520CEF1-3328-417A-92CE-BE6E8E604FD0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16539,16 +16689,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16589,47 +16739,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16654,7 +16804,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C0625DDC-5729-4C6C-8821-3F1BB92CD42E}">
+          <x14:cfRule type="dataBar" id="{6520CEF1-3328-417A-92CE-BE6E8E604FD0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -16855,43 +17005,43 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="str">
         <f aca="false">IF(Calc!$A$5="","",Calc!$A$5)</f>
-        <v/>
-      </c>
-      <c r="B7" s="47" t="str">
+        <v>3037</v>
+      </c>
+      <c r="B7" s="47" t="n">
         <f aca="false">IF($A7="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A7,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v/>
-      </c>
-      <c r="C7" s="47" t="str">
+        <v>24</v>
+      </c>
+      <c r="C7" s="47" t="n">
         <f aca="false">IF($A7="","",Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D7" s="67" t="str">
+        <v>24</v>
+      </c>
+      <c r="D7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,$B7),""))</f>
-        <v/>
-      </c>
-      <c r="E7" s="67" t="str">
+        <v>44104</v>
+      </c>
+      <c r="E7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="F7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A7&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G7" s="67" t="str">
+        <v>FY2026Q3E</v>
+      </c>
+      <c r="G7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H7" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v/>
-      </c>
-      <c r="I7" s="67" t="str">
+        <v>-46267</v>
+      </c>
+      <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="J7" s="72" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
-        <v/>
+        <v>待更新財報</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17573,18 +17723,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17700,12 +17850,22 @@
       <c r="G4" s="73"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="73"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="A5" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="74" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>182</v>
+      </c>
       <c r="E5" s="73"/>
-      <c r="F5" s="75"/>
+      <c r="F5" s="75" t="n">
+        <v>46267</v>
+      </c>
       <c r="G5" s="73"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17854,7 +18014,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -17873,7 +18033,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S123"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -17897,58 +18057,58 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17956,7 +18116,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C2" s="77" t="n">
         <v>2026</v>
@@ -17968,13 +18128,13 @@
         <v>46295</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I2" s="79"/>
       <c r="J2" s="79"/>
@@ -17991,7 +18151,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="66" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17999,7 +18159,7 @@
         <v>167</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C3" s="77" t="n">
         <v>2026</v>
@@ -18011,13 +18171,13 @@
         <v>46203</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G3" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H3" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I3" s="79" t="n">
         <v>1270380.25</v>
@@ -18050,7 +18210,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="66" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18058,7 +18218,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C4" s="77" t="n">
         <v>2026</v>
@@ -18070,13 +18230,13 @@
         <v>46112</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G4" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H4" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H4" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I4" s="79" t="n">
         <v>1134103.44</v>
@@ -18109,7 +18269,7 @@
         <v>2</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18117,7 +18277,7 @@
         <v>167</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C5" s="77" t="n">
         <v>2025</v>
@@ -18129,13 +18289,13 @@
         <v>46022</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G5" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H5" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H5" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I5" s="79" t="n">
         <v>1046090.421</v>
@@ -18168,7 +18328,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="66" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18176,7 +18336,7 @@
         <v>167</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C6" s="77" t="n">
         <v>2025</v>
@@ -18188,13 +18348,13 @@
         <v>45930</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G6" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H6" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H6" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I6" s="79" t="n">
         <v>989918.318</v>
@@ -18227,7 +18387,7 @@
         <v>4</v>
       </c>
       <c r="S6" s="66" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18235,7 +18395,7 @@
         <v>167</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C7" s="77" t="n">
         <v>2025</v>
@@ -18247,13 +18407,13 @@
         <v>45838</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G7" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H7" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H7" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I7" s="79" t="n">
         <v>933791.869</v>
@@ -18286,7 +18446,7 @@
         <v>5</v>
       </c>
       <c r="S7" s="66" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18294,7 +18454,7 @@
         <v>167</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C8" s="77" t="n">
         <v>2025</v>
@@ -18306,13 +18466,13 @@
         <v>45747</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G8" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H8" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I8" s="79" t="n">
         <v>839253.664</v>
@@ -18345,7 +18505,7 @@
         <v>6</v>
       </c>
       <c r="S8" s="66" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18353,7 +18513,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C9" s="77" t="n">
         <v>2024</v>
@@ -18365,13 +18525,13 @@
         <v>45657</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G9" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H9" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H9" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I9" s="79" t="n">
         <v>868461.178</v>
@@ -18404,7 +18564,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="66" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18412,7 +18572,7 @@
         <v>167</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C10" s="77" t="n">
         <v>2024</v>
@@ -18424,13 +18584,13 @@
         <v>45565</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G10" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H10" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H10" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I10" s="79" t="n">
         <v>759692.143</v>
@@ -18463,7 +18623,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="66" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18471,7 +18631,7 @@
         <v>167</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C11" s="77" t="n">
         <v>2024</v>
@@ -18483,13 +18643,13 @@
         <v>45473</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G11" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H11" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H11" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I11" s="79" t="n">
         <v>673510.177</v>
@@ -18522,7 +18682,7 @@
         <v>9</v>
       </c>
       <c r="S11" s="66" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18530,7 +18690,7 @@
         <v>167</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C12" s="77" t="n">
         <v>2024</v>
@@ -18542,13 +18702,13 @@
         <v>45382</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G12" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H12" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H12" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I12" s="79" t="n">
         <v>592644.201</v>
@@ -18581,7 +18741,7 @@
         <v>10</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18589,7 +18749,7 @@
         <v>167</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C13" s="77" t="n">
         <v>2023</v>
@@ -18601,13 +18761,13 @@
         <v>45291</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G13" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H13" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H13" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I13" s="79" t="n">
         <v>625528.856</v>
@@ -18640,7 +18800,7 @@
         <v>11</v>
       </c>
       <c r="S13" s="66" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18648,7 +18808,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C14" s="77" t="n">
         <v>2023</v>
@@ -18660,13 +18820,13 @@
         <v>45199</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G14" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H14" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H14" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I14" s="79" t="n">
         <v>546732.758</v>
@@ -18699,7 +18859,7 @@
         <v>12</v>
       </c>
       <c r="S14" s="66" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18707,7 +18867,7 @@
         <v>167</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C15" s="77" t="n">
         <v>2023</v>
@@ -18719,13 +18879,13 @@
         <v>45107</v>
       </c>
       <c r="F15" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G15" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H15" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H15" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I15" s="79" t="n">
         <v>480841.254</v>
@@ -18758,7 +18918,7 @@
         <v>13</v>
       </c>
       <c r="S15" s="66" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18766,7 +18926,7 @@
         <v>167</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C16" s="77" t="n">
         <v>2023</v>
@@ -18778,13 +18938,13 @@
         <v>45016</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G16" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H16" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H16" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I16" s="79" t="n">
         <v>508632.973</v>
@@ -18817,7 +18977,7 @@
         <v>14</v>
       </c>
       <c r="S16" s="66" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18825,7 +18985,7 @@
         <v>167</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C17" s="77" t="n">
         <v>2022</v>
@@ -18837,13 +18997,13 @@
         <v>44926</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G17" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H17" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H17" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I17" s="79" t="n">
         <v>625531.868</v>
@@ -18876,7 +19036,7 @@
         <v>15</v>
       </c>
       <c r="S17" s="66" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18884,7 +19044,7 @@
         <v>167</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C18" s="77" t="n">
         <v>2022</v>
@@ -18896,13 +19056,13 @@
         <v>44834</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G18" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H18" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H18" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I18" s="79" t="n">
         <v>613142.743</v>
@@ -18935,7 +19095,7 @@
         <v>16</v>
       </c>
       <c r="S18" s="66" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18943,7 +19103,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C19" s="77" t="n">
         <v>2022</v>
@@ -18955,13 +19115,13 @@
         <v>44742</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G19" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H19" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H19" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I19" s="79" t="n">
         <v>534140.808</v>
@@ -18994,7 +19154,7 @@
         <v>17</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19002,7 +19162,7 @@
         <v>167</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C20" s="77" t="n">
         <v>2022</v>
@@ -19014,13 +19174,13 @@
         <v>44651</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G20" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H20" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H20" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I20" s="79" t="n">
         <v>491075.873</v>
@@ -19053,7 +19213,7 @@
         <v>18</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19061,7 +19221,7 @@
         <v>167</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C21" s="77" t="n">
         <v>2021</v>
@@ -19073,13 +19233,13 @@
         <v>44561</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G21" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H21" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H21" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I21" s="79" t="n">
         <v>438189.306</v>
@@ -19112,7 +19272,7 @@
         <v>19</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19120,7 +19280,7 @@
         <v>167</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C22" s="77" t="n">
         <v>2021</v>
@@ -19132,13 +19292,13 @@
         <v>44469</v>
       </c>
       <c r="F22" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G22" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H22" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H22" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I22" s="79" t="n">
         <v>414670.379</v>
@@ -19171,7 +19331,7 @@
         <v>20</v>
       </c>
       <c r="S22" s="66" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19179,7 +19339,7 @@
         <v>167</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C23" s="77" t="n">
         <v>2021</v>
@@ -19191,13 +19351,13 @@
         <v>44377</v>
       </c>
       <c r="F23" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G23" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H23" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H23" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I23" s="79" t="n">
         <v>372145.122</v>
@@ -19230,7 +19390,7 @@
         <v>21</v>
       </c>
       <c r="S23" s="66" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19238,7 +19398,7 @@
         <v>167</v>
       </c>
       <c r="B24" s="76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C24" s="77" t="n">
         <v>2021</v>
@@ -19250,13 +19410,13 @@
         <v>44286</v>
       </c>
       <c r="F24" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G24" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H24" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H24" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I24" s="79" t="n">
         <v>362410.23</v>
@@ -19289,7 +19449,7 @@
         <v>22</v>
       </c>
       <c r="S24" s="66" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19297,7 +19457,7 @@
         <v>167</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C25" s="77" t="n">
         <v>2020</v>
@@ -19309,13 +19469,13 @@
         <v>44196</v>
       </c>
       <c r="F25" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G25" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H25" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I25" s="79" t="n">
         <v>361533.057</v>
@@ -19348,7 +19508,7 @@
         <v>23</v>
       </c>
       <c r="S25" s="66" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19356,7 +19516,7 @@
         <v>167</v>
       </c>
       <c r="B26" s="76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C26" s="77" t="n">
         <v>2020</v>
@@ -19368,13 +19528,13 @@
         <v>44104</v>
       </c>
       <c r="F26" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G26" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H26" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H26" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I26" s="79" t="n">
         <v>356426.204</v>
@@ -19405,7 +19565,7 @@
         <v>24</v>
       </c>
       <c r="S26" s="66" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19413,7 +19573,7 @@
         <v>171</v>
       </c>
       <c r="B27" s="76" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C27" s="77" t="n">
         <v>2026</v>
@@ -19425,13 +19585,13 @@
         <v>46295</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G27" s="76" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H27" s="76" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I27" s="79"/>
       <c r="J27" s="79"/>
@@ -19448,7 +19608,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="66" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19456,7 +19616,7 @@
         <v>171</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C28" s="77" t="n">
         <v>2026</v>
@@ -19468,13 +19628,13 @@
         <v>46203</v>
       </c>
       <c r="F28" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G28" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H28" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H28" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I28" s="79" t="n">
         <v>82549.073</v>
@@ -19507,7 +19667,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="66" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19515,7 +19675,7 @@
         <v>171</v>
       </c>
       <c r="B29" s="76" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C29" s="77" t="n">
         <v>2026</v>
@@ -19527,13 +19687,13 @@
         <v>46112</v>
       </c>
       <c r="F29" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G29" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H29" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H29" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I29" s="79" t="n">
         <v>49086.932</v>
@@ -19566,7 +19726,7 @@
         <v>2</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19574,7 +19734,7 @@
         <v>171</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C30" s="77" t="n">
         <v>2025</v>
@@ -19586,13 +19746,13 @@
         <v>46022</v>
       </c>
       <c r="F30" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G30" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H30" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H30" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I30" s="79" t="n">
         <v>30093.618</v>
@@ -19625,7 +19785,7 @@
         <v>3</v>
       </c>
       <c r="S30" s="66" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19633,7 +19793,7 @@
         <v>171</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C31" s="77" t="n">
         <v>2025</v>
@@ -19645,13 +19805,13 @@
         <v>45930</v>
       </c>
       <c r="F31" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G31" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H31" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H31" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I31" s="79" t="n">
         <v>18778.868</v>
@@ -19684,7 +19844,7 @@
         <v>4</v>
       </c>
       <c r="S31" s="66" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19692,7 +19852,7 @@
         <v>171</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C32" s="77" t="n">
         <v>2025</v>
@@ -19704,13 +19864,13 @@
         <v>45838</v>
       </c>
       <c r="F32" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G32" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H32" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H32" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I32" s="79" t="n">
         <v>10526.094</v>
@@ -19743,7 +19903,7 @@
         <v>5</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19751,7 +19911,7 @@
         <v>171</v>
       </c>
       <c r="B33" s="76" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C33" s="77" t="n">
         <v>2025</v>
@@ -19763,13 +19923,13 @@
         <v>45747</v>
       </c>
       <c r="F33" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G33" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H33" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H33" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I33" s="79" t="n">
         <v>7187.94</v>
@@ -19802,7 +19962,7 @@
         <v>6</v>
       </c>
       <c r="S33" s="66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19810,7 +19970,7 @@
         <v>171</v>
       </c>
       <c r="B34" s="76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C34" s="77" t="n">
         <v>2024</v>
@@ -19822,13 +19982,13 @@
         <v>45657</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G34" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H34" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H34" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I34" s="79" t="n">
         <v>6575.094</v>
@@ -19861,7 +20021,7 @@
         <v>7</v>
       </c>
       <c r="S34" s="66" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19869,7 +20029,7 @@
         <v>171</v>
       </c>
       <c r="B35" s="76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C35" s="77" t="n">
         <v>2024</v>
@@ -19881,13 +20041,13 @@
         <v>45565</v>
       </c>
       <c r="F35" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G35" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H35" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H35" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I35" s="79" t="n">
         <v>8132.593</v>
@@ -19920,7 +20080,7 @@
         <v>8</v>
       </c>
       <c r="S35" s="66" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19928,7 +20088,7 @@
         <v>171</v>
       </c>
       <c r="B36" s="76" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C36" s="77" t="n">
         <v>2024</v>
@@ -19940,13 +20100,13 @@
         <v>45473</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G36" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H36" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H36" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I36" s="79" t="n">
         <v>9921.043</v>
@@ -19973,7 +20133,7 @@
         <v>9</v>
       </c>
       <c r="S36" s="66" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19981,7 +20141,7 @@
         <v>171</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C37" s="77" t="n">
         <v>2024</v>
@@ -19993,13 +20153,13 @@
         <v>45382</v>
       </c>
       <c r="F37" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G37" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H37" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H37" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I37" s="79" t="n">
         <v>9502.937</v>
@@ -20032,7 +20192,7 @@
         <v>10</v>
       </c>
       <c r="S37" s="66" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20040,7 +20200,7 @@
         <v>171</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C38" s="77" t="n">
         <v>2023</v>
@@ -20052,13 +20212,13 @@
         <v>45291</v>
       </c>
       <c r="F38" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G38" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H38" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H38" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I38" s="79" t="n">
         <v>8703.978</v>
@@ -20091,7 +20251,7 @@
         <v>11</v>
       </c>
       <c r="S38" s="66" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20099,7 +20259,7 @@
         <v>171</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C39" s="77" t="n">
         <v>2023</v>
@@ -20111,13 +20271,13 @@
         <v>45199</v>
       </c>
       <c r="F39" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G39" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H39" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H39" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I39" s="79" t="n">
         <v>7736.374</v>
@@ -20150,7 +20310,7 @@
         <v>12</v>
       </c>
       <c r="S39" s="66" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20158,7 +20318,7 @@
         <v>171</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C40" s="77" t="n">
         <v>2023</v>
@@ -20170,13 +20330,13 @@
         <v>45107</v>
       </c>
       <c r="F40" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G40" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H40" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H40" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I40" s="79" t="n">
         <v>7027.071</v>
@@ -20209,7 +20369,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="66" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20217,7 +20377,7 @@
         <v>171</v>
       </c>
       <c r="B41" s="76" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C41" s="77" t="n">
         <v>2023</v>
@@ -20229,13 +20389,13 @@
         <v>45016</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G41" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H41" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H41" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I41" s="79" t="n">
         <v>6424.883</v>
@@ -20268,7 +20428,7 @@
         <v>14</v>
       </c>
       <c r="S41" s="66" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20276,7 +20436,7 @@
         <v>171</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C42" s="77" t="n">
         <v>2022</v>
@@ -20288,13 +20448,13 @@
         <v>44926</v>
       </c>
       <c r="F42" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G42" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H42" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H42" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I42" s="79" t="n">
         <v>7953.553</v>
@@ -20327,7 +20487,7 @@
         <v>15</v>
       </c>
       <c r="S42" s="66" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20335,7 +20495,7 @@
         <v>171</v>
       </c>
       <c r="B43" s="76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C43" s="77" t="n">
         <v>2022</v>
@@ -20347,13 +20507,13 @@
         <v>44834</v>
       </c>
       <c r="F43" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G43" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H43" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H43" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I43" s="79" t="n">
         <v>11021.725</v>
@@ -20386,7 +20546,7 @@
         <v>16</v>
       </c>
       <c r="S43" s="66" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20394,7 +20554,7 @@
         <v>171</v>
       </c>
       <c r="B44" s="76" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C44" s="77" t="n">
         <v>2022</v>
@@ -20406,13 +20566,13 @@
         <v>44742</v>
       </c>
       <c r="F44" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G44" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H44" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H44" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I44" s="79" t="n">
         <v>18030.672</v>
@@ -20445,7 +20605,7 @@
         <v>17</v>
       </c>
       <c r="S44" s="66" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20453,7 +20613,7 @@
         <v>171</v>
       </c>
       <c r="B45" s="76" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C45" s="77" t="n">
         <v>2022</v>
@@ -20465,13 +20625,13 @@
         <v>44651</v>
       </c>
       <c r="F45" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G45" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H45" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H45" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I45" s="79" t="n">
         <v>19946.325</v>
@@ -20504,7 +20664,7 @@
         <v>18</v>
       </c>
       <c r="S45" s="66" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20512,7 +20672,7 @@
         <v>171</v>
       </c>
       <c r="B46" s="76" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C46" s="77" t="n">
         <v>2021</v>
@@ -20524,13 +20684,13 @@
         <v>44561</v>
       </c>
       <c r="F46" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G46" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H46" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H46" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I46" s="79" t="n">
         <v>21398.949</v>
@@ -20563,7 +20723,7 @@
         <v>19</v>
       </c>
       <c r="S46" s="66" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20571,7 +20731,7 @@
         <v>171</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C47" s="77" t="n">
         <v>2021</v>
@@ -20583,13 +20743,13 @@
         <v>44469</v>
       </c>
       <c r="F47" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G47" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H47" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H47" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I47" s="79" t="n">
         <v>23837.128</v>
@@ -20622,7 +20782,7 @@
         <v>20</v>
       </c>
       <c r="S47" s="66" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20630,7 +20790,7 @@
         <v>171</v>
       </c>
       <c r="B48" s="76" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C48" s="77" t="n">
         <v>2021</v>
@@ -20642,13 +20802,13 @@
         <v>44377</v>
       </c>
       <c r="F48" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G48" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H48" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H48" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I48" s="79" t="n">
         <v>22637.468</v>
@@ -20681,7 +20841,7 @@
         <v>21</v>
       </c>
       <c r="S48" s="66" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20689,7 +20849,7 @@
         <v>171</v>
       </c>
       <c r="B49" s="76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C49" s="77" t="n">
         <v>2021</v>
@@ -20701,13 +20861,13 @@
         <v>44286</v>
       </c>
       <c r="F49" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G49" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H49" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H49" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I49" s="79" t="n">
         <v>17730.613</v>
@@ -20740,7 +20900,7 @@
         <v>22</v>
       </c>
       <c r="S49" s="66" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20748,7 +20908,7 @@
         <v>171</v>
       </c>
       <c r="B50" s="76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C50" s="77" t="n">
         <v>2020</v>
@@ -20760,13 +20920,13 @@
         <v>44196</v>
       </c>
       <c r="F50" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G50" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H50" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H50" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I50" s="79" t="n">
         <v>14773.42</v>
@@ -20799,7 +20959,7 @@
         <v>23</v>
       </c>
       <c r="S50" s="66" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20807,7 +20967,7 @@
         <v>171</v>
       </c>
       <c r="B51" s="76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C51" s="77" t="n">
         <v>2020</v>
@@ -20819,13 +20979,13 @@
         <v>44104</v>
       </c>
       <c r="F51" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G51" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H51" s="76" t="s">
         <v>205</v>
-      </c>
-      <c r="H51" s="76" t="s">
-        <v>201</v>
       </c>
       <c r="I51" s="79" t="n">
         <v>15323.867</v>
@@ -20856,15 +21016,15 @@
         <v>24</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B52" s="76" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C52" s="77" t="n">
         <v>2026</v>
@@ -20876,19 +21036,19 @@
         <v>46295</v>
       </c>
       <c r="F52" s="76" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G52" s="76" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H52" s="76" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
       <c r="K52" s="79"/>
       <c r="L52" s="80" t="n">
-        <v>99.01</v>
+        <v>3.81022</v>
       </c>
       <c r="M52" s="79"/>
       <c r="N52" s="79"/>
@@ -20899,15 +21059,15 @@
         <v>0</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B53" s="76" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C53" s="77" t="n">
         <v>2026</v>
@@ -20919,54 +21079,54 @@
         <v>46203</v>
       </c>
       <c r="F53" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G53" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H53" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H53" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I53" s="79" t="n">
-        <v>22443.411</v>
+        <v>42889.818</v>
       </c>
       <c r="J53" s="79" t="n">
-        <v>14589.612</v>
+        <v>10638.138</v>
       </c>
       <c r="K53" s="79" t="n">
-        <v>10368072000</v>
+        <v>13114938000</v>
       </c>
       <c r="L53" s="80" t="n">
-        <v>108.93</v>
+        <v>8.45</v>
       </c>
       <c r="M53" s="79" t="n">
-        <v>96.3654</v>
+        <v>1591.3226</v>
       </c>
       <c r="N53" s="79" t="n">
-        <v>0</v>
+        <v>901935</v>
       </c>
       <c r="O53" s="79" t="n">
-        <v>23288.098</v>
+        <v>123886.281</v>
       </c>
       <c r="P53" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="80" t="n">
-        <v>1615</v>
+        <v>1070</v>
       </c>
       <c r="R53" s="47" t="n">
         <v>1</v>
       </c>
       <c r="S53" s="66" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B54" s="76" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C54" s="77" t="n">
         <v>2026</v>
@@ -20978,54 +21138,54 @@
         <v>46112</v>
       </c>
       <c r="F54" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G54" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H54" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H54" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I54" s="79" t="n">
-        <v>13182.608</v>
+        <v>37446.455</v>
       </c>
       <c r="J54" s="79" t="n">
-        <v>7791.357</v>
+        <v>6726.042</v>
       </c>
       <c r="K54" s="79" t="n">
-        <v>5466357000</v>
+        <v>5042976000</v>
       </c>
       <c r="L54" s="80" t="n">
-        <v>57.49</v>
+        <v>3.28</v>
       </c>
       <c r="M54" s="79" t="n">
-        <v>96.3552</v>
+        <v>1589.2465</v>
       </c>
       <c r="N54" s="79" t="n">
-        <v>0</v>
+        <v>901935</v>
       </c>
       <c r="O54" s="79" t="n">
-        <v>14500.386</v>
+        <v>113384.008</v>
       </c>
       <c r="P54" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="80" t="n">
-        <v>847</v>
+        <v>444.5</v>
       </c>
       <c r="R54" s="47" t="n">
         <v>2</v>
       </c>
       <c r="S54" s="66" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C55" s="77" t="n">
         <v>2025</v>
@@ -21037,54 +21197,54 @@
         <v>46022</v>
       </c>
       <c r="F55" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G55" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H55" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H55" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I55" s="79" t="n">
-        <v>4806.69</v>
+        <v>34690.886</v>
       </c>
       <c r="J55" s="79" t="n">
-        <v>1597.288</v>
+        <v>5472.133</v>
       </c>
       <c r="K55" s="79" t="n">
-        <v>870716000</v>
+        <v>3534504000</v>
       </c>
       <c r="L55" s="80" t="n">
-        <v>9.26</v>
+        <v>2.32</v>
       </c>
       <c r="M55" s="79" t="n">
-        <v>96.0407</v>
+        <v>1529.6002</v>
       </c>
       <c r="N55" s="79" t="n">
-        <v>0</v>
+        <v>1001935</v>
       </c>
       <c r="O55" s="79" t="n">
-        <v>8940.787</v>
+        <v>100569.302</v>
       </c>
       <c r="P55" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="80" t="n">
-        <v>576</v>
+        <v>220</v>
       </c>
       <c r="R55" s="47" t="n">
         <v>3</v>
       </c>
       <c r="S55" s="66" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C56" s="77" t="n">
         <v>2025</v>
@@ -21096,54 +21256,54 @@
         <v>45930</v>
       </c>
       <c r="F56" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G56" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H56" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H56" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I56" s="79" t="n">
-        <v>3807.401</v>
+        <v>33994.419</v>
       </c>
       <c r="J56" s="79" t="n">
-        <v>1248.818</v>
+        <v>4548.515</v>
       </c>
       <c r="K56" s="79" t="n">
-        <v>643038000</v>
+        <v>2194489000</v>
       </c>
       <c r="L56" s="80" t="n">
-        <v>6.87</v>
+        <v>1.44</v>
       </c>
       <c r="M56" s="79" t="n">
-        <v>95.3452</v>
+        <v>1529.6642</v>
       </c>
       <c r="N56" s="79" t="n">
-        <v>0</v>
+        <v>1011935</v>
       </c>
       <c r="O56" s="79" t="n">
-        <v>7932.37</v>
+        <v>92099.518</v>
       </c>
       <c r="P56" s="80" t="n">
-        <v>9.37723774</v>
+        <v>1.50004559</v>
       </c>
       <c r="Q56" s="80" t="n">
-        <v>329.5</v>
+        <v>151.5</v>
       </c>
       <c r="R56" s="47" t="n">
         <v>4</v>
       </c>
       <c r="S56" s="66" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C57" s="77" t="n">
         <v>2025</v>
@@ -21155,54 +21315,54 @@
         <v>45838</v>
       </c>
       <c r="F57" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G57" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H57" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H57" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I57" s="79" t="n">
-        <v>3028.429</v>
+        <v>32466.045</v>
       </c>
       <c r="J57" s="79" t="n">
-        <v>785.089</v>
+        <v>4245.516</v>
       </c>
       <c r="K57" s="79" t="n">
-        <v>185349000</v>
+        <v>29607000</v>
       </c>
       <c r="L57" s="80" t="n">
-        <v>2.02</v>
+        <v>0.02</v>
       </c>
       <c r="M57" s="79" t="n">
-        <v>91.6411</v>
+        <v>1529.6762</v>
       </c>
       <c r="N57" s="79" t="n">
-        <v>0</v>
+        <v>1011935</v>
       </c>
       <c r="O57" s="79" t="n">
-        <v>7184.405</v>
+        <v>87845.402</v>
       </c>
       <c r="P57" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="80" t="n">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="R57" s="47" t="n">
         <v>5</v>
       </c>
       <c r="S57" s="66" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C58" s="77" t="n">
         <v>2025</v>
@@ -21214,54 +21374,54 @@
         <v>45747</v>
       </c>
       <c r="F58" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G58" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H58" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H58" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I58" s="79" t="n">
-        <v>2618.742</v>
+        <v>30089.532</v>
       </c>
       <c r="J58" s="79" t="n">
-        <v>800.733</v>
+        <v>4026.094</v>
       </c>
       <c r="K58" s="79" t="n">
-        <v>336540000</v>
+        <v>914544000</v>
       </c>
       <c r="L58" s="80" t="n">
-        <v>3.68</v>
+        <v>0.6</v>
       </c>
       <c r="M58" s="79" t="n">
-        <v>91.5746</v>
+        <v>1529.7227</v>
       </c>
       <c r="N58" s="79" t="n">
-        <v>0</v>
+        <v>1011935</v>
       </c>
       <c r="O58" s="79" t="n">
-        <v>7854.351</v>
+        <v>94858.309</v>
       </c>
       <c r="P58" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="80" t="n">
-        <v>250.5</v>
+        <v>92.5</v>
       </c>
       <c r="R58" s="47" t="n">
         <v>6</v>
       </c>
       <c r="S58" s="66" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C59" s="77" t="n">
         <v>2024</v>
@@ -21273,54 +21433,54 @@
         <v>45657</v>
       </c>
       <c r="F59" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G59" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H59" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H59" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I59" s="79" t="n">
-        <v>2228.005</v>
+        <v>29380.912</v>
       </c>
       <c r="J59" s="79" t="n">
-        <v>648.956</v>
+        <v>3398.125</v>
       </c>
       <c r="K59" s="79" t="n">
-        <v>271532000</v>
+        <v>56064000</v>
       </c>
       <c r="L59" s="80" t="n">
-        <v>2.97</v>
+        <v>0.04</v>
       </c>
       <c r="M59" s="79" t="n">
-        <v>91.4561</v>
+        <v>1529.9937</v>
       </c>
       <c r="N59" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O59" s="79" t="n">
-        <v>7491.143</v>
+        <v>93264.763</v>
       </c>
       <c r="P59" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="80" t="n">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="R59" s="47" t="n">
         <v>7</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C60" s="77" t="n">
         <v>2024</v>
@@ -21332,54 +21492,54 @@
         <v>45565</v>
       </c>
       <c r="F60" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G60" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H60" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H60" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I60" s="79" t="n">
-        <v>2321.419</v>
+        <v>31712.154</v>
       </c>
       <c r="J60" s="79" t="n">
-        <v>658.433</v>
+        <v>4941.696</v>
       </c>
       <c r="K60" s="79" t="n">
-        <v>188620000</v>
+        <v>997140000</v>
       </c>
       <c r="L60" s="80" t="n">
-        <v>2.08</v>
+        <v>0.66</v>
       </c>
       <c r="M60" s="79" t="n">
-        <v>91.3372</v>
+        <v>1525.1012</v>
       </c>
       <c r="N60" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O60" s="79" t="n">
-        <v>7196.228</v>
+        <v>92716.034</v>
       </c>
       <c r="P60" s="80" t="n">
-        <v>10.2</v>
+        <v>3.00000196</v>
       </c>
       <c r="Q60" s="80" t="n">
-        <v>282</v>
+        <v>144</v>
       </c>
       <c r="R60" s="47" t="n">
         <v>8</v>
       </c>
       <c r="S60" s="66" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C61" s="77" t="n">
         <v>2024</v>
@@ -21391,54 +21551,54 @@
         <v>45473</v>
       </c>
       <c r="F61" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G61" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H61" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H61" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I61" s="79" t="n">
-        <v>2190.229</v>
+        <v>27877.397</v>
       </c>
       <c r="J61" s="79" t="n">
-        <v>759.289</v>
+        <v>3683.214</v>
       </c>
       <c r="K61" s="79" t="n">
-        <v>294050000</v>
+        <v>1595286000</v>
       </c>
       <c r="L61" s="80" t="n">
-        <v>3.26</v>
+        <v>1.05</v>
       </c>
       <c r="M61" s="79" t="n">
-        <v>88.3977</v>
+        <v>1525.1062</v>
       </c>
       <c r="N61" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O61" s="79" t="n">
-        <v>6803.334</v>
+        <v>91991.945</v>
       </c>
       <c r="P61" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="80" t="n">
-        <v>302</v>
+        <v>180</v>
       </c>
       <c r="R61" s="47" t="n">
         <v>9</v>
       </c>
       <c r="S61" s="66" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C62" s="77" t="n">
         <v>2024</v>
@@ -21450,54 +21610,54 @@
         <v>45382</v>
       </c>
       <c r="F62" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G62" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H62" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H62" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I62" s="79" t="n">
-        <v>2175.989</v>
+        <v>26402.819</v>
       </c>
       <c r="J62" s="79" t="n">
-        <v>758.571</v>
+        <v>4292.126</v>
       </c>
       <c r="K62" s="79" t="n">
-        <v>351970000</v>
+        <v>2433573000</v>
       </c>
       <c r="L62" s="80" t="n">
-        <v>3.98</v>
+        <v>1.6</v>
       </c>
       <c r="M62" s="79" t="n">
-        <v>88.3977</v>
+        <v>1525.1072</v>
       </c>
       <c r="N62" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O62" s="79" t="n">
-        <v>7398.652</v>
+        <v>94583.054</v>
       </c>
       <c r="P62" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="80" t="n">
-        <v>305.5</v>
+        <v>191</v>
       </c>
       <c r="R62" s="47" t="n">
         <v>10</v>
       </c>
       <c r="S62" s="66" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B63" s="76" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C63" s="77" t="n">
         <v>2023</v>
@@ -21509,54 +21669,54 @@
         <v>45291</v>
       </c>
       <c r="F63" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G63" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H63" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H63" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I63" s="79" t="n">
-        <v>2130.049</v>
+        <v>25689.382</v>
       </c>
       <c r="J63" s="79" t="n">
-        <v>707.384</v>
+        <v>4508.234</v>
       </c>
       <c r="K63" s="79" t="n">
-        <v>262238000</v>
+        <v>2906923000</v>
       </c>
       <c r="L63" s="80" t="n">
-        <v>2.96</v>
+        <v>1.91</v>
       </c>
       <c r="M63" s="79" t="n">
-        <v>88.3977</v>
+        <v>1525.1212</v>
       </c>
       <c r="N63" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O63" s="79" t="n">
-        <v>7036.917</v>
+        <v>90660.883</v>
       </c>
       <c r="P63" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="80" t="n">
-        <v>312</v>
+        <v>176</v>
       </c>
       <c r="R63" s="47" t="n">
         <v>11</v>
       </c>
       <c r="S63" s="66" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B64" s="76" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C64" s="77" t="n">
         <v>2023</v>
@@ -21568,54 +21728,54 @@
         <v>45199</v>
       </c>
       <c r="F64" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G64" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H64" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H64" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I64" s="79" t="n">
-        <v>1993.007</v>
+        <v>26545.656</v>
       </c>
       <c r="J64" s="79" t="n">
-        <v>687.513</v>
+        <v>5229.941</v>
       </c>
       <c r="K64" s="79" t="n">
-        <v>306457000</v>
+        <v>2589228000</v>
       </c>
       <c r="L64" s="80" t="n">
-        <v>3.47</v>
+        <v>1.7</v>
       </c>
       <c r="M64" s="79" t="n">
-        <v>88.3977</v>
+        <v>1525.1302</v>
       </c>
       <c r="N64" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O64" s="79" t="n">
-        <v>6756.961</v>
+        <v>89119.219</v>
       </c>
       <c r="P64" s="80" t="n">
-        <v>13.78192729</v>
+        <v>7.99298687</v>
       </c>
       <c r="Q64" s="80" t="n">
-        <v>296.5</v>
+        <v>173.5</v>
       </c>
       <c r="R64" s="47" t="n">
         <v>12</v>
       </c>
       <c r="S64" s="66" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B65" s="76" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C65" s="77" t="n">
         <v>2023</v>
@@ -21627,54 +21787,54 @@
         <v>45107</v>
       </c>
       <c r="F65" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G65" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H65" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H65" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I65" s="79" t="n">
-        <v>1930.516</v>
+        <v>25234.907</v>
       </c>
       <c r="J65" s="79" t="n">
-        <v>636.105</v>
+        <v>5100.981</v>
       </c>
       <c r="K65" s="79" t="n">
-        <v>230718000</v>
+        <v>2388761000</v>
       </c>
       <c r="L65" s="80" t="n">
-        <v>2.66</v>
+        <v>1.57</v>
       </c>
       <c r="M65" s="79" t="n">
-        <v>86.6666</v>
+        <v>1525.1402</v>
       </c>
       <c r="N65" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O65" s="79" t="n">
-        <v>6433.521</v>
+        <v>85061.696</v>
       </c>
       <c r="P65" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="80" t="n">
-        <v>324</v>
+        <v>176</v>
       </c>
       <c r="R65" s="47" t="n">
         <v>13</v>
       </c>
       <c r="S65" s="66" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B66" s="76" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C66" s="77" t="n">
         <v>2023</v>
@@ -21686,54 +21846,54 @@
         <v>45016</v>
       </c>
       <c r="F66" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G66" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H66" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I66" s="79" t="n">
-        <v>2260.206</v>
+        <v>26566.206</v>
       </c>
       <c r="J66" s="79" t="n">
-        <v>814.91</v>
+        <v>5462.447</v>
       </c>
       <c r="K66" s="79" t="n">
-        <v>348203000</v>
+        <v>4095140000</v>
       </c>
       <c r="L66" s="80" t="n">
-        <v>4.02</v>
+        <v>2.7</v>
       </c>
       <c r="M66" s="79" t="n">
-        <v>86.6666</v>
+        <v>1523.7992</v>
       </c>
       <c r="N66" s="79" t="n">
-        <v>0</v>
+        <v>1266935</v>
       </c>
       <c r="O66" s="79" t="n">
-        <v>7382.85</v>
+        <v>95278.636</v>
       </c>
       <c r="P66" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="80" t="n">
-        <v>314</v>
+        <v>147.5</v>
       </c>
       <c r="R66" s="47" t="n">
         <v>14</v>
       </c>
       <c r="S66" s="66" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B67" s="76" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C67" s="77" t="n">
         <v>2022</v>
@@ -21745,54 +21905,54 @@
         <v>44926</v>
       </c>
       <c r="F67" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G67" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H67" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H67" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I67" s="79" t="n">
-        <v>2286.572</v>
+        <v>36689.686</v>
       </c>
       <c r="J67" s="79" t="n">
-        <v>860.807</v>
+        <v>12741.995</v>
       </c>
       <c r="K67" s="79" t="n">
-        <v>385061000</v>
+        <v>7360110000</v>
       </c>
       <c r="L67" s="80" t="n">
-        <v>4.44</v>
+        <v>4.99</v>
       </c>
       <c r="M67" s="79" t="n">
-        <v>86.5531</v>
+        <v>1478.3653</v>
       </c>
       <c r="N67" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="79" t="n">
-        <v>7012.867</v>
+        <v>85734.519</v>
       </c>
       <c r="P67" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="80" t="n">
-        <v>185.5</v>
+        <v>120</v>
       </c>
       <c r="R67" s="47" t="n">
         <v>15</v>
       </c>
       <c r="S67" s="66" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C68" s="77" t="n">
         <v>2022</v>
@@ -21804,54 +21964,54 @@
         <v>44834</v>
       </c>
       <c r="F68" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G68" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H68" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H68" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I68" s="79" t="n">
-        <v>2560.341</v>
+        <v>37453.505</v>
       </c>
       <c r="J68" s="79" t="n">
-        <v>914.902</v>
+        <v>14298.881</v>
       </c>
       <c r="K68" s="79" t="n">
-        <v>542661000</v>
+        <v>8561503000</v>
       </c>
       <c r="L68" s="80" t="n">
-        <v>6.28</v>
+        <v>5.8</v>
       </c>
       <c r="M68" s="79" t="n">
-        <v>86.4706</v>
+        <v>1478.3653</v>
       </c>
       <c r="N68" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="79" t="n">
-        <v>6611.975</v>
+        <v>78658.127</v>
       </c>
       <c r="P68" s="80" t="n">
-        <v>11.5240749</v>
+        <v>3.4</v>
       </c>
       <c r="Q68" s="80" t="n">
-        <v>161.5</v>
+        <v>117.5</v>
       </c>
       <c r="R68" s="47" t="n">
         <v>16</v>
       </c>
       <c r="S68" s="66" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B69" s="76" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="C69" s="77" t="n">
         <v>2022</v>
@@ -21863,54 +22023,54 @@
         <v>44742</v>
       </c>
       <c r="F69" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G69" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H69" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H69" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I69" s="79" t="n">
-        <v>2866.579</v>
+        <v>35634.988</v>
       </c>
       <c r="J69" s="79" t="n">
-        <v>947.502</v>
+        <v>13469.308</v>
       </c>
       <c r="K69" s="79" t="n">
-        <v>536500000</v>
+        <v>8030211000</v>
       </c>
       <c r="L69" s="80" t="n">
-        <v>6.41</v>
+        <v>5.44</v>
       </c>
       <c r="M69" s="79" t="n">
-        <v>83.895</v>
+        <v>1475.2603</v>
       </c>
       <c r="N69" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="79" t="n">
-        <v>6043.861</v>
+        <v>69657.394</v>
       </c>
       <c r="P69" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="80" t="n">
-        <v>162.5</v>
+        <v>158.5</v>
       </c>
       <c r="R69" s="47" t="n">
         <v>17</v>
       </c>
       <c r="S69" s="66" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B70" s="76" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C70" s="77" t="n">
         <v>2022</v>
@@ -21922,54 +22082,54 @@
         <v>44651</v>
       </c>
       <c r="F70" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G70" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H70" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H70" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I70" s="79" t="n">
-        <v>2589.737</v>
+        <v>30710.993</v>
       </c>
       <c r="J70" s="79" t="n">
-        <v>735.407</v>
+        <v>9922.922</v>
       </c>
       <c r="K70" s="79" t="n">
-        <v>385967000</v>
+        <v>5666681000</v>
       </c>
       <c r="L70" s="80" t="n">
-        <v>4.64</v>
+        <v>3.85</v>
       </c>
       <c r="M70" s="79" t="n">
-        <v>83.7225</v>
+        <v>1475.2603</v>
       </c>
       <c r="N70" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="79" t="n">
-        <v>6458.201</v>
+        <v>67006.677</v>
       </c>
       <c r="P70" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="80" t="n">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="R70" s="47" t="n">
         <v>18</v>
       </c>
       <c r="S70" s="66" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B71" s="76" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C71" s="77" t="n">
         <v>2021</v>
@@ -21981,54 +22141,54 @@
         <v>44561</v>
       </c>
       <c r="F71" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G71" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H71" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H71" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I71" s="79" t="n">
-        <v>2396.847</v>
+        <v>30564.295</v>
       </c>
       <c r="J71" s="79" t="n">
-        <v>677.529</v>
+        <v>8465.572</v>
       </c>
       <c r="K71" s="79" t="n">
-        <v>290253000</v>
+        <v>4996111000</v>
       </c>
       <c r="L71" s="80" t="n">
-        <v>3.51</v>
+        <v>3.38</v>
       </c>
       <c r="M71" s="79" t="n">
-        <v>82.668</v>
+        <v>1475.2603</v>
       </c>
       <c r="N71" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="79" t="n">
-        <v>5960.989</v>
+        <v>60713.562</v>
       </c>
       <c r="P71" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="80" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="R71" s="47" t="n">
         <v>19</v>
       </c>
       <c r="S71" s="66" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B72" s="76" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C72" s="77" t="n">
         <v>2021</v>
@@ -22040,54 +22200,54 @@
         <v>44469</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G72" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H72" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H72" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I72" s="79" t="n">
-        <v>2973.845</v>
+        <v>28144.601</v>
       </c>
       <c r="J72" s="79" t="n">
-        <v>975.336</v>
+        <v>6792.101</v>
       </c>
       <c r="K72" s="79" t="n">
-        <v>533714000</v>
+        <v>4215025000</v>
       </c>
       <c r="L72" s="80" t="n">
-        <v>6.46</v>
+        <v>2.87</v>
       </c>
       <c r="M72" s="79" t="n">
-        <v>82.628</v>
+        <v>1504.7323</v>
       </c>
       <c r="N72" s="79" t="n">
-        <v>0</v>
+        <v>29732000</v>
       </c>
       <c r="O72" s="79" t="n">
-        <v>5663.586</v>
+        <v>55326.117</v>
       </c>
       <c r="P72" s="80" t="n">
-        <v>6.69560253</v>
+        <v>1.39293356</v>
       </c>
       <c r="Q72" s="80" t="n">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="R72" s="47" t="n">
         <v>20</v>
       </c>
       <c r="S72" s="66" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B73" s="76" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C73" s="77" t="n">
         <v>2021</v>
@@ -22099,54 +22259,54 @@
         <v>44377</v>
       </c>
       <c r="F73" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G73" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H73" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H73" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I73" s="79" t="n">
-        <v>2885.046</v>
+        <v>24030.673</v>
       </c>
       <c r="J73" s="79" t="n">
-        <v>888.15</v>
+        <v>4649.96</v>
       </c>
       <c r="K73" s="79" t="n">
-        <v>477358000</v>
+        <v>1827640000</v>
       </c>
       <c r="L73" s="80" t="n">
-        <v>5.79</v>
+        <v>1.25</v>
       </c>
       <c r="M73" s="79" t="n">
-        <v>82.516</v>
+        <v>1504.7323</v>
       </c>
       <c r="N73" s="79" t="n">
-        <v>0</v>
+        <v>29732000</v>
       </c>
       <c r="O73" s="79" t="n">
-        <v>5668.615</v>
+        <v>53161.388</v>
       </c>
       <c r="P73" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="80" t="n">
-        <v>190.5</v>
+        <v>129</v>
       </c>
       <c r="R73" s="47" t="n">
         <v>21</v>
       </c>
       <c r="S73" s="66" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B74" s="76" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C74" s="77" t="n">
         <v>2021</v>
@@ -22158,54 +22318,54 @@
         <v>44286</v>
       </c>
       <c r="F74" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G74" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H74" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H74" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I74" s="79" t="n">
-        <v>1939.92</v>
+        <v>21823.178</v>
       </c>
       <c r="J74" s="79" t="n">
-        <v>551.203</v>
+        <v>3755.184</v>
       </c>
       <c r="K74" s="79" t="n">
-        <v>259563000</v>
+        <v>2183480000</v>
       </c>
       <c r="L74" s="80" t="n">
-        <v>3.17</v>
+        <v>1.49</v>
       </c>
       <c r="M74" s="79" t="n">
-        <v>82.459</v>
+        <v>1504.7323</v>
       </c>
       <c r="N74" s="79" t="n">
-        <v>0</v>
+        <v>37177000</v>
       </c>
       <c r="O74" s="79" t="n">
-        <v>5182.897</v>
+        <v>50578.596</v>
       </c>
       <c r="P74" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="80" t="n">
-        <v>170</v>
+        <v>91.5</v>
       </c>
       <c r="R74" s="47" t="n">
         <v>22</v>
       </c>
       <c r="S74" s="66" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B75" s="76" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C75" s="77" t="n">
         <v>2020</v>
@@ -22217,54 +22377,54 @@
         <v>44196</v>
       </c>
       <c r="F75" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G75" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H75" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H75" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I75" s="79" t="n">
-        <v>1575.49</v>
+        <v>22576.763</v>
       </c>
       <c r="J75" s="79" t="n">
-        <v>458.968</v>
+        <v>3199.618</v>
       </c>
       <c r="K75" s="79" t="n">
-        <v>175456000</v>
+        <v>2049192000</v>
       </c>
       <c r="L75" s="80" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="M75" s="79" t="n">
-        <v>81.324</v>
+        <v>1504.7323</v>
       </c>
       <c r="N75" s="79" t="n">
-        <v>0</v>
+        <v>37177000</v>
       </c>
       <c r="O75" s="79" t="n">
-        <v>4816.246</v>
+        <v>48427.01</v>
       </c>
       <c r="P75" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="80" t="n">
-        <v>166</v>
+        <v>87.4</v>
       </c>
       <c r="R75" s="47" t="n">
         <v>23</v>
       </c>
       <c r="S75" s="66" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B76" s="76" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C76" s="77" t="n">
         <v>2020</v>
@@ -22276,199 +22436,1656 @@
         <v>44104</v>
       </c>
       <c r="F76" s="76" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G76" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H76" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="H76" s="76" t="s">
-        <v>201</v>
-      </c>
       <c r="I76" s="79" t="n">
-        <v>1627.205</v>
+        <v>23038.769</v>
       </c>
       <c r="J76" s="79" t="n">
-        <v>493.122</v>
+        <v>3350.243</v>
       </c>
       <c r="K76" s="79" t="n">
-        <v>194271000</v>
+        <v>1595191000</v>
       </c>
       <c r="L76" s="80" t="n">
-        <v>2.39</v>
+        <v>1.09</v>
       </c>
       <c r="M76" s="79" t="n">
-        <v>81.324</v>
+        <v>1504.7323</v>
       </c>
       <c r="N76" s="79" t="n">
-        <v>0</v>
+        <v>38249000</v>
       </c>
       <c r="O76" s="79" t="n">
-        <v>4634.348</v>
+        <v>45927.958</v>
       </c>
       <c r="P76" s="80"/>
       <c r="Q76" s="80" t="n">
-        <v>158.5</v>
+        <v>74.4</v>
       </c>
       <c r="R76" s="47" t="n">
         <v>24</v>
       </c>
       <c r="S76" s="66" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" s="76" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D77" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="78" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F77" s="76" t="s">
+        <v>203</v>
+      </c>
+      <c r="G77" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="H77" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I77" s="79"/>
+      <c r="J77" s="79"/>
+      <c r="K77" s="79"/>
+      <c r="L77" s="80" t="n">
+        <v>99.01</v>
+      </c>
+      <c r="M77" s="79"/>
+      <c r="N77" s="79"/>
+      <c r="O77" s="79"/>
+      <c r="P77" s="80"/>
+      <c r="Q77" s="80"/>
+      <c r="R77" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="66" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B78" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C78" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D78" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="78" t="n">
+        <v>46203</v>
+      </c>
+      <c r="F78" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G78" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H78" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I78" s="79" t="n">
+        <v>22443.411</v>
+      </c>
+      <c r="J78" s="79" t="n">
+        <v>14589.612</v>
+      </c>
+      <c r="K78" s="79" t="n">
+        <v>10368072000</v>
+      </c>
+      <c r="L78" s="80" t="n">
+        <v>108.93</v>
+      </c>
+      <c r="M78" s="79" t="n">
+        <v>96.3654</v>
+      </c>
+      <c r="N78" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="79" t="n">
+        <v>23288.098</v>
+      </c>
+      <c r="P78" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="80" t="n">
+        <v>1615</v>
+      </c>
+      <c r="R78" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" s="66" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="C79" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D79" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="78" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F79" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G79" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I79" s="79" t="n">
+        <v>13182.608</v>
+      </c>
+      <c r="J79" s="79" t="n">
+        <v>7791.357</v>
+      </c>
+      <c r="K79" s="79" t="n">
+        <v>5466357000</v>
+      </c>
+      <c r="L79" s="80" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="M79" s="79" t="n">
+        <v>96.3552</v>
+      </c>
+      <c r="N79" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="79" t="n">
+        <v>14500.386</v>
+      </c>
+      <c r="P79" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="80" t="n">
+        <v>847</v>
+      </c>
+      <c r="R79" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" s="66" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D80" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="78" t="n">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G80" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H80" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I80" s="79" t="n">
+        <v>4806.69</v>
+      </c>
+      <c r="J80" s="79" t="n">
+        <v>1597.288</v>
+      </c>
+      <c r="K80" s="79" t="n">
+        <v>870716000</v>
+      </c>
+      <c r="L80" s="80" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M80" s="79" t="n">
+        <v>96.0407</v>
+      </c>
+      <c r="N80" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="79" t="n">
+        <v>8940.787</v>
+      </c>
+      <c r="P80" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="80" t="n">
+        <v>576</v>
+      </c>
+      <c r="R80" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S80" s="66" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D81" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" s="78" t="n">
+        <v>45930</v>
+      </c>
+      <c r="F81" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G81" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H81" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I81" s="79" t="n">
+        <v>3807.401</v>
+      </c>
+      <c r="J81" s="79" t="n">
+        <v>1248.818</v>
+      </c>
+      <c r="K81" s="79" t="n">
+        <v>643038000</v>
+      </c>
+      <c r="L81" s="80" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M81" s="79" t="n">
+        <v>95.3452</v>
+      </c>
+      <c r="N81" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="79" t="n">
+        <v>7932.37</v>
+      </c>
+      <c r="P81" s="80" t="n">
+        <v>9.37723774</v>
+      </c>
+      <c r="Q81" s="80" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="R81" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S81" s="66" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B82" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D82" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="78" t="n">
+        <v>45838</v>
+      </c>
+      <c r="F82" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G82" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H82" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I82" s="79" t="n">
+        <v>3028.429</v>
+      </c>
+      <c r="J82" s="79" t="n">
+        <v>785.089</v>
+      </c>
+      <c r="K82" s="79" t="n">
+        <v>185349000</v>
+      </c>
+      <c r="L82" s="80" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M82" s="79" t="n">
+        <v>91.6411</v>
+      </c>
+      <c r="N82" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="79" t="n">
+        <v>7184.405</v>
+      </c>
+      <c r="P82" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="80" t="n">
+        <v>237</v>
+      </c>
+      <c r="R82" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S82" s="66" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="C83" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D83" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="78" t="n">
+        <v>45747</v>
+      </c>
+      <c r="F83" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G83" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H83" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I83" s="79" t="n">
+        <v>2618.742</v>
+      </c>
+      <c r="J83" s="79" t="n">
+        <v>800.733</v>
+      </c>
+      <c r="K83" s="79" t="n">
+        <v>336540000</v>
+      </c>
+      <c r="L83" s="80" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M83" s="79" t="n">
+        <v>91.5746</v>
+      </c>
+      <c r="N83" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="79" t="n">
+        <v>7854.351</v>
+      </c>
+      <c r="P83" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="80" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="R83" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S83" s="66" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="C84" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D84" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="78" t="n">
+        <v>45657</v>
+      </c>
+      <c r="F84" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G84" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H84" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I84" s="79" t="n">
+        <v>2228.005</v>
+      </c>
+      <c r="J84" s="79" t="n">
+        <v>648.956</v>
+      </c>
+      <c r="K84" s="79" t="n">
+        <v>271532000</v>
+      </c>
+      <c r="L84" s="80" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M84" s="79" t="n">
+        <v>91.4561</v>
+      </c>
+      <c r="N84" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="79" t="n">
+        <v>7491.143</v>
+      </c>
+      <c r="P84" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="80" t="n">
+        <v>218</v>
+      </c>
+      <c r="R84" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="S84" s="66" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85" s="76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D85" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" s="78" t="n">
+        <v>45565</v>
+      </c>
+      <c r="F85" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G85" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H85" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I85" s="79" t="n">
+        <v>2321.419</v>
+      </c>
+      <c r="J85" s="79" t="n">
+        <v>658.433</v>
+      </c>
+      <c r="K85" s="79" t="n">
+        <v>188620000</v>
+      </c>
+      <c r="L85" s="80" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M85" s="79" t="n">
+        <v>91.3372</v>
+      </c>
+      <c r="N85" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="79" t="n">
+        <v>7196.228</v>
+      </c>
+      <c r="P85" s="80" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q85" s="80" t="n">
+        <v>282</v>
+      </c>
+      <c r="R85" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="S85" s="66" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C86" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D86" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" s="78" t="n">
+        <v>45473</v>
+      </c>
+      <c r="F86" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G86" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H86" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I86" s="79" t="n">
+        <v>2190.229</v>
+      </c>
+      <c r="J86" s="79" t="n">
+        <v>759.289</v>
+      </c>
+      <c r="K86" s="79" t="n">
+        <v>294050000</v>
+      </c>
+      <c r="L86" s="80" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M86" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N86" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="79" t="n">
+        <v>6803.334</v>
+      </c>
+      <c r="P86" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="80" t="n">
         <v>302</v>
       </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="81" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="42" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="82" t="s">
-        <v>305</v>
-      </c>
-      <c r="C80" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="82" t="s">
-        <v>307</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="82" t="s">
-        <v>308</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="82" t="s">
-        <v>309</v>
-      </c>
-      <c r="C83" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="82" t="s">
-        <v>310</v>
-      </c>
-      <c r="C84" s="24" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="82" t="s">
-        <v>311</v>
-      </c>
-      <c r="C85" s="24" t="s">
+      <c r="R86" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="S86" s="66" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="C87" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D87" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="78" t="n">
+        <v>45382</v>
+      </c>
+      <c r="F87" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G87" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H87" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I87" s="79" t="n">
+        <v>2175.989</v>
+      </c>
+      <c r="J87" s="79" t="n">
+        <v>758.571</v>
+      </c>
+      <c r="K87" s="79" t="n">
+        <v>351970000</v>
+      </c>
+      <c r="L87" s="80" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M87" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N87" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="79" t="n">
+        <v>7398.652</v>
+      </c>
+      <c r="P87" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="80" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="R87" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S87" s="66" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D88" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="78" t="n">
+        <v>45291</v>
+      </c>
+      <c r="F88" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G88" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H88" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I88" s="79" t="n">
+        <v>2130.049</v>
+      </c>
+      <c r="J88" s="79" t="n">
+        <v>707.384</v>
+      </c>
+      <c r="K88" s="79" t="n">
+        <v>262238000</v>
+      </c>
+      <c r="L88" s="80" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M88" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N88" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="79" t="n">
+        <v>7036.917</v>
+      </c>
+      <c r="P88" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="80" t="n">
         <v>312</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="82" t="s">
-        <v>313</v>
-      </c>
-      <c r="C86" s="24" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="82" t="s">
+      <c r="R88" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="S88" s="66" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="C89" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D89" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="78" t="n">
+        <v>45199</v>
+      </c>
+      <c r="F89" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G89" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H89" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I89" s="79" t="n">
+        <v>1993.007</v>
+      </c>
+      <c r="J89" s="79" t="n">
+        <v>687.513</v>
+      </c>
+      <c r="K89" s="79" t="n">
+        <v>306457000</v>
+      </c>
+      <c r="L89" s="80" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M89" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N89" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="79" t="n">
+        <v>6756.961</v>
+      </c>
+      <c r="P89" s="80" t="n">
+        <v>13.78192729</v>
+      </c>
+      <c r="Q89" s="80" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="R89" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="S89" s="66" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C90" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D90" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="78" t="n">
+        <v>45107</v>
+      </c>
+      <c r="F90" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G90" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I90" s="79" t="n">
+        <v>1930.516</v>
+      </c>
+      <c r="J90" s="79" t="n">
+        <v>636.105</v>
+      </c>
+      <c r="K90" s="79" t="n">
+        <v>230718000</v>
+      </c>
+      <c r="L90" s="80" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M90" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N90" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="79" t="n">
+        <v>6433.521</v>
+      </c>
+      <c r="P90" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="80" t="n">
+        <v>324</v>
+      </c>
+      <c r="R90" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="S90" s="66" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B91" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="C91" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D91" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="78" t="n">
+        <v>45016</v>
+      </c>
+      <c r="F91" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G91" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H91" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I91" s="79" t="n">
+        <v>2260.206</v>
+      </c>
+      <c r="J91" s="79" t="n">
+        <v>814.91</v>
+      </c>
+      <c r="K91" s="79" t="n">
+        <v>348203000</v>
+      </c>
+      <c r="L91" s="80" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M91" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N91" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="79" t="n">
+        <v>7382.85</v>
+      </c>
+      <c r="P91" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="80" t="n">
         <v>314</v>
       </c>
-      <c r="C87" s="25" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="82" t="s">
-        <v>316</v>
-      </c>
-      <c r="C88" s="24" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="82" t="s">
-        <v>318</v>
-      </c>
-      <c r="C89" s="24" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="82" t="s">
-        <v>320</v>
-      </c>
-      <c r="C90" s="25" t="s">
+      <c r="R91" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="S91" s="66" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="82" t="s">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B92" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C92" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D92" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" s="78" t="n">
+        <v>44926</v>
+      </c>
+      <c r="F92" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G92" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H92" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I92" s="79" t="n">
+        <v>2286.572</v>
+      </c>
+      <c r="J92" s="79" t="n">
+        <v>860.807</v>
+      </c>
+      <c r="K92" s="79" t="n">
+        <v>385061000</v>
+      </c>
+      <c r="L92" s="80" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="M92" s="79" t="n">
+        <v>86.5531</v>
+      </c>
+      <c r="N92" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="79" t="n">
+        <v>7012.867</v>
+      </c>
+      <c r="P92" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="80" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R92" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="S92" s="66" t="s">
         <v>322</v>
       </c>
-      <c r="C91" s="25" t="s">
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D93" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" s="78" t="n">
+        <v>44834</v>
+      </c>
+      <c r="F93" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G93" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H93" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I93" s="79" t="n">
+        <v>2560.341</v>
+      </c>
+      <c r="J93" s="79" t="n">
+        <v>914.902</v>
+      </c>
+      <c r="K93" s="79" t="n">
+        <v>542661000</v>
+      </c>
+      <c r="L93" s="80" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M93" s="79" t="n">
+        <v>86.4706</v>
+      </c>
+      <c r="N93" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="79" t="n">
+        <v>6611.975</v>
+      </c>
+      <c r="P93" s="80" t="n">
+        <v>11.5240749</v>
+      </c>
+      <c r="Q93" s="80" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="R93" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="S93" s="66" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="82" t="s">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C94" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D94" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" s="78" t="n">
+        <v>44742</v>
+      </c>
+      <c r="F94" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G94" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H94" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I94" s="79" t="n">
+        <v>2866.579</v>
+      </c>
+      <c r="J94" s="79" t="n">
+        <v>947.502</v>
+      </c>
+      <c r="K94" s="79" t="n">
+        <v>536500000</v>
+      </c>
+      <c r="L94" s="80" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M94" s="79" t="n">
+        <v>83.895</v>
+      </c>
+      <c r="N94" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="79" t="n">
+        <v>6043.861</v>
+      </c>
+      <c r="P94" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="80" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="R94" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="S94" s="66" t="s">
         <v>324</v>
       </c>
-      <c r="C92" s="24" t="s">
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B95" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="C95" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D95" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="78" t="n">
+        <v>44651</v>
+      </c>
+      <c r="F95" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G95" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H95" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I95" s="79" t="n">
+        <v>2589.737</v>
+      </c>
+      <c r="J95" s="79" t="n">
+        <v>735.407</v>
+      </c>
+      <c r="K95" s="79" t="n">
+        <v>385967000</v>
+      </c>
+      <c r="L95" s="80" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M95" s="79" t="n">
+        <v>83.7225</v>
+      </c>
+      <c r="N95" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="79" t="n">
+        <v>6458.201</v>
+      </c>
+      <c r="P95" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="80" t="n">
+        <v>215</v>
+      </c>
+      <c r="R95" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="S95" s="66" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="82" t="s">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B96" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="C96" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D96" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" s="78" t="n">
+        <v>44561</v>
+      </c>
+      <c r="F96" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G96" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H96" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I96" s="79" t="n">
+        <v>2396.847</v>
+      </c>
+      <c r="J96" s="79" t="n">
+        <v>677.529</v>
+      </c>
+      <c r="K96" s="79" t="n">
+        <v>290253000</v>
+      </c>
+      <c r="L96" s="80" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M96" s="79" t="n">
+        <v>82.668</v>
+      </c>
+      <c r="N96" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="79" t="n">
+        <v>5960.989</v>
+      </c>
+      <c r="P96" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="80" t="n">
+        <v>204</v>
+      </c>
+      <c r="R96" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="S96" s="66" t="s">
         <v>326</v>
       </c>
-      <c r="C93" s="24" t="s">
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B97" s="76" t="s">
+        <v>247</v>
+      </c>
+      <c r="C97" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D97" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="78" t="n">
+        <v>44469</v>
+      </c>
+      <c r="F97" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G97" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H97" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I97" s="79" t="n">
+        <v>2973.845</v>
+      </c>
+      <c r="J97" s="79" t="n">
+        <v>975.336</v>
+      </c>
+      <c r="K97" s="79" t="n">
+        <v>533714000</v>
+      </c>
+      <c r="L97" s="80" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M97" s="79" t="n">
+        <v>82.628</v>
+      </c>
+      <c r="N97" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="79" t="n">
+        <v>5663.586</v>
+      </c>
+      <c r="P97" s="80" t="n">
+        <v>6.69560253</v>
+      </c>
+      <c r="Q97" s="80" t="n">
+        <v>182</v>
+      </c>
+      <c r="R97" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="S97" s="66" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="82" t="s">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="C98" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D98" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" s="78" t="n">
+        <v>44377</v>
+      </c>
+      <c r="F98" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G98" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H98" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I98" s="79" t="n">
+        <v>2885.046</v>
+      </c>
+      <c r="J98" s="79" t="n">
+        <v>888.15</v>
+      </c>
+      <c r="K98" s="79" t="n">
+        <v>477358000</v>
+      </c>
+      <c r="L98" s="80" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="M98" s="79" t="n">
+        <v>82.516</v>
+      </c>
+      <c r="N98" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="79" t="n">
+        <v>5668.615</v>
+      </c>
+      <c r="P98" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="80" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="R98" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="S98" s="66" t="s">
         <v>328</v>
       </c>
-      <c r="C94" s="25" t="s">
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" s="76" t="s">
+        <v>251</v>
+      </c>
+      <c r="C99" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D99" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="78" t="n">
+        <v>44286</v>
+      </c>
+      <c r="F99" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G99" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H99" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I99" s="79" t="n">
+        <v>1939.92</v>
+      </c>
+      <c r="J99" s="79" t="n">
+        <v>551.203</v>
+      </c>
+      <c r="K99" s="79" t="n">
+        <v>259563000</v>
+      </c>
+      <c r="L99" s="80" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M99" s="79" t="n">
+        <v>82.459</v>
+      </c>
+      <c r="N99" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="79" t="n">
+        <v>5182.897</v>
+      </c>
+      <c r="P99" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="80" t="n">
+        <v>170</v>
+      </c>
+      <c r="R99" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="S99" s="66" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="82" t="s">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B100" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="C100" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D100" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" s="78" t="n">
+        <v>44196</v>
+      </c>
+      <c r="F100" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G100" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H100" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I100" s="79" t="n">
+        <v>1575.49</v>
+      </c>
+      <c r="J100" s="79" t="n">
+        <v>458.968</v>
+      </c>
+      <c r="K100" s="79" t="n">
+        <v>175456000</v>
+      </c>
+      <c r="L100" s="80" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M100" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N100" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="79" t="n">
+        <v>4816.246</v>
+      </c>
+      <c r="P100" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="80" t="n">
+        <v>166</v>
+      </c>
+      <c r="R100" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="S100" s="66" t="s">
         <v>330</v>
       </c>
-      <c r="C95" s="24" t="s">
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B101" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="C101" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D101" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" s="78" t="n">
+        <v>44104</v>
+      </c>
+      <c r="F101" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G101" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H101" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="I101" s="79" t="n">
+        <v>1627.205</v>
+      </c>
+      <c r="J101" s="79" t="n">
+        <v>493.122</v>
+      </c>
+      <c r="K101" s="79" t="n">
+        <v>194271000</v>
+      </c>
+      <c r="L101" s="80" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M101" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N101" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="79" t="n">
+        <v>4634.348</v>
+      </c>
+      <c r="P101" s="80"/>
+      <c r="Q101" s="80" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="R101" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="S101" s="66" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="81" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="42" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="82" t="s">
+        <v>334</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="82" t="s">
+        <v>336</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="82" t="s">
+        <v>337</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="82" t="s">
+        <v>338</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="82" t="s">
+        <v>339</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="82" t="s">
+        <v>340</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="82" t="s">
+        <v>342</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="82" t="s">
+        <v>343</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="82" t="s">
+        <v>345</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="82" t="s">
+        <v>347</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="82" t="s">
+        <v>349</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="82" t="s">
+        <v>351</v>
+      </c>
+      <c r="C116" s="25" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="82" t="s">
+        <v>353</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="82" t="s">
+        <v>355</v>
+      </c>
+      <c r="C118" s="24" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="82" t="s">
+        <v>357</v>
+      </c>
+      <c r="C119" s="25" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="82" t="s">
+        <v>359</v>
+      </c>
+      <c r="C120" s="24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="82" t="s">
-        <v>331</v>
-      </c>
-      <c r="C96" s="24" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="24" t="s">
-        <v>333</v>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="82" t="s">
+        <v>360</v>
+      </c>
+      <c r="C121" s="24" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="24" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S76"/>
+  <autoFilter ref="A1:S101"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -22485,7 +24102,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -22500,19 +24117,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22557,27 +24174,47 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="76" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>353.215</v>
+        <v>20.12185</v>
       </c>
       <c r="C4" s="80" t="n">
-        <v>194.82417</v>
+        <v>37.60692</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46387</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F4" s="78" t="n">
         <v>46267</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>339</v>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="80" t="n">
+        <v>353.215</v>
+      </c>
+      <c r="C5" s="80" t="n">
+        <v>194.82417</v>
+      </c>
+      <c r="D5" s="78" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E5" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="78" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dashboard!$A$2:$AC$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$101</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$126</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="439">
   <si>
     <r>
       <rPr>
@@ -3863,6 +3863,12 @@
     <t xml:space="preserve">池子</t>
   </si>
   <si>
+    <t xml:space="preserve">3034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">聯詠</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4449,6 +4455,81 @@
   </si>
   <si>
     <t xml:space="preserve">2455|24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3034|24</t>
   </si>
   <si>
     <t xml:space="preserve">5289|0</t>
@@ -6874,7 +6955,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="37">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -6941,7 +7022,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC1E5CA"/>
+          <fgColor rgb="FFF1F9F3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAFDFB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -6957,7 +7046,23 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFCCEAD4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFE6F5EA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8BCF9D"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7013,7 +7118,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF1F9F3"/>
+          <fgColor rgb="FF6DC384"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7021,7 +7126,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF6EC384"/>
+          <fgColor rgb="FFF9FDFA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAFDFA"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7724,7 +7837,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -7739,16 +7852,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7798,16 +7911,31 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>1420</v>
+        <v>543</v>
       </c>
       <c r="C5" s="78" t="n">
         <v>46267</v>
       </c>
       <c r="D5" s="78"/>
       <c r="E5" s="78" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="80" t="n">
+        <v>1420</v>
+      </c>
+      <c r="C6" s="78" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78" t="n">
         <v>46267</v>
       </c>
     </row>
@@ -7876,16 +8004,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -7894,13 +8022,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -7909,7 +8037,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -7918,16 +8046,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -7936,16 +8064,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -7954,7 +8082,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -7963,7 +8091,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -7972,7 +8100,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -7984,19 +8112,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8394,7 +8522,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>246.897867534247</v>
+        <v>222.759318493151</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8410,11 +8538,11 @@
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>5.75136599672347</v>
+        <v>6.37459303433657</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>-0.44842611440624</v>
+        <v>-0.512857668531057</v>
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
@@ -8498,7 +8626,7 @@
       </c>
       <c r="AH4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(AD4&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/AD4),"N/M"))</f>
-        <v>1.46159230182731</v>
+        <v>1.40566766680559</v>
       </c>
       <c r="AI4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,0),""))</f>
@@ -8514,7 +8642,7 @@
       </c>
       <c r="AL4" s="47" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A4,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -8730,183 +8858,183 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="str">
         <f aca="false">IF(Tickers!A6="","",Tickers!A6)</f>
-        <v/>
+        <v>3034</v>
       </c>
       <c r="B6" s="66" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A6,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>聯詠</v>
       </c>
       <c r="C6" s="66" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A6,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D6" s="51" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E6" s="48" t="str">
+        <v>543</v>
+      </c>
+      <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="F6" s="51" t="str">
+        <v>99196.28</v>
+      </c>
+      <c r="F6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="G6" s="51" t="str">
+        <v>28.67</v>
+      </c>
+      <c r="G6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=0",Raw_Q!$R$2:$R$600,"&lt;=3"),""))</f>
-        <v/>
-      </c>
-      <c r="H6" s="51" t="str">
+        <v>32.23273</v>
+      </c>
+      <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v/>
-      </c>
-      <c r="I6" s="49" t="str">
+        <v>34.7916423287671</v>
+      </c>
+      <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
-        <v/>
-      </c>
-      <c r="J6" s="52" t="str">
+        <v>-0.084610472541507</v>
+      </c>
+      <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="K6" s="52" t="str">
+        <v>18.9396581792815</v>
+      </c>
+      <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="L6" s="52" t="str">
+        <v>16.8462305240667</v>
+      </c>
+      <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="M6" s="49" t="str">
+        <v>15.6071965464828</v>
+      </c>
+      <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v/>
+        <v>0.0480544426141569</v>
       </c>
       <c r="N6" s="51" t="str">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(J6)),I6&lt;Config!$B$6),"N/M",J6/(I6*100)),"N/M"))</f>
-        <v/>
+        <v>N/M</v>
       </c>
       <c r="O6" s="51" t="str">
         <f aca="false">IF($A6="","",IFERROR(IF(OR(NOT(ISNUMBER(L6)),M6&lt;Config!$B$6),"N/M",L6/(M6*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="P6" s="51" t="str">
+        <v>N/M</v>
+      </c>
+      <c r="P6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="49" t="str">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(P6=0,"不配息",P6/D6),""))</f>
-        <v/>
-      </c>
-      <c r="R6" s="49" t="str">
+        <v>0.0515653775322284</v>
+      </c>
+      <c r="R6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
-        <v/>
-      </c>
-      <c r="S6" s="49" t="str">
+        <v>-0.125</v>
+      </c>
+      <c r="S6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="T6" s="49" t="str">
+        <v>0.0959019944239199</v>
+      </c>
+      <c r="T6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,2)-1,""))</f>
-        <v/>
-      </c>
-      <c r="U6" s="49" t="str">
+        <v>0.238268429667998</v>
+      </c>
+      <c r="U6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,3)-1,""))</f>
-        <v/>
-      </c>
-      <c r="V6" s="68" t="str">
+        <v>0.0143792345505536</v>
+      </c>
+      <c r="V6" s="68" t="n">
         <f aca="false">IF($A6="","",IFERROR((T6-U6)*100,""))</f>
-        <v/>
+        <v>22.3889195117444</v>
       </c>
       <c r="W6" s="66" t="str">
         <f aca="false">IF($A6="","",IFERROR(IF(NOT(ISNUMBER(T6)),"",IF(T6&gt;0,IF(V6&gt;0,"成長且加速","成長但減速"),IF(V6&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
-        <v/>
-      </c>
-      <c r="X6" s="68" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="X6" s="68" t="n">
         <f aca="false">IF($A6="","",IFERROR((T6-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,6)-1))*100,""))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="49" t="str">
+        <v>27.3966504483223</v>
+      </c>
+      <c r="Y6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="Z6" s="49" t="str">
+        <v>0.693811074918567</v>
+      </c>
+      <c r="Z6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/E6,""))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="49" t="str">
+        <v>0.39142949715453</v>
+      </c>
+      <c r="AA6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="50" t="str">
+        <v>0.429492751432017</v>
+      </c>
+      <c r="AB6" s="50" t="n">
         <f aca="false">IF($A6="","",IFERROR((Z6-AA6)*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AC6" s="50" t="str">
+        <v>-380.632542774863</v>
+      </c>
+      <c r="AC6" s="50" t="n">
         <f aca="false">IF($A6="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AD6" s="51" t="str">
+        <v>611.544741557178</v>
+      </c>
+      <c r="AD6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
-      </c>
-      <c r="AE6" s="48" t="str">
+        <v>113.327455602729</v>
+      </c>
+      <c r="AE6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600),""))</f>
-        <v/>
-      </c>
-      <c r="AF6" s="49" t="str">
+        <v>17446.024705</v>
+      </c>
+      <c r="AF6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))&lt;=0,"N/M",AE6/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))/2)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AG6" s="49" t="str">
+        <v>0.271316607852973</v>
+      </c>
+      <c r="AG6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(AVERAGE(AO6:AS6),""))</f>
-        <v/>
-      </c>
-      <c r="AH6" s="49" t="str">
+        <v>0.432821020049639</v>
+      </c>
+      <c r="AH6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(AD6&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/AD6),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AI6" s="51" t="str">
+        <v>0.297407894854284</v>
+      </c>
+      <c r="AI6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,0),""))</f>
-        <v/>
+        <v>9.57273</v>
       </c>
       <c r="AJ6" s="66" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A6&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AK6" s="66" t="str">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A6&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AL6" s="47" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AL6" s="47" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A6,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AM6" s="67" t="str">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AN6" s="67" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AO6" s="49" t="str">
+        <v>46267</v>
+      </c>
+      <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AP6" s="49" t="str">
+        <v>0.271316607852973</v>
+      </c>
+      <c r="AP6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=5)*(Raw_Q!$R$2:$R$600&lt;=8)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,9))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AQ6" s="49" t="str">
+        <v>0.323588491198455</v>
+      </c>
+      <c r="AQ6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,9),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=9)*(Raw_Q!$R$2:$R$600&lt;=12)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,9)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,13))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AR6" s="49" t="str">
+        <v>0.387746329305875</v>
+      </c>
+      <c r="AR6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,13),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=13)*(Raw_Q!$R$2:$R$600&lt;=16)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,13)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,17))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AS6" s="49" t="str">
+        <v>0.355158823418127</v>
+      </c>
+      <c r="AS6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,17),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=17)*(Raw_Q!$R$2:$R$600&lt;=20)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,17)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,21))/2)),""))</f>
-        <v/>
+        <v>0.826294848472765</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11641,7 +11769,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -11670,78 +11798,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -12165,7 +12293,7 @@
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>5.75136599672347</v>
+        <v>6.37459303433657</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
@@ -12241,7 +12369,7 @@
       </c>
       <c r="Y5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AH$4)</f>
-        <v>1.46159230182731</v>
+        <v>1.40566766680559</v>
       </c>
       <c r="Z5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AI$4)</f>
@@ -12381,119 +12509,119 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!A$6)</f>
-        <v/>
+        <v>3034</v>
       </c>
       <c r="B7" s="16" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!B$6)</f>
-        <v/>
+        <v>聯詠</v>
       </c>
       <c r="C7" s="16" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!C$6)</f>
-        <v/>
-      </c>
-      <c r="D7" s="17" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="18" t="str">
+        <v>543</v>
+      </c>
+      <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="18" t="str">
+        <v>18.9396581792815</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v/>
+        <v>15.6071965464828</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
-        <v/>
+        <v>N/M</v>
       </c>
       <c r="H7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!O$6)</f>
-        <v/>
-      </c>
-      <c r="I7" s="19" t="str">
+        <v>N/M</v>
+      </c>
+      <c r="I7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
-        <v/>
-      </c>
-      <c r="J7" s="19" t="str">
+        <v>0.0515653775322284</v>
+      </c>
+      <c r="J7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!R$6)</f>
-        <v/>
-      </c>
-      <c r="K7" s="19" t="str">
+        <v>-0.125</v>
+      </c>
+      <c r="K7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!T$6)</f>
-        <v/>
-      </c>
-      <c r="L7" s="19" t="str">
+        <v>0.238268429667998</v>
+      </c>
+      <c r="L7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!U$6)</f>
-        <v/>
-      </c>
-      <c r="M7" s="20" t="str">
+        <v>0.0143792345505536</v>
+      </c>
+      <c r="M7" s="20" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!V$6)</f>
-        <v/>
+        <v>22.3889195117444</v>
       </c>
       <c r="N7" s="21" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!W$6)</f>
-        <v/>
-      </c>
-      <c r="O7" s="20" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="O7" s="20" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!X$6)</f>
-        <v/>
-      </c>
-      <c r="P7" s="19" t="str">
+        <v>27.3966504483223</v>
+      </c>
+      <c r="P7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!S$6)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="19" t="str">
+        <v>0.0959019944239199</v>
+      </c>
+      <c r="Q7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Y$6)</f>
-        <v/>
-      </c>
-      <c r="R7" s="19" t="str">
+        <v>0.693811074918567</v>
+      </c>
+      <c r="R7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!I$6)</f>
-        <v/>
-      </c>
-      <c r="S7" s="19" t="str">
+        <v>-0.084610472541507</v>
+      </c>
+      <c r="S7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Z$6)</f>
-        <v/>
-      </c>
-      <c r="T7" s="19" t="str">
+        <v>0.39142949715453</v>
+      </c>
+      <c r="T7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AA$6)</f>
-        <v/>
-      </c>
-      <c r="U7" s="22" t="str">
+        <v>0.429492751432017</v>
+      </c>
+      <c r="U7" s="22" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AB$6)</f>
-        <v/>
-      </c>
-      <c r="V7" s="22" t="str">
+        <v>-380.632542774863</v>
+      </c>
+      <c r="V7" s="22" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AC$6)</f>
-        <v/>
-      </c>
-      <c r="W7" s="19" t="str">
+        <v>611.544741557178</v>
+      </c>
+      <c r="W7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AF$6)</f>
-        <v/>
-      </c>
-      <c r="X7" s="19" t="str">
+        <v>0.271316607852973</v>
+      </c>
+      <c r="X7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AG$6)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="19" t="str">
+        <v>0.432821020049639</v>
+      </c>
+      <c r="Y7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AH$6)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="17" t="str">
+        <v>0.297407894854284</v>
+      </c>
+      <c r="Z7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AI$6)</f>
-        <v/>
+        <v>9.57273</v>
       </c>
       <c r="AA7" s="16" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!AJ$6)</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AB7" s="16" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!AK$6)</f>
-        <v/>
-      </c>
-      <c r="AC7" s="23" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AC7" s="23" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!AM$6)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14379,36 +14507,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16665,7 +16793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{19B8701F-5341-4828-A4F0-A79BF3ABB556}</x14:id>
+          <x14:id>{C289EDEC-9D88-4526-8C35-35699E266173}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16681,16 +16809,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16731,47 +16859,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16796,7 +16924,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{19B8701F-5341-4828-A4F0-A79BF3ABB556}">
+          <x14:cfRule type="dataBar" id="{C289EDEC-9D88-4526-8C35-35699E266173}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17039,43 +17167,43 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!$A$6)</f>
-        <v/>
-      </c>
-      <c r="B8" s="47" t="str">
+        <v>3034</v>
+      </c>
+      <c r="B8" s="47" t="n">
         <f aca="false">IF($A8="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A8,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v/>
-      </c>
-      <c r="C8" s="47" t="str">
+        <v>24</v>
+      </c>
+      <c r="C8" s="47" t="n">
         <f aca="false">IF($A8="","",Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D8" s="67" t="str">
+        <v>24</v>
+      </c>
+      <c r="D8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,$B8),""))</f>
-        <v/>
-      </c>
-      <c r="E8" s="67" t="str">
+        <v>44104</v>
+      </c>
+      <c r="E8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="F8" s="66" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A8&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G8" s="67" t="str">
+        <v>FY2026Q3E</v>
+      </c>
+      <c r="G8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H8" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v/>
-      </c>
-      <c r="I8" s="67" t="str">
+        <v>-46267</v>
+      </c>
+      <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="J8" s="72" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
-        <v/>
+        <v>待更新財報</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17715,18 +17843,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17861,12 +17989,22 @@
       <c r="G5" s="73"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="73"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
+      <c r="A6" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="74" t="s">
+        <v>182</v>
+      </c>
       <c r="E6" s="73"/>
-      <c r="F6" s="75"/>
+      <c r="F6" s="75" t="n">
+        <v>46267</v>
+      </c>
       <c r="G6" s="73"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18006,7 +18144,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -18025,7 +18163,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S123"/>
+  <dimension ref="A1:S148"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -18049,58 +18187,58 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18108,7 +18246,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C2" s="77" t="n">
         <v>2026</v>
@@ -18120,13 +18258,13 @@
         <v>46295</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I2" s="79"/>
       <c r="J2" s="79"/>
@@ -18143,7 +18281,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="66" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18151,7 +18289,7 @@
         <v>167</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C3" s="77" t="n">
         <v>2026</v>
@@ -18163,13 +18301,13 @@
         <v>46203</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G3" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H3" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I3" s="79" t="n">
         <v>1270380.25</v>
@@ -18202,7 +18340,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="66" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18210,7 +18348,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C4" s="77" t="n">
         <v>2026</v>
@@ -18222,13 +18360,13 @@
         <v>46112</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H4" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I4" s="79" t="n">
         <v>1134103.44</v>
@@ -18261,7 +18399,7 @@
         <v>2</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18269,7 +18407,7 @@
         <v>167</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C5" s="77" t="n">
         <v>2025</v>
@@ -18281,13 +18419,13 @@
         <v>46022</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G5" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H5" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I5" s="79" t="n">
         <v>1046090.421</v>
@@ -18320,7 +18458,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="66" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18328,7 +18466,7 @@
         <v>167</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C6" s="77" t="n">
         <v>2025</v>
@@ -18340,13 +18478,13 @@
         <v>45930</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G6" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H6" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I6" s="79" t="n">
         <v>989918.318</v>
@@ -18379,7 +18517,7 @@
         <v>4</v>
       </c>
       <c r="S6" s="66" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18387,7 +18525,7 @@
         <v>167</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C7" s="77" t="n">
         <v>2025</v>
@@ -18399,13 +18537,13 @@
         <v>45838</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G7" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I7" s="79" t="n">
         <v>933791.869</v>
@@ -18438,7 +18576,7 @@
         <v>5</v>
       </c>
       <c r="S7" s="66" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18446,7 +18584,7 @@
         <v>167</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C8" s="77" t="n">
         <v>2025</v>
@@ -18458,13 +18596,13 @@
         <v>45747</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G8" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H8" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I8" s="79" t="n">
         <v>839253.664</v>
@@ -18497,7 +18635,7 @@
         <v>6</v>
       </c>
       <c r="S8" s="66" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18505,7 +18643,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C9" s="77" t="n">
         <v>2024</v>
@@ -18517,13 +18655,13 @@
         <v>45657</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G9" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H9" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I9" s="79" t="n">
         <v>868461.178</v>
@@ -18556,7 +18694,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18564,7 +18702,7 @@
         <v>167</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C10" s="77" t="n">
         <v>2024</v>
@@ -18576,13 +18714,13 @@
         <v>45565</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G10" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H10" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I10" s="79" t="n">
         <v>759692.143</v>
@@ -18615,7 +18753,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="66" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18623,7 +18761,7 @@
         <v>167</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C11" s="77" t="n">
         <v>2024</v>
@@ -18635,13 +18773,13 @@
         <v>45473</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G11" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H11" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I11" s="79" t="n">
         <v>673510.177</v>
@@ -18674,7 +18812,7 @@
         <v>9</v>
       </c>
       <c r="S11" s="66" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18682,7 +18820,7 @@
         <v>167</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C12" s="77" t="n">
         <v>2024</v>
@@ -18694,13 +18832,13 @@
         <v>45382</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G12" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H12" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I12" s="79" t="n">
         <v>592644.201</v>
@@ -18733,7 +18871,7 @@
         <v>10</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18741,7 +18879,7 @@
         <v>167</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C13" s="77" t="n">
         <v>2023</v>
@@ -18753,13 +18891,13 @@
         <v>45291</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G13" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H13" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I13" s="79" t="n">
         <v>625528.856</v>
@@ -18792,7 +18930,7 @@
         <v>11</v>
       </c>
       <c r="S13" s="66" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18800,7 +18938,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C14" s="77" t="n">
         <v>2023</v>
@@ -18812,13 +18950,13 @@
         <v>45199</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G14" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H14" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I14" s="79" t="n">
         <v>546732.758</v>
@@ -18851,7 +18989,7 @@
         <v>12</v>
       </c>
       <c r="S14" s="66" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18859,7 +18997,7 @@
         <v>167</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C15" s="77" t="n">
         <v>2023</v>
@@ -18871,13 +19009,13 @@
         <v>45107</v>
       </c>
       <c r="F15" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G15" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H15" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I15" s="79" t="n">
         <v>480841.254</v>
@@ -18910,7 +19048,7 @@
         <v>13</v>
       </c>
       <c r="S15" s="66" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18918,7 +19056,7 @@
         <v>167</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C16" s="77" t="n">
         <v>2023</v>
@@ -18930,13 +19068,13 @@
         <v>45016</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G16" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H16" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I16" s="79" t="n">
         <v>508632.973</v>
@@ -18969,7 +19107,7 @@
         <v>14</v>
       </c>
       <c r="S16" s="66" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18977,7 +19115,7 @@
         <v>167</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C17" s="77" t="n">
         <v>2022</v>
@@ -18989,13 +19127,13 @@
         <v>44926</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G17" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H17" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I17" s="79" t="n">
         <v>625531.868</v>
@@ -19028,7 +19166,7 @@
         <v>15</v>
       </c>
       <c r="S17" s="66" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19036,7 +19174,7 @@
         <v>167</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C18" s="77" t="n">
         <v>2022</v>
@@ -19048,13 +19186,13 @@
         <v>44834</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G18" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H18" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I18" s="79" t="n">
         <v>613142.743</v>
@@ -19087,7 +19225,7 @@
         <v>16</v>
       </c>
       <c r="S18" s="66" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19095,7 +19233,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C19" s="77" t="n">
         <v>2022</v>
@@ -19107,13 +19245,13 @@
         <v>44742</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G19" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H19" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I19" s="79" t="n">
         <v>534140.808</v>
@@ -19146,7 +19284,7 @@
         <v>17</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19154,7 +19292,7 @@
         <v>167</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C20" s="77" t="n">
         <v>2022</v>
@@ -19166,13 +19304,13 @@
         <v>44651</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G20" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H20" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I20" s="79" t="n">
         <v>491075.873</v>
@@ -19205,7 +19343,7 @@
         <v>18</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19213,7 +19351,7 @@
         <v>167</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C21" s="77" t="n">
         <v>2021</v>
@@ -19225,13 +19363,13 @@
         <v>44561</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G21" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H21" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I21" s="79" t="n">
         <v>438189.306</v>
@@ -19264,7 +19402,7 @@
         <v>19</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19272,7 +19410,7 @@
         <v>167</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C22" s="77" t="n">
         <v>2021</v>
@@ -19284,13 +19422,13 @@
         <v>44469</v>
       </c>
       <c r="F22" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G22" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H22" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I22" s="79" t="n">
         <v>414670.379</v>
@@ -19323,7 +19461,7 @@
         <v>20</v>
       </c>
       <c r="S22" s="66" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19331,7 +19469,7 @@
         <v>167</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C23" s="77" t="n">
         <v>2021</v>
@@ -19343,13 +19481,13 @@
         <v>44377</v>
       </c>
       <c r="F23" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G23" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H23" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I23" s="79" t="n">
         <v>372145.122</v>
@@ -19382,7 +19520,7 @@
         <v>21</v>
       </c>
       <c r="S23" s="66" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19390,7 +19528,7 @@
         <v>167</v>
       </c>
       <c r="B24" s="76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C24" s="77" t="n">
         <v>2021</v>
@@ -19402,13 +19540,13 @@
         <v>44286</v>
       </c>
       <c r="F24" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G24" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H24" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I24" s="79" t="n">
         <v>362410.23</v>
@@ -19441,7 +19579,7 @@
         <v>22</v>
       </c>
       <c r="S24" s="66" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19449,7 +19587,7 @@
         <v>167</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C25" s="77" t="n">
         <v>2020</v>
@@ -19461,13 +19599,13 @@
         <v>44196</v>
       </c>
       <c r="F25" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G25" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H25" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I25" s="79" t="n">
         <v>361533.057</v>
@@ -19500,7 +19638,7 @@
         <v>23</v>
       </c>
       <c r="S25" s="66" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19508,7 +19646,7 @@
         <v>167</v>
       </c>
       <c r="B26" s="76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C26" s="77" t="n">
         <v>2020</v>
@@ -19520,13 +19658,13 @@
         <v>44104</v>
       </c>
       <c r="F26" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G26" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H26" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I26" s="79" t="n">
         <v>356426.204</v>
@@ -19557,7 +19695,7 @@
         <v>24</v>
       </c>
       <c r="S26" s="66" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19565,7 +19703,7 @@
         <v>171</v>
       </c>
       <c r="B27" s="76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C27" s="77" t="n">
         <v>2026</v>
@@ -19577,13 +19715,13 @@
         <v>46295</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G27" s="76" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H27" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I27" s="79"/>
       <c r="J27" s="79"/>
@@ -19600,7 +19738,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="66" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19608,7 +19746,7 @@
         <v>171</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C28" s="77" t="n">
         <v>2026</v>
@@ -19620,13 +19758,13 @@
         <v>46203</v>
       </c>
       <c r="F28" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G28" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H28" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I28" s="79" t="n">
         <v>82549.073</v>
@@ -19659,7 +19797,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="66" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19667,7 +19805,7 @@
         <v>171</v>
       </c>
       <c r="B29" s="76" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C29" s="77" t="n">
         <v>2026</v>
@@ -19679,13 +19817,13 @@
         <v>46112</v>
       </c>
       <c r="F29" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G29" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H29" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I29" s="79" t="n">
         <v>49086.932</v>
@@ -19718,7 +19856,7 @@
         <v>2</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19726,7 +19864,7 @@
         <v>171</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C30" s="77" t="n">
         <v>2025</v>
@@ -19738,13 +19876,13 @@
         <v>46022</v>
       </c>
       <c r="F30" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G30" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H30" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I30" s="79" t="n">
         <v>30093.618</v>
@@ -19777,7 +19915,7 @@
         <v>3</v>
       </c>
       <c r="S30" s="66" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19785,7 +19923,7 @@
         <v>171</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C31" s="77" t="n">
         <v>2025</v>
@@ -19797,13 +19935,13 @@
         <v>45930</v>
       </c>
       <c r="F31" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G31" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H31" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I31" s="79" t="n">
         <v>18778.868</v>
@@ -19836,7 +19974,7 @@
         <v>4</v>
       </c>
       <c r="S31" s="66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19844,7 +19982,7 @@
         <v>171</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C32" s="77" t="n">
         <v>2025</v>
@@ -19856,13 +19994,13 @@
         <v>45838</v>
       </c>
       <c r="F32" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G32" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H32" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I32" s="79" t="n">
         <v>10526.094</v>
@@ -19895,7 +20033,7 @@
         <v>5</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19903,7 +20041,7 @@
         <v>171</v>
       </c>
       <c r="B33" s="76" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C33" s="77" t="n">
         <v>2025</v>
@@ -19915,13 +20053,13 @@
         <v>45747</v>
       </c>
       <c r="F33" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G33" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H33" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I33" s="79" t="n">
         <v>7187.94</v>
@@ -19954,7 +20092,7 @@
         <v>6</v>
       </c>
       <c r="S33" s="66" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19962,7 +20100,7 @@
         <v>171</v>
       </c>
       <c r="B34" s="76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C34" s="77" t="n">
         <v>2024</v>
@@ -19974,13 +20112,13 @@
         <v>45657</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G34" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H34" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I34" s="79" t="n">
         <v>6575.094</v>
@@ -20013,7 +20151,7 @@
         <v>7</v>
       </c>
       <c r="S34" s="66" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20021,7 +20159,7 @@
         <v>171</v>
       </c>
       <c r="B35" s="76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C35" s="77" t="n">
         <v>2024</v>
@@ -20033,13 +20171,13 @@
         <v>45565</v>
       </c>
       <c r="F35" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G35" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H35" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I35" s="79" t="n">
         <v>8132.593</v>
@@ -20072,7 +20210,7 @@
         <v>8</v>
       </c>
       <c r="S35" s="66" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20080,7 +20218,7 @@
         <v>171</v>
       </c>
       <c r="B36" s="76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C36" s="77" t="n">
         <v>2024</v>
@@ -20092,13 +20230,13 @@
         <v>45473</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G36" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H36" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I36" s="79" t="n">
         <v>9921.043</v>
@@ -20125,7 +20263,7 @@
         <v>9</v>
       </c>
       <c r="S36" s="66" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20133,7 +20271,7 @@
         <v>171</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C37" s="77" t="n">
         <v>2024</v>
@@ -20145,13 +20283,13 @@
         <v>45382</v>
       </c>
       <c r="F37" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G37" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H37" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I37" s="79" t="n">
         <v>9502.937</v>
@@ -20184,7 +20322,7 @@
         <v>10</v>
       </c>
       <c r="S37" s="66" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20192,7 +20330,7 @@
         <v>171</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C38" s="77" t="n">
         <v>2023</v>
@@ -20204,13 +20342,13 @@
         <v>45291</v>
       </c>
       <c r="F38" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G38" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H38" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I38" s="79" t="n">
         <v>8703.978</v>
@@ -20243,7 +20381,7 @@
         <v>11</v>
       </c>
       <c r="S38" s="66" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20251,7 +20389,7 @@
         <v>171</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C39" s="77" t="n">
         <v>2023</v>
@@ -20263,13 +20401,13 @@
         <v>45199</v>
       </c>
       <c r="F39" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G39" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H39" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I39" s="79" t="n">
         <v>7736.374</v>
@@ -20302,7 +20440,7 @@
         <v>12</v>
       </c>
       <c r="S39" s="66" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20310,7 +20448,7 @@
         <v>171</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C40" s="77" t="n">
         <v>2023</v>
@@ -20322,13 +20460,13 @@
         <v>45107</v>
       </c>
       <c r="F40" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G40" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H40" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I40" s="79" t="n">
         <v>7027.071</v>
@@ -20361,7 +20499,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="66" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20369,7 +20507,7 @@
         <v>171</v>
       </c>
       <c r="B41" s="76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C41" s="77" t="n">
         <v>2023</v>
@@ -20381,13 +20519,13 @@
         <v>45016</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G41" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H41" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I41" s="79" t="n">
         <v>6424.883</v>
@@ -20420,7 +20558,7 @@
         <v>14</v>
       </c>
       <c r="S41" s="66" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20428,7 +20566,7 @@
         <v>171</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C42" s="77" t="n">
         <v>2022</v>
@@ -20440,13 +20578,13 @@
         <v>44926</v>
       </c>
       <c r="F42" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G42" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H42" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I42" s="79" t="n">
         <v>7953.553</v>
@@ -20479,7 +20617,7 @@
         <v>15</v>
       </c>
       <c r="S42" s="66" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20487,7 +20625,7 @@
         <v>171</v>
       </c>
       <c r="B43" s="76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C43" s="77" t="n">
         <v>2022</v>
@@ -20499,13 +20637,13 @@
         <v>44834</v>
       </c>
       <c r="F43" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G43" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H43" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I43" s="79" t="n">
         <v>11021.725</v>
@@ -20538,7 +20676,7 @@
         <v>16</v>
       </c>
       <c r="S43" s="66" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20546,7 +20684,7 @@
         <v>171</v>
       </c>
       <c r="B44" s="76" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C44" s="77" t="n">
         <v>2022</v>
@@ -20558,13 +20696,13 @@
         <v>44742</v>
       </c>
       <c r="F44" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G44" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H44" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I44" s="79" t="n">
         <v>18030.672</v>
@@ -20597,7 +20735,7 @@
         <v>17</v>
       </c>
       <c r="S44" s="66" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20605,7 +20743,7 @@
         <v>171</v>
       </c>
       <c r="B45" s="76" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C45" s="77" t="n">
         <v>2022</v>
@@ -20617,13 +20755,13 @@
         <v>44651</v>
       </c>
       <c r="F45" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G45" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H45" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I45" s="79" t="n">
         <v>19946.325</v>
@@ -20656,7 +20794,7 @@
         <v>18</v>
       </c>
       <c r="S45" s="66" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20664,7 +20802,7 @@
         <v>171</v>
       </c>
       <c r="B46" s="76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C46" s="77" t="n">
         <v>2021</v>
@@ -20676,13 +20814,13 @@
         <v>44561</v>
       </c>
       <c r="F46" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G46" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H46" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I46" s="79" t="n">
         <v>21398.949</v>
@@ -20715,7 +20853,7 @@
         <v>19</v>
       </c>
       <c r="S46" s="66" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20723,7 +20861,7 @@
         <v>171</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C47" s="77" t="n">
         <v>2021</v>
@@ -20735,13 +20873,13 @@
         <v>44469</v>
       </c>
       <c r="F47" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G47" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H47" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I47" s="79" t="n">
         <v>23837.128</v>
@@ -20774,7 +20912,7 @@
         <v>20</v>
       </c>
       <c r="S47" s="66" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20782,7 +20920,7 @@
         <v>171</v>
       </c>
       <c r="B48" s="76" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C48" s="77" t="n">
         <v>2021</v>
@@ -20794,13 +20932,13 @@
         <v>44377</v>
       </c>
       <c r="F48" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G48" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H48" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I48" s="79" t="n">
         <v>22637.468</v>
@@ -20833,7 +20971,7 @@
         <v>21</v>
       </c>
       <c r="S48" s="66" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20841,7 +20979,7 @@
         <v>171</v>
       </c>
       <c r="B49" s="76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C49" s="77" t="n">
         <v>2021</v>
@@ -20853,13 +20991,13 @@
         <v>44286</v>
       </c>
       <c r="F49" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G49" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H49" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I49" s="79" t="n">
         <v>17730.613</v>
@@ -20892,7 +21030,7 @@
         <v>22</v>
       </c>
       <c r="S49" s="66" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20900,7 +21038,7 @@
         <v>171</v>
       </c>
       <c r="B50" s="76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C50" s="77" t="n">
         <v>2020</v>
@@ -20912,13 +21050,13 @@
         <v>44196</v>
       </c>
       <c r="F50" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G50" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H50" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I50" s="79" t="n">
         <v>14773.42</v>
@@ -20951,7 +21089,7 @@
         <v>23</v>
       </c>
       <c r="S50" s="66" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20959,7 +21097,7 @@
         <v>171</v>
       </c>
       <c r="B51" s="76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C51" s="77" t="n">
         <v>2020</v>
@@ -20971,13 +21109,13 @@
         <v>44104</v>
       </c>
       <c r="F51" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G51" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H51" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I51" s="79" t="n">
         <v>15323.867</v>
@@ -21008,7 +21146,7 @@
         <v>24</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21016,7 +21154,7 @@
         <v>179</v>
       </c>
       <c r="B52" s="76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C52" s="77" t="n">
         <v>2026</v>
@@ -21028,13 +21166,13 @@
         <v>46295</v>
       </c>
       <c r="F52" s="76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G52" s="76" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H52" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
@@ -21051,7 +21189,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21059,7 +21197,7 @@
         <v>179</v>
       </c>
       <c r="B53" s="76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C53" s="77" t="n">
         <v>2026</v>
@@ -21071,13 +21209,13 @@
         <v>46203</v>
       </c>
       <c r="F53" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G53" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H53" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I53" s="79" t="n">
         <v>965.373</v>
@@ -21110,7 +21248,7 @@
         <v>1</v>
       </c>
       <c r="S53" s="66" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21118,7 +21256,7 @@
         <v>179</v>
       </c>
       <c r="B54" s="76" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C54" s="77" t="n">
         <v>2026</v>
@@ -21130,13 +21268,13 @@
         <v>46112</v>
       </c>
       <c r="F54" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G54" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H54" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I54" s="79" t="n">
         <v>959.31</v>
@@ -21169,7 +21307,7 @@
         <v>2</v>
       </c>
       <c r="S54" s="66" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21177,7 +21315,7 @@
         <v>179</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C55" s="77" t="n">
         <v>2025</v>
@@ -21189,13 +21327,13 @@
         <v>46022</v>
       </c>
       <c r="F55" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G55" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H55" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I55" s="79" t="n">
         <v>959.589</v>
@@ -21228,7 +21366,7 @@
         <v>3</v>
       </c>
       <c r="S55" s="66" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21236,7 +21374,7 @@
         <v>179</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C56" s="77" t="n">
         <v>2025</v>
@@ -21248,13 +21386,13 @@
         <v>45930</v>
       </c>
       <c r="F56" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G56" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H56" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I56" s="79" t="n">
         <v>912.804</v>
@@ -21287,7 +21425,7 @@
         <v>4</v>
       </c>
       <c r="S56" s="66" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21295,7 +21433,7 @@
         <v>179</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C57" s="77" t="n">
         <v>2025</v>
@@ -21307,13 +21445,13 @@
         <v>45838</v>
       </c>
       <c r="F57" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G57" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H57" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I57" s="79" t="n">
         <v>714.087</v>
@@ -21346,7 +21484,7 @@
         <v>5</v>
       </c>
       <c r="S57" s="66" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21354,7 +21492,7 @@
         <v>179</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C58" s="77" t="n">
         <v>2025</v>
@@ -21366,13 +21504,13 @@
         <v>45747</v>
       </c>
       <c r="F58" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G58" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H58" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I58" s="79" t="n">
         <v>793.663</v>
@@ -21405,7 +21543,7 @@
         <v>6</v>
       </c>
       <c r="S58" s="66" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21413,7 +21551,7 @@
         <v>179</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C59" s="77" t="n">
         <v>2024</v>
@@ -21425,13 +21563,13 @@
         <v>45657</v>
       </c>
       <c r="F59" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G59" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H59" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I59" s="79" t="n">
         <v>722.474</v>
@@ -21464,7 +21602,7 @@
         <v>7</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21472,7 +21610,7 @@
         <v>179</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C60" s="77" t="n">
         <v>2024</v>
@@ -21484,13 +21622,13 @@
         <v>45565</v>
       </c>
       <c r="F60" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G60" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H60" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I60" s="79" t="n">
         <v>805.747</v>
@@ -21523,7 +21661,7 @@
         <v>8</v>
       </c>
       <c r="S60" s="66" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21531,7 +21669,7 @@
         <v>179</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C61" s="77" t="n">
         <v>2024</v>
@@ -21543,13 +21681,13 @@
         <v>45473</v>
       </c>
       <c r="F61" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G61" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H61" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I61" s="79" t="n">
         <v>875.601</v>
@@ -21582,7 +21720,7 @@
         <v>9</v>
       </c>
       <c r="S61" s="66" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21590,7 +21728,7 @@
         <v>179</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C62" s="77" t="n">
         <v>2024</v>
@@ -21602,13 +21740,13 @@
         <v>45382</v>
       </c>
       <c r="F62" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G62" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H62" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I62" s="79" t="n">
         <v>837.395</v>
@@ -21641,7 +21779,7 @@
         <v>10</v>
       </c>
       <c r="S62" s="66" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21649,7 +21787,7 @@
         <v>179</v>
       </c>
       <c r="B63" s="76" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C63" s="77" t="n">
         <v>2023</v>
@@ -21661,13 +21799,13 @@
         <v>45291</v>
       </c>
       <c r="F63" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G63" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H63" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I63" s="79" t="n">
         <v>936.937</v>
@@ -21700,7 +21838,7 @@
         <v>11</v>
       </c>
       <c r="S63" s="66" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21708,7 +21846,7 @@
         <v>179</v>
       </c>
       <c r="B64" s="76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C64" s="77" t="n">
         <v>2023</v>
@@ -21720,13 +21858,13 @@
         <v>45199</v>
       </c>
       <c r="F64" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G64" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H64" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I64" s="79" t="n">
         <v>768.427</v>
@@ -21759,7 +21897,7 @@
         <v>12</v>
       </c>
       <c r="S64" s="66" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21767,7 +21905,7 @@
         <v>179</v>
       </c>
       <c r="B65" s="76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C65" s="77" t="n">
         <v>2023</v>
@@ -21779,13 +21917,13 @@
         <v>45107</v>
       </c>
       <c r="F65" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G65" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H65" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I65" s="79" t="n">
         <v>594.323</v>
@@ -21818,7 +21956,7 @@
         <v>13</v>
       </c>
       <c r="S65" s="66" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21826,7 +21964,7 @@
         <v>179</v>
       </c>
       <c r="B66" s="76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C66" s="77" t="n">
         <v>2023</v>
@@ -21838,13 +21976,13 @@
         <v>45016</v>
       </c>
       <c r="F66" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G66" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H66" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I66" s="79" t="n">
         <v>394.417</v>
@@ -21877,7 +22015,7 @@
         <v>14</v>
       </c>
       <c r="S66" s="66" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21885,7 +22023,7 @@
         <v>179</v>
       </c>
       <c r="B67" s="76" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C67" s="77" t="n">
         <v>2022</v>
@@ -21897,13 +22035,13 @@
         <v>44926</v>
       </c>
       <c r="F67" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G67" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H67" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I67" s="79" t="n">
         <v>506.067</v>
@@ -21936,7 +22074,7 @@
         <v>15</v>
       </c>
       <c r="S67" s="66" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21944,7 +22082,7 @@
         <v>179</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C68" s="77" t="n">
         <v>2022</v>
@@ -21956,13 +22094,13 @@
         <v>44834</v>
       </c>
       <c r="F68" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G68" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H68" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I68" s="79" t="n">
         <v>522.089</v>
@@ -21995,7 +22133,7 @@
         <v>16</v>
       </c>
       <c r="S68" s="66" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22003,7 +22141,7 @@
         <v>179</v>
       </c>
       <c r="B69" s="76" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C69" s="77" t="n">
         <v>2022</v>
@@ -22015,13 +22153,13 @@
         <v>44742</v>
       </c>
       <c r="F69" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G69" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H69" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I69" s="79" t="n">
         <v>736.276</v>
@@ -22054,7 +22192,7 @@
         <v>17</v>
       </c>
       <c r="S69" s="66" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22062,7 +22200,7 @@
         <v>179</v>
       </c>
       <c r="B70" s="76" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C70" s="77" t="n">
         <v>2022</v>
@@ -22074,13 +22212,13 @@
         <v>44651</v>
       </c>
       <c r="F70" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G70" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H70" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I70" s="79" t="n">
         <v>839.197</v>
@@ -22113,7 +22251,7 @@
         <v>18</v>
       </c>
       <c r="S70" s="66" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22121,7 +22259,7 @@
         <v>179</v>
       </c>
       <c r="B71" s="76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C71" s="77" t="n">
         <v>2021</v>
@@ -22133,13 +22271,13 @@
         <v>44561</v>
       </c>
       <c r="F71" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G71" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H71" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I71" s="79" t="n">
         <v>875.843</v>
@@ -22172,7 +22310,7 @@
         <v>19</v>
       </c>
       <c r="S71" s="66" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22180,7 +22318,7 @@
         <v>179</v>
       </c>
       <c r="B72" s="76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C72" s="77" t="n">
         <v>2021</v>
@@ -22192,13 +22330,13 @@
         <v>44469</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G72" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H72" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I72" s="79" t="n">
         <v>947.399</v>
@@ -22231,7 +22369,7 @@
         <v>20</v>
       </c>
       <c r="S72" s="66" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22239,7 +22377,7 @@
         <v>179</v>
       </c>
       <c r="B73" s="76" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C73" s="77" t="n">
         <v>2021</v>
@@ -22251,13 +22389,13 @@
         <v>44377</v>
       </c>
       <c r="F73" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G73" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H73" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I73" s="79" t="n">
         <v>896.062</v>
@@ -22290,7 +22428,7 @@
         <v>21</v>
       </c>
       <c r="S73" s="66" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22298,7 +22436,7 @@
         <v>179</v>
       </c>
       <c r="B74" s="76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C74" s="77" t="n">
         <v>2021</v>
@@ -22310,13 +22448,13 @@
         <v>44286</v>
       </c>
       <c r="F74" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G74" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H74" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I74" s="79" t="n">
         <v>889.217</v>
@@ -22349,7 +22487,7 @@
         <v>22</v>
       </c>
       <c r="S74" s="66" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22357,7 +22495,7 @@
         <v>179</v>
       </c>
       <c r="B75" s="76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C75" s="77" t="n">
         <v>2020</v>
@@ -22369,13 +22507,13 @@
         <v>44196</v>
       </c>
       <c r="F75" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G75" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H75" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I75" s="79" t="n">
         <v>757.232</v>
@@ -22408,7 +22546,7 @@
         <v>23</v>
       </c>
       <c r="S75" s="66" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22416,7 +22554,7 @@
         <v>179</v>
       </c>
       <c r="B76" s="76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C76" s="77" t="n">
         <v>2020</v>
@@ -22428,13 +22566,13 @@
         <v>44104</v>
       </c>
       <c r="F76" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G76" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H76" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I76" s="79" t="n">
         <v>644.391</v>
@@ -22465,15 +22603,15 @@
         <v>24</v>
       </c>
       <c r="S76" s="66" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B77" s="76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C77" s="77" t="n">
         <v>2026</v>
@@ -22485,19 +22623,19 @@
         <v>46295</v>
       </c>
       <c r="F77" s="76" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G77" s="76" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H77" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I77" s="79"/>
       <c r="J77" s="79"/>
       <c r="K77" s="79"/>
       <c r="L77" s="80" t="n">
-        <v>99.01</v>
+        <v>9.57273</v>
       </c>
       <c r="M77" s="79"/>
       <c r="N77" s="79"/>
@@ -22508,15 +22646,15 @@
         <v>0</v>
       </c>
       <c r="S77" s="66" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B78" s="76" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C78" s="77" t="n">
         <v>2026</v>
@@ -22528,54 +22666,54 @@
         <v>46203</v>
       </c>
       <c r="F78" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G78" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H78" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I78" s="79" t="n">
-        <v>22443.411</v>
+        <v>28660.098</v>
       </c>
       <c r="J78" s="79" t="n">
-        <v>14589.612</v>
+        <v>12156.801</v>
       </c>
       <c r="K78" s="79" t="n">
-        <v>10368072000</v>
+        <v>6327860000</v>
       </c>
       <c r="L78" s="80" t="n">
-        <v>108.93</v>
+        <v>10.4</v>
       </c>
       <c r="M78" s="79" t="n">
-        <v>96.3654</v>
+        <v>608.5115</v>
       </c>
       <c r="N78" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="79" t="n">
-        <v>23288.098</v>
+        <v>68961.06</v>
       </c>
       <c r="P78" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="80" t="n">
-        <v>1615</v>
+        <v>535</v>
       </c>
       <c r="R78" s="47" t="n">
         <v>1</v>
       </c>
       <c r="S78" s="66" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B79" s="76" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C79" s="77" t="n">
         <v>2026</v>
@@ -22587,54 +22725,54 @@
         <v>46112</v>
       </c>
       <c r="F79" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G79" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H79" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I79" s="79" t="n">
-        <v>13182.608</v>
+        <v>23145.303</v>
       </c>
       <c r="J79" s="79" t="n">
-        <v>7791.357</v>
+        <v>9039.901</v>
       </c>
       <c r="K79" s="79" t="n">
-        <v>5466357000</v>
+        <v>3767112000</v>
       </c>
       <c r="L79" s="80" t="n">
-        <v>57.49</v>
+        <v>6.19</v>
       </c>
       <c r="M79" s="79" t="n">
-        <v>96.3552</v>
+        <v>608.5115</v>
       </c>
       <c r="N79" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="79" t="n">
-        <v>14500.386</v>
+        <v>71927.815</v>
       </c>
       <c r="P79" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="80" t="n">
-        <v>847</v>
+        <v>379.5</v>
       </c>
       <c r="R79" s="47" t="n">
         <v>2</v>
       </c>
       <c r="S79" s="66" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B80" s="76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C80" s="77" t="n">
         <v>2025</v>
@@ -22646,54 +22784,54 @@
         <v>46022</v>
       </c>
       <c r="F80" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G80" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H80" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I80" s="79" t="n">
-        <v>4806.69</v>
+        <v>22817.209</v>
       </c>
       <c r="J80" s="79" t="n">
-        <v>1597.288</v>
+        <v>8712.827</v>
       </c>
       <c r="K80" s="79" t="n">
-        <v>870716000</v>
+        <v>3689810000</v>
       </c>
       <c r="L80" s="80" t="n">
-        <v>9.26</v>
+        <v>6.07</v>
       </c>
       <c r="M80" s="79" t="n">
-        <v>96.0407</v>
+        <v>608.5115</v>
       </c>
       <c r="N80" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="79" t="n">
-        <v>8940.787</v>
+        <v>67739.247</v>
       </c>
       <c r="P80" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="80" t="n">
-        <v>576</v>
+        <v>374</v>
       </c>
       <c r="R80" s="47" t="n">
         <v>3</v>
       </c>
       <c r="S80" s="66" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B81" s="76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C81" s="77" t="n">
         <v>2025</v>
@@ -22705,54 +22843,54 @@
         <v>45930</v>
       </c>
       <c r="F81" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G81" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H81" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I81" s="79" t="n">
-        <v>3807.401</v>
+        <v>24573.67</v>
       </c>
       <c r="J81" s="79" t="n">
-        <v>1248.818</v>
+        <v>8918.821</v>
       </c>
       <c r="K81" s="79" t="n">
-        <v>643038000</v>
+        <v>3654824000</v>
       </c>
       <c r="L81" s="80" t="n">
-        <v>6.87</v>
+        <v>6.01</v>
       </c>
       <c r="M81" s="79" t="n">
-        <v>95.3452</v>
+        <v>608.5115</v>
       </c>
       <c r="N81" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="79" t="n">
-        <v>7932.37</v>
+        <v>63580.896</v>
       </c>
       <c r="P81" s="80" t="n">
-        <v>9.37723774</v>
+        <v>28</v>
       </c>
       <c r="Q81" s="80" t="n">
-        <v>329.5</v>
+        <v>426.5</v>
       </c>
       <c r="R81" s="47" t="n">
         <v>4</v>
       </c>
       <c r="S81" s="66" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B82" s="76" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C82" s="77" t="n">
         <v>2025</v>
@@ -22764,54 +22902,54 @@
         <v>45838</v>
       </c>
       <c r="F82" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G82" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H82" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I82" s="79" t="n">
-        <v>3028.429</v>
+        <v>26152.063</v>
       </c>
       <c r="J82" s="79" t="n">
-        <v>785.089</v>
+        <v>9493.648</v>
       </c>
       <c r="K82" s="79" t="n">
-        <v>185349000</v>
+        <v>3739254000</v>
       </c>
       <c r="L82" s="80" t="n">
-        <v>2.02</v>
+        <v>6.14</v>
       </c>
       <c r="M82" s="79" t="n">
-        <v>91.6411</v>
+        <v>608.5115</v>
       </c>
       <c r="N82" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="79" t="n">
-        <v>7184.405</v>
+        <v>59641.644</v>
       </c>
       <c r="P82" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="80" t="n">
-        <v>237</v>
+        <v>545</v>
       </c>
       <c r="R82" s="47" t="n">
         <v>5</v>
       </c>
       <c r="S82" s="66" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B83" s="76" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C83" s="77" t="n">
         <v>2025</v>
@@ -22823,54 +22961,54 @@
         <v>45747</v>
       </c>
       <c r="F83" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G83" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H83" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I83" s="79" t="n">
-        <v>2618.742</v>
+        <v>27120.202</v>
       </c>
       <c r="J83" s="79" t="n">
-        <v>800.733</v>
+        <v>10782.716</v>
       </c>
       <c r="K83" s="79" t="n">
-        <v>336540000</v>
+        <v>5263805000</v>
       </c>
       <c r="L83" s="80" t="n">
-        <v>3.68</v>
+        <v>8.65</v>
       </c>
       <c r="M83" s="79" t="n">
-        <v>91.5746</v>
+        <v>608.5115</v>
       </c>
       <c r="N83" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="79" t="n">
-        <v>7854.351</v>
+        <v>73131.074</v>
       </c>
       <c r="P83" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="80" t="n">
-        <v>250.5</v>
+        <v>545</v>
       </c>
       <c r="R83" s="47" t="n">
         <v>6</v>
       </c>
       <c r="S83" s="66" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B84" s="76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C84" s="77" t="n">
         <v>2024</v>
@@ -22882,54 +23020,54 @@
         <v>45657</v>
       </c>
       <c r="F84" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G84" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H84" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I84" s="79" t="n">
-        <v>2228.005</v>
+        <v>25262.519</v>
       </c>
       <c r="J84" s="79" t="n">
-        <v>648.956</v>
+        <v>9980.564</v>
       </c>
       <c r="K84" s="79" t="n">
-        <v>271532000</v>
+        <v>4801366000</v>
       </c>
       <c r="L84" s="80" t="n">
-        <v>2.97</v>
+        <v>7.89</v>
       </c>
       <c r="M84" s="79" t="n">
-        <v>91.4561</v>
+        <v>608.5115</v>
       </c>
       <c r="N84" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O84" s="79" t="n">
-        <v>7491.143</v>
+        <v>67923.372</v>
       </c>
       <c r="P84" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q84" s="80" t="n">
-        <v>218</v>
+        <v>502</v>
       </c>
       <c r="R84" s="47" t="n">
         <v>7</v>
       </c>
       <c r="S84" s="66" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B85" s="76" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C85" s="77" t="n">
         <v>2024</v>
@@ -22941,54 +23079,54 @@
         <v>45565</v>
       </c>
       <c r="F85" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G85" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H85" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I85" s="79" t="n">
-        <v>2321.419</v>
+        <v>27866.328</v>
       </c>
       <c r="J85" s="79" t="n">
-        <v>658.433</v>
+        <v>11073.966</v>
       </c>
       <c r="K85" s="79" t="n">
-        <v>188620000</v>
+        <v>5258457000</v>
       </c>
       <c r="L85" s="80" t="n">
-        <v>2.08</v>
+        <v>8.64</v>
       </c>
       <c r="M85" s="79" t="n">
-        <v>91.3372</v>
+        <v>608.5115</v>
       </c>
       <c r="N85" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O85" s="79" t="n">
-        <v>7196.228</v>
+        <v>63457.777</v>
       </c>
       <c r="P85" s="80" t="n">
-        <v>10.2</v>
+        <v>32</v>
       </c>
       <c r="Q85" s="80" t="n">
-        <v>282</v>
+        <v>518</v>
       </c>
       <c r="R85" s="47" t="n">
         <v>8</v>
       </c>
       <c r="S85" s="66" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B86" s="76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C86" s="77" t="n">
         <v>2024</v>
@@ -23000,54 +23138,54 @@
         <v>45473</v>
       </c>
       <c r="F86" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G86" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H86" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I86" s="79" t="n">
-        <v>2190.229</v>
+        <v>25231.019</v>
       </c>
       <c r="J86" s="79" t="n">
-        <v>759.289</v>
+        <v>10380.151</v>
       </c>
       <c r="K86" s="79" t="n">
-        <v>294050000</v>
+        <v>5388565000</v>
       </c>
       <c r="L86" s="80" t="n">
-        <v>3.26</v>
+        <v>8.86</v>
       </c>
       <c r="M86" s="79" t="n">
-        <v>88.3977</v>
+        <v>608.5115</v>
       </c>
       <c r="N86" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="79" t="n">
-        <v>6803.334</v>
+        <v>58153.523</v>
       </c>
       <c r="P86" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="80" t="n">
-        <v>302</v>
+        <v>606</v>
       </c>
       <c r="R86" s="47" t="n">
         <v>9</v>
       </c>
       <c r="S86" s="66" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B87" s="76" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C87" s="77" t="n">
         <v>2024</v>
@@ -23059,54 +23197,54 @@
         <v>45382</v>
       </c>
       <c r="F87" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G87" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H87" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I87" s="79" t="n">
-        <v>2175.989</v>
+        <v>24427.885</v>
       </c>
       <c r="J87" s="79" t="n">
-        <v>758.571</v>
+        <v>10037.675</v>
       </c>
       <c r="K87" s="79" t="n">
-        <v>351970000</v>
+        <v>4893633000</v>
       </c>
       <c r="L87" s="80" t="n">
-        <v>3.98</v>
+        <v>8.04</v>
       </c>
       <c r="M87" s="79" t="n">
-        <v>88.3977</v>
+        <v>608.5115</v>
       </c>
       <c r="N87" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="79" t="n">
-        <v>7398.652</v>
+        <v>72098.281</v>
       </c>
       <c r="P87" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="80" t="n">
-        <v>305.5</v>
+        <v>604</v>
       </c>
       <c r="R87" s="47" t="n">
         <v>10</v>
       </c>
       <c r="S87" s="66" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B88" s="76" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C88" s="77" t="n">
         <v>2023</v>
@@ -23118,54 +23256,54 @@
         <v>45291</v>
       </c>
       <c r="F88" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G88" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H88" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I88" s="79" t="n">
-        <v>2130.049</v>
+        <v>27153.825</v>
       </c>
       <c r="J88" s="79" t="n">
-        <v>707.384</v>
+        <v>11263.599</v>
       </c>
       <c r="K88" s="79" t="n">
-        <v>262238000</v>
+        <v>5327953000</v>
       </c>
       <c r="L88" s="80" t="n">
-        <v>2.96</v>
+        <v>8.76</v>
       </c>
       <c r="M88" s="79" t="n">
-        <v>88.3977</v>
+        <v>608.5115</v>
       </c>
       <c r="N88" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="79" t="n">
-        <v>7036.917</v>
+        <v>67216.762</v>
       </c>
       <c r="P88" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q88" s="80" t="n">
-        <v>312</v>
+        <v>517</v>
       </c>
       <c r="R88" s="47" t="n">
         <v>11</v>
       </c>
       <c r="S88" s="66" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B89" s="76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C89" s="77" t="n">
         <v>2023</v>
@@ -23177,54 +23315,54 @@
         <v>45199</v>
       </c>
       <c r="F89" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G89" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H89" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I89" s="79" t="n">
-        <v>1993.007</v>
+        <v>28929.962</v>
       </c>
       <c r="J89" s="79" t="n">
-        <v>687.513</v>
+        <v>12222.668</v>
       </c>
       <c r="K89" s="79" t="n">
-        <v>306457000</v>
+        <v>6365821000</v>
       </c>
       <c r="L89" s="80" t="n">
-        <v>3.47</v>
+        <v>10.46</v>
       </c>
       <c r="M89" s="79" t="n">
-        <v>88.3977</v>
+        <v>608.5115</v>
       </c>
       <c r="N89" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="79" t="n">
-        <v>6756.961</v>
+        <v>61657.439</v>
       </c>
       <c r="P89" s="80" t="n">
-        <v>13.78192729</v>
+        <v>37</v>
       </c>
       <c r="Q89" s="80" t="n">
-        <v>296.5</v>
+        <v>423</v>
       </c>
       <c r="R89" s="47" t="n">
         <v>12</v>
       </c>
       <c r="S89" s="66" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B90" s="76" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C90" s="77" t="n">
         <v>2023</v>
@@ -23236,54 +23374,54 @@
         <v>45107</v>
       </c>
       <c r="F90" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G90" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H90" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I90" s="79" t="n">
-        <v>1930.516</v>
+        <v>30299.029</v>
       </c>
       <c r="J90" s="79" t="n">
-        <v>636.105</v>
+        <v>12646.823</v>
       </c>
       <c r="K90" s="79" t="n">
-        <v>230718000</v>
+        <v>6871899000</v>
       </c>
       <c r="L90" s="80" t="n">
-        <v>2.66</v>
+        <v>11.29</v>
       </c>
       <c r="M90" s="79" t="n">
-        <v>86.6666</v>
+        <v>608.5115</v>
       </c>
       <c r="N90" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="79" t="n">
-        <v>6433.521</v>
+        <v>55216.656</v>
       </c>
       <c r="P90" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="80" t="n">
-        <v>324</v>
+        <v>426.5</v>
       </c>
       <c r="R90" s="47" t="n">
         <v>13</v>
       </c>
       <c r="S90" s="66" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B91" s="76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C91" s="77" t="n">
         <v>2023</v>
@@ -23295,54 +23433,54 @@
         <v>45016</v>
       </c>
       <c r="F91" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G91" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H91" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I91" s="79" t="n">
-        <v>2260.206</v>
+        <v>24045.882</v>
       </c>
       <c r="J91" s="79" t="n">
-        <v>814.91</v>
+        <v>10078.803</v>
       </c>
       <c r="K91" s="79" t="n">
-        <v>348203000</v>
+        <v>4751836000</v>
       </c>
       <c r="L91" s="80" t="n">
-        <v>4.02</v>
+        <v>7.81</v>
       </c>
       <c r="M91" s="79" t="n">
-        <v>86.6666</v>
+        <v>608.5115</v>
       </c>
       <c r="N91" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O91" s="79" t="n">
-        <v>7382.85</v>
+        <v>70945.808</v>
       </c>
       <c r="P91" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="80" t="n">
-        <v>314</v>
+        <v>431.5</v>
       </c>
       <c r="R91" s="47" t="n">
         <v>14</v>
       </c>
       <c r="S91" s="66" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B92" s="76" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C92" s="77" t="n">
         <v>2022</v>
@@ -23354,54 +23492,54 @@
         <v>44926</v>
       </c>
       <c r="F92" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G92" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H92" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I92" s="79" t="n">
-        <v>2286.572</v>
+        <v>22420.161</v>
       </c>
       <c r="J92" s="79" t="n">
-        <v>860.807</v>
+        <v>9090.355</v>
       </c>
       <c r="K92" s="79" t="n">
-        <v>385061000</v>
+        <v>4042779000</v>
       </c>
       <c r="L92" s="80" t="n">
-        <v>4.44</v>
+        <v>6.64</v>
       </c>
       <c r="M92" s="79" t="n">
-        <v>86.5531</v>
+        <v>608.5115</v>
       </c>
       <c r="N92" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="79" t="n">
-        <v>7012.867</v>
+        <v>65570.205</v>
       </c>
       <c r="P92" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="80" t="n">
-        <v>185.5</v>
+        <v>315.5</v>
       </c>
       <c r="R92" s="47" t="n">
         <v>15</v>
       </c>
       <c r="S92" s="66" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B93" s="76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C93" s="77" t="n">
         <v>2022</v>
@@ -23413,54 +23551,54 @@
         <v>44834</v>
       </c>
       <c r="F93" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G93" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H93" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I93" s="79" t="n">
-        <v>2560.341</v>
+        <v>19563.686</v>
       </c>
       <c r="J93" s="79" t="n">
-        <v>914.902</v>
+        <v>8344.293</v>
       </c>
       <c r="K93" s="79" t="n">
-        <v>542661000</v>
+        <v>4305080000</v>
       </c>
       <c r="L93" s="80" t="n">
-        <v>6.28</v>
+        <v>7.07</v>
       </c>
       <c r="M93" s="79" t="n">
-        <v>86.4706</v>
+        <v>608.5115</v>
       </c>
       <c r="N93" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="79" t="n">
-        <v>6611.975</v>
+        <v>61301.496</v>
       </c>
       <c r="P93" s="80" t="n">
-        <v>11.5240749</v>
+        <v>51.5</v>
       </c>
       <c r="Q93" s="80" t="n">
-        <v>161.5</v>
+        <v>219</v>
       </c>
       <c r="R93" s="47" t="n">
         <v>16</v>
       </c>
       <c r="S93" s="66" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B94" s="76" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C94" s="77" t="n">
         <v>2022</v>
@@ -23472,54 +23610,54 @@
         <v>44742</v>
       </c>
       <c r="F94" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G94" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H94" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I94" s="79" t="n">
-        <v>2866.579</v>
+        <v>31461.142</v>
       </c>
       <c r="J94" s="79" t="n">
-        <v>947.502</v>
+        <v>14982.46</v>
       </c>
       <c r="K94" s="79" t="n">
-        <v>536500000</v>
+        <v>8486735000</v>
       </c>
       <c r="L94" s="80" t="n">
-        <v>6.41</v>
+        <v>13.95</v>
       </c>
       <c r="M94" s="79" t="n">
-        <v>83.895</v>
+        <v>608.5115</v>
       </c>
       <c r="N94" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="79" t="n">
-        <v>6043.861</v>
+        <v>57213.395</v>
       </c>
       <c r="P94" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q94" s="80" t="n">
-        <v>162.5</v>
+        <v>302</v>
       </c>
       <c r="R94" s="47" t="n">
         <v>17</v>
       </c>
       <c r="S94" s="66" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B95" s="76" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C95" s="77" t="n">
         <v>2022</v>
@@ -23531,54 +23669,54 @@
         <v>44651</v>
       </c>
       <c r="F95" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G95" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H95" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I95" s="79" t="n">
-        <v>2589.737</v>
+        <v>36511.685</v>
       </c>
       <c r="J95" s="79" t="n">
-        <v>735.407</v>
+        <v>18524.079</v>
       </c>
       <c r="K95" s="79" t="n">
-        <v>385967000</v>
+        <v>11134928000</v>
       </c>
       <c r="L95" s="80" t="n">
-        <v>4.64</v>
+        <v>18.3</v>
       </c>
       <c r="M95" s="79" t="n">
-        <v>83.7225</v>
+        <v>608.5115</v>
       </c>
       <c r="N95" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O95" s="79" t="n">
-        <v>6458.201</v>
+        <v>80907.797</v>
       </c>
       <c r="P95" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="80" t="n">
-        <v>215</v>
+        <v>426.5</v>
       </c>
       <c r="R95" s="47" t="n">
         <v>18</v>
       </c>
       <c r="S95" s="66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B96" s="76" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C96" s="77" t="n">
         <v>2021</v>
@@ -23590,54 +23728,54 @@
         <v>44561</v>
       </c>
       <c r="F96" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G96" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H96" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I96" s="79" t="n">
-        <v>2396.847</v>
+        <v>36542.106</v>
       </c>
       <c r="J96" s="79" t="n">
-        <v>677.529</v>
+        <v>18800.964</v>
       </c>
       <c r="K96" s="79" t="n">
-        <v>290253000</v>
+        <v>10933240000</v>
       </c>
       <c r="L96" s="80" t="n">
-        <v>3.51</v>
+        <v>17.97</v>
       </c>
       <c r="M96" s="79" t="n">
-        <v>82.668</v>
+        <v>608.5115</v>
       </c>
       <c r="N96" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O96" s="79" t="n">
-        <v>5960.989</v>
+        <v>70451.323</v>
       </c>
       <c r="P96" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q96" s="80" t="n">
-        <v>204</v>
+        <v>539</v>
       </c>
       <c r="R96" s="47" t="n">
         <v>19</v>
       </c>
       <c r="S96" s="66" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B97" s="76" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C97" s="77" t="n">
         <v>2021</v>
@@ -23649,54 +23787,54 @@
         <v>44469</v>
       </c>
       <c r="F97" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G97" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H97" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I97" s="79" t="n">
-        <v>2973.845</v>
+        <v>38345.587</v>
       </c>
       <c r="J97" s="79" t="n">
-        <v>975.336</v>
+        <v>19917.256</v>
       </c>
       <c r="K97" s="79" t="n">
-        <v>533714000</v>
+        <v>12271038000</v>
       </c>
       <c r="L97" s="80" t="n">
-        <v>6.46</v>
+        <v>20.17</v>
       </c>
       <c r="M97" s="79" t="n">
-        <v>82.628</v>
+        <v>608.5115</v>
       </c>
       <c r="N97" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O97" s="79" t="n">
-        <v>5663.586</v>
+        <v>59279.226</v>
       </c>
       <c r="P97" s="80" t="n">
-        <v>6.69560253</v>
+        <v>15.6</v>
       </c>
       <c r="Q97" s="80" t="n">
-        <v>182</v>
+        <v>410</v>
       </c>
       <c r="R97" s="47" t="n">
         <v>20</v>
       </c>
       <c r="S97" s="66" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B98" s="76" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C98" s="77" t="n">
         <v>2021</v>
@@ -23708,54 +23846,54 @@
         <v>44377</v>
       </c>
       <c r="F98" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G98" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H98" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I98" s="79" t="n">
-        <v>2885.046</v>
+        <v>34111.302</v>
       </c>
       <c r="J98" s="79" t="n">
-        <v>888.15</v>
+        <v>17166.736</v>
       </c>
       <c r="K98" s="79" t="n">
-        <v>477358000</v>
+        <v>9786068000</v>
       </c>
       <c r="L98" s="80" t="n">
-        <v>5.79</v>
+        <v>16.08</v>
       </c>
       <c r="M98" s="79" t="n">
-        <v>82.516</v>
+        <v>608.5115</v>
       </c>
       <c r="N98" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O98" s="79" t="n">
-        <v>5668.615</v>
+        <v>46461.763</v>
       </c>
       <c r="P98" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q98" s="80" t="n">
-        <v>190.5</v>
+        <v>499</v>
       </c>
       <c r="R98" s="47" t="n">
         <v>21</v>
       </c>
       <c r="S98" s="66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B99" s="76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C99" s="77" t="n">
         <v>2021</v>
@@ -23767,54 +23905,54 @@
         <v>44286</v>
       </c>
       <c r="F99" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G99" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H99" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I99" s="79" t="n">
-        <v>1939.92</v>
+        <v>26366.515</v>
       </c>
       <c r="J99" s="79" t="n">
-        <v>551.203</v>
+        <v>11506.568</v>
       </c>
       <c r="K99" s="79" t="n">
-        <v>259563000</v>
+        <v>5875214000</v>
       </c>
       <c r="L99" s="80" t="n">
-        <v>3.17</v>
+        <v>9.66</v>
       </c>
       <c r="M99" s="79" t="n">
-        <v>82.459</v>
+        <v>608.5115</v>
       </c>
       <c r="N99" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="79" t="n">
-        <v>5182.897</v>
+        <v>46019.727</v>
       </c>
       <c r="P99" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q99" s="80" t="n">
-        <v>170</v>
+        <v>575</v>
       </c>
       <c r="R99" s="47" t="n">
         <v>22</v>
       </c>
       <c r="S99" s="66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B100" s="76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C100" s="77" t="n">
         <v>2020</v>
@@ -23826,54 +23964,54 @@
         <v>44196</v>
       </c>
       <c r="F100" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G100" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H100" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I100" s="79" t="n">
-        <v>1575.49</v>
+        <v>22452.842</v>
       </c>
       <c r="J100" s="79" t="n">
-        <v>458.968</v>
+        <v>8538.771</v>
       </c>
       <c r="K100" s="79" t="n">
-        <v>175456000</v>
+        <v>3644209000</v>
       </c>
       <c r="L100" s="80" t="n">
-        <v>2.16</v>
+        <v>5.99</v>
       </c>
       <c r="M100" s="79" t="n">
-        <v>81.324</v>
+        <v>608.5115</v>
       </c>
       <c r="N100" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="79" t="n">
-        <v>4816.246</v>
+        <v>39943.203</v>
       </c>
       <c r="P100" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q100" s="80" t="n">
-        <v>166</v>
+        <v>369</v>
       </c>
       <c r="R100" s="47" t="n">
         <v>23</v>
       </c>
       <c r="S100" s="66" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B101" s="76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C101" s="77" t="n">
         <v>2020</v>
@@ -23885,199 +24023,1656 @@
         <v>44104</v>
       </c>
       <c r="F101" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G101" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H101" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I101" s="79" t="n">
-        <v>1627.205</v>
+        <v>22001.236</v>
       </c>
       <c r="J101" s="79" t="n">
-        <v>493.122</v>
+        <v>7580.021</v>
       </c>
       <c r="K101" s="79" t="n">
-        <v>194271000</v>
+        <v>3405156000</v>
       </c>
       <c r="L101" s="80" t="n">
-        <v>2.39</v>
+        <v>5.6</v>
       </c>
       <c r="M101" s="79" t="n">
-        <v>81.324</v>
+        <v>608.5115</v>
       </c>
       <c r="N101" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O101" s="79" t="n">
-        <v>4634.348</v>
+        <v>35469.351</v>
       </c>
       <c r="P101" s="80"/>
       <c r="Q101" s="80" t="n">
-        <v>158.5</v>
+        <v>265.5</v>
       </c>
       <c r="R101" s="47" t="n">
         <v>24</v>
       </c>
       <c r="S101" s="66" t="s">
-        <v>331</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B102" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="C102" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D102" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" s="78" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F102" s="76" t="s">
+        <v>205</v>
+      </c>
+      <c r="G102" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="H102" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I102" s="79"/>
+      <c r="J102" s="79"/>
+      <c r="K102" s="79"/>
+      <c r="L102" s="80" t="n">
+        <v>99.01</v>
+      </c>
+      <c r="M102" s="79"/>
+      <c r="N102" s="79"/>
+      <c r="O102" s="79"/>
+      <c r="P102" s="80"/>
+      <c r="Q102" s="80"/>
+      <c r="R102" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="66" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="81" t="s">
-        <v>332</v>
+      <c r="A103" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B103" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="C103" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D103" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" s="78" t="n">
+        <v>46203</v>
+      </c>
+      <c r="F103" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G103" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H103" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I103" s="79" t="n">
+        <v>22443.411</v>
+      </c>
+      <c r="J103" s="79" t="n">
+        <v>14589.612</v>
+      </c>
+      <c r="K103" s="79" t="n">
+        <v>10368072000</v>
+      </c>
+      <c r="L103" s="80" t="n">
+        <v>108.93</v>
+      </c>
+      <c r="M103" s="79" t="n">
+        <v>96.3654</v>
+      </c>
+      <c r="N103" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="79" t="n">
+        <v>23288.098</v>
+      </c>
+      <c r="P103" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="80" t="n">
+        <v>1615</v>
+      </c>
+      <c r="R103" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" s="66" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="42" t="s">
-        <v>333</v>
+      <c r="A104" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B104" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="C104" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D104" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="78" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F104" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G104" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H104" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I104" s="79" t="n">
+        <v>13182.608</v>
+      </c>
+      <c r="J104" s="79" t="n">
+        <v>7791.357</v>
+      </c>
+      <c r="K104" s="79" t="n">
+        <v>5466357000</v>
+      </c>
+      <c r="L104" s="80" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="M104" s="79" t="n">
+        <v>96.3552</v>
+      </c>
+      <c r="N104" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="79" t="n">
+        <v>14500.386</v>
+      </c>
+      <c r="P104" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="80" t="n">
+        <v>847</v>
+      </c>
+      <c r="R104" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S104" s="66" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="82" t="s">
-        <v>334</v>
-      </c>
-      <c r="C105" s="24" t="s">
-        <v>335</v>
+      <c r="A105" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B105" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C105" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D105" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" s="78" t="n">
+        <v>46022</v>
+      </c>
+      <c r="F105" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G105" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H105" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I105" s="79" t="n">
+        <v>4806.69</v>
+      </c>
+      <c r="J105" s="79" t="n">
+        <v>1597.288</v>
+      </c>
+      <c r="K105" s="79" t="n">
+        <v>870716000</v>
+      </c>
+      <c r="L105" s="80" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M105" s="79" t="n">
+        <v>96.0407</v>
+      </c>
+      <c r="N105" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="79" t="n">
+        <v>8940.787</v>
+      </c>
+      <c r="P105" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="80" t="n">
+        <v>576</v>
+      </c>
+      <c r="R105" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S105" s="66" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="82" t="s">
-        <v>336</v>
-      </c>
-      <c r="C106" s="24" t="s">
-        <v>335</v>
+      <c r="A106" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B106" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="C106" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D106" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" s="78" t="n">
+        <v>45930</v>
+      </c>
+      <c r="F106" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G106" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H106" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I106" s="79" t="n">
+        <v>3807.401</v>
+      </c>
+      <c r="J106" s="79" t="n">
+        <v>1248.818</v>
+      </c>
+      <c r="K106" s="79" t="n">
+        <v>643038000</v>
+      </c>
+      <c r="L106" s="80" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M106" s="79" t="n">
+        <v>95.3452</v>
+      </c>
+      <c r="N106" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="79" t="n">
+        <v>7932.37</v>
+      </c>
+      <c r="P106" s="80" t="n">
+        <v>9.37723774</v>
+      </c>
+      <c r="Q106" s="80" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="R106" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S106" s="66" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="82" t="s">
-        <v>337</v>
-      </c>
-      <c r="C107" s="24" t="s">
-        <v>335</v>
+      <c r="A107" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B107" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="C107" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D107" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="78" t="n">
+        <v>45838</v>
+      </c>
+      <c r="F107" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G107" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H107" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I107" s="79" t="n">
+        <v>3028.429</v>
+      </c>
+      <c r="J107" s="79" t="n">
+        <v>785.089</v>
+      </c>
+      <c r="K107" s="79" t="n">
+        <v>185349000</v>
+      </c>
+      <c r="L107" s="80" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M107" s="79" t="n">
+        <v>91.6411</v>
+      </c>
+      <c r="N107" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="79" t="n">
+        <v>7184.405</v>
+      </c>
+      <c r="P107" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="80" t="n">
+        <v>237</v>
+      </c>
+      <c r="R107" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S107" s="66" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="82" t="s">
-        <v>338</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>335</v>
+      <c r="A108" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B108" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="C108" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D108" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="78" t="n">
+        <v>45747</v>
+      </c>
+      <c r="F108" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G108" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H108" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I108" s="79" t="n">
+        <v>2618.742</v>
+      </c>
+      <c r="J108" s="79" t="n">
+        <v>800.733</v>
+      </c>
+      <c r="K108" s="79" t="n">
+        <v>336540000</v>
+      </c>
+      <c r="L108" s="80" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M108" s="79" t="n">
+        <v>91.5746</v>
+      </c>
+      <c r="N108" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="79" t="n">
+        <v>7854.351</v>
+      </c>
+      <c r="P108" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="80" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="R108" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S108" s="66" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="82" t="s">
-        <v>339</v>
-      </c>
-      <c r="C109" s="24" t="s">
-        <v>335</v>
+      <c r="A109" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B109" s="76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C109" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D109" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" s="78" t="n">
+        <v>45657</v>
+      </c>
+      <c r="F109" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G109" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H109" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I109" s="79" t="n">
+        <v>2228.005</v>
+      </c>
+      <c r="J109" s="79" t="n">
+        <v>648.956</v>
+      </c>
+      <c r="K109" s="79" t="n">
+        <v>271532000</v>
+      </c>
+      <c r="L109" s="80" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M109" s="79" t="n">
+        <v>91.4561</v>
+      </c>
+      <c r="N109" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="79" t="n">
+        <v>7491.143</v>
+      </c>
+      <c r="P109" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="80" t="n">
+        <v>218</v>
+      </c>
+      <c r="R109" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="S109" s="66" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="82" t="s">
-        <v>340</v>
-      </c>
-      <c r="C110" s="24" t="s">
-        <v>341</v>
+      <c r="A110" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B110" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C110" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D110" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" s="78" t="n">
+        <v>45565</v>
+      </c>
+      <c r="F110" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G110" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H110" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I110" s="79" t="n">
+        <v>2321.419</v>
+      </c>
+      <c r="J110" s="79" t="n">
+        <v>658.433</v>
+      </c>
+      <c r="K110" s="79" t="n">
+        <v>188620000</v>
+      </c>
+      <c r="L110" s="80" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M110" s="79" t="n">
+        <v>91.3372</v>
+      </c>
+      <c r="N110" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="79" t="n">
+        <v>7196.228</v>
+      </c>
+      <c r="P110" s="80" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q110" s="80" t="n">
+        <v>282</v>
+      </c>
+      <c r="R110" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="S110" s="66" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="82" t="s">
-        <v>342</v>
-      </c>
-      <c r="C111" s="24" t="s">
-        <v>341</v>
+      <c r="A111" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B111" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="C111" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D111" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="78" t="n">
+        <v>45473</v>
+      </c>
+      <c r="F111" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G111" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H111" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I111" s="79" t="n">
+        <v>2190.229</v>
+      </c>
+      <c r="J111" s="79" t="n">
+        <v>759.289</v>
+      </c>
+      <c r="K111" s="79" t="n">
+        <v>294050000</v>
+      </c>
+      <c r="L111" s="80" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M111" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N111" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="79" t="n">
+        <v>6803.334</v>
+      </c>
+      <c r="P111" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="80" t="n">
+        <v>302</v>
+      </c>
+      <c r="R111" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="S111" s="66" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="82" t="s">
-        <v>343</v>
-      </c>
-      <c r="C112" s="25" t="s">
+      <c r="A112" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B112" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="C112" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D112" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="78" t="n">
+        <v>45382</v>
+      </c>
+      <c r="F112" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G112" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H112" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I112" s="79" t="n">
+        <v>2175.989</v>
+      </c>
+      <c r="J112" s="79" t="n">
+        <v>758.571</v>
+      </c>
+      <c r="K112" s="79" t="n">
+        <v>351970000</v>
+      </c>
+      <c r="L112" s="80" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M112" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N112" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="79" t="n">
+        <v>7398.652</v>
+      </c>
+      <c r="P112" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="80" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="R112" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S112" s="66" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="82" t="s">
+      <c r="A113" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B113" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="C113" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D113" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" s="78" t="n">
+        <v>45291</v>
+      </c>
+      <c r="F113" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G113" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H113" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I113" s="79" t="n">
+        <v>2130.049</v>
+      </c>
+      <c r="J113" s="79" t="n">
+        <v>707.384</v>
+      </c>
+      <c r="K113" s="79" t="n">
+        <v>262238000</v>
+      </c>
+      <c r="L113" s="80" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M113" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N113" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="79" t="n">
+        <v>7036.917</v>
+      </c>
+      <c r="P113" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="80" t="n">
+        <v>312</v>
+      </c>
+      <c r="R113" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="S113" s="66" t="s">
         <v>345</v>
       </c>
-      <c r="C113" s="24" t="s">
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C114" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D114" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="78" t="n">
+        <v>45199</v>
+      </c>
+      <c r="F114" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G114" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H114" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I114" s="79" t="n">
+        <v>1993.007</v>
+      </c>
+      <c r="J114" s="79" t="n">
+        <v>687.513</v>
+      </c>
+      <c r="K114" s="79" t="n">
+        <v>306457000</v>
+      </c>
+      <c r="L114" s="80" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M114" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N114" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="79" t="n">
+        <v>6756.961</v>
+      </c>
+      <c r="P114" s="80" t="n">
+        <v>13.78192729</v>
+      </c>
+      <c r="Q114" s="80" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="R114" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="S114" s="66" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="82" t="s">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B115" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="C115" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D115" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" s="78" t="n">
+        <v>45107</v>
+      </c>
+      <c r="F115" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G115" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H115" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I115" s="79" t="n">
+        <v>1930.516</v>
+      </c>
+      <c r="J115" s="79" t="n">
+        <v>636.105</v>
+      </c>
+      <c r="K115" s="79" t="n">
+        <v>230718000</v>
+      </c>
+      <c r="L115" s="80" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M115" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N115" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="79" t="n">
+        <v>6433.521</v>
+      </c>
+      <c r="P115" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" s="80" t="n">
+        <v>324</v>
+      </c>
+      <c r="R115" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="S115" s="66" t="s">
         <v>347</v>
       </c>
-      <c r="C114" s="24" t="s">
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B116" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C116" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D116" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="78" t="n">
+        <v>45016</v>
+      </c>
+      <c r="F116" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G116" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H116" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I116" s="79" t="n">
+        <v>2260.206</v>
+      </c>
+      <c r="J116" s="79" t="n">
+        <v>814.91</v>
+      </c>
+      <c r="K116" s="79" t="n">
+        <v>348203000</v>
+      </c>
+      <c r="L116" s="80" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M116" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N116" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="79" t="n">
+        <v>7382.85</v>
+      </c>
+      <c r="P116" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="80" t="n">
+        <v>314</v>
+      </c>
+      <c r="R116" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="S116" s="66" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="82" t="s">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B117" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="C117" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D117" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="78" t="n">
+        <v>44926</v>
+      </c>
+      <c r="F117" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G117" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H117" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I117" s="79" t="n">
+        <v>2286.572</v>
+      </c>
+      <c r="J117" s="79" t="n">
+        <v>860.807</v>
+      </c>
+      <c r="K117" s="79" t="n">
+        <v>385061000</v>
+      </c>
+      <c r="L117" s="80" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="M117" s="79" t="n">
+        <v>86.5531</v>
+      </c>
+      <c r="N117" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="79" t="n">
+        <v>7012.867</v>
+      </c>
+      <c r="P117" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="80" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R117" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="S117" s="66" t="s">
         <v>349</v>
       </c>
-      <c r="C115" s="25" t="s">
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B118" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C118" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D118" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" s="78" t="n">
+        <v>44834</v>
+      </c>
+      <c r="F118" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G118" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H118" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I118" s="79" t="n">
+        <v>2560.341</v>
+      </c>
+      <c r="J118" s="79" t="n">
+        <v>914.902</v>
+      </c>
+      <c r="K118" s="79" t="n">
+        <v>542661000</v>
+      </c>
+      <c r="L118" s="80" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M118" s="79" t="n">
+        <v>86.4706</v>
+      </c>
+      <c r="N118" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="79" t="n">
+        <v>6611.975</v>
+      </c>
+      <c r="P118" s="80" t="n">
+        <v>11.5240749</v>
+      </c>
+      <c r="Q118" s="80" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="R118" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="S118" s="66" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="82" t="s">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B119" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="C119" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D119" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" s="78" t="n">
+        <v>44742</v>
+      </c>
+      <c r="F119" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G119" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H119" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I119" s="79" t="n">
+        <v>2866.579</v>
+      </c>
+      <c r="J119" s="79" t="n">
+        <v>947.502</v>
+      </c>
+      <c r="K119" s="79" t="n">
+        <v>536500000</v>
+      </c>
+      <c r="L119" s="80" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M119" s="79" t="n">
+        <v>83.895</v>
+      </c>
+      <c r="N119" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="79" t="n">
+        <v>6043.861</v>
+      </c>
+      <c r="P119" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="80" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="R119" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="S119" s="66" t="s">
         <v>351</v>
       </c>
-      <c r="C116" s="25" t="s">
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B120" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="C120" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D120" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="78" t="n">
+        <v>44651</v>
+      </c>
+      <c r="F120" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G120" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H120" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I120" s="79" t="n">
+        <v>2589.737</v>
+      </c>
+      <c r="J120" s="79" t="n">
+        <v>735.407</v>
+      </c>
+      <c r="K120" s="79" t="n">
+        <v>385967000</v>
+      </c>
+      <c r="L120" s="80" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M120" s="79" t="n">
+        <v>83.7225</v>
+      </c>
+      <c r="N120" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="79" t="n">
+        <v>6458.201</v>
+      </c>
+      <c r="P120" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="80" t="n">
+        <v>215</v>
+      </c>
+      <c r="R120" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="S120" s="66" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="82" t="s">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B121" s="76" t="s">
+        <v>247</v>
+      </c>
+      <c r="C121" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D121" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" s="78" t="n">
+        <v>44561</v>
+      </c>
+      <c r="F121" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G121" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H121" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I121" s="79" t="n">
+        <v>2396.847</v>
+      </c>
+      <c r="J121" s="79" t="n">
+        <v>677.529</v>
+      </c>
+      <c r="K121" s="79" t="n">
+        <v>290253000</v>
+      </c>
+      <c r="L121" s="80" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M121" s="79" t="n">
+        <v>82.668</v>
+      </c>
+      <c r="N121" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="79" t="n">
+        <v>5960.989</v>
+      </c>
+      <c r="P121" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="80" t="n">
+        <v>204</v>
+      </c>
+      <c r="R121" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="S121" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="C117" s="24" t="s">
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B122" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="C122" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D122" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="78" t="n">
+        <v>44469</v>
+      </c>
+      <c r="F122" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G122" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H122" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I122" s="79" t="n">
+        <v>2973.845</v>
+      </c>
+      <c r="J122" s="79" t="n">
+        <v>975.336</v>
+      </c>
+      <c r="K122" s="79" t="n">
+        <v>533714000</v>
+      </c>
+      <c r="L122" s="80" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M122" s="79" t="n">
+        <v>82.628</v>
+      </c>
+      <c r="N122" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="79" t="n">
+        <v>5663.586</v>
+      </c>
+      <c r="P122" s="80" t="n">
+        <v>6.69560253</v>
+      </c>
+      <c r="Q122" s="80" t="n">
+        <v>182</v>
+      </c>
+      <c r="R122" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="S122" s="66" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="82" t="s">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B123" s="76" t="s">
+        <v>251</v>
+      </c>
+      <c r="C123" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D123" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="78" t="n">
+        <v>44377</v>
+      </c>
+      <c r="F123" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G123" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H123" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I123" s="79" t="n">
+        <v>2885.046</v>
+      </c>
+      <c r="J123" s="79" t="n">
+        <v>888.15</v>
+      </c>
+      <c r="K123" s="79" t="n">
+        <v>477358000</v>
+      </c>
+      <c r="L123" s="80" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="M123" s="79" t="n">
+        <v>82.516</v>
+      </c>
+      <c r="N123" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="79" t="n">
+        <v>5668.615</v>
+      </c>
+      <c r="P123" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="80" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="R123" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="S123" s="66" t="s">
         <v>355</v>
       </c>
-      <c r="C118" s="24" t="s">
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B124" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="C124" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D124" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="78" t="n">
+        <v>44286</v>
+      </c>
+      <c r="F124" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G124" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H124" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I124" s="79" t="n">
+        <v>1939.92</v>
+      </c>
+      <c r="J124" s="79" t="n">
+        <v>551.203</v>
+      </c>
+      <c r="K124" s="79" t="n">
+        <v>259563000</v>
+      </c>
+      <c r="L124" s="80" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M124" s="79" t="n">
+        <v>82.459</v>
+      </c>
+      <c r="N124" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="79" t="n">
+        <v>5182.897</v>
+      </c>
+      <c r="P124" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="80" t="n">
+        <v>170</v>
+      </c>
+      <c r="R124" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="S124" s="66" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="82" t="s">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B125" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="C125" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D125" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" s="78" t="n">
+        <v>44196</v>
+      </c>
+      <c r="F125" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G125" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H125" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I125" s="79" t="n">
+        <v>1575.49</v>
+      </c>
+      <c r="J125" s="79" t="n">
+        <v>458.968</v>
+      </c>
+      <c r="K125" s="79" t="n">
+        <v>175456000</v>
+      </c>
+      <c r="L125" s="80" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M125" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N125" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="79" t="n">
+        <v>4816.246</v>
+      </c>
+      <c r="P125" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="80" t="n">
+        <v>166</v>
+      </c>
+      <c r="R125" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="S125" s="66" t="s">
         <v>357</v>
       </c>
-      <c r="C119" s="25" t="s">
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B126" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="C126" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D126" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" s="78" t="n">
+        <v>44104</v>
+      </c>
+      <c r="F126" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="G126" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="H126" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="I126" s="79" t="n">
+        <v>1627.205</v>
+      </c>
+      <c r="J126" s="79" t="n">
+        <v>493.122</v>
+      </c>
+      <c r="K126" s="79" t="n">
+        <v>194271000</v>
+      </c>
+      <c r="L126" s="80" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M126" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N126" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="79" t="n">
+        <v>4634.348</v>
+      </c>
+      <c r="P126" s="80"/>
+      <c r="Q126" s="80" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="R126" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="S126" s="66" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="82" t="s">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="81" t="s">
         <v>359</v>
       </c>
-      <c r="C120" s="24" t="s">
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="42" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="82" t="s">
+        <v>361</v>
+      </c>
+      <c r="C130" s="24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="82" t="s">
+        <v>363</v>
+      </c>
+      <c r="C131" s="24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="82" t="s">
+        <v>364</v>
+      </c>
+      <c r="C132" s="24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="82" t="s">
+        <v>365</v>
+      </c>
+      <c r="C133" s="24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="82" t="s">
+        <v>366</v>
+      </c>
+      <c r="C134" s="24" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="82" t="s">
+        <v>367</v>
+      </c>
+      <c r="C135" s="24" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="82" t="s">
+        <v>369</v>
+      </c>
+      <c r="C136" s="24" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="82" t="s">
+        <v>370</v>
+      </c>
+      <c r="C137" s="25" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="82" t="s">
+        <v>372</v>
+      </c>
+      <c r="C138" s="24" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="82" t="s">
+        <v>374</v>
+      </c>
+      <c r="C139" s="24" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="82" t="s">
+        <v>376</v>
+      </c>
+      <c r="C140" s="25" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="82" t="s">
+        <v>378</v>
+      </c>
+      <c r="C141" s="25" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="82" t="s">
+        <v>380</v>
+      </c>
+      <c r="C142" s="24" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="82" t="s">
+        <v>382</v>
+      </c>
+      <c r="C143" s="24" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="82" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="25" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="82" t="s">
+        <v>386</v>
+      </c>
+      <c r="C145" s="24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="82" t="s">
-        <v>360</v>
-      </c>
-      <c r="C121" s="24" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="24" t="s">
-        <v>362</v>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="82" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="24" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="24" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S101"/>
+  <autoFilter ref="A1:S126"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -24094,7 +25689,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -24109,19 +25704,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24186,27 +25781,47 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="76" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>353.215</v>
+        <v>33.70448</v>
       </c>
       <c r="C5" s="80" t="n">
-        <v>194.82417</v>
+        <v>35.32413</v>
       </c>
       <c r="D5" s="78" t="n">
         <v>46387</v>
       </c>
       <c r="E5" s="77" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F5" s="78" t="n">
         <v>46267</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>368</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="80" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="C6" s="80" t="n">
+        <v>165.48225</v>
+      </c>
+      <c r="D6" s="78" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E6" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="78" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -7022,7 +7022,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF1F9F3"/>
+          <fgColor rgb="FFF2FAF4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7030,7 +7030,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFAFDFB"/>
+          <fgColor rgb="FFF9FDFA"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7118,7 +7118,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF6DC384"/>
+          <fgColor rgb="FFF1F9F3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7126,7 +7126,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF9FDFA"/>
+          <fgColor rgb="FF6DC384"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7869,14 +7869,14 @@
         <v>167</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D2" s="78"/>
       <c r="E2" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7884,14 +7884,14 @@
         <v>171</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>518</v>
+        <v>477.5</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D3" s="78"/>
       <c r="E3" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7899,14 +7899,14 @@
         <v>179</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7914,14 +7914,14 @@
         <v>183</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D5" s="78"/>
       <c r="E5" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7929,14 +7929,14 @@
         <v>176</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>1420</v>
+        <v>1345</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
   </sheetData>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>130.79132890411</v>
+        <v>130.885810246575</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8166,15 +8166,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>27.6425591098748</v>
+        <v>27.7005099675475</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>24.5796544152119</v>
+        <v>24.6311840890383</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.2351538132056</v>
+        <v>18.2601918076336</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8182,11 +8182,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>0.519370204697048</v>
+        <v>0.520459031121989</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.569190860318125</v>
+        <v>0.569972394586226</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.0092243606624738</v>
+        <v>0.00920506283682008</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>518</v>
+        <v>477.5</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>85.63905</v>
+        <v>88.4262504109589</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8348,19 +8348,19 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>19.0791896869245</v>
+        <v>17.5874769797422</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>10.9057567868861</v>
+        <v>10.0530866133941</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>6.04864252931344</v>
+        <v>5.39998018440033</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>0.471707381194523</v>
+        <v>0.484757826636219</v>
       </c>
       <c r="N3" s="51" t="str">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(J3)),I3&lt;Config!$B$6),"N/M",J3/(I3*100)),"N/M"))</f>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.128228702166929</v>
+        <v>0.111395420304429</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="AH3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(AD3&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/AD3),"N/M"))</f>
-        <v>0.695734066852749</v>
+        <v>0.712915003319671</v>
       </c>
       <c r="AI3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,0),""))</f>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1420</v>
+        <v>1345</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>222.759318493151</v>
+        <v>246.463920054795</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8530,23 +8530,23 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>7.77869076965215</v>
+        <v>7.36784442618461</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>5.16946375914668</v>
+        <v>4.89642870144527</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>6.37459303433657</v>
+        <v>5.45718821522021</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>-0.512857668531057</v>
+        <v>-0.44842611440624</v>
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.00486734143037023</v>
+        <v>0.0046102635379211</v>
       </c>
       <c r="O4" s="51" t="str">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00660368854929578</v>
+        <v>0.00697192397026022</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="AH4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(AD4&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/AD4),"N/M"))</f>
-        <v>1.40566766680559</v>
+        <v>1.46159230182731</v>
       </c>
       <c r="AI4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,0),""))</f>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="AL4" s="47" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A4,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.64497863013699</v>
+        <v>7.65450780821918</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8712,15 +8712,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>131.553398058252</v>
+        <v>127.427184466019</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>115.459419848369</v>
+        <v>111.837998930616</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>70.8962086386222</v>
+        <v>68.5870356597286</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8728,11 +8728,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>2.13669531878053</v>
+        <v>2.06967719992579</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>1.08242101007701</v>
+        <v>1.04716528348383</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00483497514760148</v>
+        <v>0.00499153624761905</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>34.7916423287671</v>
+        <v>34.7960797260274</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8894,15 +8894,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>18.9396581792815</v>
+        <v>18.381583536798</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>16.8462305240667</v>
+        <v>16.3498406743704</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>15.6071965464828</v>
+        <v>15.1453843119518</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="Q6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(P6=0,"不配息",P6/D6),""))</f>
-        <v>0.0515653775322284</v>
+        <v>0.0531309297912714</v>
       </c>
       <c r="R6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12049,27 +12049,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>27.6425591098748</v>
+        <v>27.7005099675475</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.2351538132056</v>
+        <v>18.2601918076336</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>0.519370204697048</v>
+        <v>0.520459031121989</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.569190860318125</v>
+        <v>0.569972394586226</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.0092243606624738</v>
+        <v>0.00920506283682008</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -12167,15 +12167,15 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>518</v>
+        <v>477.5</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>19.0791896869245</v>
+        <v>17.5874769797422</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>6.04864252931344</v>
+        <v>5.39998018440033</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.128228702166929</v>
+        <v>0.111395420304429</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -12251,7 +12251,7 @@
       </c>
       <c r="Y4" s="19" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!AH$3)</f>
-        <v>0.695734066852749</v>
+        <v>0.712915003319671</v>
       </c>
       <c r="Z4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!AI$3)</f>
@@ -12285,19 +12285,19 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>1420</v>
+        <v>1345</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>7.77869076965215</v>
+        <v>7.36784442618461</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>6.37459303433657</v>
+        <v>5.45718821522021</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.00486734143037023</v>
+        <v>0.0046102635379211</v>
       </c>
       <c r="H5" s="17" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00660368854929578</v>
+        <v>0.00697192397026022</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="Y5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AH$4)</f>
-        <v>1.40566766680559</v>
+        <v>1.46159230182731</v>
       </c>
       <c r="Z5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!AI$4)</f>
@@ -12403,27 +12403,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>131.553398058252</v>
+        <v>127.427184466019</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>70.8962086386222</v>
+        <v>68.5870356597286</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>2.13669531878053</v>
+        <v>2.06967719992579</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>1.08242101007701</v>
+        <v>1.04716528348383</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00483497514760148</v>
+        <v>0.00499153624761905</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12521,15 +12521,15 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>18.9396581792815</v>
+        <v>18.381583536798</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>15.6071965464828</v>
+        <v>15.1453843119518</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
-        <v>0.0515653775322284</v>
+        <v>0.0531309297912714</v>
       </c>
       <c r="J7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!R$6)</f>
@@ -16793,7 +16793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C289EDEC-9D88-4526-8C35-35699E266173}</x14:id>
+          <x14:id>{494B4171-B19A-454C-A8CD-3EA767289239}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16924,7 +16924,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C289EDEC-9D88-4526-8C35-35699E266173}">
+          <x14:cfRule type="dataBar" id="{494B4171-B19A-454C-A8CD-3EA767289239}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17027,11 +17027,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46267</v>
+        <v>-46268</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="J4" s="72" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -17069,11 +17069,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46267</v>
+        <v>-46268</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="J5" s="72" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -17111,11 +17111,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46267</v>
+        <v>-46268</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="J6" s="72" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -17153,11 +17153,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46267</v>
+        <v>-46268</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="J7" s="72" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -17195,11 +17195,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46267</v>
+        <v>-46268</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="J8" s="72" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -25736,7 +25736,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25744,10 +25744,10 @@
         <v>171</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>65.04435</v>
+        <v>66.6506</v>
       </c>
       <c r="C3" s="80" t="n">
-        <v>95.72625</v>
+        <v>98.96</v>
       </c>
       <c r="D3" s="78" t="n">
         <v>46387</v>
@@ -25756,7 +25756,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25776,7 +25776,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25796,7 +25796,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25804,19 +25804,19 @@
         <v>176</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>339.7</v>
+        <v>353.215</v>
       </c>
       <c r="C6" s="80" t="n">
-        <v>165.48225</v>
+        <v>194.82417</v>
       </c>
       <c r="D6" s="78" t="n">
         <v>46387</v>
       </c>
       <c r="E6" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -7869,14 +7869,14 @@
         <v>167</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>2390</v>
+        <v>2410</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D2" s="78"/>
       <c r="E2" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7884,14 +7884,14 @@
         <v>171</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>477.5</v>
+        <v>496</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D3" s="78"/>
       <c r="E3" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7899,14 +7899,14 @@
         <v>179</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7914,14 +7914,14 @@
         <v>183</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D5" s="78"/>
       <c r="E5" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7929,14 +7929,14 @@
         <v>176</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>1345</v>
+        <v>1360</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
   </sheetData>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2390</v>
+        <v>2410</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>130.885810246575</v>
+        <v>130.980291589041</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8166,15 +8166,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>27.7005099675475</v>
+        <v>27.9323133982383</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>24.6311840890383</v>
+        <v>24.8373027843441</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.2601918076336</v>
+        <v>18.3997147262546</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8182,11 +8182,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>0.520459031121989</v>
+        <v>0.524814336821755</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.569972394586226</v>
+        <v>0.574327453550767</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00920506283682008</v>
+        <v>0.00912867227385892</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8286,7 +8286,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>477.5</v>
+        <v>496</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>88.4262504109589</v>
+        <v>88.5147693150685</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8348,15 +8348,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>17.5874769797422</v>
+        <v>18.268876611418</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>10.0530866133941</v>
+        <v>10.4425779272114</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>5.39998018440033</v>
+        <v>5.60358462026249</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.111395420304429</v>
+        <v>0.115595547144567</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1345</v>
+        <v>1360</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>246.463920054795</v>
+        <v>246.029972575342</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8530,15 +8530,15 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>7.36784442618461</v>
+        <v>7.45001369487812</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>4.89642870144527</v>
+        <v>4.95103571298555</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>5.45718821522021</v>
+        <v>5.52778178107354</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.0046102635379211</v>
+        <v>0.00466167911641093</v>
       </c>
       <c r="O4" s="51" t="str">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
@@ -8558,7 +8558,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00697192397026022</v>
+        <v>0.00689502775</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.65450780821918</v>
+        <v>7.66403698630137</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8712,15 +8712,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>127.427184466019</v>
+        <v>128.155339805825</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>111.837998930616</v>
+        <v>112.477073210219</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>68.5870356597286</v>
+        <v>68.8931957066155</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8728,11 +8728,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>2.06967719992579</v>
+        <v>2.08150392678251</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>1.04716528348383</v>
+        <v>1.05183963876403</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00499153624761905</v>
+        <v>0.00496317524621212</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>34.7960797260274</v>
+        <v>34.8005171232877</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8894,15 +8894,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>18.381583536798</v>
+        <v>18.2769445413324</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>16.3498406743704</v>
+        <v>16.2567675775524</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>15.1453843119518</v>
+        <v>15.0572475157087</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="Q6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(P6=0,"不配息",P6/D6),""))</f>
-        <v>0.0531309297912714</v>
+        <v>0.0534351145038168</v>
       </c>
       <c r="R6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12049,27 +12049,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>2390</v>
+        <v>2410</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>27.7005099675475</v>
+        <v>27.9323133982383</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.2601918076336</v>
+        <v>18.3997147262546</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>0.520459031121989</v>
+        <v>0.524814336821755</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.569972394586226</v>
+        <v>0.574327453550767</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00920506283682008</v>
+        <v>0.00912867227385892</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -12167,15 +12167,15 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>477.5</v>
+        <v>496</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>17.5874769797422</v>
+        <v>18.268876611418</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>5.39998018440033</v>
+        <v>5.60358462026249</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.111395420304429</v>
+        <v>0.115595547144567</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -12285,19 +12285,19 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>1345</v>
+        <v>1360</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>7.36784442618461</v>
+        <v>7.45001369487812</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>5.45718821522021</v>
+        <v>5.52778178107354</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.0046102635379211</v>
+        <v>0.00466167911641093</v>
       </c>
       <c r="H5" s="17" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
@@ -12305,7 +12305,7 @@
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00697192397026022</v>
+        <v>0.00689502775</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12403,27 +12403,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>127.427184466019</v>
+        <v>128.155339805825</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>68.5870356597286</v>
+        <v>68.8931957066155</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>2.06967719992579</v>
+        <v>2.08150392678251</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>1.04716528348383</v>
+        <v>1.05183963876403</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00499153624761905</v>
+        <v>0.00496317524621212</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12521,15 +12521,15 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>18.381583536798</v>
+        <v>18.2769445413324</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>15.1453843119518</v>
+        <v>15.0572475157087</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
-        <v>0.0531309297912714</v>
+        <v>0.0534351145038168</v>
       </c>
       <c r="J7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!R$6)</f>
@@ -16793,7 +16793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{494B4171-B19A-454C-A8CD-3EA767289239}</x14:id>
+          <x14:id>{B5BAE14D-27E4-43F0-87A6-ABF71F7835C7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16924,7 +16924,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{494B4171-B19A-454C-A8CD-3EA767289239}">
+          <x14:cfRule type="dataBar" id="{B5BAE14D-27E4-43F0-87A6-ABF71F7835C7}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17027,11 +17027,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46268</v>
+        <v>-46269</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="J4" s="72" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -17069,11 +17069,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46268</v>
+        <v>-46269</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="J5" s="72" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -17111,11 +17111,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46268</v>
+        <v>-46269</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="J6" s="72" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -17153,11 +17153,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46268</v>
+        <v>-46269</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="J7" s="72" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -17195,11 +17195,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46268</v>
+        <v>-46269</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="J8" s="72" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -25736,7 +25736,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25756,7 +25756,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25776,7 +25776,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25796,7 +25796,7 @@
         <v>14</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25816,7 +25816,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dashboard!$A$2:$AC$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$126</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$151</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="467">
   <si>
     <r>
       <rPr>
@@ -3869,6 +3869,33 @@
     <t xml:space="preserve">聯詠</t>
   </si>
   <si>
+    <t xml:space="preserve">3665</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">貿聯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-KY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">其他電子業</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4530,6 +4557,81 @@
   </si>
   <si>
     <t xml:space="preserve">3034|24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3665|24</t>
   </si>
   <si>
     <t xml:space="preserve">5289|0</t>
@@ -6955,7 +7057,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="42">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7062,7 +7164,23 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFE7F5EB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF8BCF9D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F2E5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7118,6 +7236,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF80CA93"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF1F9F3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7142,6 +7268,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFDE2E2"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFE2F3E7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7151,6 +7285,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE8F6EB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFFFE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7837,7 +7979,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -7852,16 +7994,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>396</v>
+        <v>424</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7872,11 +8014,11 @@
         <v>2410</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="D2" s="78"/>
       <c r="E2" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7887,11 +8029,11 @@
         <v>496</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="D3" s="78"/>
       <c r="E3" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7902,11 +8044,11 @@
         <v>528</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7917,26 +8059,41 @@
         <v>524</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="D5" s="78"/>
       <c r="E5" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>1360</v>
+        <v>2145</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="80" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C7" s="78" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78" t="n">
+        <v>46272</v>
       </c>
     </row>
   </sheetData>
@@ -8004,16 +8161,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -8022,13 +8179,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -8037,7 +8194,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -8046,16 +8203,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>407</v>
+        <v>435</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>408</v>
+        <v>436</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>410</v>
+        <v>438</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -8064,16 +8221,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>413</v>
+        <v>441</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>414</v>
+        <v>442</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -8082,7 +8239,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -8091,7 +8248,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>416</v>
+        <v>444</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -8100,7 +8257,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -8112,19 +8269,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8158,7 +8315,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>130.980291589041</v>
+        <v>131.263735616438</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8174,7 +8331,7 @@
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.3997147262546</v>
+        <v>18.3599833471309</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8186,7 +8343,7 @@
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.574327453550767</v>
+        <v>0.573087280964525</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8286,7 +8443,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8340,7 +8497,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>88.5147693150685</v>
+        <v>88.7803260273973</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8356,7 +8513,7 @@
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>5.60358462026249</v>
+        <v>5.58682336722819</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8368,7 +8525,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.115595547144567</v>
+        <v>0.115249781648616</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8468,7 +8625,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8522,7 +8679,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>246.029972575342</v>
+        <v>244.728130136986</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8538,7 +8695,7 @@
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>5.52778178107354</v>
+        <v>5.55718706810999</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8650,7 +8807,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8704,7 +8861,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.66403698630137</v>
+        <v>7.74777465753425</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8720,11 +8877,11 @@
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>68.8931957066155</v>
+        <v>68.1486005128649</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>0.65497812753633</v>
+        <v>0.662737738911773</v>
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
@@ -8732,7 +8889,7 @@
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>1.05183963876403</v>
+        <v>1.02828911817767</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8808,7 +8965,7 @@
       </c>
       <c r="AH5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(AD5&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/AD5),"N/M"))</f>
-        <v>0.265876622636104</v>
+        <v>0.266803878578997</v>
       </c>
       <c r="AI5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,0),""))</f>
@@ -8824,7 +8981,7 @@
       </c>
       <c r="AL5" s="47" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A5,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -8832,7 +8989,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8886,7 +9043,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>34.8005171232877</v>
+        <v>34.8138293150685</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8902,7 +9059,7 @@
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>15.0572475157087</v>
+        <v>15.0514898909209</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9014,7 +9171,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -9040,183 +9197,183 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="str">
         <f aca="false">IF(Tickers!A7="","",Tickers!A7)</f>
-        <v/>
+        <v>3665</v>
       </c>
       <c r="B7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A7,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>貿聯-KY</v>
       </c>
       <c r="C7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A7,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D7" s="51" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E7" s="48" t="str">
+        <v>2145</v>
+      </c>
+      <c r="E7" s="48" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="F7" s="51" t="str">
+        <v>82337.996</v>
+      </c>
+      <c r="F7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="G7" s="51" t="str">
+        <v>54.53</v>
+      </c>
+      <c r="G7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=0",Raw_Q!$R$2:$R$600,"&lt;=3"),""))</f>
-        <v/>
-      </c>
-      <c r="H7" s="51" t="str">
+        <v>59.76375</v>
+      </c>
+      <c r="H7" s="51" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v/>
-      </c>
-      <c r="I7" s="49" t="str">
+        <v>99.2946760273973</v>
+      </c>
+      <c r="I7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
-        <v/>
-      </c>
-      <c r="J7" s="52" t="str">
+        <v>0.574646260467803</v>
+      </c>
+      <c r="J7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(F7&lt;=0,"N/M",D7/F7),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="K7" s="52" t="str">
+        <v>39.3361452411517</v>
+      </c>
+      <c r="K7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(G7&lt;=0,"N/M",D7/G7),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="L7" s="52" t="str">
+        <v>35.8913220806927</v>
+      </c>
+      <c r="L7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(H7&lt;=0,"N/M",D7/H7),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="M7" s="49" t="str">
+        <v>21.6023666707785</v>
+      </c>
+      <c r="M7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v/>
-      </c>
-      <c r="N7" s="51" t="str">
+        <v>0.749526340295787</v>
+      </c>
+      <c r="N7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(J7)),I7&lt;Config!$B$6),"N/M",J7/(I7*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="O7" s="51" t="str">
+        <v>0.684527994824664</v>
+      </c>
+      <c r="O7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(L7)),M7&lt;Config!$B$6),"N/M",L7/(M7*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="P7" s="51" t="str">
+        <v>0.288213575819811</v>
+      </c>
+      <c r="P7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="49" t="str">
+        <v>10.50548249</v>
+      </c>
+      <c r="Q7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(P7=0,"不配息",P7/D7),""))</f>
-        <v/>
-      </c>
-      <c r="R7" s="49" t="str">
+        <v>0.00489766083449883</v>
+      </c>
+      <c r="R7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
-        <v/>
-      </c>
-      <c r="S7" s="49" t="str">
+        <v>0.196424031741944</v>
+      </c>
+      <c r="S7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="T7" s="49" t="str">
+        <v>0.374873740117713</v>
+      </c>
+      <c r="T7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,2)-1,""))</f>
-        <v/>
-      </c>
-      <c r="U7" s="49" t="str">
+        <v>0.115873258795717</v>
+      </c>
+      <c r="U7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,3)-1,""))</f>
-        <v/>
-      </c>
-      <c r="V7" s="68" t="str">
+        <v>0.0547870056790802</v>
+      </c>
+      <c r="V7" s="68" t="n">
         <f aca="false">IF($A7="","",IFERROR((T7-U7)*100,""))</f>
-        <v/>
+        <v>6.10862531166365</v>
       </c>
       <c r="W7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(IF(NOT(ISNUMBER(T7)),"",IF(T7&gt;0,IF(V7&gt;0,"成長且加速","成長但減速"),IF(V7&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
-        <v/>
-      </c>
-      <c r="X7" s="68" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="X7" s="68" t="n">
         <f aca="false">IF($A7="","",IFERROR((T7-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,6)-1))*100,""))</f>
-        <v/>
-      </c>
-      <c r="Y7" s="49" t="str">
+        <v>6.54698200053601</v>
+      </c>
+      <c r="Y7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="Z7" s="49" t="str">
+        <v>0.449715370018975</v>
+      </c>
+      <c r="Z7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/E7,""))</f>
-        <v/>
-      </c>
-      <c r="AA7" s="49" t="str">
+        <v>0.310848347584267</v>
+      </c>
+      <c r="AA7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v/>
-      </c>
-      <c r="AB7" s="50" t="str">
+        <v>0.279551522958118</v>
+      </c>
+      <c r="AB7" s="50" t="n">
         <f aca="false">IF($A7="","",IFERROR((Z7-AA7)*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AC7" s="50" t="str">
+        <v>312.968246261493</v>
+      </c>
+      <c r="AC7" s="50" t="n">
         <f aca="false">IF($A7="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AD7" s="51" t="str">
+        <v>-38.5940363433762</v>
+      </c>
+      <c r="AD7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
-      </c>
-      <c r="AE7" s="48" t="str">
+        <v>254.066067796332</v>
+      </c>
+      <c r="AE7" s="48" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600),""))</f>
-        <v/>
-      </c>
-      <c r="AF7" s="49" t="str">
+        <v>10634.496537</v>
+      </c>
+      <c r="AF7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))&lt;=0,"N/M",AE7/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))/2)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AG7" s="49" t="str">
+        <v>0.246843882201776</v>
+      </c>
+      <c r="AG7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(AVERAGE(AO7:AS7),""))</f>
-        <v/>
-      </c>
-      <c r="AH7" s="49" t="str">
+        <v>0.180759126269984</v>
+      </c>
+      <c r="AH7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(AD7&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/AD7),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AI7" s="51" t="str">
+        <v>0.258245623152622</v>
+      </c>
+      <c r="AI7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,0),""))</f>
-        <v/>
+        <v>18.74375</v>
       </c>
       <c r="AJ7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A7&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AK7" s="66" t="str">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A7&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AL7" s="47" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AL7" s="47" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A7,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AM7" s="67" t="str">
+        <v>2</v>
+      </c>
+      <c r="AM7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AN7" s="67" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AO7" s="49" t="str">
+        <v>46272</v>
+      </c>
+      <c r="AO7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AP7" s="49" t="str">
+        <v>0.246843882201776</v>
+      </c>
+      <c r="AP7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=5)*(Raw_Q!$R$2:$R$600&lt;=8)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,9))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AQ7" s="49" t="str">
+        <v>0.208536280060511</v>
+      </c>
+      <c r="AQ7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,9),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=9)*(Raw_Q!$R$2:$R$600&lt;=12)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,9)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,13))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AR7" s="49" t="str">
+        <v>0.115704213687219</v>
+      </c>
+      <c r="AR7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,13),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=13)*(Raw_Q!$R$2:$R$600&lt;=16)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,13)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,17))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AS7" s="49" t="str">
+        <v>0.151426557202254</v>
+      </c>
+      <c r="AS7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,17),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=17)*(Raw_Q!$R$2:$R$600&lt;=20)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,17)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,21))/2)),""))</f>
-        <v/>
+        <v>0.181284698198162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11769,7 +11926,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>423</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -11798,78 +11955,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -12057,7 +12214,7 @@
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.3997147262546</v>
+        <v>18.3599833471309</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
@@ -12065,7 +12222,7 @@
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.574327453550767</v>
+        <v>0.573087280964525</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
@@ -12175,7 +12332,7 @@
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>5.60358462026249</v>
+        <v>5.58682336722819</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -12183,7 +12340,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.115595547144567</v>
+        <v>0.115249781648616</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -12293,7 +12450,7 @@
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>5.52778178107354</v>
+        <v>5.55718706810999</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
@@ -12411,7 +12568,7 @@
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>68.8931957066155</v>
+        <v>68.1486005128649</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
@@ -12419,7 +12576,7 @@
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>1.05183963876403</v>
+        <v>1.02828911817767</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
@@ -12487,7 +12644,7 @@
       </c>
       <c r="Y6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AH$5)</f>
-        <v>0.265876622636104</v>
+        <v>0.266803878578997</v>
       </c>
       <c r="Z6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!AI$5)</f>
@@ -12529,7 +12686,7 @@
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>15.0572475157087</v>
+        <v>15.0514898909209</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
@@ -12627,119 +12784,119 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!A$7)</f>
-        <v/>
+        <v>3665</v>
       </c>
       <c r="B8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!B$7)</f>
-        <v/>
+        <v>貿聯-KY</v>
       </c>
       <c r="C8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!C$7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="17" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!D$7)</f>
-        <v/>
-      </c>
-      <c r="E8" s="18" t="str">
+        <v>2145</v>
+      </c>
+      <c r="E8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!J$7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="18" t="str">
+        <v>39.3361452411517</v>
+      </c>
+      <c r="F8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!L$7)</f>
-        <v/>
-      </c>
-      <c r="G8" s="17" t="str">
+        <v>21.6023666707785</v>
+      </c>
+      <c r="G8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!N$7)</f>
-        <v/>
-      </c>
-      <c r="H8" s="17" t="str">
+        <v>0.684527994824664</v>
+      </c>
+      <c r="H8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!O$7)</f>
-        <v/>
-      </c>
-      <c r="I8" s="19" t="str">
+        <v>0.288213575819811</v>
+      </c>
+      <c r="I8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!Q$7)</f>
-        <v/>
-      </c>
-      <c r="J8" s="19" t="str">
+        <v>0.00489766083449883</v>
+      </c>
+      <c r="J8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!R$7)</f>
-        <v/>
-      </c>
-      <c r="K8" s="19" t="str">
+        <v>0.196424031741944</v>
+      </c>
+      <c r="K8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!T$7)</f>
-        <v/>
-      </c>
-      <c r="L8" s="19" t="str">
+        <v>0.115873258795717</v>
+      </c>
+      <c r="L8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!U$7)</f>
-        <v/>
-      </c>
-      <c r="M8" s="20" t="str">
+        <v>0.0547870056790802</v>
+      </c>
+      <c r="M8" s="20" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!V$7)</f>
-        <v/>
+        <v>6.10862531166365</v>
       </c>
       <c r="N8" s="21" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!W$7)</f>
-        <v/>
-      </c>
-      <c r="O8" s="20" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="O8" s="20" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!X$7)</f>
-        <v/>
-      </c>
-      <c r="P8" s="19" t="str">
+        <v>6.54698200053601</v>
+      </c>
+      <c r="P8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!S$7)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="19" t="str">
+        <v>0.374873740117713</v>
+      </c>
+      <c r="Q8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!Y$7)</f>
-        <v/>
-      </c>
-      <c r="R8" s="19" t="str">
+        <v>0.449715370018975</v>
+      </c>
+      <c r="R8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!I$7)</f>
-        <v/>
-      </c>
-      <c r="S8" s="19" t="str">
+        <v>0.574646260467803</v>
+      </c>
+      <c r="S8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!Z$7)</f>
-        <v/>
-      </c>
-      <c r="T8" s="19" t="str">
+        <v>0.310848347584267</v>
+      </c>
+      <c r="T8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AA$7)</f>
-        <v/>
-      </c>
-      <c r="U8" s="22" t="str">
+        <v>0.279551522958118</v>
+      </c>
+      <c r="U8" s="22" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AB$7)</f>
-        <v/>
-      </c>
-      <c r="V8" s="22" t="str">
+        <v>312.968246261493</v>
+      </c>
+      <c r="V8" s="22" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AC$7)</f>
-        <v/>
-      </c>
-      <c r="W8" s="19" t="str">
+        <v>-38.5940363433762</v>
+      </c>
+      <c r="W8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AF$7)</f>
-        <v/>
-      </c>
-      <c r="X8" s="19" t="str">
+        <v>0.246843882201776</v>
+      </c>
+      <c r="X8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AG$7)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="19" t="str">
+        <v>0.180759126269984</v>
+      </c>
+      <c r="Y8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AH$7)</f>
-        <v/>
-      </c>
-      <c r="Z8" s="17" t="str">
+        <v>0.258245623152622</v>
+      </c>
+      <c r="Z8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AI$7)</f>
-        <v/>
+        <v>18.74375</v>
       </c>
       <c r="AA8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AJ$7)</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AB8" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!AK$7)</f>
-        <v/>
-      </c>
-      <c r="AC8" s="23" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AC8" s="23" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!AM$7)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14507,36 +14664,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16793,7 +16950,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B5BAE14D-27E4-43F0-87A6-ABF71F7835C7}</x14:id>
+          <x14:id>{E76FD4B0-B2E5-4F57-A569-976E4B3C68A1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16809,16 +16966,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16859,47 +17016,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16924,7 +17081,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B5BAE14D-27E4-43F0-87A6-ABF71F7835C7}">
+          <x14:cfRule type="dataBar" id="{E76FD4B0-B2E5-4F57-A569-976E4B3C68A1}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17027,11 +17184,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46269</v>
+        <v>-46272</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="J4" s="72" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -17069,11 +17226,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46269</v>
+        <v>-46272</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="J5" s="72" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -17111,11 +17268,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46269</v>
+        <v>-46272</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="J6" s="72" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -17153,11 +17310,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46269</v>
+        <v>-46272</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="J7" s="72" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -17195,11 +17352,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46269</v>
+        <v>-46272</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="J8" s="72" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -17209,43 +17366,43 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="str">
         <f aca="false">IF(Calc!$A$7="","",Calc!$A$7)</f>
-        <v/>
-      </c>
-      <c r="B9" s="47" t="str">
+        <v>3665</v>
+      </c>
+      <c r="B9" s="47" t="n">
         <f aca="false">IF($A9="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A9,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v/>
-      </c>
-      <c r="C9" s="47" t="str">
+        <v>24</v>
+      </c>
+      <c r="C9" s="47" t="n">
         <f aca="false">IF($A9="","",Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D9" s="67" t="str">
+        <v>24</v>
+      </c>
+      <c r="D9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,$B9),""))</f>
-        <v/>
-      </c>
-      <c r="E9" s="67" t="str">
+        <v>44104</v>
+      </c>
+      <c r="E9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="F9" s="66" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A9&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G9" s="67" t="str">
+        <v>FY2026Q3E</v>
+      </c>
+      <c r="G9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H9" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" s="47" t="n">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A9,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v/>
-      </c>
-      <c r="I9" s="67" t="str">
+        <v>-46272</v>
+      </c>
+      <c r="I9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>46272</v>
       </c>
       <c r="J9" s="72" t="str">
         <f aca="true">IF($A9="","",IF($B9=0,"未抓取",IF($B9&lt;$C9,"需補歷史 ("&amp;($C9-$B9)&amp;" 季)",IF(TODAY()&gt;$G9,"待更新財報","OK"))))</f>
-        <v/>
+        <v>待更新財報</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17843,18 +18000,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18008,12 +18165,22 @@
       <c r="G6" s="73"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
+      <c r="A7" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="74" t="s">
+        <v>182</v>
+      </c>
       <c r="E7" s="73"/>
-      <c r="F7" s="75"/>
+      <c r="F7" s="75" t="n">
+        <v>46272</v>
+      </c>
       <c r="G7" s="73"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18144,7 +18311,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -18163,7 +18330,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S148"/>
+  <dimension ref="A1:S173"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -18187,58 +18354,58 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18246,7 +18413,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C2" s="77" t="n">
         <v>2026</v>
@@ -18258,13 +18425,13 @@
         <v>46295</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I2" s="79"/>
       <c r="J2" s="79"/>
@@ -18281,7 +18448,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="66" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18289,7 +18456,7 @@
         <v>167</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C3" s="77" t="n">
         <v>2026</v>
@@ -18301,13 +18468,13 @@
         <v>46203</v>
       </c>
       <c r="F3" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G3" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G3" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I3" s="79" t="n">
         <v>1270380.25</v>
@@ -18340,7 +18507,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="66" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18348,7 +18515,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C4" s="77" t="n">
         <v>2026</v>
@@ -18360,13 +18527,13 @@
         <v>46112</v>
       </c>
       <c r="F4" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G4" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H4" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G4" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I4" s="79" t="n">
         <v>1134103.44</v>
@@ -18399,7 +18566,7 @@
         <v>2</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18407,7 +18574,7 @@
         <v>167</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C5" s="77" t="n">
         <v>2025</v>
@@ -18419,13 +18586,13 @@
         <v>46022</v>
       </c>
       <c r="F5" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G5" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I5" s="79" t="n">
         <v>1046090.421</v>
@@ -18458,7 +18625,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="66" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18466,7 +18633,7 @@
         <v>167</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C6" s="77" t="n">
         <v>2025</v>
@@ -18478,13 +18645,13 @@
         <v>45930</v>
       </c>
       <c r="F6" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H6" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G6" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I6" s="79" t="n">
         <v>989918.318</v>
@@ -18517,7 +18684,7 @@
         <v>4</v>
       </c>
       <c r="S6" s="66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18525,7 +18692,7 @@
         <v>167</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C7" s="77" t="n">
         <v>2025</v>
@@ -18537,13 +18704,13 @@
         <v>45838</v>
       </c>
       <c r="F7" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G7" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I7" s="79" t="n">
         <v>933791.869</v>
@@ -18576,7 +18743,7 @@
         <v>5</v>
       </c>
       <c r="S7" s="66" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18584,7 +18751,7 @@
         <v>167</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C8" s="77" t="n">
         <v>2025</v>
@@ -18596,13 +18763,13 @@
         <v>45747</v>
       </c>
       <c r="F8" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H8" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G8" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I8" s="79" t="n">
         <v>839253.664</v>
@@ -18635,7 +18802,7 @@
         <v>6</v>
       </c>
       <c r="S8" s="66" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18643,7 +18810,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C9" s="77" t="n">
         <v>2024</v>
@@ -18655,13 +18822,13 @@
         <v>45657</v>
       </c>
       <c r="F9" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G9" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H9" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G9" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I9" s="79" t="n">
         <v>868461.178</v>
@@ -18694,7 +18861,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="66" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18702,7 +18869,7 @@
         <v>167</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C10" s="77" t="n">
         <v>2024</v>
@@ -18714,13 +18881,13 @@
         <v>45565</v>
       </c>
       <c r="F10" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H10" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G10" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H10" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I10" s="79" t="n">
         <v>759692.143</v>
@@ -18753,7 +18920,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="66" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18761,7 +18928,7 @@
         <v>167</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C11" s="77" t="n">
         <v>2024</v>
@@ -18773,13 +18940,13 @@
         <v>45473</v>
       </c>
       <c r="F11" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G11" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H11" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G11" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I11" s="79" t="n">
         <v>673510.177</v>
@@ -18812,7 +18979,7 @@
         <v>9</v>
       </c>
       <c r="S11" s="66" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18820,7 +18987,7 @@
         <v>167</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C12" s="77" t="n">
         <v>2024</v>
@@ -18832,13 +18999,13 @@
         <v>45382</v>
       </c>
       <c r="F12" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H12" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G12" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H12" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I12" s="79" t="n">
         <v>592644.201</v>
@@ -18871,7 +19038,7 @@
         <v>10</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18879,7 +19046,7 @@
         <v>167</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C13" s="77" t="n">
         <v>2023</v>
@@ -18891,13 +19058,13 @@
         <v>45291</v>
       </c>
       <c r="F13" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G13" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H13" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G13" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H13" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I13" s="79" t="n">
         <v>625528.856</v>
@@ -18930,7 +19097,7 @@
         <v>11</v>
       </c>
       <c r="S13" s="66" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18938,7 +19105,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C14" s="77" t="n">
         <v>2023</v>
@@ -18950,13 +19117,13 @@
         <v>45199</v>
       </c>
       <c r="F14" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H14" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G14" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H14" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I14" s="79" t="n">
         <v>546732.758</v>
@@ -18989,7 +19156,7 @@
         <v>12</v>
       </c>
       <c r="S14" s="66" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18997,7 +19164,7 @@
         <v>167</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C15" s="77" t="n">
         <v>2023</v>
@@ -19009,13 +19176,13 @@
         <v>45107</v>
       </c>
       <c r="F15" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G15" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H15" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G15" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H15" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I15" s="79" t="n">
         <v>480841.254</v>
@@ -19048,7 +19215,7 @@
         <v>13</v>
       </c>
       <c r="S15" s="66" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19056,7 +19223,7 @@
         <v>167</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C16" s="77" t="n">
         <v>2023</v>
@@ -19068,13 +19235,13 @@
         <v>45016</v>
       </c>
       <c r="F16" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G16" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H16" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G16" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H16" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I16" s="79" t="n">
         <v>508632.973</v>
@@ -19107,7 +19274,7 @@
         <v>14</v>
       </c>
       <c r="S16" s="66" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19115,7 +19282,7 @@
         <v>167</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C17" s="77" t="n">
         <v>2022</v>
@@ -19127,13 +19294,13 @@
         <v>44926</v>
       </c>
       <c r="F17" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G17" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H17" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G17" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H17" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I17" s="79" t="n">
         <v>625531.868</v>
@@ -19166,7 +19333,7 @@
         <v>15</v>
       </c>
       <c r="S17" s="66" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19174,7 +19341,7 @@
         <v>167</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C18" s="77" t="n">
         <v>2022</v>
@@ -19186,13 +19353,13 @@
         <v>44834</v>
       </c>
       <c r="F18" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G18" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H18" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G18" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H18" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I18" s="79" t="n">
         <v>613142.743</v>
@@ -19225,7 +19392,7 @@
         <v>16</v>
       </c>
       <c r="S18" s="66" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19233,7 +19400,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C19" s="77" t="n">
         <v>2022</v>
@@ -19245,13 +19412,13 @@
         <v>44742</v>
       </c>
       <c r="F19" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G19" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H19" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G19" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H19" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I19" s="79" t="n">
         <v>534140.808</v>
@@ -19284,7 +19451,7 @@
         <v>17</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19292,7 +19459,7 @@
         <v>167</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C20" s="77" t="n">
         <v>2022</v>
@@ -19304,13 +19471,13 @@
         <v>44651</v>
       </c>
       <c r="F20" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G20" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H20" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G20" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H20" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I20" s="79" t="n">
         <v>491075.873</v>
@@ -19343,7 +19510,7 @@
         <v>18</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19351,7 +19518,7 @@
         <v>167</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C21" s="77" t="n">
         <v>2021</v>
@@ -19363,13 +19530,13 @@
         <v>44561</v>
       </c>
       <c r="F21" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G21" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H21" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G21" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H21" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I21" s="79" t="n">
         <v>438189.306</v>
@@ -19402,7 +19569,7 @@
         <v>19</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19410,7 +19577,7 @@
         <v>167</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C22" s="77" t="n">
         <v>2021</v>
@@ -19422,13 +19589,13 @@
         <v>44469</v>
       </c>
       <c r="F22" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G22" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H22" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G22" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H22" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I22" s="79" t="n">
         <v>414670.379</v>
@@ -19461,7 +19628,7 @@
         <v>20</v>
       </c>
       <c r="S22" s="66" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19469,7 +19636,7 @@
         <v>167</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C23" s="77" t="n">
         <v>2021</v>
@@ -19481,13 +19648,13 @@
         <v>44377</v>
       </c>
       <c r="F23" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G23" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H23" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G23" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H23" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I23" s="79" t="n">
         <v>372145.122</v>
@@ -19520,7 +19687,7 @@
         <v>21</v>
       </c>
       <c r="S23" s="66" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19528,7 +19695,7 @@
         <v>167</v>
       </c>
       <c r="B24" s="76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C24" s="77" t="n">
         <v>2021</v>
@@ -19540,13 +19707,13 @@
         <v>44286</v>
       </c>
       <c r="F24" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G24" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H24" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G24" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H24" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I24" s="79" t="n">
         <v>362410.23</v>
@@ -19579,7 +19746,7 @@
         <v>22</v>
       </c>
       <c r="S24" s="66" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19587,7 +19754,7 @@
         <v>167</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C25" s="77" t="n">
         <v>2020</v>
@@ -19599,13 +19766,13 @@
         <v>44196</v>
       </c>
       <c r="F25" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G25" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H25" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G25" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I25" s="79" t="n">
         <v>361533.057</v>
@@ -19638,7 +19805,7 @@
         <v>23</v>
       </c>
       <c r="S25" s="66" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19646,7 +19813,7 @@
         <v>167</v>
       </c>
       <c r="B26" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C26" s="77" t="n">
         <v>2020</v>
@@ -19658,13 +19825,13 @@
         <v>44104</v>
       </c>
       <c r="F26" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G26" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H26" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G26" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H26" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I26" s="79" t="n">
         <v>356426.204</v>
@@ -19695,7 +19862,7 @@
         <v>24</v>
       </c>
       <c r="S26" s="66" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19703,7 +19870,7 @@
         <v>171</v>
       </c>
       <c r="B27" s="76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C27" s="77" t="n">
         <v>2026</v>
@@ -19715,13 +19882,13 @@
         <v>46295</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G27" s="76" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H27" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I27" s="79"/>
       <c r="J27" s="79"/>
@@ -19738,7 +19905,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="66" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19746,7 +19913,7 @@
         <v>171</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C28" s="77" t="n">
         <v>2026</v>
@@ -19758,13 +19925,13 @@
         <v>46203</v>
       </c>
       <c r="F28" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G28" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H28" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G28" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H28" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I28" s="79" t="n">
         <v>82549.073</v>
@@ -19797,7 +19964,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="66" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19805,7 +19972,7 @@
         <v>171</v>
       </c>
       <c r="B29" s="76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C29" s="77" t="n">
         <v>2026</v>
@@ -19817,13 +19984,13 @@
         <v>46112</v>
       </c>
       <c r="F29" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G29" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G29" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H29" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I29" s="79" t="n">
         <v>49086.932</v>
@@ -19856,7 +20023,7 @@
         <v>2</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19864,7 +20031,7 @@
         <v>171</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C30" s="77" t="n">
         <v>2025</v>
@@ -19876,13 +20043,13 @@
         <v>46022</v>
       </c>
       <c r="F30" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G30" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H30" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G30" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H30" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I30" s="79" t="n">
         <v>30093.618</v>
@@ -19915,7 +20082,7 @@
         <v>3</v>
       </c>
       <c r="S30" s="66" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19923,7 +20090,7 @@
         <v>171</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C31" s="77" t="n">
         <v>2025</v>
@@ -19935,13 +20102,13 @@
         <v>45930</v>
       </c>
       <c r="F31" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G31" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H31" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G31" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H31" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I31" s="79" t="n">
         <v>18778.868</v>
@@ -19974,7 +20141,7 @@
         <v>4</v>
       </c>
       <c r="S31" s="66" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19982,7 +20149,7 @@
         <v>171</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C32" s="77" t="n">
         <v>2025</v>
@@ -19994,13 +20161,13 @@
         <v>45838</v>
       </c>
       <c r="F32" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G32" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H32" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G32" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H32" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I32" s="79" t="n">
         <v>10526.094</v>
@@ -20033,7 +20200,7 @@
         <v>5</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20041,7 +20208,7 @@
         <v>171</v>
       </c>
       <c r="B33" s="76" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C33" s="77" t="n">
         <v>2025</v>
@@ -20053,13 +20220,13 @@
         <v>45747</v>
       </c>
       <c r="F33" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G33" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H33" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G33" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H33" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I33" s="79" t="n">
         <v>7187.94</v>
@@ -20092,7 +20259,7 @@
         <v>6</v>
       </c>
       <c r="S33" s="66" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20100,7 +20267,7 @@
         <v>171</v>
       </c>
       <c r="B34" s="76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C34" s="77" t="n">
         <v>2024</v>
@@ -20112,13 +20279,13 @@
         <v>45657</v>
       </c>
       <c r="F34" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G34" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H34" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G34" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H34" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I34" s="79" t="n">
         <v>6575.094</v>
@@ -20151,7 +20318,7 @@
         <v>7</v>
       </c>
       <c r="S34" s="66" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20159,7 +20326,7 @@
         <v>171</v>
       </c>
       <c r="B35" s="76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C35" s="77" t="n">
         <v>2024</v>
@@ -20171,13 +20338,13 @@
         <v>45565</v>
       </c>
       <c r="F35" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G35" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H35" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G35" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H35" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I35" s="79" t="n">
         <v>8132.593</v>
@@ -20210,7 +20377,7 @@
         <v>8</v>
       </c>
       <c r="S35" s="66" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20218,7 +20385,7 @@
         <v>171</v>
       </c>
       <c r="B36" s="76" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C36" s="77" t="n">
         <v>2024</v>
@@ -20230,13 +20397,13 @@
         <v>45473</v>
       </c>
       <c r="F36" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G36" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H36" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G36" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H36" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I36" s="79" t="n">
         <v>9921.043</v>
@@ -20263,7 +20430,7 @@
         <v>9</v>
       </c>
       <c r="S36" s="66" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20271,7 +20438,7 @@
         <v>171</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C37" s="77" t="n">
         <v>2024</v>
@@ -20283,13 +20450,13 @@
         <v>45382</v>
       </c>
       <c r="F37" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G37" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H37" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G37" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H37" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I37" s="79" t="n">
         <v>9502.937</v>
@@ -20322,7 +20489,7 @@
         <v>10</v>
       </c>
       <c r="S37" s="66" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20330,7 +20497,7 @@
         <v>171</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C38" s="77" t="n">
         <v>2023</v>
@@ -20342,13 +20509,13 @@
         <v>45291</v>
       </c>
       <c r="F38" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G38" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H38" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G38" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H38" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I38" s="79" t="n">
         <v>8703.978</v>
@@ -20381,7 +20548,7 @@
         <v>11</v>
       </c>
       <c r="S38" s="66" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20389,7 +20556,7 @@
         <v>171</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C39" s="77" t="n">
         <v>2023</v>
@@ -20401,13 +20568,13 @@
         <v>45199</v>
       </c>
       <c r="F39" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G39" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H39" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G39" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H39" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I39" s="79" t="n">
         <v>7736.374</v>
@@ -20440,7 +20607,7 @@
         <v>12</v>
       </c>
       <c r="S39" s="66" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20448,7 +20615,7 @@
         <v>171</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C40" s="77" t="n">
         <v>2023</v>
@@ -20460,13 +20627,13 @@
         <v>45107</v>
       </c>
       <c r="F40" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G40" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H40" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G40" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H40" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I40" s="79" t="n">
         <v>7027.071</v>
@@ -20499,7 +20666,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="66" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20507,7 +20674,7 @@
         <v>171</v>
       </c>
       <c r="B41" s="76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C41" s="77" t="n">
         <v>2023</v>
@@ -20519,13 +20686,13 @@
         <v>45016</v>
       </c>
       <c r="F41" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G41" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H41" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G41" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H41" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I41" s="79" t="n">
         <v>6424.883</v>
@@ -20558,7 +20725,7 @@
         <v>14</v>
       </c>
       <c r="S41" s="66" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20566,7 +20733,7 @@
         <v>171</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C42" s="77" t="n">
         <v>2022</v>
@@ -20578,13 +20745,13 @@
         <v>44926</v>
       </c>
       <c r="F42" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G42" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H42" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G42" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H42" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I42" s="79" t="n">
         <v>7953.553</v>
@@ -20617,7 +20784,7 @@
         <v>15</v>
       </c>
       <c r="S42" s="66" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20625,7 +20792,7 @@
         <v>171</v>
       </c>
       <c r="B43" s="76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C43" s="77" t="n">
         <v>2022</v>
@@ -20637,13 +20804,13 @@
         <v>44834</v>
       </c>
       <c r="F43" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G43" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H43" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G43" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H43" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I43" s="79" t="n">
         <v>11021.725</v>
@@ -20676,7 +20843,7 @@
         <v>16</v>
       </c>
       <c r="S43" s="66" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20684,7 +20851,7 @@
         <v>171</v>
       </c>
       <c r="B44" s="76" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C44" s="77" t="n">
         <v>2022</v>
@@ -20696,13 +20863,13 @@
         <v>44742</v>
       </c>
       <c r="F44" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G44" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H44" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G44" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H44" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I44" s="79" t="n">
         <v>18030.672</v>
@@ -20735,7 +20902,7 @@
         <v>17</v>
       </c>
       <c r="S44" s="66" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20743,7 +20910,7 @@
         <v>171</v>
       </c>
       <c r="B45" s="76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C45" s="77" t="n">
         <v>2022</v>
@@ -20755,13 +20922,13 @@
         <v>44651</v>
       </c>
       <c r="F45" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G45" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H45" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G45" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H45" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I45" s="79" t="n">
         <v>19946.325</v>
@@ -20794,7 +20961,7 @@
         <v>18</v>
       </c>
       <c r="S45" s="66" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20802,7 +20969,7 @@
         <v>171</v>
       </c>
       <c r="B46" s="76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C46" s="77" t="n">
         <v>2021</v>
@@ -20814,13 +20981,13 @@
         <v>44561</v>
       </c>
       <c r="F46" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G46" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H46" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G46" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H46" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I46" s="79" t="n">
         <v>21398.949</v>
@@ -20853,7 +21020,7 @@
         <v>19</v>
       </c>
       <c r="S46" s="66" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20861,7 +21028,7 @@
         <v>171</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C47" s="77" t="n">
         <v>2021</v>
@@ -20873,13 +21040,13 @@
         <v>44469</v>
       </c>
       <c r="F47" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G47" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H47" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G47" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H47" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I47" s="79" t="n">
         <v>23837.128</v>
@@ -20912,7 +21079,7 @@
         <v>20</v>
       </c>
       <c r="S47" s="66" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20920,7 +21087,7 @@
         <v>171</v>
       </c>
       <c r="B48" s="76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C48" s="77" t="n">
         <v>2021</v>
@@ -20932,13 +21099,13 @@
         <v>44377</v>
       </c>
       <c r="F48" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G48" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H48" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G48" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H48" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I48" s="79" t="n">
         <v>22637.468</v>
@@ -20971,7 +21138,7 @@
         <v>21</v>
       </c>
       <c r="S48" s="66" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20979,7 +21146,7 @@
         <v>171</v>
       </c>
       <c r="B49" s="76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C49" s="77" t="n">
         <v>2021</v>
@@ -20991,13 +21158,13 @@
         <v>44286</v>
       </c>
       <c r="F49" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G49" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H49" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G49" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H49" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I49" s="79" t="n">
         <v>17730.613</v>
@@ -21030,7 +21197,7 @@
         <v>22</v>
       </c>
       <c r="S49" s="66" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21038,7 +21205,7 @@
         <v>171</v>
       </c>
       <c r="B50" s="76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C50" s="77" t="n">
         <v>2020</v>
@@ -21050,13 +21217,13 @@
         <v>44196</v>
       </c>
       <c r="F50" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G50" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H50" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G50" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H50" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I50" s="79" t="n">
         <v>14773.42</v>
@@ -21089,7 +21256,7 @@
         <v>23</v>
       </c>
       <c r="S50" s="66" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21097,7 +21264,7 @@
         <v>171</v>
       </c>
       <c r="B51" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C51" s="77" t="n">
         <v>2020</v>
@@ -21109,13 +21276,13 @@
         <v>44104</v>
       </c>
       <c r="F51" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G51" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H51" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G51" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H51" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I51" s="79" t="n">
         <v>15323.867</v>
@@ -21146,7 +21313,7 @@
         <v>24</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21154,7 +21321,7 @@
         <v>179</v>
       </c>
       <c r="B52" s="76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C52" s="77" t="n">
         <v>2026</v>
@@ -21166,13 +21333,13 @@
         <v>46295</v>
       </c>
       <c r="F52" s="76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G52" s="76" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H52" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
@@ -21189,7 +21356,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21197,7 +21364,7 @@
         <v>179</v>
       </c>
       <c r="B53" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C53" s="77" t="n">
         <v>2026</v>
@@ -21209,13 +21376,13 @@
         <v>46203</v>
       </c>
       <c r="F53" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G53" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H53" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G53" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H53" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I53" s="79" t="n">
         <v>965.373</v>
@@ -21248,7 +21415,7 @@
         <v>1</v>
       </c>
       <c r="S53" s="66" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21256,7 +21423,7 @@
         <v>179</v>
       </c>
       <c r="B54" s="76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C54" s="77" t="n">
         <v>2026</v>
@@ -21268,13 +21435,13 @@
         <v>46112</v>
       </c>
       <c r="F54" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G54" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H54" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G54" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H54" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I54" s="79" t="n">
         <v>959.31</v>
@@ -21307,7 +21474,7 @@
         <v>2</v>
       </c>
       <c r="S54" s="66" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21315,7 +21482,7 @@
         <v>179</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C55" s="77" t="n">
         <v>2025</v>
@@ -21327,13 +21494,13 @@
         <v>46022</v>
       </c>
       <c r="F55" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G55" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H55" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G55" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H55" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I55" s="79" t="n">
         <v>959.589</v>
@@ -21366,7 +21533,7 @@
         <v>3</v>
       </c>
       <c r="S55" s="66" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21374,7 +21541,7 @@
         <v>179</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C56" s="77" t="n">
         <v>2025</v>
@@ -21386,13 +21553,13 @@
         <v>45930</v>
       </c>
       <c r="F56" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G56" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H56" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G56" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H56" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I56" s="79" t="n">
         <v>912.804</v>
@@ -21425,7 +21592,7 @@
         <v>4</v>
       </c>
       <c r="S56" s="66" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21433,7 +21600,7 @@
         <v>179</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C57" s="77" t="n">
         <v>2025</v>
@@ -21445,13 +21612,13 @@
         <v>45838</v>
       </c>
       <c r="F57" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G57" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H57" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G57" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H57" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I57" s="79" t="n">
         <v>714.087</v>
@@ -21484,7 +21651,7 @@
         <v>5</v>
       </c>
       <c r="S57" s="66" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21492,7 +21659,7 @@
         <v>179</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C58" s="77" t="n">
         <v>2025</v>
@@ -21504,13 +21671,13 @@
         <v>45747</v>
       </c>
       <c r="F58" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G58" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H58" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G58" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H58" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I58" s="79" t="n">
         <v>793.663</v>
@@ -21543,7 +21710,7 @@
         <v>6</v>
       </c>
       <c r="S58" s="66" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21551,7 +21718,7 @@
         <v>179</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C59" s="77" t="n">
         <v>2024</v>
@@ -21563,13 +21730,13 @@
         <v>45657</v>
       </c>
       <c r="F59" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G59" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H59" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G59" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H59" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I59" s="79" t="n">
         <v>722.474</v>
@@ -21602,7 +21769,7 @@
         <v>7</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21610,7 +21777,7 @@
         <v>179</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C60" s="77" t="n">
         <v>2024</v>
@@ -21622,13 +21789,13 @@
         <v>45565</v>
       </c>
       <c r="F60" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G60" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H60" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G60" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H60" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I60" s="79" t="n">
         <v>805.747</v>
@@ -21661,7 +21828,7 @@
         <v>8</v>
       </c>
       <c r="S60" s="66" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21669,7 +21836,7 @@
         <v>179</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C61" s="77" t="n">
         <v>2024</v>
@@ -21681,13 +21848,13 @@
         <v>45473</v>
       </c>
       <c r="F61" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G61" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H61" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G61" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H61" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I61" s="79" t="n">
         <v>875.601</v>
@@ -21720,7 +21887,7 @@
         <v>9</v>
       </c>
       <c r="S61" s="66" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21728,7 +21895,7 @@
         <v>179</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C62" s="77" t="n">
         <v>2024</v>
@@ -21740,13 +21907,13 @@
         <v>45382</v>
       </c>
       <c r="F62" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G62" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H62" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G62" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H62" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I62" s="79" t="n">
         <v>837.395</v>
@@ -21779,7 +21946,7 @@
         <v>10</v>
       </c>
       <c r="S62" s="66" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21787,7 +21954,7 @@
         <v>179</v>
       </c>
       <c r="B63" s="76" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C63" s="77" t="n">
         <v>2023</v>
@@ -21799,13 +21966,13 @@
         <v>45291</v>
       </c>
       <c r="F63" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G63" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H63" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G63" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H63" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I63" s="79" t="n">
         <v>936.937</v>
@@ -21838,7 +22005,7 @@
         <v>11</v>
       </c>
       <c r="S63" s="66" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21846,7 +22013,7 @@
         <v>179</v>
       </c>
       <c r="B64" s="76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C64" s="77" t="n">
         <v>2023</v>
@@ -21858,13 +22025,13 @@
         <v>45199</v>
       </c>
       <c r="F64" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G64" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H64" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G64" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H64" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I64" s="79" t="n">
         <v>768.427</v>
@@ -21897,7 +22064,7 @@
         <v>12</v>
       </c>
       <c r="S64" s="66" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21905,7 +22072,7 @@
         <v>179</v>
       </c>
       <c r="B65" s="76" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C65" s="77" t="n">
         <v>2023</v>
@@ -21917,13 +22084,13 @@
         <v>45107</v>
       </c>
       <c r="F65" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G65" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H65" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G65" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H65" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I65" s="79" t="n">
         <v>594.323</v>
@@ -21956,7 +22123,7 @@
         <v>13</v>
       </c>
       <c r="S65" s="66" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21964,7 +22131,7 @@
         <v>179</v>
       </c>
       <c r="B66" s="76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C66" s="77" t="n">
         <v>2023</v>
@@ -21976,13 +22143,13 @@
         <v>45016</v>
       </c>
       <c r="F66" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G66" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H66" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G66" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H66" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I66" s="79" t="n">
         <v>394.417</v>
@@ -22015,7 +22182,7 @@
         <v>14</v>
       </c>
       <c r="S66" s="66" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22023,7 +22190,7 @@
         <v>179</v>
       </c>
       <c r="B67" s="76" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C67" s="77" t="n">
         <v>2022</v>
@@ -22035,13 +22202,13 @@
         <v>44926</v>
       </c>
       <c r="F67" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G67" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H67" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G67" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H67" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I67" s="79" t="n">
         <v>506.067</v>
@@ -22074,7 +22241,7 @@
         <v>15</v>
       </c>
       <c r="S67" s="66" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22082,7 +22249,7 @@
         <v>179</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C68" s="77" t="n">
         <v>2022</v>
@@ -22094,13 +22261,13 @@
         <v>44834</v>
       </c>
       <c r="F68" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G68" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H68" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G68" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H68" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I68" s="79" t="n">
         <v>522.089</v>
@@ -22133,7 +22300,7 @@
         <v>16</v>
       </c>
       <c r="S68" s="66" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22141,7 +22308,7 @@
         <v>179</v>
       </c>
       <c r="B69" s="76" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C69" s="77" t="n">
         <v>2022</v>
@@ -22153,13 +22320,13 @@
         <v>44742</v>
       </c>
       <c r="F69" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G69" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H69" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G69" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H69" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I69" s="79" t="n">
         <v>736.276</v>
@@ -22192,7 +22359,7 @@
         <v>17</v>
       </c>
       <c r="S69" s="66" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22200,7 +22367,7 @@
         <v>179</v>
       </c>
       <c r="B70" s="76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C70" s="77" t="n">
         <v>2022</v>
@@ -22212,13 +22379,13 @@
         <v>44651</v>
       </c>
       <c r="F70" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G70" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H70" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G70" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H70" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I70" s="79" t="n">
         <v>839.197</v>
@@ -22251,7 +22418,7 @@
         <v>18</v>
       </c>
       <c r="S70" s="66" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22259,7 +22426,7 @@
         <v>179</v>
       </c>
       <c r="B71" s="76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C71" s="77" t="n">
         <v>2021</v>
@@ -22271,13 +22438,13 @@
         <v>44561</v>
       </c>
       <c r="F71" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G71" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H71" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G71" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H71" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I71" s="79" t="n">
         <v>875.843</v>
@@ -22310,7 +22477,7 @@
         <v>19</v>
       </c>
       <c r="S71" s="66" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22318,7 +22485,7 @@
         <v>179</v>
       </c>
       <c r="B72" s="76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C72" s="77" t="n">
         <v>2021</v>
@@ -22330,13 +22497,13 @@
         <v>44469</v>
       </c>
       <c r="F72" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G72" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H72" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G72" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H72" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I72" s="79" t="n">
         <v>947.399</v>
@@ -22369,7 +22536,7 @@
         <v>20</v>
       </c>
       <c r="S72" s="66" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22377,7 +22544,7 @@
         <v>179</v>
       </c>
       <c r="B73" s="76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C73" s="77" t="n">
         <v>2021</v>
@@ -22389,13 +22556,13 @@
         <v>44377</v>
       </c>
       <c r="F73" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G73" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H73" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G73" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H73" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I73" s="79" t="n">
         <v>896.062</v>
@@ -22428,7 +22595,7 @@
         <v>21</v>
       </c>
       <c r="S73" s="66" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22436,7 +22603,7 @@
         <v>179</v>
       </c>
       <c r="B74" s="76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C74" s="77" t="n">
         <v>2021</v>
@@ -22448,13 +22615,13 @@
         <v>44286</v>
       </c>
       <c r="F74" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G74" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H74" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G74" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H74" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I74" s="79" t="n">
         <v>889.217</v>
@@ -22487,7 +22654,7 @@
         <v>22</v>
       </c>
       <c r="S74" s="66" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22495,7 +22662,7 @@
         <v>179</v>
       </c>
       <c r="B75" s="76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C75" s="77" t="n">
         <v>2020</v>
@@ -22507,13 +22674,13 @@
         <v>44196</v>
       </c>
       <c r="F75" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G75" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H75" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G75" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H75" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I75" s="79" t="n">
         <v>757.232</v>
@@ -22546,7 +22713,7 @@
         <v>23</v>
       </c>
       <c r="S75" s="66" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22554,7 +22721,7 @@
         <v>179</v>
       </c>
       <c r="B76" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C76" s="77" t="n">
         <v>2020</v>
@@ -22566,13 +22733,13 @@
         <v>44104</v>
       </c>
       <c r="F76" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G76" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H76" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G76" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H76" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I76" s="79" t="n">
         <v>644.391</v>
@@ -22603,7 +22770,7 @@
         <v>24</v>
       </c>
       <c r="S76" s="66" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22611,7 +22778,7 @@
         <v>183</v>
       </c>
       <c r="B77" s="76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C77" s="77" t="n">
         <v>2026</v>
@@ -22623,13 +22790,13 @@
         <v>46295</v>
       </c>
       <c r="F77" s="76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G77" s="76" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H77" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I77" s="79"/>
       <c r="J77" s="79"/>
@@ -22646,7 +22813,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="66" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22654,7 +22821,7 @@
         <v>183</v>
       </c>
       <c r="B78" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C78" s="77" t="n">
         <v>2026</v>
@@ -22666,13 +22833,13 @@
         <v>46203</v>
       </c>
       <c r="F78" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G78" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H78" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G78" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H78" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I78" s="79" t="n">
         <v>28660.098</v>
@@ -22705,7 +22872,7 @@
         <v>1</v>
       </c>
       <c r="S78" s="66" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22713,7 +22880,7 @@
         <v>183</v>
       </c>
       <c r="B79" s="76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C79" s="77" t="n">
         <v>2026</v>
@@ -22725,13 +22892,13 @@
         <v>46112</v>
       </c>
       <c r="F79" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G79" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H79" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G79" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H79" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I79" s="79" t="n">
         <v>23145.303</v>
@@ -22764,7 +22931,7 @@
         <v>2</v>
       </c>
       <c r="S79" s="66" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22772,7 +22939,7 @@
         <v>183</v>
       </c>
       <c r="B80" s="76" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C80" s="77" t="n">
         <v>2025</v>
@@ -22784,13 +22951,13 @@
         <v>46022</v>
       </c>
       <c r="F80" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G80" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H80" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G80" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H80" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I80" s="79" t="n">
         <v>22817.209</v>
@@ -22823,7 +22990,7 @@
         <v>3</v>
       </c>
       <c r="S80" s="66" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22831,7 +22998,7 @@
         <v>183</v>
       </c>
       <c r="B81" s="76" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C81" s="77" t="n">
         <v>2025</v>
@@ -22843,13 +23010,13 @@
         <v>45930</v>
       </c>
       <c r="F81" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G81" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H81" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G81" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H81" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I81" s="79" t="n">
         <v>24573.67</v>
@@ -22882,7 +23049,7 @@
         <v>4</v>
       </c>
       <c r="S81" s="66" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22890,7 +23057,7 @@
         <v>183</v>
       </c>
       <c r="B82" s="76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C82" s="77" t="n">
         <v>2025</v>
@@ -22902,13 +23069,13 @@
         <v>45838</v>
       </c>
       <c r="F82" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G82" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H82" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G82" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H82" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I82" s="79" t="n">
         <v>26152.063</v>
@@ -22941,7 +23108,7 @@
         <v>5</v>
       </c>
       <c r="S82" s="66" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22949,7 +23116,7 @@
         <v>183</v>
       </c>
       <c r="B83" s="76" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C83" s="77" t="n">
         <v>2025</v>
@@ -22961,13 +23128,13 @@
         <v>45747</v>
       </c>
       <c r="F83" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G83" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H83" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G83" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H83" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I83" s="79" t="n">
         <v>27120.202</v>
@@ -23000,7 +23167,7 @@
         <v>6</v>
       </c>
       <c r="S83" s="66" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23008,7 +23175,7 @@
         <v>183</v>
       </c>
       <c r="B84" s="76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C84" s="77" t="n">
         <v>2024</v>
@@ -23020,13 +23187,13 @@
         <v>45657</v>
       </c>
       <c r="F84" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G84" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H84" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G84" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H84" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I84" s="79" t="n">
         <v>25262.519</v>
@@ -23059,7 +23226,7 @@
         <v>7</v>
       </c>
       <c r="S84" s="66" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23067,7 +23234,7 @@
         <v>183</v>
       </c>
       <c r="B85" s="76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C85" s="77" t="n">
         <v>2024</v>
@@ -23079,13 +23246,13 @@
         <v>45565</v>
       </c>
       <c r="F85" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G85" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H85" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G85" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H85" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I85" s="79" t="n">
         <v>27866.328</v>
@@ -23118,7 +23285,7 @@
         <v>8</v>
       </c>
       <c r="S85" s="66" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23126,7 +23293,7 @@
         <v>183</v>
       </c>
       <c r="B86" s="76" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C86" s="77" t="n">
         <v>2024</v>
@@ -23138,13 +23305,13 @@
         <v>45473</v>
       </c>
       <c r="F86" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G86" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H86" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G86" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H86" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I86" s="79" t="n">
         <v>25231.019</v>
@@ -23177,7 +23344,7 @@
         <v>9</v>
       </c>
       <c r="S86" s="66" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23185,7 +23352,7 @@
         <v>183</v>
       </c>
       <c r="B87" s="76" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C87" s="77" t="n">
         <v>2024</v>
@@ -23197,13 +23364,13 @@
         <v>45382</v>
       </c>
       <c r="F87" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G87" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H87" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G87" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H87" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I87" s="79" t="n">
         <v>24427.885</v>
@@ -23236,7 +23403,7 @@
         <v>10</v>
       </c>
       <c r="S87" s="66" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23244,7 +23411,7 @@
         <v>183</v>
       </c>
       <c r="B88" s="76" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C88" s="77" t="n">
         <v>2023</v>
@@ -23256,13 +23423,13 @@
         <v>45291</v>
       </c>
       <c r="F88" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G88" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H88" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G88" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H88" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I88" s="79" t="n">
         <v>27153.825</v>
@@ -23295,7 +23462,7 @@
         <v>11</v>
       </c>
       <c r="S88" s="66" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23303,7 +23470,7 @@
         <v>183</v>
       </c>
       <c r="B89" s="76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C89" s="77" t="n">
         <v>2023</v>
@@ -23315,13 +23482,13 @@
         <v>45199</v>
       </c>
       <c r="F89" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G89" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H89" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G89" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H89" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I89" s="79" t="n">
         <v>28929.962</v>
@@ -23354,7 +23521,7 @@
         <v>12</v>
       </c>
       <c r="S89" s="66" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23362,7 +23529,7 @@
         <v>183</v>
       </c>
       <c r="B90" s="76" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C90" s="77" t="n">
         <v>2023</v>
@@ -23374,13 +23541,13 @@
         <v>45107</v>
       </c>
       <c r="F90" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G90" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H90" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G90" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H90" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I90" s="79" t="n">
         <v>30299.029</v>
@@ -23413,7 +23580,7 @@
         <v>13</v>
       </c>
       <c r="S90" s="66" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23421,7 +23588,7 @@
         <v>183</v>
       </c>
       <c r="B91" s="76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C91" s="77" t="n">
         <v>2023</v>
@@ -23433,13 +23600,13 @@
         <v>45016</v>
       </c>
       <c r="F91" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G91" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H91" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G91" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H91" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I91" s="79" t="n">
         <v>24045.882</v>
@@ -23472,7 +23639,7 @@
         <v>14</v>
       </c>
       <c r="S91" s="66" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23480,7 +23647,7 @@
         <v>183</v>
       </c>
       <c r="B92" s="76" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C92" s="77" t="n">
         <v>2022</v>
@@ -23492,13 +23659,13 @@
         <v>44926</v>
       </c>
       <c r="F92" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G92" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H92" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G92" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H92" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I92" s="79" t="n">
         <v>22420.161</v>
@@ -23531,7 +23698,7 @@
         <v>15</v>
       </c>
       <c r="S92" s="66" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23539,7 +23706,7 @@
         <v>183</v>
       </c>
       <c r="B93" s="76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C93" s="77" t="n">
         <v>2022</v>
@@ -23551,13 +23718,13 @@
         <v>44834</v>
       </c>
       <c r="F93" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G93" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H93" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G93" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H93" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I93" s="79" t="n">
         <v>19563.686</v>
@@ -23590,7 +23757,7 @@
         <v>16</v>
       </c>
       <c r="S93" s="66" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23598,7 +23765,7 @@
         <v>183</v>
       </c>
       <c r="B94" s="76" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C94" s="77" t="n">
         <v>2022</v>
@@ -23610,13 +23777,13 @@
         <v>44742</v>
       </c>
       <c r="F94" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G94" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H94" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G94" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H94" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I94" s="79" t="n">
         <v>31461.142</v>
@@ -23649,7 +23816,7 @@
         <v>17</v>
       </c>
       <c r="S94" s="66" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23657,7 +23824,7 @@
         <v>183</v>
       </c>
       <c r="B95" s="76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C95" s="77" t="n">
         <v>2022</v>
@@ -23669,13 +23836,13 @@
         <v>44651</v>
       </c>
       <c r="F95" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G95" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H95" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G95" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H95" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I95" s="79" t="n">
         <v>36511.685</v>
@@ -23708,7 +23875,7 @@
         <v>18</v>
       </c>
       <c r="S95" s="66" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23716,7 +23883,7 @@
         <v>183</v>
       </c>
       <c r="B96" s="76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C96" s="77" t="n">
         <v>2021</v>
@@ -23728,13 +23895,13 @@
         <v>44561</v>
       </c>
       <c r="F96" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G96" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H96" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G96" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H96" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I96" s="79" t="n">
         <v>36542.106</v>
@@ -23767,7 +23934,7 @@
         <v>19</v>
       </c>
       <c r="S96" s="66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23775,7 +23942,7 @@
         <v>183</v>
       </c>
       <c r="B97" s="76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C97" s="77" t="n">
         <v>2021</v>
@@ -23787,13 +23954,13 @@
         <v>44469</v>
       </c>
       <c r="F97" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G97" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H97" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G97" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H97" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I97" s="79" t="n">
         <v>38345.587</v>
@@ -23826,7 +23993,7 @@
         <v>20</v>
       </c>
       <c r="S97" s="66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23834,7 +24001,7 @@
         <v>183</v>
       </c>
       <c r="B98" s="76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C98" s="77" t="n">
         <v>2021</v>
@@ -23846,13 +24013,13 @@
         <v>44377</v>
       </c>
       <c r="F98" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G98" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H98" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G98" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H98" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I98" s="79" t="n">
         <v>34111.302</v>
@@ -23885,7 +24052,7 @@
         <v>21</v>
       </c>
       <c r="S98" s="66" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23893,7 +24060,7 @@
         <v>183</v>
       </c>
       <c r="B99" s="76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C99" s="77" t="n">
         <v>2021</v>
@@ -23905,13 +24072,13 @@
         <v>44286</v>
       </c>
       <c r="F99" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G99" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H99" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G99" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H99" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I99" s="79" t="n">
         <v>26366.515</v>
@@ -23944,7 +24111,7 @@
         <v>22</v>
       </c>
       <c r="S99" s="66" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23952,7 +24119,7 @@
         <v>183</v>
       </c>
       <c r="B100" s="76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C100" s="77" t="n">
         <v>2020</v>
@@ -23964,13 +24131,13 @@
         <v>44196</v>
       </c>
       <c r="F100" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G100" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H100" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G100" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H100" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I100" s="79" t="n">
         <v>22452.842</v>
@@ -24003,7 +24170,7 @@
         <v>23</v>
       </c>
       <c r="S100" s="66" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24011,7 +24178,7 @@
         <v>183</v>
       </c>
       <c r="B101" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C101" s="77" t="n">
         <v>2020</v>
@@ -24023,13 +24190,13 @@
         <v>44104</v>
       </c>
       <c r="F101" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G101" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H101" s="76" t="s">
         <v>210</v>
-      </c>
-      <c r="G101" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H101" s="76" t="s">
-        <v>207</v>
       </c>
       <c r="I101" s="79" t="n">
         <v>22001.236</v>
@@ -24060,15 +24227,15 @@
         <v>24</v>
       </c>
       <c r="S101" s="66" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B102" s="76" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C102" s="77" t="n">
         <v>2026</v>
@@ -24080,19 +24247,19 @@
         <v>46295</v>
       </c>
       <c r="F102" s="76" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G102" s="76" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H102" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I102" s="79"/>
       <c r="J102" s="79"/>
       <c r="K102" s="79"/>
       <c r="L102" s="80" t="n">
-        <v>99.01</v>
+        <v>18.74375</v>
       </c>
       <c r="M102" s="79"/>
       <c r="N102" s="79"/>
@@ -24103,15 +24270,15 @@
         <v>0</v>
       </c>
       <c r="S102" s="66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B103" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C103" s="77" t="n">
         <v>2026</v>
@@ -24123,54 +24290,54 @@
         <v>46203</v>
       </c>
       <c r="F103" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G103" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H103" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G103" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H103" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I103" s="79" t="n">
-        <v>22443.411</v>
+        <v>23281.188</v>
       </c>
       <c r="J103" s="79" t="n">
-        <v>14589.612</v>
+        <v>7154.196</v>
       </c>
       <c r="K103" s="79" t="n">
-        <v>10368072000</v>
+        <v>2981775000</v>
       </c>
       <c r="L103" s="80" t="n">
-        <v>108.93</v>
+        <v>15.28</v>
       </c>
       <c r="M103" s="79" t="n">
-        <v>96.3654</v>
+        <v>195.0784</v>
       </c>
       <c r="N103" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O103" s="79" t="n">
-        <v>23288.098</v>
+        <v>49562.802</v>
       </c>
       <c r="P103" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q103" s="80" t="n">
-        <v>1615</v>
+        <v>1915</v>
       </c>
       <c r="R103" s="47" t="n">
         <v>1</v>
       </c>
       <c r="S103" s="66" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C104" s="77" t="n">
         <v>2026</v>
@@ -24182,54 +24349,54 @@
         <v>46112</v>
       </c>
       <c r="F104" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G104" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H104" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G104" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H104" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I104" s="79" t="n">
-        <v>13182.608</v>
+        <v>20863.649</v>
       </c>
       <c r="J104" s="79" t="n">
-        <v>7791.357</v>
+        <v>6001.841</v>
       </c>
       <c r="K104" s="79" t="n">
-        <v>5466357000</v>
+        <v>2273834000</v>
       </c>
       <c r="L104" s="80" t="n">
-        <v>57.49</v>
+        <v>11.66</v>
       </c>
       <c r="M104" s="79" t="n">
-        <v>96.3552</v>
+        <v>195.0784</v>
       </c>
       <c r="N104" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O104" s="79" t="n">
-        <v>14500.386</v>
+        <v>46639.663</v>
       </c>
       <c r="P104" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q104" s="80" t="n">
-        <v>847</v>
+        <v>1740</v>
       </c>
       <c r="R104" s="47" t="n">
         <v>2</v>
       </c>
       <c r="S104" s="66" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B105" s="76" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C105" s="77" t="n">
         <v>2025</v>
@@ -24241,54 +24408,54 @@
         <v>46022</v>
       </c>
       <c r="F105" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G105" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H105" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G105" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H105" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I105" s="79" t="n">
-        <v>4806.69</v>
+        <v>19779.964</v>
       </c>
       <c r="J105" s="79" t="n">
-        <v>1597.288</v>
+        <v>6315.679</v>
       </c>
       <c r="K105" s="79" t="n">
-        <v>870716000</v>
+        <v>2740078000</v>
       </c>
       <c r="L105" s="80" t="n">
-        <v>9.26</v>
+        <v>14.08</v>
       </c>
       <c r="M105" s="79" t="n">
-        <v>96.0407</v>
+        <v>194.9699</v>
       </c>
       <c r="N105" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O105" s="79" t="n">
-        <v>8940.787</v>
+        <v>46634.452</v>
       </c>
       <c r="P105" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q105" s="80" t="n">
-        <v>576</v>
+        <v>1520</v>
       </c>
       <c r="R105" s="47" t="n">
         <v>3</v>
       </c>
       <c r="S105" s="66" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B106" s="76" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C106" s="77" t="n">
         <v>2025</v>
@@ -24300,54 +24467,54 @@
         <v>45930</v>
       </c>
       <c r="F106" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G106" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H106" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G106" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H106" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I106" s="79" t="n">
-        <v>3807.401</v>
+        <v>18413.195</v>
       </c>
       <c r="J106" s="79" t="n">
-        <v>1248.818</v>
+        <v>6122.914</v>
       </c>
       <c r="K106" s="79" t="n">
-        <v>643038000</v>
+        <v>2628697000</v>
       </c>
       <c r="L106" s="80" t="n">
-        <v>6.87</v>
+        <v>13.51</v>
       </c>
       <c r="M106" s="79" t="n">
-        <v>95.3452</v>
+        <v>194.9599</v>
       </c>
       <c r="N106" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O106" s="79" t="n">
-        <v>7932.37</v>
+        <v>42028.78</v>
       </c>
       <c r="P106" s="80" t="n">
-        <v>9.37723774</v>
+        <v>10.50548249</v>
       </c>
       <c r="Q106" s="80" t="n">
-        <v>329.5</v>
+        <v>1030</v>
       </c>
       <c r="R106" s="47" t="n">
         <v>4</v>
       </c>
       <c r="S106" s="66" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B107" s="76" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C107" s="77" t="n">
         <v>2025</v>
@@ -24359,54 +24526,54 @@
         <v>45838</v>
       </c>
       <c r="F107" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G107" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H107" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G107" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H107" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I107" s="79" t="n">
-        <v>3028.429</v>
+        <v>16933.328</v>
       </c>
       <c r="J107" s="79" t="n">
-        <v>785.089</v>
+        <v>5268.882</v>
       </c>
       <c r="K107" s="79" t="n">
-        <v>185349000</v>
+        <v>2024484000</v>
       </c>
       <c r="L107" s="80" t="n">
-        <v>2.02</v>
+        <v>10.54</v>
       </c>
       <c r="M107" s="79" t="n">
-        <v>91.6411</v>
+        <v>192.0711</v>
       </c>
       <c r="N107" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="79" t="n">
-        <v>7184.405</v>
+        <v>36600.942</v>
       </c>
       <c r="P107" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q107" s="80" t="n">
-        <v>237</v>
+        <v>848</v>
       </c>
       <c r="R107" s="47" t="n">
         <v>5</v>
       </c>
       <c r="S107" s="66" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B108" s="76" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C108" s="77" t="n">
         <v>2025</v>
@@ -24418,54 +24585,54 @@
         <v>45747</v>
       </c>
       <c r="F108" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G108" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H108" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G108" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H108" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I108" s="79" t="n">
-        <v>2618.742</v>
+        <v>16120.785</v>
       </c>
       <c r="J108" s="79" t="n">
-        <v>800.733</v>
+        <v>4897.124</v>
       </c>
       <c r="K108" s="79" t="n">
-        <v>336540000</v>
+        <v>1612107000</v>
       </c>
       <c r="L108" s="80" t="n">
-        <v>3.68</v>
+        <v>8.49</v>
       </c>
       <c r="M108" s="79" t="n">
-        <v>91.5746</v>
+        <v>190.0832</v>
       </c>
       <c r="N108" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O108" s="79" t="n">
-        <v>7854.351</v>
+        <v>36910.274</v>
       </c>
       <c r="P108" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q108" s="80" t="n">
-        <v>250.5</v>
+        <v>504</v>
       </c>
       <c r="R108" s="47" t="n">
         <v>6</v>
       </c>
       <c r="S108" s="66" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B109" s="76" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C109" s="77" t="n">
         <v>2024</v>
@@ -24477,54 +24644,54 @@
         <v>45657</v>
       </c>
       <c r="F109" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G109" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H109" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G109" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H109" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I109" s="79" t="n">
-        <v>2228.005</v>
+        <v>14411.637</v>
       </c>
       <c r="J109" s="79" t="n">
-        <v>648.956</v>
+        <v>4147.995</v>
       </c>
       <c r="K109" s="79" t="n">
-        <v>271532000</v>
+        <v>1555805000</v>
       </c>
       <c r="L109" s="80" t="n">
-        <v>2.97</v>
+        <v>8.53</v>
       </c>
       <c r="M109" s="79" t="n">
-        <v>91.4561</v>
+        <v>189.5543</v>
       </c>
       <c r="N109" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O109" s="79" t="n">
-        <v>7491.143</v>
+        <v>36208.816</v>
       </c>
       <c r="P109" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q109" s="80" t="n">
-        <v>218</v>
+        <v>612</v>
       </c>
       <c r="R109" s="47" t="n">
         <v>7</v>
       </c>
       <c r="S109" s="66" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B110" s="76" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C110" s="77" t="n">
         <v>2024</v>
@@ -24536,54 +24703,54 @@
         <v>45565</v>
       </c>
       <c r="F110" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G110" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H110" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G110" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H110" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I110" s="79" t="n">
-        <v>2321.419</v>
+        <v>14259.287</v>
       </c>
       <c r="J110" s="79" t="n">
-        <v>658.433</v>
+        <v>4181.908</v>
       </c>
       <c r="K110" s="79" t="n">
-        <v>188620000</v>
+        <v>1257207000</v>
       </c>
       <c r="L110" s="80" t="n">
-        <v>2.08</v>
+        <v>7.07</v>
       </c>
       <c r="M110" s="79" t="n">
-        <v>91.3372</v>
+        <v>183.3902</v>
       </c>
       <c r="N110" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O110" s="79" t="n">
-        <v>7196.228</v>
+        <v>33244.409</v>
       </c>
       <c r="P110" s="80" t="n">
-        <v>10.2</v>
+        <v>8.7807351</v>
       </c>
       <c r="Q110" s="80" t="n">
-        <v>282</v>
+        <v>461</v>
       </c>
       <c r="R110" s="47" t="n">
         <v>8</v>
       </c>
       <c r="S110" s="66" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B111" s="76" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C111" s="77" t="n">
         <v>2024</v>
@@ -24595,54 +24762,54 @@
         <v>45473</v>
       </c>
       <c r="F111" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G111" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H111" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G111" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H111" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I111" s="79" t="n">
-        <v>2190.229</v>
+        <v>12983.996</v>
       </c>
       <c r="J111" s="79" t="n">
-        <v>759.289</v>
+        <v>3649.998</v>
       </c>
       <c r="K111" s="79" t="n">
-        <v>294050000</v>
+        <v>1002454000</v>
       </c>
       <c r="L111" s="80" t="n">
-        <v>3.26</v>
+        <v>6.13</v>
       </c>
       <c r="M111" s="79" t="n">
-        <v>88.3977</v>
+        <v>166.5369</v>
       </c>
       <c r="N111" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="79" t="n">
-        <v>6803.334</v>
+        <v>26234.193</v>
       </c>
       <c r="P111" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q111" s="80" t="n">
-        <v>302</v>
+        <v>374</v>
       </c>
       <c r="R111" s="47" t="n">
         <v>9</v>
       </c>
       <c r="S111" s="66" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B112" s="76" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C112" s="77" t="n">
         <v>2024</v>
@@ -24654,54 +24821,54 @@
         <v>45382</v>
       </c>
       <c r="F112" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G112" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H112" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G112" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H112" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I112" s="79" t="n">
-        <v>2175.989</v>
+        <v>12425.561</v>
       </c>
       <c r="J112" s="79" t="n">
-        <v>758.571</v>
+        <v>3272.937</v>
       </c>
       <c r="K112" s="79" t="n">
-        <v>351970000</v>
+        <v>580672000</v>
       </c>
       <c r="L112" s="80" t="n">
-        <v>3.98</v>
+        <v>3.56</v>
       </c>
       <c r="M112" s="79" t="n">
-        <v>88.3977</v>
+        <v>163.4296</v>
       </c>
       <c r="N112" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O112" s="79" t="n">
-        <v>7398.652</v>
+        <v>24110.138</v>
       </c>
       <c r="P112" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="80" t="n">
-        <v>305.5</v>
+        <v>259</v>
       </c>
       <c r="R112" s="47" t="n">
         <v>10</v>
       </c>
       <c r="S112" s="66" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B113" s="76" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C113" s="77" t="n">
         <v>2023</v>
@@ -24713,54 +24880,54 @@
         <v>45291</v>
       </c>
       <c r="F113" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G113" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H113" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G113" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H113" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I113" s="79" t="n">
-        <v>2130.049</v>
+        <v>12195.595</v>
       </c>
       <c r="J113" s="79" t="n">
-        <v>707.384</v>
+        <v>2990.764</v>
       </c>
       <c r="K113" s="79" t="n">
-        <v>262238000</v>
+        <v>507876000</v>
       </c>
       <c r="L113" s="80" t="n">
-        <v>2.96</v>
+        <v>3.11</v>
       </c>
       <c r="M113" s="79" t="n">
-        <v>88.3977</v>
+        <v>163.3091</v>
       </c>
       <c r="N113" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="79" t="n">
-        <v>7036.917</v>
+        <v>24585.036</v>
       </c>
       <c r="P113" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q113" s="80" t="n">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="R113" s="47" t="n">
         <v>11</v>
       </c>
       <c r="S113" s="66" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B114" s="76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C114" s="77" t="n">
         <v>2023</v>
@@ -24772,54 +24939,54 @@
         <v>45199</v>
       </c>
       <c r="F114" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G114" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H114" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G114" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H114" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I114" s="79" t="n">
-        <v>1993.007</v>
+        <v>13150.145</v>
       </c>
       <c r="J114" s="79" t="n">
-        <v>687.513</v>
+        <v>3509.563</v>
       </c>
       <c r="K114" s="79" t="n">
-        <v>306457000</v>
+        <v>740556000</v>
       </c>
       <c r="L114" s="80" t="n">
-        <v>3.47</v>
+        <v>4.54</v>
       </c>
       <c r="M114" s="79" t="n">
-        <v>88.3977</v>
+        <v>163.3091</v>
       </c>
       <c r="N114" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="79" t="n">
-        <v>6756.961</v>
+        <v>24173.791</v>
       </c>
       <c r="P114" s="80" t="n">
-        <v>13.78192729</v>
+        <v>9.88572038</v>
       </c>
       <c r="Q114" s="80" t="n">
-        <v>296.5</v>
+        <v>270</v>
       </c>
       <c r="R114" s="47" t="n">
         <v>12</v>
       </c>
       <c r="S114" s="66" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B115" s="76" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C115" s="77" t="n">
         <v>2023</v>
@@ -24831,54 +24998,54 @@
         <v>45107</v>
       </c>
       <c r="F115" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G115" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H115" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G115" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H115" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I115" s="79" t="n">
-        <v>1930.516</v>
+        <v>13004.395</v>
       </c>
       <c r="J115" s="79" t="n">
-        <v>636.105</v>
+        <v>2850.162</v>
       </c>
       <c r="K115" s="79" t="n">
-        <v>230718000</v>
+        <v>440991000</v>
       </c>
       <c r="L115" s="80" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="M115" s="79" t="n">
-        <v>86.6666</v>
+        <v>161.5773</v>
       </c>
       <c r="N115" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="79" t="n">
-        <v>6433.521</v>
+        <v>23063.842</v>
       </c>
       <c r="P115" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="80" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="R115" s="47" t="n">
         <v>13</v>
       </c>
       <c r="S115" s="66" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B116" s="76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C116" s="77" t="n">
         <v>2023</v>
@@ -24890,54 +25057,54 @@
         <v>45016</v>
       </c>
       <c r="F116" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G116" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H116" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G116" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H116" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I116" s="79" t="n">
-        <v>2260.206</v>
+        <v>12701.656</v>
       </c>
       <c r="J116" s="79" t="n">
-        <v>814.91</v>
+        <v>3236.323</v>
       </c>
       <c r="K116" s="79" t="n">
-        <v>348203000</v>
+        <v>627932000</v>
       </c>
       <c r="L116" s="80" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="M116" s="79" t="n">
-        <v>86.6666</v>
+        <v>156.5623</v>
       </c>
       <c r="N116" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O116" s="79" t="n">
-        <v>7382.85</v>
+        <v>21836.795</v>
       </c>
       <c r="P116" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q116" s="80" t="n">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="R116" s="47" t="n">
         <v>14</v>
       </c>
       <c r="S116" s="66" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B117" s="76" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C117" s="77" t="n">
         <v>2022</v>
@@ -24949,54 +25116,54 @@
         <v>44926</v>
       </c>
       <c r="F117" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G117" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H117" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G117" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H117" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I117" s="79" t="n">
-        <v>2286.572</v>
+        <v>13600.543</v>
       </c>
       <c r="J117" s="79" t="n">
-        <v>860.807</v>
+        <v>3572.38</v>
       </c>
       <c r="K117" s="79" t="n">
-        <v>385061000</v>
+        <v>922388000</v>
       </c>
       <c r="L117" s="80" t="n">
-        <v>4.44</v>
+        <v>5.88</v>
       </c>
       <c r="M117" s="79" t="n">
-        <v>86.5531</v>
+        <v>156.4463</v>
       </c>
       <c r="N117" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O117" s="79" t="n">
-        <v>7012.867</v>
+        <v>22485.042</v>
       </c>
       <c r="P117" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q117" s="80" t="n">
-        <v>185.5</v>
+        <v>236.5</v>
       </c>
       <c r="R117" s="47" t="n">
         <v>15</v>
       </c>
       <c r="S117" s="66" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B118" s="76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C118" s="77" t="n">
         <v>2022</v>
@@ -25008,54 +25175,54 @@
         <v>44834</v>
       </c>
       <c r="F118" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G118" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H118" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G118" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H118" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I118" s="79" t="n">
-        <v>2560.341</v>
+        <v>14526.402</v>
       </c>
       <c r="J118" s="79" t="n">
-        <v>914.902</v>
+        <v>3740.877</v>
       </c>
       <c r="K118" s="79" t="n">
-        <v>542661000</v>
+        <v>1184084000</v>
       </c>
       <c r="L118" s="80" t="n">
-        <v>6.28</v>
+        <v>7.64</v>
       </c>
       <c r="M118" s="79" t="n">
-        <v>86.4706</v>
+        <v>156.4273</v>
       </c>
       <c r="N118" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O118" s="79" t="n">
-        <v>6611.975</v>
+        <v>20970.774</v>
       </c>
       <c r="P118" s="80" t="n">
-        <v>11.5240749</v>
+        <v>9.44960126</v>
       </c>
       <c r="Q118" s="80" t="n">
-        <v>161.5</v>
+        <v>280.5</v>
       </c>
       <c r="R118" s="47" t="n">
         <v>16</v>
       </c>
       <c r="S118" s="66" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B119" s="76" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C119" s="77" t="n">
         <v>2022</v>
@@ -25067,54 +25234,54 @@
         <v>44742</v>
       </c>
       <c r="F119" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G119" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H119" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G119" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H119" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I119" s="79" t="n">
-        <v>2866.579</v>
+        <v>13963.028</v>
       </c>
       <c r="J119" s="79" t="n">
-        <v>947.502</v>
+        <v>3625.501</v>
       </c>
       <c r="K119" s="79" t="n">
-        <v>536500000</v>
+        <v>1172964000</v>
       </c>
       <c r="L119" s="80" t="n">
-        <v>6.41</v>
+        <v>7.68</v>
       </c>
       <c r="M119" s="79" t="n">
-        <v>83.895</v>
+        <v>152.7509</v>
       </c>
       <c r="N119" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O119" s="79" t="n">
-        <v>6043.861</v>
+        <v>19031.3</v>
       </c>
       <c r="P119" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q119" s="80" t="n">
-        <v>162.5</v>
+        <v>308.5</v>
       </c>
       <c r="R119" s="47" t="n">
         <v>17</v>
       </c>
       <c r="S119" s="66" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B120" s="76" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C120" s="77" t="n">
         <v>2022</v>
@@ -25126,54 +25293,54 @@
         <v>44651</v>
       </c>
       <c r="F120" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G120" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H120" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G120" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H120" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I120" s="79" t="n">
-        <v>2589.737</v>
+        <v>11667.198</v>
       </c>
       <c r="J120" s="79" t="n">
-        <v>735.407</v>
+        <v>2848.725</v>
       </c>
       <c r="K120" s="79" t="n">
-        <v>385967000</v>
+        <v>558944000</v>
       </c>
       <c r="L120" s="80" t="n">
-        <v>4.64</v>
+        <v>3.74</v>
       </c>
       <c r="M120" s="79" t="n">
-        <v>83.7225</v>
+        <v>152.6274</v>
       </c>
       <c r="N120" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O120" s="79" t="n">
-        <v>6458.201</v>
+        <v>18361.569</v>
       </c>
       <c r="P120" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q120" s="80" t="n">
-        <v>215</v>
+        <v>296.5</v>
       </c>
       <c r="R120" s="47" t="n">
         <v>18</v>
       </c>
       <c r="S120" s="66" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B121" s="76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C121" s="77" t="n">
         <v>2021</v>
@@ -25185,54 +25352,54 @@
         <v>44561</v>
       </c>
       <c r="F121" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G121" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H121" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G121" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H121" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I121" s="79" t="n">
-        <v>2396.847</v>
+        <v>7998.723</v>
       </c>
       <c r="J121" s="79" t="n">
-        <v>677.529</v>
+        <v>1842.97</v>
       </c>
       <c r="K121" s="79" t="n">
-        <v>290253000</v>
+        <v>568796000</v>
       </c>
       <c r="L121" s="80" t="n">
-        <v>3.51</v>
+        <v>4.2</v>
       </c>
       <c r="M121" s="79" t="n">
-        <v>82.668</v>
+        <v>137.4573</v>
       </c>
       <c r="N121" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O121" s="79" t="n">
-        <v>5960.989</v>
+        <v>15124.585</v>
       </c>
       <c r="P121" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="80" t="n">
-        <v>204</v>
+        <v>261</v>
       </c>
       <c r="R121" s="47" t="n">
         <v>19</v>
       </c>
       <c r="S121" s="66" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B122" s="76" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C122" s="77" t="n">
         <v>2021</v>
@@ -25244,54 +25411,54 @@
         <v>44469</v>
       </c>
       <c r="F122" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G122" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H122" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G122" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H122" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I122" s="79" t="n">
-        <v>2973.845</v>
+        <v>7415.446</v>
       </c>
       <c r="J122" s="79" t="n">
-        <v>975.336</v>
+        <v>1754.141</v>
       </c>
       <c r="K122" s="79" t="n">
-        <v>533714000</v>
+        <v>606283000</v>
       </c>
       <c r="L122" s="80" t="n">
-        <v>6.46</v>
+        <v>4.54</v>
       </c>
       <c r="M122" s="79" t="n">
-        <v>82.628</v>
+        <v>133.6901</v>
       </c>
       <c r="N122" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O122" s="79" t="n">
-        <v>5663.586</v>
+        <v>13768.063</v>
       </c>
       <c r="P122" s="80" t="n">
-        <v>6.69560253</v>
+        <v>8.02486316</v>
       </c>
       <c r="Q122" s="80" t="n">
-        <v>182</v>
+        <v>223.5</v>
       </c>
       <c r="R122" s="47" t="n">
         <v>20</v>
       </c>
       <c r="S122" s="66" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B123" s="76" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C123" s="77" t="n">
         <v>2021</v>
@@ -25303,54 +25470,54 @@
         <v>44377</v>
       </c>
       <c r="F123" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G123" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H123" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G123" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H123" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I123" s="79" t="n">
-        <v>2885.046</v>
+        <v>7015.992</v>
       </c>
       <c r="J123" s="79" t="n">
-        <v>888.15</v>
+        <v>1670.731</v>
       </c>
       <c r="K123" s="79" t="n">
-        <v>477358000</v>
+        <v>551411000</v>
       </c>
       <c r="L123" s="80" t="n">
-        <v>5.79</v>
+        <v>4.13</v>
       </c>
       <c r="M123" s="79" t="n">
-        <v>82.516</v>
+        <v>133.6363</v>
       </c>
       <c r="N123" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O123" s="79" t="n">
-        <v>5668.615</v>
+        <v>13273.987</v>
       </c>
       <c r="P123" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q123" s="80" t="n">
-        <v>190.5</v>
+        <v>259</v>
       </c>
       <c r="R123" s="47" t="n">
         <v>21</v>
       </c>
       <c r="S123" s="66" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B124" s="76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C124" s="77" t="n">
         <v>2021</v>
@@ -25362,54 +25529,54 @@
         <v>44286</v>
       </c>
       <c r="F124" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G124" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H124" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G124" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H124" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I124" s="79" t="n">
-        <v>1939.92</v>
+        <v>6134.214</v>
       </c>
       <c r="J124" s="79" t="n">
-        <v>551.203</v>
+        <v>1361.63</v>
       </c>
       <c r="K124" s="79" t="n">
-        <v>259563000</v>
+        <v>309648000</v>
       </c>
       <c r="L124" s="80" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="M124" s="79" t="n">
-        <v>82.459</v>
+        <v>133.6363</v>
       </c>
       <c r="N124" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O124" s="79" t="n">
-        <v>5182.897</v>
+        <v>12907.3</v>
       </c>
       <c r="P124" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q124" s="80" t="n">
-        <v>170</v>
+        <v>266</v>
       </c>
       <c r="R124" s="47" t="n">
         <v>22</v>
       </c>
       <c r="S124" s="66" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B125" s="76" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C125" s="77" t="n">
         <v>2020</v>
@@ -25421,54 +25588,54 @@
         <v>44196</v>
       </c>
       <c r="F125" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G125" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H125" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G125" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H125" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I125" s="79" t="n">
-        <v>1575.49</v>
+        <v>6266.652</v>
       </c>
       <c r="J125" s="79" t="n">
-        <v>458.968</v>
+        <v>1550.737</v>
       </c>
       <c r="K125" s="79" t="n">
-        <v>175456000</v>
+        <v>589079000</v>
       </c>
       <c r="L125" s="80" t="n">
-        <v>2.16</v>
+        <v>4.52</v>
       </c>
       <c r="M125" s="79" t="n">
-        <v>81.324</v>
+        <v>130.5694</v>
       </c>
       <c r="N125" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O125" s="79" t="n">
-        <v>4816.246</v>
+        <v>13237.341</v>
       </c>
       <c r="P125" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q125" s="80" t="n">
-        <v>166</v>
+        <v>243.5</v>
       </c>
       <c r="R125" s="47" t="n">
         <v>23</v>
       </c>
       <c r="S125" s="66" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B126" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C126" s="77" t="n">
         <v>2020</v>
@@ -25480,199 +25647,1656 @@
         <v>44104</v>
       </c>
       <c r="F126" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G126" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H126" s="76" t="s">
         <v>210</v>
       </c>
-      <c r="G126" s="76" t="s">
-        <v>211</v>
-      </c>
-      <c r="H126" s="76" t="s">
-        <v>207</v>
-      </c>
       <c r="I126" s="79" t="n">
-        <v>1627.205</v>
+        <v>6049.454</v>
       </c>
       <c r="J126" s="79" t="n">
-        <v>493.122</v>
+        <v>1589.297</v>
       </c>
       <c r="K126" s="79" t="n">
-        <v>194271000</v>
+        <v>499580000</v>
       </c>
       <c r="L126" s="80" t="n">
-        <v>2.39</v>
+        <v>3.83</v>
       </c>
       <c r="M126" s="79" t="n">
-        <v>81.324</v>
+        <v>130.5694</v>
       </c>
       <c r="N126" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O126" s="79" t="n">
-        <v>4634.348</v>
+        <v>12368.366</v>
       </c>
       <c r="P126" s="80"/>
       <c r="Q126" s="80" t="n">
-        <v>158.5</v>
+        <v>225.5</v>
       </c>
       <c r="R126" s="47" t="n">
         <v>24</v>
       </c>
       <c r="S126" s="66" t="s">
-        <v>358</v>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B127" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="C127" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D127" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" s="78" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F127" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G127" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H127" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I127" s="79"/>
+      <c r="J127" s="79"/>
+      <c r="K127" s="79"/>
+      <c r="L127" s="80" t="n">
+        <v>99.01</v>
+      </c>
+      <c r="M127" s="79"/>
+      <c r="N127" s="79"/>
+      <c r="O127" s="79"/>
+      <c r="P127" s="80"/>
+      <c r="Q127" s="80"/>
+      <c r="R127" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="66" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="81" t="s">
-        <v>359</v>
+      <c r="A128" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B128" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="C128" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D128" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" s="78" t="n">
+        <v>46203</v>
+      </c>
+      <c r="F128" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G128" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H128" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I128" s="79" t="n">
+        <v>22443.411</v>
+      </c>
+      <c r="J128" s="79" t="n">
+        <v>14589.612</v>
+      </c>
+      <c r="K128" s="79" t="n">
+        <v>10368072000</v>
+      </c>
+      <c r="L128" s="80" t="n">
+        <v>108.93</v>
+      </c>
+      <c r="M128" s="79" t="n">
+        <v>96.3654</v>
+      </c>
+      <c r="N128" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="79" t="n">
+        <v>23288.098</v>
+      </c>
+      <c r="P128" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="80" t="n">
+        <v>1615</v>
+      </c>
+      <c r="R128" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S128" s="66" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="42" t="s">
-        <v>360</v>
+      <c r="A129" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B129" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="C129" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D129" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="78" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F129" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G129" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H129" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I129" s="79" t="n">
+        <v>13182.608</v>
+      </c>
+      <c r="J129" s="79" t="n">
+        <v>7791.357</v>
+      </c>
+      <c r="K129" s="79" t="n">
+        <v>5466357000</v>
+      </c>
+      <c r="L129" s="80" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="M129" s="79" t="n">
+        <v>96.3552</v>
+      </c>
+      <c r="N129" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="79" t="n">
+        <v>14500.386</v>
+      </c>
+      <c r="P129" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="80" t="n">
+        <v>847</v>
+      </c>
+      <c r="R129" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S129" s="66" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="82" t="s">
-        <v>361</v>
-      </c>
-      <c r="C130" s="24" t="s">
-        <v>362</v>
+      <c r="A130" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B130" s="76" t="s">
+        <v>218</v>
+      </c>
+      <c r="C130" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D130" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E130" s="78" t="n">
+        <v>46022</v>
+      </c>
+      <c r="F130" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G130" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H130" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I130" s="79" t="n">
+        <v>4806.69</v>
+      </c>
+      <c r="J130" s="79" t="n">
+        <v>1597.288</v>
+      </c>
+      <c r="K130" s="79" t="n">
+        <v>870716000</v>
+      </c>
+      <c r="L130" s="80" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="M130" s="79" t="n">
+        <v>96.0407</v>
+      </c>
+      <c r="N130" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="79" t="n">
+        <v>8940.787</v>
+      </c>
+      <c r="P130" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="80" t="n">
+        <v>576</v>
+      </c>
+      <c r="R130" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S130" s="66" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="82" t="s">
-        <v>363</v>
-      </c>
-      <c r="C131" s="24" t="s">
-        <v>362</v>
+      <c r="A131" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B131" s="76" t="s">
+        <v>220</v>
+      </c>
+      <c r="C131" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D131" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="78" t="n">
+        <v>45930</v>
+      </c>
+      <c r="F131" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G131" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H131" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I131" s="79" t="n">
+        <v>3807.401</v>
+      </c>
+      <c r="J131" s="79" t="n">
+        <v>1248.818</v>
+      </c>
+      <c r="K131" s="79" t="n">
+        <v>643038000</v>
+      </c>
+      <c r="L131" s="80" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="M131" s="79" t="n">
+        <v>95.3452</v>
+      </c>
+      <c r="N131" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="79" t="n">
+        <v>7932.37</v>
+      </c>
+      <c r="P131" s="80" t="n">
+        <v>9.37723774</v>
+      </c>
+      <c r="Q131" s="80" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="R131" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S131" s="66" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="82" t="s">
-        <v>364</v>
-      </c>
-      <c r="C132" s="24" t="s">
-        <v>362</v>
+      <c r="A132" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B132" s="76" t="s">
+        <v>222</v>
+      </c>
+      <c r="C132" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D132" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" s="78" t="n">
+        <v>45838</v>
+      </c>
+      <c r="F132" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G132" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H132" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I132" s="79" t="n">
+        <v>3028.429</v>
+      </c>
+      <c r="J132" s="79" t="n">
+        <v>785.089</v>
+      </c>
+      <c r="K132" s="79" t="n">
+        <v>185349000</v>
+      </c>
+      <c r="L132" s="80" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M132" s="79" t="n">
+        <v>91.6411</v>
+      </c>
+      <c r="N132" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="79" t="n">
+        <v>7184.405</v>
+      </c>
+      <c r="P132" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="80" t="n">
+        <v>237</v>
+      </c>
+      <c r="R132" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S132" s="66" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="82" t="s">
-        <v>365</v>
-      </c>
-      <c r="C133" s="24" t="s">
-        <v>362</v>
+      <c r="A133" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B133" s="76" t="s">
+        <v>224</v>
+      </c>
+      <c r="C133" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D133" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="78" t="n">
+        <v>45747</v>
+      </c>
+      <c r="F133" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G133" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H133" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I133" s="79" t="n">
+        <v>2618.742</v>
+      </c>
+      <c r="J133" s="79" t="n">
+        <v>800.733</v>
+      </c>
+      <c r="K133" s="79" t="n">
+        <v>336540000</v>
+      </c>
+      <c r="L133" s="80" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="M133" s="79" t="n">
+        <v>91.5746</v>
+      </c>
+      <c r="N133" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="79" t="n">
+        <v>7854.351</v>
+      </c>
+      <c r="P133" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="80" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="R133" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S133" s="66" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="82" t="s">
-        <v>366</v>
-      </c>
-      <c r="C134" s="24" t="s">
-        <v>362</v>
+      <c r="A134" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B134" s="76" t="s">
+        <v>226</v>
+      </c>
+      <c r="C134" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D134" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E134" s="78" t="n">
+        <v>45657</v>
+      </c>
+      <c r="F134" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G134" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H134" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I134" s="79" t="n">
+        <v>2228.005</v>
+      </c>
+      <c r="J134" s="79" t="n">
+        <v>648.956</v>
+      </c>
+      <c r="K134" s="79" t="n">
+        <v>271532000</v>
+      </c>
+      <c r="L134" s="80" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="M134" s="79" t="n">
+        <v>91.4561</v>
+      </c>
+      <c r="N134" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="79" t="n">
+        <v>7491.143</v>
+      </c>
+      <c r="P134" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="80" t="n">
+        <v>218</v>
+      </c>
+      <c r="R134" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="S134" s="66" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="82" t="s">
-        <v>367</v>
-      </c>
-      <c r="C135" s="24" t="s">
-        <v>368</v>
+      <c r="A135" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B135" s="76" t="s">
+        <v>228</v>
+      </c>
+      <c r="C135" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D135" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E135" s="78" t="n">
+        <v>45565</v>
+      </c>
+      <c r="F135" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G135" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H135" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I135" s="79" t="n">
+        <v>2321.419</v>
+      </c>
+      <c r="J135" s="79" t="n">
+        <v>658.433</v>
+      </c>
+      <c r="K135" s="79" t="n">
+        <v>188620000</v>
+      </c>
+      <c r="L135" s="80" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M135" s="79" t="n">
+        <v>91.3372</v>
+      </c>
+      <c r="N135" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="79" t="n">
+        <v>7196.228</v>
+      </c>
+      <c r="P135" s="80" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q135" s="80" t="n">
+        <v>282</v>
+      </c>
+      <c r="R135" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="S135" s="66" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="82" t="s">
-        <v>369</v>
-      </c>
-      <c r="C136" s="24" t="s">
-        <v>368</v>
+      <c r="A136" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B136" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="C136" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D136" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="78" t="n">
+        <v>45473</v>
+      </c>
+      <c r="F136" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G136" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H136" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I136" s="79" t="n">
+        <v>2190.229</v>
+      </c>
+      <c r="J136" s="79" t="n">
+        <v>759.289</v>
+      </c>
+      <c r="K136" s="79" t="n">
+        <v>294050000</v>
+      </c>
+      <c r="L136" s="80" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M136" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N136" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="79" t="n">
+        <v>6803.334</v>
+      </c>
+      <c r="P136" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="80" t="n">
+        <v>302</v>
+      </c>
+      <c r="R136" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="S136" s="66" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="82" t="s">
-        <v>370</v>
-      </c>
-      <c r="C137" s="25" t="s">
-        <v>371</v>
+      <c r="A137" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B137" s="76" t="s">
+        <v>232</v>
+      </c>
+      <c r="C137" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D137" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="78" t="n">
+        <v>45382</v>
+      </c>
+      <c r="F137" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G137" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H137" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I137" s="79" t="n">
+        <v>2175.989</v>
+      </c>
+      <c r="J137" s="79" t="n">
+        <v>758.571</v>
+      </c>
+      <c r="K137" s="79" t="n">
+        <v>351970000</v>
+      </c>
+      <c r="L137" s="80" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="M137" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N137" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="79" t="n">
+        <v>7398.652</v>
+      </c>
+      <c r="P137" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="80" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="R137" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S137" s="66" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="82" t="s">
-        <v>372</v>
-      </c>
-      <c r="C138" s="24" t="s">
+      <c r="A138" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B138" s="76" t="s">
+        <v>234</v>
+      </c>
+      <c r="C138" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D138" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" s="78" t="n">
+        <v>45291</v>
+      </c>
+      <c r="F138" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G138" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H138" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I138" s="79" t="n">
+        <v>2130.049</v>
+      </c>
+      <c r="J138" s="79" t="n">
+        <v>707.384</v>
+      </c>
+      <c r="K138" s="79" t="n">
+        <v>262238000</v>
+      </c>
+      <c r="L138" s="80" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M138" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N138" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="79" t="n">
+        <v>7036.917</v>
+      </c>
+      <c r="P138" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="80" t="n">
+        <v>312</v>
+      </c>
+      <c r="R138" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="S138" s="66" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="82" t="s">
+      <c r="A139" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B139" s="76" t="s">
+        <v>236</v>
+      </c>
+      <c r="C139" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D139" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" s="78" t="n">
+        <v>45199</v>
+      </c>
+      <c r="F139" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G139" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H139" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I139" s="79" t="n">
+        <v>1993.007</v>
+      </c>
+      <c r="J139" s="79" t="n">
+        <v>687.513</v>
+      </c>
+      <c r="K139" s="79" t="n">
+        <v>306457000</v>
+      </c>
+      <c r="L139" s="80" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M139" s="79" t="n">
+        <v>88.3977</v>
+      </c>
+      <c r="N139" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="79" t="n">
+        <v>6756.961</v>
+      </c>
+      <c r="P139" s="80" t="n">
+        <v>13.78192729</v>
+      </c>
+      <c r="Q139" s="80" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="R139" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="S139" s="66" t="s">
         <v>374</v>
       </c>
-      <c r="C139" s="24" t="s">
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B140" s="76" t="s">
+        <v>238</v>
+      </c>
+      <c r="C140" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D140" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" s="78" t="n">
+        <v>45107</v>
+      </c>
+      <c r="F140" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G140" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H140" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I140" s="79" t="n">
+        <v>1930.516</v>
+      </c>
+      <c r="J140" s="79" t="n">
+        <v>636.105</v>
+      </c>
+      <c r="K140" s="79" t="n">
+        <v>230718000</v>
+      </c>
+      <c r="L140" s="80" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M140" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N140" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="79" t="n">
+        <v>6433.521</v>
+      </c>
+      <c r="P140" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" s="80" t="n">
+        <v>324</v>
+      </c>
+      <c r="R140" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="S140" s="66" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="82" t="s">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B141" s="76" t="s">
+        <v>240</v>
+      </c>
+      <c r="C141" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D141" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="78" t="n">
+        <v>45016</v>
+      </c>
+      <c r="F141" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G141" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H141" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I141" s="79" t="n">
+        <v>2260.206</v>
+      </c>
+      <c r="J141" s="79" t="n">
+        <v>814.91</v>
+      </c>
+      <c r="K141" s="79" t="n">
+        <v>348203000</v>
+      </c>
+      <c r="L141" s="80" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="M141" s="79" t="n">
+        <v>86.6666</v>
+      </c>
+      <c r="N141" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="79" t="n">
+        <v>7382.85</v>
+      </c>
+      <c r="P141" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" s="80" t="n">
+        <v>314</v>
+      </c>
+      <c r="R141" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="S141" s="66" t="s">
         <v>376</v>
       </c>
-      <c r="C140" s="25" t="s">
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B142" s="76" t="s">
+        <v>242</v>
+      </c>
+      <c r="C142" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D142" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E142" s="78" t="n">
+        <v>44926</v>
+      </c>
+      <c r="F142" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G142" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H142" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I142" s="79" t="n">
+        <v>2286.572</v>
+      </c>
+      <c r="J142" s="79" t="n">
+        <v>860.807</v>
+      </c>
+      <c r="K142" s="79" t="n">
+        <v>385061000</v>
+      </c>
+      <c r="L142" s="80" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="M142" s="79" t="n">
+        <v>86.5531</v>
+      </c>
+      <c r="N142" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="79" t="n">
+        <v>7012.867</v>
+      </c>
+      <c r="P142" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" s="80" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R142" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="S142" s="66" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="82" t="s">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B143" s="76" t="s">
+        <v>244</v>
+      </c>
+      <c r="C143" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D143" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" s="78" t="n">
+        <v>44834</v>
+      </c>
+      <c r="F143" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G143" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H143" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I143" s="79" t="n">
+        <v>2560.341</v>
+      </c>
+      <c r="J143" s="79" t="n">
+        <v>914.902</v>
+      </c>
+      <c r="K143" s="79" t="n">
+        <v>542661000</v>
+      </c>
+      <c r="L143" s="80" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="M143" s="79" t="n">
+        <v>86.4706</v>
+      </c>
+      <c r="N143" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="79" t="n">
+        <v>6611.975</v>
+      </c>
+      <c r="P143" s="80" t="n">
+        <v>11.5240749</v>
+      </c>
+      <c r="Q143" s="80" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="R143" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="S143" s="66" t="s">
         <v>378</v>
       </c>
-      <c r="C141" s="25" t="s">
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B144" s="76" t="s">
+        <v>246</v>
+      </c>
+      <c r="C144" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D144" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" s="78" t="n">
+        <v>44742</v>
+      </c>
+      <c r="F144" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G144" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H144" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I144" s="79" t="n">
+        <v>2866.579</v>
+      </c>
+      <c r="J144" s="79" t="n">
+        <v>947.502</v>
+      </c>
+      <c r="K144" s="79" t="n">
+        <v>536500000</v>
+      </c>
+      <c r="L144" s="80" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="M144" s="79" t="n">
+        <v>83.895</v>
+      </c>
+      <c r="N144" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="79" t="n">
+        <v>6043.861</v>
+      </c>
+      <c r="P144" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="80" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="R144" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="S144" s="66" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="82" t="s">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B145" s="76" t="s">
+        <v>248</v>
+      </c>
+      <c r="C145" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D145" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" s="78" t="n">
+        <v>44651</v>
+      </c>
+      <c r="F145" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G145" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H145" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I145" s="79" t="n">
+        <v>2589.737</v>
+      </c>
+      <c r="J145" s="79" t="n">
+        <v>735.407</v>
+      </c>
+      <c r="K145" s="79" t="n">
+        <v>385967000</v>
+      </c>
+      <c r="L145" s="80" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="M145" s="79" t="n">
+        <v>83.7225</v>
+      </c>
+      <c r="N145" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="79" t="n">
+        <v>6458.201</v>
+      </c>
+      <c r="P145" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="80" t="n">
+        <v>215</v>
+      </c>
+      <c r="R145" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="S145" s="66" t="s">
         <v>380</v>
       </c>
-      <c r="C142" s="24" t="s">
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B146" s="76" t="s">
+        <v>250</v>
+      </c>
+      <c r="C146" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D146" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E146" s="78" t="n">
+        <v>44561</v>
+      </c>
+      <c r="F146" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G146" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H146" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I146" s="79" t="n">
+        <v>2396.847</v>
+      </c>
+      <c r="J146" s="79" t="n">
+        <v>677.529</v>
+      </c>
+      <c r="K146" s="79" t="n">
+        <v>290253000</v>
+      </c>
+      <c r="L146" s="80" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M146" s="79" t="n">
+        <v>82.668</v>
+      </c>
+      <c r="N146" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="79" t="n">
+        <v>5960.989</v>
+      </c>
+      <c r="P146" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="80" t="n">
+        <v>204</v>
+      </c>
+      <c r="R146" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="S146" s="66" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="82" t="s">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B147" s="76" t="s">
+        <v>252</v>
+      </c>
+      <c r="C147" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D147" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" s="78" t="n">
+        <v>44469</v>
+      </c>
+      <c r="F147" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G147" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H147" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I147" s="79" t="n">
+        <v>2973.845</v>
+      </c>
+      <c r="J147" s="79" t="n">
+        <v>975.336</v>
+      </c>
+      <c r="K147" s="79" t="n">
+        <v>533714000</v>
+      </c>
+      <c r="L147" s="80" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M147" s="79" t="n">
+        <v>82.628</v>
+      </c>
+      <c r="N147" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="79" t="n">
+        <v>5663.586</v>
+      </c>
+      <c r="P147" s="80" t="n">
+        <v>6.69560253</v>
+      </c>
+      <c r="Q147" s="80" t="n">
+        <v>182</v>
+      </c>
+      <c r="R147" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="S147" s="66" t="s">
         <v>382</v>
       </c>
-      <c r="C143" s="24" t="s">
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B148" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="C148" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D148" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" s="78" t="n">
+        <v>44377</v>
+      </c>
+      <c r="F148" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G148" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H148" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I148" s="79" t="n">
+        <v>2885.046</v>
+      </c>
+      <c r="J148" s="79" t="n">
+        <v>888.15</v>
+      </c>
+      <c r="K148" s="79" t="n">
+        <v>477358000</v>
+      </c>
+      <c r="L148" s="80" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="M148" s="79" t="n">
+        <v>82.516</v>
+      </c>
+      <c r="N148" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="79" t="n">
+        <v>5668.615</v>
+      </c>
+      <c r="P148" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" s="80" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="R148" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="S148" s="66" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="82" t="s">
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B149" s="76" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D149" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="78" t="n">
+        <v>44286</v>
+      </c>
+      <c r="F149" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G149" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H149" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I149" s="79" t="n">
+        <v>1939.92</v>
+      </c>
+      <c r="J149" s="79" t="n">
+        <v>551.203</v>
+      </c>
+      <c r="K149" s="79" t="n">
+        <v>259563000</v>
+      </c>
+      <c r="L149" s="80" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M149" s="79" t="n">
+        <v>82.459</v>
+      </c>
+      <c r="N149" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="79" t="n">
+        <v>5182.897</v>
+      </c>
+      <c r="P149" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" s="80" t="n">
+        <v>170</v>
+      </c>
+      <c r="R149" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="S149" s="66" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="25" t="s">
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B150" s="76" t="s">
+        <v>258</v>
+      </c>
+      <c r="C150" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D150" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E150" s="78" t="n">
+        <v>44196</v>
+      </c>
+      <c r="F150" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G150" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H150" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I150" s="79" t="n">
+        <v>1575.49</v>
+      </c>
+      <c r="J150" s="79" t="n">
+        <v>458.968</v>
+      </c>
+      <c r="K150" s="79" t="n">
+        <v>175456000</v>
+      </c>
+      <c r="L150" s="80" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M150" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N150" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="79" t="n">
+        <v>4816.246</v>
+      </c>
+      <c r="P150" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" s="80" t="n">
+        <v>166</v>
+      </c>
+      <c r="R150" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="S150" s="66" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="82" t="s">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B151" s="76" t="s">
+        <v>260</v>
+      </c>
+      <c r="C151" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D151" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E151" s="78" t="n">
+        <v>44104</v>
+      </c>
+      <c r="F151" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="G151" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="H151" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="I151" s="79" t="n">
+        <v>1627.205</v>
+      </c>
+      <c r="J151" s="79" t="n">
+        <v>493.122</v>
+      </c>
+      <c r="K151" s="79" t="n">
+        <v>194271000</v>
+      </c>
+      <c r="L151" s="80" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M151" s="79" t="n">
+        <v>81.324</v>
+      </c>
+      <c r="N151" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="79" t="n">
+        <v>4634.348</v>
+      </c>
+      <c r="P151" s="80"/>
+      <c r="Q151" s="80" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="R151" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="S151" s="66" t="s">
         <v>386</v>
       </c>
-      <c r="C145" s="24" t="s">
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="81" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="42" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="82" t="s">
+        <v>389</v>
+      </c>
+      <c r="C155" s="24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="82" t="s">
+        <v>391</v>
+      </c>
+      <c r="C156" s="24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="82" t="s">
+        <v>392</v>
+      </c>
+      <c r="C157" s="24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="82" t="s">
+        <v>393</v>
+      </c>
+      <c r="C158" s="24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="82" t="s">
+        <v>394</v>
+      </c>
+      <c r="C159" s="24" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="82" t="s">
+        <v>395</v>
+      </c>
+      <c r="C160" s="24" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="C161" s="24" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="C162" s="25" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="82" t="s">
+        <v>400</v>
+      </c>
+      <c r="C163" s="24" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="82" t="s">
+        <v>402</v>
+      </c>
+      <c r="C164" s="24" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="82" t="s">
+        <v>404</v>
+      </c>
+      <c r="C165" s="25" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="82" t="s">
+        <v>406</v>
+      </c>
+      <c r="C166" s="25" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="82" t="s">
+        <v>408</v>
+      </c>
+      <c r="C167" s="24" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="82" t="s">
+        <v>410</v>
+      </c>
+      <c r="C168" s="24" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="82" t="s">
+        <v>412</v>
+      </c>
+      <c r="C169" s="25" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="82" t="s">
+        <v>414</v>
+      </c>
+      <c r="C170" s="24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="82" t="s">
-        <v>387</v>
-      </c>
-      <c r="C146" s="24" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="24" t="s">
-        <v>389</v>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="82" t="s">
+        <v>415</v>
+      </c>
+      <c r="C171" s="24" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="24" t="s">
+        <v>417</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S126"/>
+  <autoFilter ref="A1:S151"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -25689,7 +27313,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -25704,19 +27328,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>390</v>
+        <v>418</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>391</v>
+        <v>419</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>392</v>
+        <v>420</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>393</v>
+        <v>421</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>394</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25736,7 +27360,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25756,7 +27380,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25764,19 +27388,19 @@
         <v>179</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>5.31033</v>
+        <v>5.32885</v>
       </c>
       <c r="C4" s="80" t="n">
-        <v>8.78848</v>
+        <v>8.86048</v>
       </c>
       <c r="D4" s="78" t="n">
         <v>46387</v>
       </c>
       <c r="E4" s="77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25796,18 +27420,18 @@
         <v>14</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="76" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>353.215</v>
+        <v>65.61145</v>
       </c>
       <c r="C6" s="80" t="n">
-        <v>194.82417</v>
+        <v>114.78896</v>
       </c>
       <c r="D6" s="78" t="n">
         <v>46387</v>
@@ -25816,12 +27440,32 @@
         <v>2</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
-        <v>395</v>
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="80" t="n">
+        <v>353.215</v>
+      </c>
+      <c r="C7" s="80" t="n">
+        <v>194.82417</v>
+      </c>
+      <c r="D7" s="78" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E7" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="78" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="25" t="s">
+        <v>423</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Dashboard!$A$2:$AC$22</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$151</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">Raw_Q!$A$1:$S$176</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="495">
   <si>
     <r>
       <rPr>
@@ -3896,6 +3896,15 @@
     <t xml:space="preserve">其他電子業</t>
   </si>
   <si>
+    <t xml:space="preserve">5434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">崇越</t>
+  </si>
+  <si>
+    <t xml:space="preserve">電子通路業</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4707,6 +4716,81 @@
   </si>
   <si>
     <t xml:space="preserve">5289|24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5434|24</t>
   </si>
   <si>
     <r>
@@ -7057,7 +7141,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="48">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7124,6 +7208,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFC8E8D0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF2FAF4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7149,6 +7241,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFCCEAD4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5F5E9"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7188,7 +7288,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE5F5E9"/>
+          <fgColor rgb="FFE5F4E9"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7244,6 +7344,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFA7DAB4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFF1F9F3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7268,6 +7376,22 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFE4F4E8"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF74C589"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFDE2E2"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7285,6 +7409,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE8F6EB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAFDFB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7979,7 +8111,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -7994,16 +8126,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>424</v>
+        <v>452</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8093,6 +8225,21 @@
       </c>
       <c r="D7" s="78"/>
       <c r="E7" s="78" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="80" t="n">
+        <v>538</v>
+      </c>
+      <c r="C8" s="78" t="n">
+        <v>46272</v>
+      </c>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78" t="n">
         <v>46272</v>
       </c>
     </row>
@@ -8161,16 +8308,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>427</v>
+        <v>455</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -8179,13 +8326,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -8194,7 +8341,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -8203,16 +8350,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -8221,16 +8368,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -8239,7 +8386,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>443</v>
+        <v>471</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -8248,7 +8395,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -8257,7 +8404,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -8269,19 +8416,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9379,183 +9526,183 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="str">
         <f aca="false">IF(Tickers!A8="","",Tickers!A8)</f>
-        <v/>
+        <v>5434</v>
       </c>
       <c r="B8" s="66" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Tickers!$B$2:$B$100,MATCH($A8,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>崇越</v>
       </c>
       <c r="C8" s="66" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A8,Tickers!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="D8" s="51" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="E8" s="48" t="str">
+        <v>538</v>
+      </c>
+      <c r="E8" s="48" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="F8" s="51" t="str">
+        <v>74199.323</v>
+      </c>
+      <c r="F8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="G8" s="51" t="str">
+        <v>26.89</v>
+      </c>
+      <c r="G8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=0",Raw_Q!$R$2:$R$600,"&lt;=3"),""))</f>
-        <v/>
-      </c>
-      <c r="H8" s="51" t="str">
+        <v>29.04333</v>
+      </c>
+      <c r="H8" s="51" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v/>
-      </c>
-      <c r="I8" s="49" t="str">
+        <v>33.1938356164384</v>
+      </c>
+      <c r="I8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
-        <v/>
-      </c>
-      <c r="J8" s="52" t="str">
+        <v>0.381808838643371</v>
+      </c>
+      <c r="J8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(F8&lt;=0,"N/M",D8/F8),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="K8" s="52" t="str">
+        <v>20.0074377091856</v>
+      </c>
+      <c r="K8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(G8&lt;=0,"N/M",D8/G8),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="L8" s="52" t="str">
+        <v>18.5240466571843</v>
+      </c>
+      <c r="L8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(H8&lt;=0,"N/M",D8/H8),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="M8" s="49" t="str">
+        <v>16.2078286527867</v>
+      </c>
+      <c r="M8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v/>
-      </c>
-      <c r="N8" s="51" t="str">
+        <v>0.126350245499182</v>
+      </c>
+      <c r="N8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(J8)),I8&lt;Config!$B$6),"N/M",J8/(I8*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="O8" s="51" t="str">
+        <v>0.524017143769517</v>
+      </c>
+      <c r="O8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(L8)),M8&lt;Config!$B$6),"N/M",L8/(M8*100)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="P8" s="51" t="str">
+        <v>1.2827698584006</v>
+      </c>
+      <c r="P8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="49" t="str">
+        <v>11.98556796</v>
+      </c>
+      <c r="Q8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(P8=0,"不配息",P8/D8),""))</f>
-        <v/>
+        <v>0.0222780073605948</v>
       </c>
       <c r="R8" s="49" t="str">
         <f aca="false">IF($A8="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
         <v/>
       </c>
-      <c r="S8" s="49" t="str">
+      <c r="S8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="T8" s="49" t="str">
+        <v>0.225972502259101</v>
+      </c>
+      <c r="T8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,2)-1,""))</f>
-        <v/>
-      </c>
-      <c r="U8" s="49" t="str">
+        <v>0.123469656829816</v>
+      </c>
+      <c r="U8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,3)-1,""))</f>
-        <v/>
-      </c>
-      <c r="V8" s="68" t="str">
+        <v>0.0715692637358045</v>
+      </c>
+      <c r="V8" s="68" t="n">
         <f aca="false">IF($A8="","",IFERROR((T8-U8)*100,""))</f>
-        <v/>
+        <v>5.19003930940118</v>
       </c>
       <c r="W8" s="66" t="str">
         <f aca="false">IF($A8="","",IFERROR(IF(NOT(ISNUMBER(T8)),"",IF(T8&gt;0,IF(V8&gt;0,"成長且加速","成長但減速"),IF(V8&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
-        <v/>
-      </c>
-      <c r="X8" s="68" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="X8" s="68" t="n">
         <f aca="false">IF($A8="","",IFERROR((T8-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,6)-1))*100,""))</f>
-        <v/>
-      </c>
-      <c r="Y8" s="49" t="str">
+        <v>4.55869805123967</v>
+      </c>
+      <c r="Y8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v/>
-      </c>
-      <c r="Z8" s="49" t="str">
+        <v>0.656903765690377</v>
+      </c>
+      <c r="Z8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/E8,""))</f>
-        <v/>
-      </c>
-      <c r="AA8" s="49" t="str">
+        <v>0.133194867559641</v>
+      </c>
+      <c r="AA8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v/>
-      </c>
-      <c r="AB8" s="50" t="str">
+        <v>0.129706276539687</v>
+      </c>
+      <c r="AB8" s="50" t="n">
         <f aca="false">IF($A8="","",IFERROR((Z8-AA8)*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AC8" s="50" t="str">
+        <v>34.8859101995386</v>
+      </c>
+      <c r="AC8" s="50" t="n">
         <f aca="false">IF($A8="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))*10000,""))</f>
-        <v/>
-      </c>
-      <c r="AD8" s="51" t="str">
+        <v>179.187320515826</v>
+      </c>
+      <c r="AD8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
-      </c>
-      <c r="AE8" s="48" t="str">
+        <v>113.269957939879</v>
+      </c>
+      <c r="AE8" s="48" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600),""))</f>
-        <v/>
-      </c>
-      <c r="AF8" s="49" t="str">
+        <v>5193.559288</v>
+      </c>
+      <c r="AF8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))&lt;=0,"N/M",AE8/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))/2)),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AG8" s="49" t="str">
+        <v>0.266038124541508</v>
+      </c>
+      <c r="AG8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(AVERAGE(AO8:AS8),""))</f>
-        <v/>
-      </c>
-      <c r="AH8" s="49" t="str">
+        <v>0.245635724640652</v>
+      </c>
+      <c r="AH8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(AD8&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))/AD8),"N/M"))</f>
-        <v/>
-      </c>
-      <c r="AI8" s="51" t="str">
+        <v>0.269709643718728</v>
+      </c>
+      <c r="AI8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,0),""))</f>
-        <v/>
+        <v>7.90333</v>
       </c>
       <c r="AJ8" s="66" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A8&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AK8" s="66" t="str">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A8&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AL8" s="47" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AL8" s="47" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A8,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AM8" s="67" t="str">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AN8" s="67" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="AO8" s="49" t="str">
+        <v>46272</v>
+      </c>
+      <c r="AO8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AP8" s="49" t="str">
+        <v>0.266038124541508</v>
+      </c>
+      <c r="AP8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=5)*(Raw_Q!$R$2:$R$600&lt;=8)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,9))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AQ8" s="49" t="str">
+        <v>0.228765086921287</v>
+      </c>
+      <c r="AQ8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,9),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=9)*(Raw_Q!$R$2:$R$600&lt;=12)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,9)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,13))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AR8" s="49" t="str">
+        <v>0.230764398498844</v>
+      </c>
+      <c r="AR8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,13),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=13)*(Raw_Q!$R$2:$R$600&lt;=16)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,13)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,17))/2)),""))</f>
-        <v/>
-      </c>
-      <c r="AS8" s="49" t="str">
+        <v>0.241434704991433</v>
+      </c>
+      <c r="AS8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,17),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=17)*(Raw_Q!$R$2:$R$600&lt;=20)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,17)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,21))/2)),""))</f>
-        <v/>
+        <v>0.261176308250188</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11926,7 +12073,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -11955,78 +12102,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>455</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>461</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -12902,119 +13049,119 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!A$8)</f>
-        <v/>
+        <v>5434</v>
       </c>
       <c r="B9" s="16" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!B$8)</f>
-        <v/>
+        <v>崇越</v>
       </c>
       <c r="C9" s="16" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!C$8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="17" t="str">
+        <v>池子</v>
+      </c>
+      <c r="D9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!D$8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="18" t="str">
+        <v>538</v>
+      </c>
+      <c r="E9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!J$8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="18" t="str">
+        <v>20.0074377091856</v>
+      </c>
+      <c r="F9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!L$8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="17" t="str">
+        <v>16.2078286527867</v>
+      </c>
+      <c r="G9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!N$8)</f>
-        <v/>
-      </c>
-      <c r="H9" s="17" t="str">
+        <v>0.524017143769517</v>
+      </c>
+      <c r="H9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!O$8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="19" t="str">
+        <v>1.2827698584006</v>
+      </c>
+      <c r="I9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!Q$8)</f>
-        <v/>
+        <v>0.0222780073605948</v>
       </c>
       <c r="J9" s="19" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!R$8)</f>
         <v/>
       </c>
-      <c r="K9" s="19" t="str">
+      <c r="K9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!T$8)</f>
-        <v/>
-      </c>
-      <c r="L9" s="19" t="str">
+        <v>0.123469656829816</v>
+      </c>
+      <c r="L9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!U$8)</f>
-        <v/>
-      </c>
-      <c r="M9" s="20" t="str">
+        <v>0.0715692637358045</v>
+      </c>
+      <c r="M9" s="20" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!V$8)</f>
-        <v/>
+        <v>5.19003930940118</v>
       </c>
       <c r="N9" s="21" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!W$8)</f>
-        <v/>
-      </c>
-      <c r="O9" s="20" t="str">
+        <v>成長且加速</v>
+      </c>
+      <c r="O9" s="20" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!X$8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="19" t="str">
+        <v>4.55869805123967</v>
+      </c>
+      <c r="P9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!S$8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="19" t="str">
+        <v>0.225972502259101</v>
+      </c>
+      <c r="Q9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!Y$8)</f>
-        <v/>
-      </c>
-      <c r="R9" s="19" t="str">
+        <v>0.656903765690377</v>
+      </c>
+      <c r="R9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!I$8)</f>
-        <v/>
-      </c>
-      <c r="S9" s="19" t="str">
+        <v>0.381808838643371</v>
+      </c>
+      <c r="S9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!Z$8)</f>
-        <v/>
-      </c>
-      <c r="T9" s="19" t="str">
+        <v>0.133194867559641</v>
+      </c>
+      <c r="T9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AA$8)</f>
-        <v/>
-      </c>
-      <c r="U9" s="22" t="str">
+        <v>0.129706276539687</v>
+      </c>
+      <c r="U9" s="22" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AB$8)</f>
-        <v/>
-      </c>
-      <c r="V9" s="22" t="str">
+        <v>34.8859101995386</v>
+      </c>
+      <c r="V9" s="22" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AC$8)</f>
-        <v/>
-      </c>
-      <c r="W9" s="19" t="str">
+        <v>179.187320515826</v>
+      </c>
+      <c r="W9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AF$8)</f>
-        <v/>
-      </c>
-      <c r="X9" s="19" t="str">
+        <v>0.266038124541508</v>
+      </c>
+      <c r="X9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AG$8)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="19" t="str">
+        <v>0.245635724640652</v>
+      </c>
+      <c r="Y9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AH$8)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="17" t="str">
+        <v>0.269709643718728</v>
+      </c>
+      <c r="Z9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AI$8)</f>
-        <v/>
+        <v>7.90333</v>
       </c>
       <c r="AA9" s="16" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!AJ$8)</f>
-        <v/>
+        <v>FY2026Q3E</v>
       </c>
       <c r="AB9" s="16" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!AK$8)</f>
-        <v/>
-      </c>
-      <c r="AC9" s="23" t="str">
+        <v>consensus</v>
+      </c>
+      <c r="AC9" s="23" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!AM$8)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14664,36 +14811,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="30">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="34">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="40">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16950,7 +17097,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E76FD4B0-B2E5-4F57-A569-976E4B3C68A1}</x14:id>
+          <x14:id>{A82CED29-E4B5-4F2D-80E6-E73BFDA17A52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -16966,16 +17113,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="31">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="32">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="33">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17016,47 +17163,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="35">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="41">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17081,7 +17228,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{E76FD4B0-B2E5-4F57-A569-976E4B3C68A1}">
+          <x14:cfRule type="dataBar" id="{A82CED29-E4B5-4F2D-80E6-E73BFDA17A52}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17408,43 +17555,43 @@
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!$A$8)</f>
-        <v/>
-      </c>
-      <c r="B10" s="47" t="str">
+        <v>5434</v>
+      </c>
+      <c r="B10" s="47" t="n">
         <f aca="false">IF($A10="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A10,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v/>
-      </c>
-      <c r="C10" s="47" t="str">
+        <v>24</v>
+      </c>
+      <c r="C10" s="47" t="n">
         <f aca="false">IF($A10="","",Config!$B$4)</f>
-        <v/>
-      </c>
-      <c r="D10" s="67" t="str">
+        <v>24</v>
+      </c>
+      <c r="D10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,$B10),""))</f>
-        <v/>
-      </c>
-      <c r="E10" s="67" t="str">
+        <v>44104</v>
+      </c>
+      <c r="E10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v/>
+        <v>46203</v>
       </c>
       <c r="F10" s="66" t="str">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A10&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v/>
-      </c>
-      <c r="G10" s="67" t="str">
+        <v>FY2026Q3E</v>
+      </c>
+      <c r="G10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A10,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
-      </c>
-      <c r="H10" s="47" t="str">
+        <v>0</v>
+      </c>
+      <c r="H10" s="47" t="n">
         <f aca="true">IF($A10="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A10,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v/>
-      </c>
-      <c r="I10" s="67" t="str">
+        <v>-46272</v>
+      </c>
+      <c r="I10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A10,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v/>
+        <v>46272</v>
       </c>
       <c r="J10" s="72" t="str">
         <f aca="true">IF($A10="","",IF($B10=0,"未抓取",IF($B10&lt;$C10,"需補歷史 ("&amp;($C10-$B10)&amp;" 季)",IF(TODAY()&gt;$G10,"待更新財報","OK"))))</f>
-        <v/>
+        <v>待更新財報</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18000,18 +18147,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="36">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="42">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="37">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="43">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="38">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="39">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18184,12 +18331,22 @@
       <c r="G7" s="73"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
+      <c r="A8" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="74" t="s">
+        <v>182</v>
+      </c>
       <c r="E8" s="73"/>
-      <c r="F8" s="75"/>
+      <c r="F8" s="75" t="n">
+        <v>46272</v>
+      </c>
       <c r="G8" s="73"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18311,7 +18468,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -18330,7 +18487,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S173"/>
+  <dimension ref="A1:S198"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -18354,58 +18511,58 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18413,7 +18570,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C2" s="77" t="n">
         <v>2026</v>
@@ -18425,13 +18582,13 @@
         <v>46295</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I2" s="79"/>
       <c r="J2" s="79"/>
@@ -18448,7 +18605,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="66" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18456,7 +18613,7 @@
         <v>167</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C3" s="77" t="n">
         <v>2026</v>
@@ -18468,13 +18625,13 @@
         <v>46203</v>
       </c>
       <c r="F3" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G3" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H3" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G3" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H3" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I3" s="79" t="n">
         <v>1270380.25</v>
@@ -18507,7 +18664,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="66" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18515,7 +18672,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C4" s="77" t="n">
         <v>2026</v>
@@ -18527,13 +18684,13 @@
         <v>46112</v>
       </c>
       <c r="F4" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G4" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H4" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G4" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H4" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I4" s="79" t="n">
         <v>1134103.44</v>
@@ -18566,7 +18723,7 @@
         <v>2</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18574,7 +18731,7 @@
         <v>167</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C5" s="77" t="n">
         <v>2025</v>
@@ -18586,13 +18743,13 @@
         <v>46022</v>
       </c>
       <c r="F5" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G5" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H5" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I5" s="79" t="n">
         <v>1046090.421</v>
@@ -18625,7 +18782,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="66" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18633,7 +18790,7 @@
         <v>167</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C6" s="77" t="n">
         <v>2025</v>
@@ -18645,13 +18802,13 @@
         <v>45930</v>
       </c>
       <c r="F6" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G6" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H6" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G6" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H6" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I6" s="79" t="n">
         <v>989918.318</v>
@@ -18684,7 +18841,7 @@
         <v>4</v>
       </c>
       <c r="S6" s="66" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18692,7 +18849,7 @@
         <v>167</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C7" s="77" t="n">
         <v>2025</v>
@@ -18704,13 +18861,13 @@
         <v>45838</v>
       </c>
       <c r="F7" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G7" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H7" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G7" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H7" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I7" s="79" t="n">
         <v>933791.869</v>
@@ -18743,7 +18900,7 @@
         <v>5</v>
       </c>
       <c r="S7" s="66" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18751,7 +18908,7 @@
         <v>167</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C8" s="77" t="n">
         <v>2025</v>
@@ -18763,13 +18920,13 @@
         <v>45747</v>
       </c>
       <c r="F8" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G8" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H8" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G8" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H8" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I8" s="79" t="n">
         <v>839253.664</v>
@@ -18802,7 +18959,7 @@
         <v>6</v>
       </c>
       <c r="S8" s="66" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18810,7 +18967,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C9" s="77" t="n">
         <v>2024</v>
@@ -18822,13 +18979,13 @@
         <v>45657</v>
       </c>
       <c r="F9" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G9" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H9" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G9" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H9" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I9" s="79" t="n">
         <v>868461.178</v>
@@ -18861,7 +19018,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="66" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18869,7 +19026,7 @@
         <v>167</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C10" s="77" t="n">
         <v>2024</v>
@@ -18881,13 +19038,13 @@
         <v>45565</v>
       </c>
       <c r="F10" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G10" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H10" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G10" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H10" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I10" s="79" t="n">
         <v>759692.143</v>
@@ -18920,7 +19077,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="66" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18928,7 +19085,7 @@
         <v>167</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C11" s="77" t="n">
         <v>2024</v>
@@ -18940,13 +19097,13 @@
         <v>45473</v>
       </c>
       <c r="F11" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G11" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H11" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G11" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H11" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I11" s="79" t="n">
         <v>673510.177</v>
@@ -18979,7 +19136,7 @@
         <v>9</v>
       </c>
       <c r="S11" s="66" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18987,7 +19144,7 @@
         <v>167</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C12" s="77" t="n">
         <v>2024</v>
@@ -18999,13 +19156,13 @@
         <v>45382</v>
       </c>
       <c r="F12" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H12" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G12" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H12" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I12" s="79" t="n">
         <v>592644.201</v>
@@ -19038,7 +19195,7 @@
         <v>10</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19046,7 +19203,7 @@
         <v>167</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C13" s="77" t="n">
         <v>2023</v>
@@ -19058,13 +19215,13 @@
         <v>45291</v>
       </c>
       <c r="F13" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G13" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H13" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G13" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H13" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I13" s="79" t="n">
         <v>625528.856</v>
@@ -19097,7 +19254,7 @@
         <v>11</v>
       </c>
       <c r="S13" s="66" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19105,7 +19262,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C14" s="77" t="n">
         <v>2023</v>
@@ -19117,13 +19274,13 @@
         <v>45199</v>
       </c>
       <c r="F14" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H14" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G14" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H14" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I14" s="79" t="n">
         <v>546732.758</v>
@@ -19156,7 +19313,7 @@
         <v>12</v>
       </c>
       <c r="S14" s="66" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19164,7 +19321,7 @@
         <v>167</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C15" s="77" t="n">
         <v>2023</v>
@@ -19176,13 +19333,13 @@
         <v>45107</v>
       </c>
       <c r="F15" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H15" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G15" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H15" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I15" s="79" t="n">
         <v>480841.254</v>
@@ -19215,7 +19372,7 @@
         <v>13</v>
       </c>
       <c r="S15" s="66" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19223,7 +19380,7 @@
         <v>167</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C16" s="77" t="n">
         <v>2023</v>
@@ -19235,13 +19392,13 @@
         <v>45016</v>
       </c>
       <c r="F16" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G16" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H16" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G16" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H16" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I16" s="79" t="n">
         <v>508632.973</v>
@@ -19274,7 +19431,7 @@
         <v>14</v>
       </c>
       <c r="S16" s="66" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19282,7 +19439,7 @@
         <v>167</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C17" s="77" t="n">
         <v>2022</v>
@@ -19294,13 +19451,13 @@
         <v>44926</v>
       </c>
       <c r="F17" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G17" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H17" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G17" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H17" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I17" s="79" t="n">
         <v>625531.868</v>
@@ -19333,7 +19490,7 @@
         <v>15</v>
       </c>
       <c r="S17" s="66" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19341,7 +19498,7 @@
         <v>167</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C18" s="77" t="n">
         <v>2022</v>
@@ -19353,13 +19510,13 @@
         <v>44834</v>
       </c>
       <c r="F18" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G18" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H18" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G18" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H18" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I18" s="79" t="n">
         <v>613142.743</v>
@@ -19392,7 +19549,7 @@
         <v>16</v>
       </c>
       <c r="S18" s="66" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19400,7 +19557,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C19" s="77" t="n">
         <v>2022</v>
@@ -19412,13 +19569,13 @@
         <v>44742</v>
       </c>
       <c r="F19" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H19" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G19" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H19" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I19" s="79" t="n">
         <v>534140.808</v>
@@ -19451,7 +19608,7 @@
         <v>17</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19459,7 +19616,7 @@
         <v>167</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C20" s="77" t="n">
         <v>2022</v>
@@ -19471,13 +19628,13 @@
         <v>44651</v>
       </c>
       <c r="F20" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G20" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H20" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G20" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H20" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I20" s="79" t="n">
         <v>491075.873</v>
@@ -19510,7 +19667,7 @@
         <v>18</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19518,7 +19675,7 @@
         <v>167</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C21" s="77" t="n">
         <v>2021</v>
@@ -19530,13 +19687,13 @@
         <v>44561</v>
       </c>
       <c r="F21" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G21" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H21" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G21" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H21" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I21" s="79" t="n">
         <v>438189.306</v>
@@ -19569,7 +19726,7 @@
         <v>19</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19577,7 +19734,7 @@
         <v>167</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C22" s="77" t="n">
         <v>2021</v>
@@ -19589,13 +19746,13 @@
         <v>44469</v>
       </c>
       <c r="F22" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G22" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H22" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G22" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H22" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I22" s="79" t="n">
         <v>414670.379</v>
@@ -19628,7 +19785,7 @@
         <v>20</v>
       </c>
       <c r="S22" s="66" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19636,7 +19793,7 @@
         <v>167</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C23" s="77" t="n">
         <v>2021</v>
@@ -19648,13 +19805,13 @@
         <v>44377</v>
       </c>
       <c r="F23" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G23" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H23" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G23" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H23" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I23" s="79" t="n">
         <v>372145.122</v>
@@ -19687,7 +19844,7 @@
         <v>21</v>
       </c>
       <c r="S23" s="66" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19695,7 +19852,7 @@
         <v>167</v>
       </c>
       <c r="B24" s="76" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C24" s="77" t="n">
         <v>2021</v>
@@ -19707,13 +19864,13 @@
         <v>44286</v>
       </c>
       <c r="F24" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G24" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H24" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G24" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H24" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I24" s="79" t="n">
         <v>362410.23</v>
@@ -19746,7 +19903,7 @@
         <v>22</v>
       </c>
       <c r="S24" s="66" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19754,7 +19911,7 @@
         <v>167</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C25" s="77" t="n">
         <v>2020</v>
@@ -19766,13 +19923,13 @@
         <v>44196</v>
       </c>
       <c r="F25" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G25" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H25" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G25" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I25" s="79" t="n">
         <v>361533.057</v>
@@ -19805,7 +19962,7 @@
         <v>23</v>
       </c>
       <c r="S25" s="66" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19813,7 +19970,7 @@
         <v>167</v>
       </c>
       <c r="B26" s="76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C26" s="77" t="n">
         <v>2020</v>
@@ -19825,13 +19982,13 @@
         <v>44104</v>
       </c>
       <c r="F26" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G26" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H26" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G26" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H26" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I26" s="79" t="n">
         <v>356426.204</v>
@@ -19862,7 +20019,7 @@
         <v>24</v>
       </c>
       <c r="S26" s="66" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19870,7 +20027,7 @@
         <v>171</v>
       </c>
       <c r="B27" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C27" s="77" t="n">
         <v>2026</v>
@@ -19882,13 +20039,13 @@
         <v>46295</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G27" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H27" s="76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I27" s="79"/>
       <c r="J27" s="79"/>
@@ -19905,7 +20062,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="66" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19913,7 +20070,7 @@
         <v>171</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C28" s="77" t="n">
         <v>2026</v>
@@ -19925,13 +20082,13 @@
         <v>46203</v>
       </c>
       <c r="F28" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G28" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H28" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G28" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H28" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I28" s="79" t="n">
         <v>82549.073</v>
@@ -19964,7 +20121,7 @@
         <v>1</v>
       </c>
       <c r="S28" s="66" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19972,7 +20129,7 @@
         <v>171</v>
       </c>
       <c r="B29" s="76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C29" s="77" t="n">
         <v>2026</v>
@@ -19984,13 +20141,13 @@
         <v>46112</v>
       </c>
       <c r="F29" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G29" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H29" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G29" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H29" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I29" s="79" t="n">
         <v>49086.932</v>
@@ -20023,7 +20180,7 @@
         <v>2</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20031,7 +20188,7 @@
         <v>171</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C30" s="77" t="n">
         <v>2025</v>
@@ -20043,13 +20200,13 @@
         <v>46022</v>
       </c>
       <c r="F30" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G30" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H30" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G30" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H30" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I30" s="79" t="n">
         <v>30093.618</v>
@@ -20082,7 +20239,7 @@
         <v>3</v>
       </c>
       <c r="S30" s="66" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20090,7 +20247,7 @@
         <v>171</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C31" s="77" t="n">
         <v>2025</v>
@@ -20102,13 +20259,13 @@
         <v>45930</v>
       </c>
       <c r="F31" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G31" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H31" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G31" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H31" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I31" s="79" t="n">
         <v>18778.868</v>
@@ -20141,7 +20298,7 @@
         <v>4</v>
       </c>
       <c r="S31" s="66" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20149,7 +20306,7 @@
         <v>171</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C32" s="77" t="n">
         <v>2025</v>
@@ -20161,13 +20318,13 @@
         <v>45838</v>
       </c>
       <c r="F32" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G32" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H32" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G32" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H32" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I32" s="79" t="n">
         <v>10526.094</v>
@@ -20200,7 +20357,7 @@
         <v>5</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20208,7 +20365,7 @@
         <v>171</v>
       </c>
       <c r="B33" s="76" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C33" s="77" t="n">
         <v>2025</v>
@@ -20220,13 +20377,13 @@
         <v>45747</v>
       </c>
       <c r="F33" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G33" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H33" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G33" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H33" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I33" s="79" t="n">
         <v>7187.94</v>
@@ -20259,7 +20416,7 @@
         <v>6</v>
       </c>
       <c r="S33" s="66" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20267,7 +20424,7 @@
         <v>171</v>
       </c>
       <c r="B34" s="76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C34" s="77" t="n">
         <v>2024</v>
@@ -20279,13 +20436,13 @@
         <v>45657</v>
       </c>
       <c r="F34" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G34" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H34" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G34" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H34" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I34" s="79" t="n">
         <v>6575.094</v>
@@ -20318,7 +20475,7 @@
         <v>7</v>
       </c>
       <c r="S34" s="66" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20326,7 +20483,7 @@
         <v>171</v>
       </c>
       <c r="B35" s="76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C35" s="77" t="n">
         <v>2024</v>
@@ -20338,13 +20495,13 @@
         <v>45565</v>
       </c>
       <c r="F35" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G35" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H35" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G35" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H35" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I35" s="79" t="n">
         <v>8132.593</v>
@@ -20377,7 +20534,7 @@
         <v>8</v>
       </c>
       <c r="S35" s="66" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20385,7 +20542,7 @@
         <v>171</v>
       </c>
       <c r="B36" s="76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C36" s="77" t="n">
         <v>2024</v>
@@ -20397,13 +20554,13 @@
         <v>45473</v>
       </c>
       <c r="F36" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G36" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H36" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G36" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H36" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I36" s="79" t="n">
         <v>9921.043</v>
@@ -20430,7 +20587,7 @@
         <v>9</v>
       </c>
       <c r="S36" s="66" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20438,7 +20595,7 @@
         <v>171</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C37" s="77" t="n">
         <v>2024</v>
@@ -20450,13 +20607,13 @@
         <v>45382</v>
       </c>
       <c r="F37" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H37" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G37" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H37" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I37" s="79" t="n">
         <v>9502.937</v>
@@ -20489,7 +20646,7 @@
         <v>10</v>
       </c>
       <c r="S37" s="66" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20497,7 +20654,7 @@
         <v>171</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C38" s="77" t="n">
         <v>2023</v>
@@ -20509,13 +20666,13 @@
         <v>45291</v>
       </c>
       <c r="F38" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G38" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H38" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G38" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H38" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I38" s="79" t="n">
         <v>8703.978</v>
@@ -20548,7 +20705,7 @@
         <v>11</v>
       </c>
       <c r="S38" s="66" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20556,7 +20713,7 @@
         <v>171</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C39" s="77" t="n">
         <v>2023</v>
@@ -20568,13 +20725,13 @@
         <v>45199</v>
       </c>
       <c r="F39" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G39" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H39" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G39" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H39" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I39" s="79" t="n">
         <v>7736.374</v>
@@ -20607,7 +20764,7 @@
         <v>12</v>
       </c>
       <c r="S39" s="66" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20615,7 +20772,7 @@
         <v>171</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C40" s="77" t="n">
         <v>2023</v>
@@ -20627,13 +20784,13 @@
         <v>45107</v>
       </c>
       <c r="F40" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G40" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H40" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G40" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H40" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I40" s="79" t="n">
         <v>7027.071</v>
@@ -20666,7 +20823,7 @@
         <v>13</v>
       </c>
       <c r="S40" s="66" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20674,7 +20831,7 @@
         <v>171</v>
       </c>
       <c r="B41" s="76" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C41" s="77" t="n">
         <v>2023</v>
@@ -20686,13 +20843,13 @@
         <v>45016</v>
       </c>
       <c r="F41" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G41" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H41" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G41" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H41" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I41" s="79" t="n">
         <v>6424.883</v>
@@ -20725,7 +20882,7 @@
         <v>14</v>
       </c>
       <c r="S41" s="66" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20733,7 +20890,7 @@
         <v>171</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C42" s="77" t="n">
         <v>2022</v>
@@ -20745,13 +20902,13 @@
         <v>44926</v>
       </c>
       <c r="F42" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G42" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H42" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G42" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H42" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I42" s="79" t="n">
         <v>7953.553</v>
@@ -20784,7 +20941,7 @@
         <v>15</v>
       </c>
       <c r="S42" s="66" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20792,7 +20949,7 @@
         <v>171</v>
       </c>
       <c r="B43" s="76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C43" s="77" t="n">
         <v>2022</v>
@@ -20804,13 +20961,13 @@
         <v>44834</v>
       </c>
       <c r="F43" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G43" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H43" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G43" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H43" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I43" s="79" t="n">
         <v>11021.725</v>
@@ -20843,7 +21000,7 @@
         <v>16</v>
       </c>
       <c r="S43" s="66" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20851,7 +21008,7 @@
         <v>171</v>
       </c>
       <c r="B44" s="76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C44" s="77" t="n">
         <v>2022</v>
@@ -20863,13 +21020,13 @@
         <v>44742</v>
       </c>
       <c r="F44" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G44" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H44" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G44" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H44" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I44" s="79" t="n">
         <v>18030.672</v>
@@ -20902,7 +21059,7 @@
         <v>17</v>
       </c>
       <c r="S44" s="66" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20910,7 +21067,7 @@
         <v>171</v>
       </c>
       <c r="B45" s="76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C45" s="77" t="n">
         <v>2022</v>
@@ -20922,13 +21079,13 @@
         <v>44651</v>
       </c>
       <c r="F45" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G45" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H45" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G45" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H45" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I45" s="79" t="n">
         <v>19946.325</v>
@@ -20961,7 +21118,7 @@
         <v>18</v>
       </c>
       <c r="S45" s="66" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20969,7 +21126,7 @@
         <v>171</v>
       </c>
       <c r="B46" s="76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C46" s="77" t="n">
         <v>2021</v>
@@ -20981,13 +21138,13 @@
         <v>44561</v>
       </c>
       <c r="F46" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G46" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H46" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G46" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H46" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I46" s="79" t="n">
         <v>21398.949</v>
@@ -21020,7 +21177,7 @@
         <v>19</v>
       </c>
       <c r="S46" s="66" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21028,7 +21185,7 @@
         <v>171</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C47" s="77" t="n">
         <v>2021</v>
@@ -21040,13 +21197,13 @@
         <v>44469</v>
       </c>
       <c r="F47" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G47" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G47" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H47" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I47" s="79" t="n">
         <v>23837.128</v>
@@ -21079,7 +21236,7 @@
         <v>20</v>
       </c>
       <c r="S47" s="66" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21087,7 +21244,7 @@
         <v>171</v>
       </c>
       <c r="B48" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C48" s="77" t="n">
         <v>2021</v>
@@ -21099,13 +21256,13 @@
         <v>44377</v>
       </c>
       <c r="F48" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G48" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H48" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G48" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H48" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I48" s="79" t="n">
         <v>22637.468</v>
@@ -21138,7 +21295,7 @@
         <v>21</v>
       </c>
       <c r="S48" s="66" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21146,7 +21303,7 @@
         <v>171</v>
       </c>
       <c r="B49" s="76" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C49" s="77" t="n">
         <v>2021</v>
@@ -21158,13 +21315,13 @@
         <v>44286</v>
       </c>
       <c r="F49" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G49" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H49" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G49" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H49" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I49" s="79" t="n">
         <v>17730.613</v>
@@ -21197,7 +21354,7 @@
         <v>22</v>
       </c>
       <c r="S49" s="66" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21205,7 +21362,7 @@
         <v>171</v>
       </c>
       <c r="B50" s="76" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C50" s="77" t="n">
         <v>2020</v>
@@ -21217,13 +21374,13 @@
         <v>44196</v>
       </c>
       <c r="F50" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G50" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H50" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G50" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H50" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I50" s="79" t="n">
         <v>14773.42</v>
@@ -21256,7 +21413,7 @@
         <v>23</v>
       </c>
       <c r="S50" s="66" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21264,7 +21421,7 @@
         <v>171</v>
       </c>
       <c r="B51" s="76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C51" s="77" t="n">
         <v>2020</v>
@@ -21276,13 +21433,13 @@
         <v>44104</v>
       </c>
       <c r="F51" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G51" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H51" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G51" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H51" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I51" s="79" t="n">
         <v>15323.867</v>
@@ -21313,7 +21470,7 @@
         <v>24</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21321,7 +21478,7 @@
         <v>179</v>
       </c>
       <c r="B52" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C52" s="77" t="n">
         <v>2026</v>
@@ -21333,13 +21490,13 @@
         <v>46295</v>
       </c>
       <c r="F52" s="76" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G52" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H52" s="76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
@@ -21356,7 +21513,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21364,7 +21521,7 @@
         <v>179</v>
       </c>
       <c r="B53" s="76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C53" s="77" t="n">
         <v>2026</v>
@@ -21376,13 +21533,13 @@
         <v>46203</v>
       </c>
       <c r="F53" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G53" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H53" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G53" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H53" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I53" s="79" t="n">
         <v>965.373</v>
@@ -21415,7 +21572,7 @@
         <v>1</v>
       </c>
       <c r="S53" s="66" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21423,7 +21580,7 @@
         <v>179</v>
       </c>
       <c r="B54" s="76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C54" s="77" t="n">
         <v>2026</v>
@@ -21435,13 +21592,13 @@
         <v>46112</v>
       </c>
       <c r="F54" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G54" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H54" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G54" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H54" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I54" s="79" t="n">
         <v>959.31</v>
@@ -21474,7 +21631,7 @@
         <v>2</v>
       </c>
       <c r="S54" s="66" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21482,7 +21639,7 @@
         <v>179</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C55" s="77" t="n">
         <v>2025</v>
@@ -21494,13 +21651,13 @@
         <v>46022</v>
       </c>
       <c r="F55" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G55" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H55" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G55" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H55" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I55" s="79" t="n">
         <v>959.589</v>
@@ -21533,7 +21690,7 @@
         <v>3</v>
       </c>
       <c r="S55" s="66" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21541,7 +21698,7 @@
         <v>179</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C56" s="77" t="n">
         <v>2025</v>
@@ -21553,13 +21710,13 @@
         <v>45930</v>
       </c>
       <c r="F56" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G56" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H56" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G56" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H56" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I56" s="79" t="n">
         <v>912.804</v>
@@ -21592,7 +21749,7 @@
         <v>4</v>
       </c>
       <c r="S56" s="66" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21600,7 +21757,7 @@
         <v>179</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C57" s="77" t="n">
         <v>2025</v>
@@ -21612,13 +21769,13 @@
         <v>45838</v>
       </c>
       <c r="F57" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G57" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H57" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G57" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H57" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I57" s="79" t="n">
         <v>714.087</v>
@@ -21651,7 +21808,7 @@
         <v>5</v>
       </c>
       <c r="S57" s="66" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21659,7 +21816,7 @@
         <v>179</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C58" s="77" t="n">
         <v>2025</v>
@@ -21671,13 +21828,13 @@
         <v>45747</v>
       </c>
       <c r="F58" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G58" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H58" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G58" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H58" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I58" s="79" t="n">
         <v>793.663</v>
@@ -21710,7 +21867,7 @@
         <v>6</v>
       </c>
       <c r="S58" s="66" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21718,7 +21875,7 @@
         <v>179</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C59" s="77" t="n">
         <v>2024</v>
@@ -21730,13 +21887,13 @@
         <v>45657</v>
       </c>
       <c r="F59" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G59" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H59" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G59" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H59" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I59" s="79" t="n">
         <v>722.474</v>
@@ -21769,7 +21926,7 @@
         <v>7</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21777,7 +21934,7 @@
         <v>179</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C60" s="77" t="n">
         <v>2024</v>
@@ -21789,13 +21946,13 @@
         <v>45565</v>
       </c>
       <c r="F60" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G60" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H60" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G60" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H60" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I60" s="79" t="n">
         <v>805.747</v>
@@ -21828,7 +21985,7 @@
         <v>8</v>
       </c>
       <c r="S60" s="66" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21836,7 +21993,7 @@
         <v>179</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C61" s="77" t="n">
         <v>2024</v>
@@ -21848,13 +22005,13 @@
         <v>45473</v>
       </c>
       <c r="F61" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G61" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H61" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G61" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H61" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I61" s="79" t="n">
         <v>875.601</v>
@@ -21887,7 +22044,7 @@
         <v>9</v>
       </c>
       <c r="S61" s="66" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21895,7 +22052,7 @@
         <v>179</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C62" s="77" t="n">
         <v>2024</v>
@@ -21907,13 +22064,13 @@
         <v>45382</v>
       </c>
       <c r="F62" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G62" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H62" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G62" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H62" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I62" s="79" t="n">
         <v>837.395</v>
@@ -21946,7 +22103,7 @@
         <v>10</v>
       </c>
       <c r="S62" s="66" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21954,7 +22111,7 @@
         <v>179</v>
       </c>
       <c r="B63" s="76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C63" s="77" t="n">
         <v>2023</v>
@@ -21966,13 +22123,13 @@
         <v>45291</v>
       </c>
       <c r="F63" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G63" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H63" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G63" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H63" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I63" s="79" t="n">
         <v>936.937</v>
@@ -22005,7 +22162,7 @@
         <v>11</v>
       </c>
       <c r="S63" s="66" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22013,7 +22170,7 @@
         <v>179</v>
       </c>
       <c r="B64" s="76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C64" s="77" t="n">
         <v>2023</v>
@@ -22025,13 +22182,13 @@
         <v>45199</v>
       </c>
       <c r="F64" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G64" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H64" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G64" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H64" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I64" s="79" t="n">
         <v>768.427</v>
@@ -22064,7 +22221,7 @@
         <v>12</v>
       </c>
       <c r="S64" s="66" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22072,7 +22229,7 @@
         <v>179</v>
       </c>
       <c r="B65" s="76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C65" s="77" t="n">
         <v>2023</v>
@@ -22084,13 +22241,13 @@
         <v>45107</v>
       </c>
       <c r="F65" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G65" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H65" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G65" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H65" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I65" s="79" t="n">
         <v>594.323</v>
@@ -22123,7 +22280,7 @@
         <v>13</v>
       </c>
       <c r="S65" s="66" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22131,7 +22288,7 @@
         <v>179</v>
       </c>
       <c r="B66" s="76" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C66" s="77" t="n">
         <v>2023</v>
@@ -22143,13 +22300,13 @@
         <v>45016</v>
       </c>
       <c r="F66" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G66" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H66" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G66" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H66" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I66" s="79" t="n">
         <v>394.417</v>
@@ -22182,7 +22339,7 @@
         <v>14</v>
       </c>
       <c r="S66" s="66" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22190,7 +22347,7 @@
         <v>179</v>
       </c>
       <c r="B67" s="76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C67" s="77" t="n">
         <v>2022</v>
@@ -22202,13 +22359,13 @@
         <v>44926</v>
       </c>
       <c r="F67" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G67" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H67" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G67" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H67" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I67" s="79" t="n">
         <v>506.067</v>
@@ -22241,7 +22398,7 @@
         <v>15</v>
       </c>
       <c r="S67" s="66" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22249,7 +22406,7 @@
         <v>179</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C68" s="77" t="n">
         <v>2022</v>
@@ -22261,13 +22418,13 @@
         <v>44834</v>
       </c>
       <c r="F68" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G68" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H68" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G68" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H68" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I68" s="79" t="n">
         <v>522.089</v>
@@ -22300,7 +22457,7 @@
         <v>16</v>
       </c>
       <c r="S68" s="66" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22308,7 +22465,7 @@
         <v>179</v>
       </c>
       <c r="B69" s="76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C69" s="77" t="n">
         <v>2022</v>
@@ -22320,13 +22477,13 @@
         <v>44742</v>
       </c>
       <c r="F69" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G69" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H69" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G69" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H69" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I69" s="79" t="n">
         <v>736.276</v>
@@ -22359,7 +22516,7 @@
         <v>17</v>
       </c>
       <c r="S69" s="66" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22367,7 +22524,7 @@
         <v>179</v>
       </c>
       <c r="B70" s="76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C70" s="77" t="n">
         <v>2022</v>
@@ -22379,13 +22536,13 @@
         <v>44651</v>
       </c>
       <c r="F70" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G70" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H70" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G70" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H70" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I70" s="79" t="n">
         <v>839.197</v>
@@ -22418,7 +22575,7 @@
         <v>18</v>
       </c>
       <c r="S70" s="66" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22426,7 +22583,7 @@
         <v>179</v>
       </c>
       <c r="B71" s="76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C71" s="77" t="n">
         <v>2021</v>
@@ -22438,13 +22595,13 @@
         <v>44561</v>
       </c>
       <c r="F71" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G71" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H71" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G71" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H71" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I71" s="79" t="n">
         <v>875.843</v>
@@ -22477,7 +22634,7 @@
         <v>19</v>
       </c>
       <c r="S71" s="66" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22485,7 +22642,7 @@
         <v>179</v>
       </c>
       <c r="B72" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C72" s="77" t="n">
         <v>2021</v>
@@ -22497,13 +22654,13 @@
         <v>44469</v>
       </c>
       <c r="F72" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G72" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H72" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G72" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H72" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I72" s="79" t="n">
         <v>947.399</v>
@@ -22536,7 +22693,7 @@
         <v>20</v>
       </c>
       <c r="S72" s="66" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22544,7 +22701,7 @@
         <v>179</v>
       </c>
       <c r="B73" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C73" s="77" t="n">
         <v>2021</v>
@@ -22556,13 +22713,13 @@
         <v>44377</v>
       </c>
       <c r="F73" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G73" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H73" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G73" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H73" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I73" s="79" t="n">
         <v>896.062</v>
@@ -22595,7 +22752,7 @@
         <v>21</v>
       </c>
       <c r="S73" s="66" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22603,7 +22760,7 @@
         <v>179</v>
       </c>
       <c r="B74" s="76" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C74" s="77" t="n">
         <v>2021</v>
@@ -22615,13 +22772,13 @@
         <v>44286</v>
       </c>
       <c r="F74" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G74" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H74" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G74" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H74" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I74" s="79" t="n">
         <v>889.217</v>
@@ -22654,7 +22811,7 @@
         <v>22</v>
       </c>
       <c r="S74" s="66" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22662,7 +22819,7 @@
         <v>179</v>
       </c>
       <c r="B75" s="76" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C75" s="77" t="n">
         <v>2020</v>
@@ -22674,13 +22831,13 @@
         <v>44196</v>
       </c>
       <c r="F75" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G75" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H75" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G75" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H75" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I75" s="79" t="n">
         <v>757.232</v>
@@ -22713,7 +22870,7 @@
         <v>23</v>
       </c>
       <c r="S75" s="66" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22721,7 +22878,7 @@
         <v>179</v>
       </c>
       <c r="B76" s="76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C76" s="77" t="n">
         <v>2020</v>
@@ -22733,13 +22890,13 @@
         <v>44104</v>
       </c>
       <c r="F76" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G76" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H76" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G76" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H76" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I76" s="79" t="n">
         <v>644.391</v>
@@ -22770,7 +22927,7 @@
         <v>24</v>
       </c>
       <c r="S76" s="66" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22778,7 +22935,7 @@
         <v>183</v>
       </c>
       <c r="B77" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C77" s="77" t="n">
         <v>2026</v>
@@ -22790,13 +22947,13 @@
         <v>46295</v>
       </c>
       <c r="F77" s="76" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G77" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H77" s="76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I77" s="79"/>
       <c r="J77" s="79"/>
@@ -22813,7 +22970,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="66" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22821,7 +22978,7 @@
         <v>183</v>
       </c>
       <c r="B78" s="76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C78" s="77" t="n">
         <v>2026</v>
@@ -22833,13 +22990,13 @@
         <v>46203</v>
       </c>
       <c r="F78" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G78" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H78" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G78" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H78" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I78" s="79" t="n">
         <v>28660.098</v>
@@ -22872,7 +23029,7 @@
         <v>1</v>
       </c>
       <c r="S78" s="66" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22880,7 +23037,7 @@
         <v>183</v>
       </c>
       <c r="B79" s="76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C79" s="77" t="n">
         <v>2026</v>
@@ -22892,13 +23049,13 @@
         <v>46112</v>
       </c>
       <c r="F79" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G79" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H79" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G79" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H79" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I79" s="79" t="n">
         <v>23145.303</v>
@@ -22931,7 +23088,7 @@
         <v>2</v>
       </c>
       <c r="S79" s="66" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22939,7 +23096,7 @@
         <v>183</v>
       </c>
       <c r="B80" s="76" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C80" s="77" t="n">
         <v>2025</v>
@@ -22951,13 +23108,13 @@
         <v>46022</v>
       </c>
       <c r="F80" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G80" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H80" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G80" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H80" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I80" s="79" t="n">
         <v>22817.209</v>
@@ -22990,7 +23147,7 @@
         <v>3</v>
       </c>
       <c r="S80" s="66" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22998,7 +23155,7 @@
         <v>183</v>
       </c>
       <c r="B81" s="76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C81" s="77" t="n">
         <v>2025</v>
@@ -23010,13 +23167,13 @@
         <v>45930</v>
       </c>
       <c r="F81" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G81" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H81" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G81" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H81" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I81" s="79" t="n">
         <v>24573.67</v>
@@ -23049,7 +23206,7 @@
         <v>4</v>
       </c>
       <c r="S81" s="66" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23057,7 +23214,7 @@
         <v>183</v>
       </c>
       <c r="B82" s="76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C82" s="77" t="n">
         <v>2025</v>
@@ -23069,13 +23226,13 @@
         <v>45838</v>
       </c>
       <c r="F82" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G82" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H82" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G82" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H82" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I82" s="79" t="n">
         <v>26152.063</v>
@@ -23108,7 +23265,7 @@
         <v>5</v>
       </c>
       <c r="S82" s="66" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23116,7 +23273,7 @@
         <v>183</v>
       </c>
       <c r="B83" s="76" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C83" s="77" t="n">
         <v>2025</v>
@@ -23128,13 +23285,13 @@
         <v>45747</v>
       </c>
       <c r="F83" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G83" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H83" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G83" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H83" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I83" s="79" t="n">
         <v>27120.202</v>
@@ -23167,7 +23324,7 @@
         <v>6</v>
       </c>
       <c r="S83" s="66" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23175,7 +23332,7 @@
         <v>183</v>
       </c>
       <c r="B84" s="76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C84" s="77" t="n">
         <v>2024</v>
@@ -23187,13 +23344,13 @@
         <v>45657</v>
       </c>
       <c r="F84" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G84" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H84" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G84" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H84" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I84" s="79" t="n">
         <v>25262.519</v>
@@ -23226,7 +23383,7 @@
         <v>7</v>
       </c>
       <c r="S84" s="66" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23234,7 +23391,7 @@
         <v>183</v>
       </c>
       <c r="B85" s="76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C85" s="77" t="n">
         <v>2024</v>
@@ -23246,13 +23403,13 @@
         <v>45565</v>
       </c>
       <c r="F85" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G85" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H85" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G85" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H85" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I85" s="79" t="n">
         <v>27866.328</v>
@@ -23285,7 +23442,7 @@
         <v>8</v>
       </c>
       <c r="S85" s="66" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23293,7 +23450,7 @@
         <v>183</v>
       </c>
       <c r="B86" s="76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C86" s="77" t="n">
         <v>2024</v>
@@ -23305,13 +23462,13 @@
         <v>45473</v>
       </c>
       <c r="F86" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G86" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H86" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G86" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H86" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I86" s="79" t="n">
         <v>25231.019</v>
@@ -23344,7 +23501,7 @@
         <v>9</v>
       </c>
       <c r="S86" s="66" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23352,7 +23509,7 @@
         <v>183</v>
       </c>
       <c r="B87" s="76" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C87" s="77" t="n">
         <v>2024</v>
@@ -23364,13 +23521,13 @@
         <v>45382</v>
       </c>
       <c r="F87" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G87" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H87" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G87" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H87" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I87" s="79" t="n">
         <v>24427.885</v>
@@ -23403,7 +23560,7 @@
         <v>10</v>
       </c>
       <c r="S87" s="66" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23411,7 +23568,7 @@
         <v>183</v>
       </c>
       <c r="B88" s="76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C88" s="77" t="n">
         <v>2023</v>
@@ -23423,13 +23580,13 @@
         <v>45291</v>
       </c>
       <c r="F88" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G88" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H88" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G88" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H88" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I88" s="79" t="n">
         <v>27153.825</v>
@@ -23462,7 +23619,7 @@
         <v>11</v>
       </c>
       <c r="S88" s="66" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23470,7 +23627,7 @@
         <v>183</v>
       </c>
       <c r="B89" s="76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C89" s="77" t="n">
         <v>2023</v>
@@ -23482,13 +23639,13 @@
         <v>45199</v>
       </c>
       <c r="F89" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G89" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H89" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G89" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H89" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I89" s="79" t="n">
         <v>28929.962</v>
@@ -23521,7 +23678,7 @@
         <v>12</v>
       </c>
       <c r="S89" s="66" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23529,7 +23686,7 @@
         <v>183</v>
       </c>
       <c r="B90" s="76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C90" s="77" t="n">
         <v>2023</v>
@@ -23541,13 +23698,13 @@
         <v>45107</v>
       </c>
       <c r="F90" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G90" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H90" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G90" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H90" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I90" s="79" t="n">
         <v>30299.029</v>
@@ -23580,7 +23737,7 @@
         <v>13</v>
       </c>
       <c r="S90" s="66" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23588,7 +23745,7 @@
         <v>183</v>
       </c>
       <c r="B91" s="76" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C91" s="77" t="n">
         <v>2023</v>
@@ -23600,13 +23757,13 @@
         <v>45016</v>
       </c>
       <c r="F91" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G91" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H91" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G91" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H91" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I91" s="79" t="n">
         <v>24045.882</v>
@@ -23639,7 +23796,7 @@
         <v>14</v>
       </c>
       <c r="S91" s="66" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23647,7 +23804,7 @@
         <v>183</v>
       </c>
       <c r="B92" s="76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C92" s="77" t="n">
         <v>2022</v>
@@ -23659,13 +23816,13 @@
         <v>44926</v>
       </c>
       <c r="F92" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G92" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H92" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G92" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H92" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I92" s="79" t="n">
         <v>22420.161</v>
@@ -23698,7 +23855,7 @@
         <v>15</v>
       </c>
       <c r="S92" s="66" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23706,7 +23863,7 @@
         <v>183</v>
       </c>
       <c r="B93" s="76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C93" s="77" t="n">
         <v>2022</v>
@@ -23718,13 +23875,13 @@
         <v>44834</v>
       </c>
       <c r="F93" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G93" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H93" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G93" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H93" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I93" s="79" t="n">
         <v>19563.686</v>
@@ -23757,7 +23914,7 @@
         <v>16</v>
       </c>
       <c r="S93" s="66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23765,7 +23922,7 @@
         <v>183</v>
       </c>
       <c r="B94" s="76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C94" s="77" t="n">
         <v>2022</v>
@@ -23777,13 +23934,13 @@
         <v>44742</v>
       </c>
       <c r="F94" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G94" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H94" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G94" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H94" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I94" s="79" t="n">
         <v>31461.142</v>
@@ -23816,7 +23973,7 @@
         <v>17</v>
       </c>
       <c r="S94" s="66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23824,7 +23981,7 @@
         <v>183</v>
       </c>
       <c r="B95" s="76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C95" s="77" t="n">
         <v>2022</v>
@@ -23836,13 +23993,13 @@
         <v>44651</v>
       </c>
       <c r="F95" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G95" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H95" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G95" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H95" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I95" s="79" t="n">
         <v>36511.685</v>
@@ -23875,7 +24032,7 @@
         <v>18</v>
       </c>
       <c r="S95" s="66" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23883,7 +24040,7 @@
         <v>183</v>
       </c>
       <c r="B96" s="76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C96" s="77" t="n">
         <v>2021</v>
@@ -23895,13 +24052,13 @@
         <v>44561</v>
       </c>
       <c r="F96" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G96" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H96" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G96" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H96" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I96" s="79" t="n">
         <v>36542.106</v>
@@ -23934,7 +24091,7 @@
         <v>19</v>
       </c>
       <c r="S96" s="66" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23942,7 +24099,7 @@
         <v>183</v>
       </c>
       <c r="B97" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C97" s="77" t="n">
         <v>2021</v>
@@ -23954,13 +24111,13 @@
         <v>44469</v>
       </c>
       <c r="F97" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G97" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H97" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G97" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H97" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I97" s="79" t="n">
         <v>38345.587</v>
@@ -23993,7 +24150,7 @@
         <v>20</v>
       </c>
       <c r="S97" s="66" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24001,7 +24158,7 @@
         <v>183</v>
       </c>
       <c r="B98" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C98" s="77" t="n">
         <v>2021</v>
@@ -24013,13 +24170,13 @@
         <v>44377</v>
       </c>
       <c r="F98" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G98" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H98" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G98" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H98" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I98" s="79" t="n">
         <v>34111.302</v>
@@ -24052,7 +24209,7 @@
         <v>21</v>
       </c>
       <c r="S98" s="66" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24060,7 +24217,7 @@
         <v>183</v>
       </c>
       <c r="B99" s="76" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C99" s="77" t="n">
         <v>2021</v>
@@ -24072,13 +24229,13 @@
         <v>44286</v>
       </c>
       <c r="F99" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G99" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H99" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G99" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H99" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I99" s="79" t="n">
         <v>26366.515</v>
@@ -24111,7 +24268,7 @@
         <v>22</v>
       </c>
       <c r="S99" s="66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24119,7 +24276,7 @@
         <v>183</v>
       </c>
       <c r="B100" s="76" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C100" s="77" t="n">
         <v>2020</v>
@@ -24131,13 +24288,13 @@
         <v>44196</v>
       </c>
       <c r="F100" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G100" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H100" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G100" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H100" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I100" s="79" t="n">
         <v>22452.842</v>
@@ -24170,7 +24327,7 @@
         <v>23</v>
       </c>
       <c r="S100" s="66" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24178,7 +24335,7 @@
         <v>183</v>
       </c>
       <c r="B101" s="76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C101" s="77" t="n">
         <v>2020</v>
@@ -24190,13 +24347,13 @@
         <v>44104</v>
       </c>
       <c r="F101" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G101" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H101" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G101" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H101" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I101" s="79" t="n">
         <v>22001.236</v>
@@ -24227,7 +24384,7 @@
         <v>24</v>
       </c>
       <c r="S101" s="66" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24235,7 +24392,7 @@
         <v>185</v>
       </c>
       <c r="B102" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C102" s="77" t="n">
         <v>2026</v>
@@ -24247,13 +24404,13 @@
         <v>46295</v>
       </c>
       <c r="F102" s="76" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G102" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H102" s="76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I102" s="79"/>
       <c r="J102" s="79"/>
@@ -24270,7 +24427,7 @@
         <v>0</v>
       </c>
       <c r="S102" s="66" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24278,7 +24435,7 @@
         <v>185</v>
       </c>
       <c r="B103" s="76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C103" s="77" t="n">
         <v>2026</v>
@@ -24290,13 +24447,13 @@
         <v>46203</v>
       </c>
       <c r="F103" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G103" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H103" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G103" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H103" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I103" s="79" t="n">
         <v>23281.188</v>
@@ -24329,7 +24486,7 @@
         <v>1</v>
       </c>
       <c r="S103" s="66" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24337,7 +24494,7 @@
         <v>185</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C104" s="77" t="n">
         <v>2026</v>
@@ -24349,13 +24506,13 @@
         <v>46112</v>
       </c>
       <c r="F104" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G104" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H104" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G104" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H104" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I104" s="79" t="n">
         <v>20863.649</v>
@@ -24388,7 +24545,7 @@
         <v>2</v>
       </c>
       <c r="S104" s="66" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24396,7 +24553,7 @@
         <v>185</v>
       </c>
       <c r="B105" s="76" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C105" s="77" t="n">
         <v>2025</v>
@@ -24408,13 +24565,13 @@
         <v>46022</v>
       </c>
       <c r="F105" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G105" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H105" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G105" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H105" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I105" s="79" t="n">
         <v>19779.964</v>
@@ -24447,7 +24604,7 @@
         <v>3</v>
       </c>
       <c r="S105" s="66" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24455,7 +24612,7 @@
         <v>185</v>
       </c>
       <c r="B106" s="76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C106" s="77" t="n">
         <v>2025</v>
@@ -24467,13 +24624,13 @@
         <v>45930</v>
       </c>
       <c r="F106" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G106" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H106" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G106" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H106" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I106" s="79" t="n">
         <v>18413.195</v>
@@ -24506,7 +24663,7 @@
         <v>4</v>
       </c>
       <c r="S106" s="66" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24514,7 +24671,7 @@
         <v>185</v>
       </c>
       <c r="B107" s="76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C107" s="77" t="n">
         <v>2025</v>
@@ -24526,13 +24683,13 @@
         <v>45838</v>
       </c>
       <c r="F107" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G107" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H107" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G107" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H107" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I107" s="79" t="n">
         <v>16933.328</v>
@@ -24565,7 +24722,7 @@
         <v>5</v>
       </c>
       <c r="S107" s="66" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24573,7 +24730,7 @@
         <v>185</v>
       </c>
       <c r="B108" s="76" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C108" s="77" t="n">
         <v>2025</v>
@@ -24585,13 +24742,13 @@
         <v>45747</v>
       </c>
       <c r="F108" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G108" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H108" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G108" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H108" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I108" s="79" t="n">
         <v>16120.785</v>
@@ -24624,7 +24781,7 @@
         <v>6</v>
       </c>
       <c r="S108" s="66" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24632,7 +24789,7 @@
         <v>185</v>
       </c>
       <c r="B109" s="76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C109" s="77" t="n">
         <v>2024</v>
@@ -24644,13 +24801,13 @@
         <v>45657</v>
       </c>
       <c r="F109" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G109" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H109" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G109" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H109" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I109" s="79" t="n">
         <v>14411.637</v>
@@ -24683,7 +24840,7 @@
         <v>7</v>
       </c>
       <c r="S109" s="66" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24691,7 +24848,7 @@
         <v>185</v>
       </c>
       <c r="B110" s="76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C110" s="77" t="n">
         <v>2024</v>
@@ -24703,13 +24860,13 @@
         <v>45565</v>
       </c>
       <c r="F110" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G110" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H110" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G110" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H110" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I110" s="79" t="n">
         <v>14259.287</v>
@@ -24742,7 +24899,7 @@
         <v>8</v>
       </c>
       <c r="S110" s="66" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24750,7 +24907,7 @@
         <v>185</v>
       </c>
       <c r="B111" s="76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C111" s="77" t="n">
         <v>2024</v>
@@ -24762,13 +24919,13 @@
         <v>45473</v>
       </c>
       <c r="F111" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G111" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H111" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G111" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H111" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I111" s="79" t="n">
         <v>12983.996</v>
@@ -24801,7 +24958,7 @@
         <v>9</v>
       </c>
       <c r="S111" s="66" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24809,7 +24966,7 @@
         <v>185</v>
       </c>
       <c r="B112" s="76" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C112" s="77" t="n">
         <v>2024</v>
@@ -24821,13 +24978,13 @@
         <v>45382</v>
       </c>
       <c r="F112" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G112" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H112" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G112" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H112" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I112" s="79" t="n">
         <v>12425.561</v>
@@ -24860,7 +25017,7 @@
         <v>10</v>
       </c>
       <c r="S112" s="66" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24868,7 +25025,7 @@
         <v>185</v>
       </c>
       <c r="B113" s="76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C113" s="77" t="n">
         <v>2023</v>
@@ -24880,13 +25037,13 @@
         <v>45291</v>
       </c>
       <c r="F113" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G113" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H113" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G113" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H113" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I113" s="79" t="n">
         <v>12195.595</v>
@@ -24919,7 +25076,7 @@
         <v>11</v>
       </c>
       <c r="S113" s="66" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24927,7 +25084,7 @@
         <v>185</v>
       </c>
       <c r="B114" s="76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C114" s="77" t="n">
         <v>2023</v>
@@ -24939,13 +25096,13 @@
         <v>45199</v>
       </c>
       <c r="F114" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G114" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H114" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G114" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H114" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I114" s="79" t="n">
         <v>13150.145</v>
@@ -24978,7 +25135,7 @@
         <v>12</v>
       </c>
       <c r="S114" s="66" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24986,7 +25143,7 @@
         <v>185</v>
       </c>
       <c r="B115" s="76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C115" s="77" t="n">
         <v>2023</v>
@@ -24998,13 +25155,13 @@
         <v>45107</v>
       </c>
       <c r="F115" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G115" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H115" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G115" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H115" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I115" s="79" t="n">
         <v>13004.395</v>
@@ -25037,7 +25194,7 @@
         <v>13</v>
       </c>
       <c r="S115" s="66" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25045,7 +25202,7 @@
         <v>185</v>
       </c>
       <c r="B116" s="76" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C116" s="77" t="n">
         <v>2023</v>
@@ -25057,13 +25214,13 @@
         <v>45016</v>
       </c>
       <c r="F116" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G116" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H116" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G116" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H116" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I116" s="79" t="n">
         <v>12701.656</v>
@@ -25096,7 +25253,7 @@
         <v>14</v>
       </c>
       <c r="S116" s="66" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25104,7 +25261,7 @@
         <v>185</v>
       </c>
       <c r="B117" s="76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C117" s="77" t="n">
         <v>2022</v>
@@ -25116,13 +25273,13 @@
         <v>44926</v>
       </c>
       <c r="F117" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G117" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H117" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G117" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H117" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I117" s="79" t="n">
         <v>13600.543</v>
@@ -25155,7 +25312,7 @@
         <v>15</v>
       </c>
       <c r="S117" s="66" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25163,7 +25320,7 @@
         <v>185</v>
       </c>
       <c r="B118" s="76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C118" s="77" t="n">
         <v>2022</v>
@@ -25175,13 +25332,13 @@
         <v>44834</v>
       </c>
       <c r="F118" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G118" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H118" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G118" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H118" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I118" s="79" t="n">
         <v>14526.402</v>
@@ -25214,7 +25371,7 @@
         <v>16</v>
       </c>
       <c r="S118" s="66" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25222,7 +25379,7 @@
         <v>185</v>
       </c>
       <c r="B119" s="76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C119" s="77" t="n">
         <v>2022</v>
@@ -25234,13 +25391,13 @@
         <v>44742</v>
       </c>
       <c r="F119" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G119" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H119" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G119" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H119" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I119" s="79" t="n">
         <v>13963.028</v>
@@ -25273,7 +25430,7 @@
         <v>17</v>
       </c>
       <c r="S119" s="66" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25281,7 +25438,7 @@
         <v>185</v>
       </c>
       <c r="B120" s="76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C120" s="77" t="n">
         <v>2022</v>
@@ -25293,13 +25450,13 @@
         <v>44651</v>
       </c>
       <c r="F120" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G120" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H120" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G120" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H120" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I120" s="79" t="n">
         <v>11667.198</v>
@@ -25332,7 +25489,7 @@
         <v>18</v>
       </c>
       <c r="S120" s="66" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25340,7 +25497,7 @@
         <v>185</v>
       </c>
       <c r="B121" s="76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C121" s="77" t="n">
         <v>2021</v>
@@ -25352,13 +25509,13 @@
         <v>44561</v>
       </c>
       <c r="F121" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G121" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H121" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G121" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H121" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I121" s="79" t="n">
         <v>7998.723</v>
@@ -25391,7 +25548,7 @@
         <v>19</v>
       </c>
       <c r="S121" s="66" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25399,7 +25556,7 @@
         <v>185</v>
       </c>
       <c r="B122" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C122" s="77" t="n">
         <v>2021</v>
@@ -25411,13 +25568,13 @@
         <v>44469</v>
       </c>
       <c r="F122" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G122" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H122" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G122" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H122" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I122" s="79" t="n">
         <v>7415.446</v>
@@ -25450,7 +25607,7 @@
         <v>20</v>
       </c>
       <c r="S122" s="66" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25458,7 +25615,7 @@
         <v>185</v>
       </c>
       <c r="B123" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C123" s="77" t="n">
         <v>2021</v>
@@ -25470,13 +25627,13 @@
         <v>44377</v>
       </c>
       <c r="F123" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G123" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H123" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G123" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H123" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I123" s="79" t="n">
         <v>7015.992</v>
@@ -25509,7 +25666,7 @@
         <v>21</v>
       </c>
       <c r="S123" s="66" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25517,7 +25674,7 @@
         <v>185</v>
       </c>
       <c r="B124" s="76" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C124" s="77" t="n">
         <v>2021</v>
@@ -25529,13 +25686,13 @@
         <v>44286</v>
       </c>
       <c r="F124" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G124" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H124" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G124" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H124" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I124" s="79" t="n">
         <v>6134.214</v>
@@ -25568,7 +25725,7 @@
         <v>22</v>
       </c>
       <c r="S124" s="66" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25576,7 +25733,7 @@
         <v>185</v>
       </c>
       <c r="B125" s="76" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C125" s="77" t="n">
         <v>2020</v>
@@ -25588,13 +25745,13 @@
         <v>44196</v>
       </c>
       <c r="F125" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G125" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H125" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G125" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H125" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I125" s="79" t="n">
         <v>6266.652</v>
@@ -25627,7 +25784,7 @@
         <v>23</v>
       </c>
       <c r="S125" s="66" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25635,7 +25792,7 @@
         <v>185</v>
       </c>
       <c r="B126" s="76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C126" s="77" t="n">
         <v>2020</v>
@@ -25647,13 +25804,13 @@
         <v>44104</v>
       </c>
       <c r="F126" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G126" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H126" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G126" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H126" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I126" s="79" t="n">
         <v>6049.454</v>
@@ -25684,7 +25841,7 @@
         <v>24</v>
       </c>
       <c r="S126" s="66" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25692,7 +25849,7 @@
         <v>176</v>
       </c>
       <c r="B127" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C127" s="77" t="n">
         <v>2026</v>
@@ -25704,13 +25861,13 @@
         <v>46295</v>
       </c>
       <c r="F127" s="76" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G127" s="76" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H127" s="76" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I127" s="79"/>
       <c r="J127" s="79"/>
@@ -25727,7 +25884,7 @@
         <v>0</v>
       </c>
       <c r="S127" s="66" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25735,7 +25892,7 @@
         <v>176</v>
       </c>
       <c r="B128" s="76" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C128" s="77" t="n">
         <v>2026</v>
@@ -25747,13 +25904,13 @@
         <v>46203</v>
       </c>
       <c r="F128" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G128" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H128" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G128" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H128" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I128" s="79" t="n">
         <v>22443.411</v>
@@ -25786,7 +25943,7 @@
         <v>1</v>
       </c>
       <c r="S128" s="66" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25794,7 +25951,7 @@
         <v>176</v>
       </c>
       <c r="B129" s="76" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C129" s="77" t="n">
         <v>2026</v>
@@ -25806,13 +25963,13 @@
         <v>46112</v>
       </c>
       <c r="F129" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G129" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H129" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G129" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H129" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I129" s="79" t="n">
         <v>13182.608</v>
@@ -25845,7 +26002,7 @@
         <v>2</v>
       </c>
       <c r="S129" s="66" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25853,7 +26010,7 @@
         <v>176</v>
       </c>
       <c r="B130" s="76" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C130" s="77" t="n">
         <v>2025</v>
@@ -25865,13 +26022,13 @@
         <v>46022</v>
       </c>
       <c r="F130" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G130" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H130" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G130" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H130" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I130" s="79" t="n">
         <v>4806.69</v>
@@ -25904,7 +26061,7 @@
         <v>3</v>
       </c>
       <c r="S130" s="66" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25912,7 +26069,7 @@
         <v>176</v>
       </c>
       <c r="B131" s="76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C131" s="77" t="n">
         <v>2025</v>
@@ -25924,13 +26081,13 @@
         <v>45930</v>
       </c>
       <c r="F131" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G131" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H131" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G131" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H131" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I131" s="79" t="n">
         <v>3807.401</v>
@@ -25963,7 +26120,7 @@
         <v>4</v>
       </c>
       <c r="S131" s="66" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25971,7 +26128,7 @@
         <v>176</v>
       </c>
       <c r="B132" s="76" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C132" s="77" t="n">
         <v>2025</v>
@@ -25983,13 +26140,13 @@
         <v>45838</v>
       </c>
       <c r="F132" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G132" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H132" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G132" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H132" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I132" s="79" t="n">
         <v>3028.429</v>
@@ -26022,7 +26179,7 @@
         <v>5</v>
       </c>
       <c r="S132" s="66" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26030,7 +26187,7 @@
         <v>176</v>
       </c>
       <c r="B133" s="76" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C133" s="77" t="n">
         <v>2025</v>
@@ -26042,13 +26199,13 @@
         <v>45747</v>
       </c>
       <c r="F133" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G133" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H133" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G133" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H133" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I133" s="79" t="n">
         <v>2618.742</v>
@@ -26081,7 +26238,7 @@
         <v>6</v>
       </c>
       <c r="S133" s="66" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26089,7 +26246,7 @@
         <v>176</v>
       </c>
       <c r="B134" s="76" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C134" s="77" t="n">
         <v>2024</v>
@@ -26101,13 +26258,13 @@
         <v>45657</v>
       </c>
       <c r="F134" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G134" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H134" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G134" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H134" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I134" s="79" t="n">
         <v>2228.005</v>
@@ -26140,7 +26297,7 @@
         <v>7</v>
       </c>
       <c r="S134" s="66" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26148,7 +26305,7 @@
         <v>176</v>
       </c>
       <c r="B135" s="76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C135" s="77" t="n">
         <v>2024</v>
@@ -26160,13 +26317,13 @@
         <v>45565</v>
       </c>
       <c r="F135" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G135" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H135" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G135" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H135" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I135" s="79" t="n">
         <v>2321.419</v>
@@ -26199,7 +26356,7 @@
         <v>8</v>
       </c>
       <c r="S135" s="66" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26207,7 +26364,7 @@
         <v>176</v>
       </c>
       <c r="B136" s="76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C136" s="77" t="n">
         <v>2024</v>
@@ -26219,13 +26376,13 @@
         <v>45473</v>
       </c>
       <c r="F136" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G136" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H136" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G136" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H136" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I136" s="79" t="n">
         <v>2190.229</v>
@@ -26258,7 +26415,7 @@
         <v>9</v>
       </c>
       <c r="S136" s="66" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26266,7 +26423,7 @@
         <v>176</v>
       </c>
       <c r="B137" s="76" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C137" s="77" t="n">
         <v>2024</v>
@@ -26278,13 +26435,13 @@
         <v>45382</v>
       </c>
       <c r="F137" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G137" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H137" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G137" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H137" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I137" s="79" t="n">
         <v>2175.989</v>
@@ -26317,7 +26474,7 @@
         <v>10</v>
       </c>
       <c r="S137" s="66" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26325,7 +26482,7 @@
         <v>176</v>
       </c>
       <c r="B138" s="76" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C138" s="77" t="n">
         <v>2023</v>
@@ -26337,13 +26494,13 @@
         <v>45291</v>
       </c>
       <c r="F138" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G138" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H138" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G138" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H138" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I138" s="79" t="n">
         <v>2130.049</v>
@@ -26376,7 +26533,7 @@
         <v>11</v>
       </c>
       <c r="S138" s="66" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26384,7 +26541,7 @@
         <v>176</v>
       </c>
       <c r="B139" s="76" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C139" s="77" t="n">
         <v>2023</v>
@@ -26396,13 +26553,13 @@
         <v>45199</v>
       </c>
       <c r="F139" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G139" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H139" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G139" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H139" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I139" s="79" t="n">
         <v>1993.007</v>
@@ -26435,7 +26592,7 @@
         <v>12</v>
       </c>
       <c r="S139" s="66" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26443,7 +26600,7 @@
         <v>176</v>
       </c>
       <c r="B140" s="76" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C140" s="77" t="n">
         <v>2023</v>
@@ -26455,13 +26612,13 @@
         <v>45107</v>
       </c>
       <c r="F140" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G140" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H140" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G140" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H140" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I140" s="79" t="n">
         <v>1930.516</v>
@@ -26494,7 +26651,7 @@
         <v>13</v>
       </c>
       <c r="S140" s="66" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26502,7 +26659,7 @@
         <v>176</v>
       </c>
       <c r="B141" s="76" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C141" s="77" t="n">
         <v>2023</v>
@@ -26514,13 +26671,13 @@
         <v>45016</v>
       </c>
       <c r="F141" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G141" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H141" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G141" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H141" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I141" s="79" t="n">
         <v>2260.206</v>
@@ -26553,7 +26710,7 @@
         <v>14</v>
       </c>
       <c r="S141" s="66" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26561,7 +26718,7 @@
         <v>176</v>
       </c>
       <c r="B142" s="76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C142" s="77" t="n">
         <v>2022</v>
@@ -26573,13 +26730,13 @@
         <v>44926</v>
       </c>
       <c r="F142" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G142" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H142" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G142" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H142" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I142" s="79" t="n">
         <v>2286.572</v>
@@ -26612,7 +26769,7 @@
         <v>15</v>
       </c>
       <c r="S142" s="66" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26620,7 +26777,7 @@
         <v>176</v>
       </c>
       <c r="B143" s="76" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C143" s="77" t="n">
         <v>2022</v>
@@ -26632,13 +26789,13 @@
         <v>44834</v>
       </c>
       <c r="F143" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G143" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H143" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G143" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H143" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I143" s="79" t="n">
         <v>2560.341</v>
@@ -26671,7 +26828,7 @@
         <v>16</v>
       </c>
       <c r="S143" s="66" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26679,7 +26836,7 @@
         <v>176</v>
       </c>
       <c r="B144" s="76" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C144" s="77" t="n">
         <v>2022</v>
@@ -26691,13 +26848,13 @@
         <v>44742</v>
       </c>
       <c r="F144" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G144" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H144" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G144" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H144" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I144" s="79" t="n">
         <v>2866.579</v>
@@ -26730,7 +26887,7 @@
         <v>17</v>
       </c>
       <c r="S144" s="66" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26738,7 +26895,7 @@
         <v>176</v>
       </c>
       <c r="B145" s="76" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C145" s="77" t="n">
         <v>2022</v>
@@ -26750,13 +26907,13 @@
         <v>44651</v>
       </c>
       <c r="F145" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G145" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H145" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G145" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H145" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I145" s="79" t="n">
         <v>2589.737</v>
@@ -26789,7 +26946,7 @@
         <v>18</v>
       </c>
       <c r="S145" s="66" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26797,7 +26954,7 @@
         <v>176</v>
       </c>
       <c r="B146" s="76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C146" s="77" t="n">
         <v>2021</v>
@@ -26809,13 +26966,13 @@
         <v>44561</v>
       </c>
       <c r="F146" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G146" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H146" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G146" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H146" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I146" s="79" t="n">
         <v>2396.847</v>
@@ -26848,7 +27005,7 @@
         <v>19</v>
       </c>
       <c r="S146" s="66" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26856,7 +27013,7 @@
         <v>176</v>
       </c>
       <c r="B147" s="76" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C147" s="77" t="n">
         <v>2021</v>
@@ -26868,13 +27025,13 @@
         <v>44469</v>
       </c>
       <c r="F147" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G147" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H147" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G147" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H147" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I147" s="79" t="n">
         <v>2973.845</v>
@@ -26907,7 +27064,7 @@
         <v>20</v>
       </c>
       <c r="S147" s="66" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26915,7 +27072,7 @@
         <v>176</v>
       </c>
       <c r="B148" s="76" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C148" s="77" t="n">
         <v>2021</v>
@@ -26927,13 +27084,13 @@
         <v>44377</v>
       </c>
       <c r="F148" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G148" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H148" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G148" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H148" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I148" s="79" t="n">
         <v>2885.046</v>
@@ -26966,7 +27123,7 @@
         <v>21</v>
       </c>
       <c r="S148" s="66" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26974,7 +27131,7 @@
         <v>176</v>
       </c>
       <c r="B149" s="76" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C149" s="77" t="n">
         <v>2021</v>
@@ -26986,13 +27143,13 @@
         <v>44286</v>
       </c>
       <c r="F149" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G149" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H149" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G149" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H149" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I149" s="79" t="n">
         <v>1939.92</v>
@@ -27025,7 +27182,7 @@
         <v>22</v>
       </c>
       <c r="S149" s="66" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27033,7 +27190,7 @@
         <v>176</v>
       </c>
       <c r="B150" s="76" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C150" s="77" t="n">
         <v>2020</v>
@@ -27045,13 +27202,13 @@
         <v>44196</v>
       </c>
       <c r="F150" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G150" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H150" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G150" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H150" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I150" s="79" t="n">
         <v>1575.49</v>
@@ -27084,7 +27241,7 @@
         <v>23</v>
       </c>
       <c r="S150" s="66" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27092,7 +27249,7 @@
         <v>176</v>
       </c>
       <c r="B151" s="76" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C151" s="77" t="n">
         <v>2020</v>
@@ -27104,13 +27261,13 @@
         <v>44104</v>
       </c>
       <c r="F151" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G151" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H151" s="76" t="s">
         <v>213</v>
-      </c>
-      <c r="G151" s="76" t="s">
-        <v>214</v>
-      </c>
-      <c r="H151" s="76" t="s">
-        <v>210</v>
       </c>
       <c r="I151" s="79" t="n">
         <v>1627.205</v>
@@ -27141,162 +27298,1619 @@
         <v>24</v>
       </c>
       <c r="S151" s="66" t="s">
-        <v>386</v>
+        <v>389</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B152" s="76" t="s">
+        <v>210</v>
+      </c>
+      <c r="C152" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D152" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E152" s="78" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F152" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="G152" s="76" t="s">
+        <v>212</v>
+      </c>
+      <c r="H152" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I152" s="79"/>
+      <c r="J152" s="79"/>
+      <c r="K152" s="79"/>
+      <c r="L152" s="80" t="n">
+        <v>7.90333</v>
+      </c>
+      <c r="M152" s="79"/>
+      <c r="N152" s="79"/>
+      <c r="O152" s="79"/>
+      <c r="P152" s="80"/>
+      <c r="Q152" s="80"/>
+      <c r="R152" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" s="66" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="81" t="s">
-        <v>387</v>
+      <c r="A153" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B153" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="C153" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D153" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" s="78" t="n">
+        <v>46203</v>
+      </c>
+      <c r="F153" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G153" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H153" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I153" s="79" t="n">
+        <v>20825.411</v>
+      </c>
+      <c r="J153" s="79" t="n">
+        <v>2810.847</v>
+      </c>
+      <c r="K153" s="79" t="n">
+        <v>1535124000</v>
+      </c>
+      <c r="L153" s="80" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="M153" s="79" t="n">
+        <v>194.008</v>
+      </c>
+      <c r="N153" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="79" t="n">
+        <v>21975.278</v>
+      </c>
+      <c r="P153" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" s="80" t="n">
+        <v>549</v>
+      </c>
+      <c r="R153" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S153" s="66" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="42" t="s">
-        <v>388</v>
+      <c r="A154" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B154" s="76" t="s">
+        <v>219</v>
+      </c>
+      <c r="C154" s="77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D154" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" s="78" t="n">
+        <v>46112</v>
+      </c>
+      <c r="F154" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G154" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H154" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I154" s="79" t="n">
+        <v>18536.692</v>
+      </c>
+      <c r="J154" s="79" t="n">
+        <v>2517.46</v>
+      </c>
+      <c r="K154" s="79" t="n">
+        <v>1322921000</v>
+      </c>
+      <c r="L154" s="80" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="M154" s="79" t="n">
+        <v>193.6577</v>
+      </c>
+      <c r="N154" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="79" t="n">
+        <v>19214.366</v>
+      </c>
+      <c r="P154" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="80" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="R154" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S154" s="66" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="82" t="s">
-        <v>389</v>
-      </c>
-      <c r="C155" s="24" t="s">
-        <v>390</v>
+      <c r="A155" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B155" s="76" t="s">
+        <v>221</v>
+      </c>
+      <c r="C155" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D155" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E155" s="78" t="n">
+        <v>46022</v>
+      </c>
+      <c r="F155" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G155" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H155" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I155" s="79" t="n">
+        <v>17298.641</v>
+      </c>
+      <c r="J155" s="79" t="n">
+        <v>2303.334</v>
+      </c>
+      <c r="K155" s="79" t="n">
+        <v>1223169000</v>
+      </c>
+      <c r="L155" s="80" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="M155" s="79" t="n">
+        <v>192.3546</v>
+      </c>
+      <c r="N155" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="79" t="n">
+        <v>19999.753</v>
+      </c>
+      <c r="P155" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="80" t="n">
+        <v>291</v>
+      </c>
+      <c r="R155" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S155" s="66" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="82" t="s">
-        <v>391</v>
-      </c>
-      <c r="C156" s="24" t="s">
-        <v>390</v>
+      <c r="A156" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B156" s="76" t="s">
+        <v>223</v>
+      </c>
+      <c r="C156" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D156" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E156" s="78" t="n">
+        <v>45930</v>
+      </c>
+      <c r="F156" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G156" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H156" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I156" s="79" t="n">
+        <v>17538.579</v>
+      </c>
+      <c r="J156" s="79" t="n">
+        <v>2251.328</v>
+      </c>
+      <c r="K156" s="79" t="n">
+        <v>1103412000</v>
+      </c>
+      <c r="L156" s="80" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M156" s="79" t="n">
+        <v>192.1998</v>
+      </c>
+      <c r="N156" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="79" t="n">
+        <v>18739.987</v>
+      </c>
+      <c r="P156" s="80" t="n">
+        <v>11.98556796</v>
+      </c>
+      <c r="Q156" s="80" t="n">
+        <v>314</v>
+      </c>
+      <c r="R156" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="S156" s="66" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="82" t="s">
-        <v>392</v>
-      </c>
-      <c r="C157" s="24" t="s">
-        <v>390</v>
+      <c r="A157" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B157" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="C157" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D157" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" s="78" t="n">
+        <v>45838</v>
+      </c>
+      <c r="F157" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G157" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H157" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I157" s="79" t="n">
+        <v>16986.85</v>
+      </c>
+      <c r="J157" s="79" t="n">
+        <v>1988.366</v>
+      </c>
+      <c r="K157" s="79" t="n">
+        <v>914696000</v>
+      </c>
+      <c r="L157" s="80" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="M157" s="79" t="n">
+        <v>191.3427</v>
+      </c>
+      <c r="N157" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" s="79" t="n">
+        <v>17068.444</v>
+      </c>
+      <c r="P157" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" s="80" t="n">
+        <v>274.5</v>
+      </c>
+      <c r="R157" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S157" s="66" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="82" t="s">
-        <v>393</v>
-      </c>
-      <c r="C158" s="24" t="s">
-        <v>390</v>
+      <c r="A158" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B158" s="76" t="s">
+        <v>227</v>
+      </c>
+      <c r="C158" s="77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D158" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" s="78" t="n">
+        <v>45747</v>
+      </c>
+      <c r="F158" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G158" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H158" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I158" s="79" t="n">
+        <v>15759.461</v>
+      </c>
+      <c r="J158" s="79" t="n">
+        <v>2107.35</v>
+      </c>
+      <c r="K158" s="79" t="n">
+        <v>939170000</v>
+      </c>
+      <c r="L158" s="80" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="M158" s="79" t="n">
+        <v>191.3323</v>
+      </c>
+      <c r="N158" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="79" t="n">
+        <v>16498.529</v>
+      </c>
+      <c r="P158" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" s="80" t="n">
+        <v>261</v>
+      </c>
+      <c r="R158" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="S158" s="66" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="82" t="s">
-        <v>394</v>
-      </c>
-      <c r="C159" s="24" t="s">
-        <v>390</v>
+      <c r="A159" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B159" s="76" t="s">
+        <v>229</v>
+      </c>
+      <c r="C159" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D159" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E159" s="78" t="n">
+        <v>45657</v>
+      </c>
+      <c r="F159" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G159" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H159" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I159" s="79" t="n">
+        <v>15907.231</v>
+      </c>
+      <c r="J159" s="79" t="n">
+        <v>2057.74</v>
+      </c>
+      <c r="K159" s="79" t="n">
+        <v>923666000</v>
+      </c>
+      <c r="L159" s="80" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="M159" s="79" t="n">
+        <v>191.0393</v>
+      </c>
+      <c r="N159" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" s="79" t="n">
+        <v>17771.222</v>
+      </c>
+      <c r="P159" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" s="80" t="n">
+        <v>280</v>
+      </c>
+      <c r="R159" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="S159" s="66" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="82" t="s">
-        <v>395</v>
-      </c>
-      <c r="C160" s="24" t="s">
-        <v>396</v>
+      <c r="A160" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B160" s="76" t="s">
+        <v>231</v>
+      </c>
+      <c r="C160" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D160" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E160" s="78" t="n">
+        <v>45565</v>
+      </c>
+      <c r="F160" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G160" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H160" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I160" s="79" t="n">
+        <v>15366.525</v>
+      </c>
+      <c r="J160" s="79" t="n">
+        <v>2043.096</v>
+      </c>
+      <c r="K160" s="79" t="n">
+        <v>936620000</v>
+      </c>
+      <c r="L160" s="80" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="M160" s="79" t="n">
+        <v>190.554</v>
+      </c>
+      <c r="N160" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="79" t="n">
+        <v>16789.65</v>
+      </c>
+      <c r="P160" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" s="80" t="n">
+        <v>282</v>
+      </c>
+      <c r="R160" s="47" t="n">
+        <v>8</v>
+      </c>
+      <c r="S160" s="66" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="82" t="s">
-        <v>397</v>
-      </c>
-      <c r="C161" s="24" t="s">
-        <v>396</v>
+      <c r="A161" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B161" s="76" t="s">
+        <v>233</v>
+      </c>
+      <c r="C161" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D161" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" s="78" t="n">
+        <v>45473</v>
+      </c>
+      <c r="F161" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G161" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H161" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I161" s="79" t="n">
+        <v>13791.78</v>
+      </c>
+      <c r="J161" s="79" t="n">
+        <v>1931.406</v>
+      </c>
+      <c r="K161" s="79" t="n">
+        <v>1020612000</v>
+      </c>
+      <c r="L161" s="80" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="M161" s="79" t="n">
+        <v>188.7641</v>
+      </c>
+      <c r="N161" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="79" t="n">
+        <v>15437.575</v>
+      </c>
+      <c r="P161" s="80" t="n">
+        <v>9.99658303</v>
+      </c>
+      <c r="Q161" s="80" t="n">
+        <v>275</v>
+      </c>
+      <c r="R161" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="S161" s="66" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="82" t="s">
-        <v>398</v>
-      </c>
-      <c r="C162" s="25" t="s">
-        <v>399</v>
+      <c r="A162" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B162" s="76" t="s">
+        <v>235</v>
+      </c>
+      <c r="C162" s="77" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D162" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="78" t="n">
+        <v>45382</v>
+      </c>
+      <c r="F162" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G162" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H162" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I162" s="79" t="n">
+        <v>11931.577</v>
+      </c>
+      <c r="J162" s="79" t="n">
+        <v>1685.728</v>
+      </c>
+      <c r="K162" s="79" t="n">
+        <v>775037000</v>
+      </c>
+      <c r="L162" s="80" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="M162" s="79" t="n">
+        <v>188.7001</v>
+      </c>
+      <c r="N162" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="79" t="n">
+        <v>14274.286</v>
+      </c>
+      <c r="P162" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="80" t="n">
+        <v>219</v>
+      </c>
+      <c r="R162" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="S162" s="66" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="82" t="s">
-        <v>400</v>
-      </c>
-      <c r="C163" s="24" t="s">
+      <c r="A163" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B163" s="76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C163" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D163" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E163" s="78" t="n">
+        <v>45291</v>
+      </c>
+      <c r="F163" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G163" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H163" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I163" s="79" t="n">
+        <v>12233.421</v>
+      </c>
+      <c r="J163" s="79" t="n">
+        <v>1593.449</v>
+      </c>
+      <c r="K163" s="79" t="n">
+        <v>633558000</v>
+      </c>
+      <c r="L163" s="80" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="M163" s="79" t="n">
+        <v>188.6996</v>
+      </c>
+      <c r="N163" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="79" t="n">
+        <v>15109.065</v>
+      </c>
+      <c r="P163" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="80" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R163" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="S163" s="66" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="82" t="s">
+      <c r="A164" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B164" s="76" t="s">
+        <v>239</v>
+      </c>
+      <c r="C164" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D164" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E164" s="78" t="n">
+        <v>45199</v>
+      </c>
+      <c r="F164" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G164" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H164" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I164" s="79" t="n">
+        <v>12492.338</v>
+      </c>
+      <c r="J164" s="79" t="n">
+        <v>1743.119</v>
+      </c>
+      <c r="K164" s="79" t="n">
+        <v>791913000</v>
+      </c>
+      <c r="L164" s="80" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="M164" s="79" t="n">
+        <v>188.6996</v>
+      </c>
+      <c r="N164" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="79" t="n">
+        <v>14413.298</v>
+      </c>
+      <c r="P164" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="80" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="R164" s="47" t="n">
+        <v>12</v>
+      </c>
+      <c r="S164" s="66" t="s">
         <v>402</v>
       </c>
-      <c r="C164" s="24" t="s">
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B165" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="C165" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D165" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" s="78" t="n">
+        <v>45107</v>
+      </c>
+      <c r="F165" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G165" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H165" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I165" s="79" t="n">
+        <v>12055.351</v>
+      </c>
+      <c r="J165" s="79" t="n">
+        <v>1581.488</v>
+      </c>
+      <c r="K165" s="79" t="n">
+        <v>669619000</v>
+      </c>
+      <c r="L165" s="80" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="M165" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N165" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="79" t="n">
+        <v>12564.042</v>
+      </c>
+      <c r="P165" s="80" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q165" s="80" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R165" s="47" t="n">
+        <v>13</v>
+      </c>
+      <c r="S165" s="66" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="82" t="s">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B166" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="C166" s="77" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D166" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="78" t="n">
+        <v>45016</v>
+      </c>
+      <c r="F166" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G166" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H166" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I166" s="79" t="n">
+        <v>12492.345</v>
+      </c>
+      <c r="J166" s="79" t="n">
+        <v>1500.744</v>
+      </c>
+      <c r="K166" s="79" t="n">
+        <v>739934000</v>
+      </c>
+      <c r="L166" s="80" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="M166" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N166" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" s="79" t="n">
+        <v>11830.406</v>
+      </c>
+      <c r="P166" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="80" t="n">
+        <v>189</v>
+      </c>
+      <c r="R166" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="S166" s="66" t="s">
         <v>404</v>
       </c>
-      <c r="C165" s="25" t="s">
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B167" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="C167" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D167" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E167" s="78" t="n">
+        <v>44926</v>
+      </c>
+      <c r="F167" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G167" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H167" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I167" s="79" t="n">
+        <v>13377.459</v>
+      </c>
+      <c r="J167" s="79" t="n">
+        <v>1601.395</v>
+      </c>
+      <c r="K167" s="79" t="n">
+        <v>565094000</v>
+      </c>
+      <c r="L167" s="80" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="M167" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N167" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="79" t="n">
+        <v>12959.644</v>
+      </c>
+      <c r="P167" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="80" t="n">
+        <v>164</v>
+      </c>
+      <c r="R167" s="47" t="n">
+        <v>15</v>
+      </c>
+      <c r="S167" s="66" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="82" t="s">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B168" s="76" t="s">
+        <v>247</v>
+      </c>
+      <c r="C168" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D168" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E168" s="78" t="n">
+        <v>44834</v>
+      </c>
+      <c r="F168" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G168" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H168" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I168" s="79" t="n">
+        <v>13792.845</v>
+      </c>
+      <c r="J168" s="79" t="n">
+        <v>1840.106</v>
+      </c>
+      <c r="K168" s="79" t="n">
+        <v>893203000</v>
+      </c>
+      <c r="L168" s="80" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="M168" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N168" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" s="79" t="n">
+        <v>12162.603</v>
+      </c>
+      <c r="P168" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="80" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="R168" s="47" t="n">
+        <v>16</v>
+      </c>
+      <c r="S168" s="66" t="s">
         <v>406</v>
       </c>
-      <c r="C166" s="25" t="s">
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B169" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="C169" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D169" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" s="78" t="n">
+        <v>44742</v>
+      </c>
+      <c r="F169" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G169" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H169" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I169" s="79" t="n">
+        <v>13225.334</v>
+      </c>
+      <c r="J169" s="79" t="n">
+        <v>1622.386</v>
+      </c>
+      <c r="K169" s="79" t="n">
+        <v>900267000</v>
+      </c>
+      <c r="L169" s="80" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="M169" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N169" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" s="79" t="n">
+        <v>11202.522</v>
+      </c>
+      <c r="P169" s="80" t="n">
+        <v>8.8</v>
+      </c>
+      <c r="Q169" s="80" t="n">
+        <v>138</v>
+      </c>
+      <c r="R169" s="47" t="n">
+        <v>17</v>
+      </c>
+      <c r="S169" s="66" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="82" t="s">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B170" s="76" t="s">
+        <v>251</v>
+      </c>
+      <c r="C170" s="77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D170" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" s="78" t="n">
+        <v>44651</v>
+      </c>
+      <c r="F170" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G170" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H170" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I170" s="79" t="n">
+        <v>12582.577</v>
+      </c>
+      <c r="J170" s="79" t="n">
+        <v>1461.477</v>
+      </c>
+      <c r="K170" s="79" t="n">
+        <v>659914000</v>
+      </c>
+      <c r="L170" s="80" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M170" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N170" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="79" t="n">
+        <v>10707.907</v>
+      </c>
+      <c r="P170" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="80" t="n">
+        <v>170</v>
+      </c>
+      <c r="R170" s="47" t="n">
+        <v>18</v>
+      </c>
+      <c r="S170" s="66" t="s">
         <v>408</v>
       </c>
-      <c r="C167" s="24" t="s">
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B171" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="C171" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D171" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E171" s="78" t="n">
+        <v>44561</v>
+      </c>
+      <c r="F171" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G171" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H171" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I171" s="79" t="n">
+        <v>11766.16</v>
+      </c>
+      <c r="J171" s="79" t="n">
+        <v>1498.856</v>
+      </c>
+      <c r="K171" s="79" t="n">
+        <v>633208000</v>
+      </c>
+      <c r="L171" s="80" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="M171" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N171" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="79" t="n">
+        <v>11596.572</v>
+      </c>
+      <c r="P171" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="80" t="n">
+        <v>158</v>
+      </c>
+      <c r="R171" s="47" t="n">
+        <v>19</v>
+      </c>
+      <c r="S171" s="66" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="82" t="s">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B172" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="C172" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D172" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E172" s="78" t="n">
+        <v>44469</v>
+      </c>
+      <c r="F172" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G172" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H172" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I172" s="79" t="n">
+        <v>10988.763</v>
+      </c>
+      <c r="J172" s="79" t="n">
+        <v>1338.868</v>
+      </c>
+      <c r="K172" s="79" t="n">
+        <v>593514000</v>
+      </c>
+      <c r="L172" s="80" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M172" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N172" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" s="79" t="n">
+        <v>10701.466</v>
+      </c>
+      <c r="P172" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="80" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="R172" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="S172" s="66" t="s">
         <v>410</v>
       </c>
-      <c r="C168" s="24" t="s">
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B173" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="C173" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D173" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" s="78" t="n">
+        <v>44377</v>
+      </c>
+      <c r="F173" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G173" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H173" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I173" s="79" t="n">
+        <v>10381.154</v>
+      </c>
+      <c r="J173" s="79" t="n">
+        <v>1276.802</v>
+      </c>
+      <c r="K173" s="79" t="n">
+        <v>613334000</v>
+      </c>
+      <c r="L173" s="80" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M173" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N173" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" s="79" t="n">
+        <v>10141.465</v>
+      </c>
+      <c r="P173" s="80" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q173" s="80" t="n">
+        <v>125</v>
+      </c>
+      <c r="R173" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="S173" s="66" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="82" t="s">
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B174" s="76" t="s">
+        <v>259</v>
+      </c>
+      <c r="C174" s="77" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D174" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="78" t="n">
+        <v>44286</v>
+      </c>
+      <c r="F174" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G174" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H174" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I174" s="79" t="n">
+        <v>9532.889</v>
+      </c>
+      <c r="J174" s="79" t="n">
+        <v>1097.678</v>
+      </c>
+      <c r="K174" s="79" t="n">
+        <v>454402000</v>
+      </c>
+      <c r="L174" s="80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M174" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N174" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="79" t="n">
+        <v>9570.395</v>
+      </c>
+      <c r="P174" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="80" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="R174" s="47" t="n">
+        <v>22</v>
+      </c>
+      <c r="S174" s="66" t="s">
         <v>412</v>
       </c>
-      <c r="C169" s="25" t="s">
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B175" s="76" t="s">
+        <v>261</v>
+      </c>
+      <c r="C175" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D175" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E175" s="78" t="n">
+        <v>44196</v>
+      </c>
+      <c r="F175" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G175" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H175" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I175" s="79" t="n">
+        <v>8938.602</v>
+      </c>
+      <c r="J175" s="79" t="n">
+        <v>1094.556</v>
+      </c>
+      <c r="K175" s="79" t="n">
+        <v>548182000</v>
+      </c>
+      <c r="L175" s="80" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="M175" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N175" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="79" t="n">
+        <v>10573.627</v>
+      </c>
+      <c r="P175" s="80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="80" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="R175" s="47" t="n">
+        <v>23</v>
+      </c>
+      <c r="S175" s="66" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="82" t="s">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B176" s="76" t="s">
+        <v>263</v>
+      </c>
+      <c r="C176" s="77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D176" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E176" s="78" t="n">
+        <v>44104</v>
+      </c>
+      <c r="F176" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="G176" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="H176" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="I176" s="79" t="n">
+        <v>9067.715</v>
+      </c>
+      <c r="J176" s="79" t="n">
+        <v>1028.467</v>
+      </c>
+      <c r="K176" s="79" t="n">
+        <v>521666000</v>
+      </c>
+      <c r="L176" s="80" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M176" s="79" t="n">
+        <v>181.6996</v>
+      </c>
+      <c r="N176" s="79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" s="79" t="n">
+        <v>9893.143</v>
+      </c>
+      <c r="P176" s="80"/>
+      <c r="Q176" s="80" t="n">
+        <v>114</v>
+      </c>
+      <c r="R176" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="S176" s="66" t="s">
         <v>414</v>
       </c>
-      <c r="C170" s="24" t="s">
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="81" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="42" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="82" t="s">
+        <v>417</v>
+      </c>
+      <c r="C180" s="24" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="82" t="s">
+        <v>419</v>
+      </c>
+      <c r="C181" s="24" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="82" t="s">
+        <v>420</v>
+      </c>
+      <c r="C182" s="24" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="82" t="s">
+        <v>421</v>
+      </c>
+      <c r="C183" s="24" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="82" t="s">
+        <v>422</v>
+      </c>
+      <c r="C184" s="24" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="82" t="s">
+        <v>423</v>
+      </c>
+      <c r="C185" s="24" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="82" t="s">
+        <v>425</v>
+      </c>
+      <c r="C186" s="24" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="82" t="s">
+        <v>426</v>
+      </c>
+      <c r="C187" s="25" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="82" t="s">
+        <v>428</v>
+      </c>
+      <c r="C188" s="24" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="82" t="s">
+        <v>430</v>
+      </c>
+      <c r="C189" s="24" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="82" t="s">
+        <v>432</v>
+      </c>
+      <c r="C190" s="25" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="82" t="s">
+        <v>434</v>
+      </c>
+      <c r="C191" s="25" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="82" t="s">
+        <v>436</v>
+      </c>
+      <c r="C192" s="24" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="82" t="s">
+        <v>438</v>
+      </c>
+      <c r="C193" s="24" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="82" t="s">
+        <v>440</v>
+      </c>
+      <c r="C194" s="25" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="82" t="s">
+        <v>442</v>
+      </c>
+      <c r="C195" s="24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="82" t="s">
-        <v>415</v>
-      </c>
-      <c r="C171" s="24" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="24" t="s">
-        <v>417</v>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="82" t="s">
+        <v>443</v>
+      </c>
+      <c r="C196" s="24" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="24" t="s">
+        <v>445</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S151"/>
+  <autoFilter ref="A1:S176"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -27313,7 +28927,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -27328,19 +28942,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>422</v>
+        <v>450</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27463,9 +29077,29 @@
         <v>46272</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
-        <v>423</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="76" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="80" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="C8" s="80" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="D8" s="78" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E8" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="78" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="25" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="524">
   <si>
     <r>
       <rPr>
@@ -3861,6 +3861,9 @@
   </si>
   <si>
     <t xml:space="preserve">池子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPO</t>
   </si>
   <si>
     <t xml:space="preserve">3034</t>
@@ -8266,16 +8269,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8295,7 +8298,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B3" s="80" t="n">
         <v>361</v>
@@ -8340,7 +8343,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" s="80" t="n">
         <v>524</v>
@@ -8355,7 +8358,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="80" t="n">
         <v>2145</v>
@@ -8385,7 +8388,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="80" t="n">
         <v>538</v>
@@ -8463,16 +8466,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -8481,13 +8484,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -8496,7 +8499,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -8505,16 +8508,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -8523,16 +8526,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -8541,7 +8544,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -8550,7 +8553,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -8559,7 +8562,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -8571,19 +8574,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12228,7 +12231,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -12257,78 +12260,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -17252,7 +17255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6A6BCD22-7C42-4B93-AA79-609BEF4A45D4}</x14:id>
+          <x14:id>{8FCA1B15-646A-405F-B145-97E4842CD03E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17383,7 +17386,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6A6BCD22-7C42-4B93-AA79-609BEF4A45D4}">
+          <x14:cfRule type="dataBar" id="{8FCA1B15-646A-405F-B145-97E4842CD03E}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18441,7 +18444,9 @@
       <c r="D5" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="E5" s="73"/>
+      <c r="E5" s="73" t="s">
+        <v>183</v>
+      </c>
       <c r="F5" s="75" t="n">
         <v>46267</v>
       </c>
@@ -18449,10 +18454,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="73" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C6" s="74" t="s">
         <v>169</v>
@@ -18468,13 +18473,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="74" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D7" s="74" t="s">
         <v>182</v>
@@ -18487,13 +18492,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="73" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" s="74" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D8" s="74" t="s">
         <v>182</v>
@@ -18506,13 +18511,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="73" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C9" s="74" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D9" s="74" t="s">
         <v>182</v>
@@ -18633,7 +18638,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -18676,58 +18681,58 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18735,7 +18740,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" s="77" t="n">
         <v>2026</v>
@@ -18747,13 +18752,13 @@
         <v>46295</v>
       </c>
       <c r="F2" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G2" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H2" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I2" s="79"/>
       <c r="J2" s="79"/>
@@ -18770,7 +18775,7 @@
         <v>0</v>
       </c>
       <c r="S2" s="66" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18778,7 +18783,7 @@
         <v>167</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C3" s="77" t="n">
         <v>2026</v>
@@ -18790,13 +18795,13 @@
         <v>46203</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G3" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H3" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I3" s="79" t="n">
         <v>1270380.25</v>
@@ -18829,7 +18834,7 @@
         <v>1</v>
       </c>
       <c r="S3" s="66" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18837,7 +18842,7 @@
         <v>167</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C4" s="77" t="n">
         <v>2026</v>
@@ -18849,13 +18854,13 @@
         <v>46112</v>
       </c>
       <c r="F4" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H4" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I4" s="79" t="n">
         <v>1134103.44</v>
@@ -18888,7 +18893,7 @@
         <v>2</v>
       </c>
       <c r="S4" s="66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18896,7 +18901,7 @@
         <v>167</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C5" s="77" t="n">
         <v>2025</v>
@@ -18908,13 +18913,13 @@
         <v>46022</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G5" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H5" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I5" s="79" t="n">
         <v>1046090.421</v>
@@ -18947,7 +18952,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="66" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18955,7 +18960,7 @@
         <v>167</v>
       </c>
       <c r="B6" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C6" s="77" t="n">
         <v>2025</v>
@@ -18967,13 +18972,13 @@
         <v>45930</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G6" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H6" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I6" s="79" t="n">
         <v>989918.318</v>
@@ -19006,7 +19011,7 @@
         <v>4</v>
       </c>
       <c r="S6" s="66" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19014,7 +19019,7 @@
         <v>167</v>
       </c>
       <c r="B7" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C7" s="77" t="n">
         <v>2025</v>
@@ -19026,13 +19031,13 @@
         <v>45838</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G7" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I7" s="79" t="n">
         <v>933791.869</v>
@@ -19065,7 +19070,7 @@
         <v>5</v>
       </c>
       <c r="S7" s="66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19073,7 +19078,7 @@
         <v>167</v>
       </c>
       <c r="B8" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C8" s="77" t="n">
         <v>2025</v>
@@ -19085,13 +19090,13 @@
         <v>45747</v>
       </c>
       <c r="F8" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G8" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H8" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I8" s="79" t="n">
         <v>839253.664</v>
@@ -19124,7 +19129,7 @@
         <v>6</v>
       </c>
       <c r="S8" s="66" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19132,7 +19137,7 @@
         <v>167</v>
       </c>
       <c r="B9" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C9" s="77" t="n">
         <v>2024</v>
@@ -19144,13 +19149,13 @@
         <v>45657</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G9" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H9" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I9" s="79" t="n">
         <v>868461.178</v>
@@ -19183,7 +19188,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="66" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19191,7 +19196,7 @@
         <v>167</v>
       </c>
       <c r="B10" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C10" s="77" t="n">
         <v>2024</v>
@@ -19203,13 +19208,13 @@
         <v>45565</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G10" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H10" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I10" s="79" t="n">
         <v>759692.143</v>
@@ -19242,7 +19247,7 @@
         <v>8</v>
       </c>
       <c r="S10" s="66" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19250,7 +19255,7 @@
         <v>167</v>
       </c>
       <c r="B11" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C11" s="77" t="n">
         <v>2024</v>
@@ -19262,13 +19267,13 @@
         <v>45473</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G11" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H11" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I11" s="79" t="n">
         <v>673510.177</v>
@@ -19301,7 +19306,7 @@
         <v>9</v>
       </c>
       <c r="S11" s="66" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19309,7 +19314,7 @@
         <v>167</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C12" s="77" t="n">
         <v>2024</v>
@@ -19321,13 +19326,13 @@
         <v>45382</v>
       </c>
       <c r="F12" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G12" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H12" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I12" s="79" t="n">
         <v>592644.201</v>
@@ -19360,7 +19365,7 @@
         <v>10</v>
       </c>
       <c r="S12" s="66" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19368,7 +19373,7 @@
         <v>167</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C13" s="77" t="n">
         <v>2023</v>
@@ -19380,13 +19385,13 @@
         <v>45291</v>
       </c>
       <c r="F13" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G13" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H13" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I13" s="79" t="n">
         <v>625528.856</v>
@@ -19419,7 +19424,7 @@
         <v>11</v>
       </c>
       <c r="S13" s="66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19427,7 +19432,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C14" s="77" t="n">
         <v>2023</v>
@@ -19439,13 +19444,13 @@
         <v>45199</v>
       </c>
       <c r="F14" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G14" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H14" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I14" s="79" t="n">
         <v>546732.758</v>
@@ -19478,7 +19483,7 @@
         <v>12</v>
       </c>
       <c r="S14" s="66" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19486,7 +19491,7 @@
         <v>167</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C15" s="77" t="n">
         <v>2023</v>
@@ -19498,13 +19503,13 @@
         <v>45107</v>
       </c>
       <c r="F15" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G15" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H15" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I15" s="79" t="n">
         <v>480841.254</v>
@@ -19537,7 +19542,7 @@
         <v>13</v>
       </c>
       <c r="S15" s="66" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19545,7 +19550,7 @@
         <v>167</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C16" s="77" t="n">
         <v>2023</v>
@@ -19557,13 +19562,13 @@
         <v>45016</v>
       </c>
       <c r="F16" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G16" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H16" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I16" s="79" t="n">
         <v>508632.973</v>
@@ -19596,7 +19601,7 @@
         <v>14</v>
       </c>
       <c r="S16" s="66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19604,7 +19609,7 @@
         <v>167</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C17" s="77" t="n">
         <v>2022</v>
@@ -19616,13 +19621,13 @@
         <v>44926</v>
       </c>
       <c r="F17" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G17" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H17" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I17" s="79" t="n">
         <v>625531.868</v>
@@ -19655,7 +19660,7 @@
         <v>15</v>
       </c>
       <c r="S17" s="66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19663,7 +19668,7 @@
         <v>167</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C18" s="77" t="n">
         <v>2022</v>
@@ -19675,13 +19680,13 @@
         <v>44834</v>
       </c>
       <c r="F18" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G18" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H18" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I18" s="79" t="n">
         <v>613142.743</v>
@@ -19714,7 +19719,7 @@
         <v>16</v>
       </c>
       <c r="S18" s="66" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19722,7 +19727,7 @@
         <v>167</v>
       </c>
       <c r="B19" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C19" s="77" t="n">
         <v>2022</v>
@@ -19734,13 +19739,13 @@
         <v>44742</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G19" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H19" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I19" s="79" t="n">
         <v>534140.808</v>
@@ -19773,7 +19778,7 @@
         <v>17</v>
       </c>
       <c r="S19" s="66" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19781,7 +19786,7 @@
         <v>167</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C20" s="77" t="n">
         <v>2022</v>
@@ -19793,13 +19798,13 @@
         <v>44651</v>
       </c>
       <c r="F20" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G20" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H20" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I20" s="79" t="n">
         <v>491075.873</v>
@@ -19832,7 +19837,7 @@
         <v>18</v>
       </c>
       <c r="S20" s="66" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19840,7 +19845,7 @@
         <v>167</v>
       </c>
       <c r="B21" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C21" s="77" t="n">
         <v>2021</v>
@@ -19852,13 +19857,13 @@
         <v>44561</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G21" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H21" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I21" s="79" t="n">
         <v>438189.306</v>
@@ -19891,7 +19896,7 @@
         <v>19</v>
       </c>
       <c r="S21" s="66" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19899,7 +19904,7 @@
         <v>167</v>
       </c>
       <c r="B22" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C22" s="77" t="n">
         <v>2021</v>
@@ -19911,13 +19916,13 @@
         <v>44469</v>
       </c>
       <c r="F22" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G22" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H22" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I22" s="79" t="n">
         <v>414670.379</v>
@@ -19950,7 +19955,7 @@
         <v>20</v>
       </c>
       <c r="S22" s="66" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19958,7 +19963,7 @@
         <v>167</v>
       </c>
       <c r="B23" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="77" t="n">
         <v>2021</v>
@@ -19970,13 +19975,13 @@
         <v>44377</v>
       </c>
       <c r="F23" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G23" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H23" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I23" s="79" t="n">
         <v>372145.122</v>
@@ -20009,7 +20014,7 @@
         <v>21</v>
       </c>
       <c r="S23" s="66" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20017,7 +20022,7 @@
         <v>167</v>
       </c>
       <c r="B24" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C24" s="77" t="n">
         <v>2021</v>
@@ -20029,13 +20034,13 @@
         <v>44286</v>
       </c>
       <c r="F24" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G24" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H24" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I24" s="79" t="n">
         <v>362410.23</v>
@@ -20068,7 +20073,7 @@
         <v>22</v>
       </c>
       <c r="S24" s="66" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20076,7 +20081,7 @@
         <v>167</v>
       </c>
       <c r="B25" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" s="77" t="n">
         <v>2020</v>
@@ -20088,13 +20093,13 @@
         <v>44196</v>
       </c>
       <c r="F25" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G25" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H25" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I25" s="79" t="n">
         <v>361533.057</v>
@@ -20127,7 +20132,7 @@
         <v>23</v>
       </c>
       <c r="S25" s="66" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20135,7 +20140,7 @@
         <v>167</v>
       </c>
       <c r="B26" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C26" s="77" t="n">
         <v>2020</v>
@@ -20147,13 +20152,13 @@
         <v>44104</v>
       </c>
       <c r="F26" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G26" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H26" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I26" s="79" t="n">
         <v>356426.204</v>
@@ -20184,15 +20189,15 @@
         <v>24</v>
       </c>
       <c r="S26" s="66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B27" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C27" s="77" t="n">
         <v>2026</v>
@@ -20204,13 +20209,13 @@
         <v>46295</v>
       </c>
       <c r="F27" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G27" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H27" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I27" s="79"/>
       <c r="J27" s="79"/>
@@ -20227,15 +20232,15 @@
         <v>0</v>
       </c>
       <c r="S27" s="66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B28" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C28" s="77" t="n">
         <v>2026</v>
@@ -20247,13 +20252,13 @@
         <v>46203</v>
       </c>
       <c r="F28" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G28" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H28" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I28" s="79" t="n">
         <v>144214.433</v>
@@ -20286,15 +20291,15 @@
         <v>1</v>
       </c>
       <c r="S28" s="66" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B29" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C29" s="77" t="n">
         <v>2026</v>
@@ -20306,13 +20311,13 @@
         <v>46112</v>
       </c>
       <c r="F29" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G29" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H29" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I29" s="79" t="n">
         <v>105057.33</v>
@@ -20345,15 +20350,15 @@
         <v>2</v>
       </c>
       <c r="S29" s="66" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C30" s="77" t="n">
         <v>2025</v>
@@ -20365,13 +20370,13 @@
         <v>46022</v>
       </c>
       <c r="F30" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G30" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H30" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I30" s="79" t="n">
         <v>89349.64</v>
@@ -20404,15 +20409,15 @@
         <v>3</v>
       </c>
       <c r="S30" s="66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B31" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C31" s="77" t="n">
         <v>2025</v>
@@ -20424,13 +20429,13 @@
         <v>45930</v>
       </c>
       <c r="F31" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G31" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H31" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I31" s="79" t="n">
         <v>79581.474</v>
@@ -20463,15 +20468,15 @@
         <v>4</v>
       </c>
       <c r="S31" s="66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C32" s="77" t="n">
         <v>2025</v>
@@ -20483,13 +20488,13 @@
         <v>45838</v>
       </c>
       <c r="F32" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G32" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H32" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I32" s="79" t="n">
         <v>102258.116</v>
@@ -20522,15 +20527,15 @@
         <v>5</v>
       </c>
       <c r="S32" s="66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B33" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C33" s="77" t="n">
         <v>2025</v>
@@ -20542,13 +20547,13 @@
         <v>45747</v>
       </c>
       <c r="F33" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G33" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H33" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I33" s="79" t="n">
         <v>65747.43</v>
@@ -20581,15 +20586,15 @@
         <v>6</v>
       </c>
       <c r="S33" s="66" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B34" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C34" s="77" t="n">
         <v>2024</v>
@@ -20601,13 +20606,13 @@
         <v>45657</v>
       </c>
       <c r="F34" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G34" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H34" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I34" s="79" t="n">
         <v>65615.165</v>
@@ -20640,15 +20645,15 @@
         <v>7</v>
       </c>
       <c r="S34" s="66" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B35" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C35" s="77" t="n">
         <v>2024</v>
@@ -20660,13 +20665,13 @@
         <v>45565</v>
       </c>
       <c r="F35" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G35" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H35" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I35" s="79" t="n">
         <v>70445.855</v>
@@ -20699,15 +20704,15 @@
         <v>8</v>
       </c>
       <c r="S35" s="66" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B36" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C36" s="77" t="n">
         <v>2024</v>
@@ -20719,13 +20724,13 @@
         <v>45473</v>
       </c>
       <c r="F36" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G36" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H36" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I36" s="79" t="n">
         <v>73923.373</v>
@@ -20758,15 +20763,15 @@
         <v>9</v>
       </c>
       <c r="S36" s="66" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C37" s="77" t="n">
         <v>2024</v>
@@ -20778,13 +20783,13 @@
         <v>45382</v>
       </c>
       <c r="F37" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G37" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H37" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I37" s="79" t="n">
         <v>55164.386</v>
@@ -20817,15 +20822,15 @@
         <v>10</v>
       </c>
       <c r="S37" s="66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B38" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C38" s="77" t="n">
         <v>2023</v>
@@ -20837,13 +20842,13 @@
         <v>45291</v>
       </c>
       <c r="F38" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G38" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H38" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I38" s="79" t="n">
         <v>45596.208</v>
@@ -20876,15 +20881,15 @@
         <v>11</v>
       </c>
       <c r="S38" s="66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B39" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C39" s="77" t="n">
         <v>2023</v>
@@ -20896,13 +20901,13 @@
         <v>45199</v>
       </c>
       <c r="F39" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G39" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H39" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I39" s="79" t="n">
         <v>37013.385</v>
@@ -20935,15 +20940,15 @@
         <v>12</v>
       </c>
       <c r="S39" s="66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B40" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C40" s="77" t="n">
         <v>2023</v>
@@ -20955,13 +20960,13 @@
         <v>45107</v>
       </c>
       <c r="F40" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G40" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H40" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I40" s="79" t="n">
         <v>26133.8</v>
@@ -20994,15 +20999,15 @@
         <v>13</v>
       </c>
       <c r="S40" s="66" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B41" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C41" s="77" t="n">
         <v>2023</v>
@@ -21014,13 +21019,13 @@
         <v>45016</v>
       </c>
       <c r="F41" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G41" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H41" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I41" s="79" t="n">
         <v>28030.016</v>
@@ -21053,15 +21058,15 @@
         <v>14</v>
       </c>
       <c r="S41" s="66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C42" s="77" t="n">
         <v>2022</v>
@@ -21073,13 +21078,13 @@
         <v>44926</v>
       </c>
       <c r="F42" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G42" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H42" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I42" s="79" t="n">
         <v>27799.638</v>
@@ -21112,15 +21117,15 @@
         <v>15</v>
       </c>
       <c r="S42" s="66" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B43" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C43" s="77" t="n">
         <v>2022</v>
@@ -21132,13 +21137,13 @@
         <v>44834</v>
       </c>
       <c r="F43" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G43" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H43" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I43" s="79" t="n">
         <v>24192.106</v>
@@ -21171,15 +21176,15 @@
         <v>16</v>
       </c>
       <c r="S43" s="66" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B44" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C44" s="77" t="n">
         <v>2022</v>
@@ -21191,13 +21196,13 @@
         <v>44742</v>
       </c>
       <c r="F44" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G44" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H44" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I44" s="79" t="n">
         <v>22661.655</v>
@@ -21230,15 +21235,15 @@
         <v>17</v>
       </c>
       <c r="S44" s="66" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B45" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C45" s="77" t="n">
         <v>2022</v>
@@ -21250,13 +21255,13 @@
         <v>44651</v>
       </c>
       <c r="F45" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G45" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H45" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I45" s="79" t="n">
         <v>32610.245</v>
@@ -21289,15 +21294,15 @@
         <v>18</v>
       </c>
       <c r="S45" s="66" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B46" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C46" s="77" t="n">
         <v>2021</v>
@@ -21309,13 +21314,13 @@
         <v>44561</v>
       </c>
       <c r="F46" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G46" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H46" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I46" s="79" t="n">
         <v>30456.56</v>
@@ -21348,15 +21353,15 @@
         <v>19</v>
       </c>
       <c r="S46" s="66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B47" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C47" s="77" t="n">
         <v>2021</v>
@@ -21368,13 +21373,13 @@
         <v>44469</v>
       </c>
       <c r="F47" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G47" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H47" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I47" s="79" t="n">
         <v>31294.579</v>
@@ -21407,15 +21412,15 @@
         <v>20</v>
       </c>
       <c r="S47" s="66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B48" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C48" s="77" t="n">
         <v>2021</v>
@@ -21427,13 +21432,13 @@
         <v>44377</v>
       </c>
       <c r="F48" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G48" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H48" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I48" s="79" t="n">
         <v>31787.258</v>
@@ -21466,15 +21471,15 @@
         <v>21</v>
       </c>
       <c r="S48" s="66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B49" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C49" s="77" t="n">
         <v>2021</v>
@@ -21486,13 +21491,13 @@
         <v>44286</v>
       </c>
       <c r="F49" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G49" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H49" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I49" s="79" t="n">
         <v>28366.96</v>
@@ -21525,15 +21530,15 @@
         <v>22</v>
       </c>
       <c r="S49" s="66" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B50" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C50" s="77" t="n">
         <v>2020</v>
@@ -21545,13 +21550,13 @@
         <v>44196</v>
       </c>
       <c r="F50" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G50" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H50" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I50" s="79" t="n">
         <v>23457.829</v>
@@ -21584,15 +21589,15 @@
         <v>23</v>
       </c>
       <c r="S50" s="66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B51" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C51" s="77" t="n">
         <v>2020</v>
@@ -21604,13 +21609,13 @@
         <v>44104</v>
       </c>
       <c r="F51" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G51" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H51" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I51" s="79" t="n">
         <v>23003.636</v>
@@ -21641,7 +21646,7 @@
         <v>24</v>
       </c>
       <c r="S51" s="66" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21649,7 +21654,7 @@
         <v>171</v>
       </c>
       <c r="B52" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C52" s="77" t="n">
         <v>2026</v>
@@ -21661,13 +21666,13 @@
         <v>46295</v>
       </c>
       <c r="F52" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G52" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H52" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
@@ -21684,7 +21689,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="66" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21692,7 +21697,7 @@
         <v>171</v>
       </c>
       <c r="B53" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C53" s="77" t="n">
         <v>2026</v>
@@ -21704,13 +21709,13 @@
         <v>46203</v>
       </c>
       <c r="F53" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G53" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H53" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I53" s="79" t="n">
         <v>82549.073</v>
@@ -21743,7 +21748,7 @@
         <v>1</v>
       </c>
       <c r="S53" s="66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21751,7 +21756,7 @@
         <v>171</v>
       </c>
       <c r="B54" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C54" s="77" t="n">
         <v>2026</v>
@@ -21763,13 +21768,13 @@
         <v>46112</v>
       </c>
       <c r="F54" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G54" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H54" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I54" s="79" t="n">
         <v>49086.932</v>
@@ -21802,7 +21807,7 @@
         <v>2</v>
       </c>
       <c r="S54" s="66" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21810,7 +21815,7 @@
         <v>171</v>
       </c>
       <c r="B55" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C55" s="77" t="n">
         <v>2025</v>
@@ -21822,13 +21827,13 @@
         <v>46022</v>
       </c>
       <c r="F55" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G55" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H55" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I55" s="79" t="n">
         <v>30093.618</v>
@@ -21861,7 +21866,7 @@
         <v>3</v>
       </c>
       <c r="S55" s="66" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21869,7 +21874,7 @@
         <v>171</v>
       </c>
       <c r="B56" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C56" s="77" t="n">
         <v>2025</v>
@@ -21881,13 +21886,13 @@
         <v>45930</v>
       </c>
       <c r="F56" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G56" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H56" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I56" s="79" t="n">
         <v>18778.868</v>
@@ -21920,7 +21925,7 @@
         <v>4</v>
       </c>
       <c r="S56" s="66" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21928,7 +21933,7 @@
         <v>171</v>
       </c>
       <c r="B57" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C57" s="77" t="n">
         <v>2025</v>
@@ -21940,13 +21945,13 @@
         <v>45838</v>
       </c>
       <c r="F57" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G57" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H57" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I57" s="79" t="n">
         <v>10526.094</v>
@@ -21979,7 +21984,7 @@
         <v>5</v>
       </c>
       <c r="S57" s="66" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21987,7 +21992,7 @@
         <v>171</v>
       </c>
       <c r="B58" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C58" s="77" t="n">
         <v>2025</v>
@@ -21999,13 +22004,13 @@
         <v>45747</v>
       </c>
       <c r="F58" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G58" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H58" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I58" s="79" t="n">
         <v>7187.94</v>
@@ -22038,7 +22043,7 @@
         <v>6</v>
       </c>
       <c r="S58" s="66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22046,7 +22051,7 @@
         <v>171</v>
       </c>
       <c r="B59" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C59" s="77" t="n">
         <v>2024</v>
@@ -22058,13 +22063,13 @@
         <v>45657</v>
       </c>
       <c r="F59" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G59" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H59" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I59" s="79" t="n">
         <v>6575.094</v>
@@ -22097,7 +22102,7 @@
         <v>7</v>
       </c>
       <c r="S59" s="66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22105,7 +22110,7 @@
         <v>171</v>
       </c>
       <c r="B60" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C60" s="77" t="n">
         <v>2024</v>
@@ -22117,13 +22122,13 @@
         <v>45565</v>
       </c>
       <c r="F60" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G60" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H60" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I60" s="79" t="n">
         <v>8132.593</v>
@@ -22156,7 +22161,7 @@
         <v>8</v>
       </c>
       <c r="S60" s="66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22164,7 +22169,7 @@
         <v>171</v>
       </c>
       <c r="B61" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C61" s="77" t="n">
         <v>2024</v>
@@ -22176,13 +22181,13 @@
         <v>45473</v>
       </c>
       <c r="F61" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G61" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H61" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I61" s="79" t="n">
         <v>9921.043</v>
@@ -22209,7 +22214,7 @@
         <v>9</v>
       </c>
       <c r="S61" s="66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22217,7 +22222,7 @@
         <v>171</v>
       </c>
       <c r="B62" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C62" s="77" t="n">
         <v>2024</v>
@@ -22229,13 +22234,13 @@
         <v>45382</v>
       </c>
       <c r="F62" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G62" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H62" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I62" s="79" t="n">
         <v>9502.937</v>
@@ -22268,7 +22273,7 @@
         <v>10</v>
       </c>
       <c r="S62" s="66" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22276,7 +22281,7 @@
         <v>171</v>
       </c>
       <c r="B63" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C63" s="77" t="n">
         <v>2023</v>
@@ -22288,13 +22293,13 @@
         <v>45291</v>
       </c>
       <c r="F63" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G63" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I63" s="79" t="n">
         <v>8703.978</v>
@@ -22327,7 +22332,7 @@
         <v>11</v>
       </c>
       <c r="S63" s="66" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22335,7 +22340,7 @@
         <v>171</v>
       </c>
       <c r="B64" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C64" s="77" t="n">
         <v>2023</v>
@@ -22347,13 +22352,13 @@
         <v>45199</v>
       </c>
       <c r="F64" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G64" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H64" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I64" s="79" t="n">
         <v>7736.374</v>
@@ -22386,7 +22391,7 @@
         <v>12</v>
       </c>
       <c r="S64" s="66" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22394,7 +22399,7 @@
         <v>171</v>
       </c>
       <c r="B65" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C65" s="77" t="n">
         <v>2023</v>
@@ -22406,13 +22411,13 @@
         <v>45107</v>
       </c>
       <c r="F65" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G65" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H65" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I65" s="79" t="n">
         <v>7027.071</v>
@@ -22445,7 +22450,7 @@
         <v>13</v>
       </c>
       <c r="S65" s="66" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22453,7 +22458,7 @@
         <v>171</v>
       </c>
       <c r="B66" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C66" s="77" t="n">
         <v>2023</v>
@@ -22465,13 +22470,13 @@
         <v>45016</v>
       </c>
       <c r="F66" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G66" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H66" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I66" s="79" t="n">
         <v>6424.883</v>
@@ -22504,7 +22509,7 @@
         <v>14</v>
       </c>
       <c r="S66" s="66" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22512,7 +22517,7 @@
         <v>171</v>
       </c>
       <c r="B67" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C67" s="77" t="n">
         <v>2022</v>
@@ -22524,13 +22529,13 @@
         <v>44926</v>
       </c>
       <c r="F67" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G67" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H67" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I67" s="79" t="n">
         <v>7953.553</v>
@@ -22563,7 +22568,7 @@
         <v>15</v>
       </c>
       <c r="S67" s="66" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22571,7 +22576,7 @@
         <v>171</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C68" s="77" t="n">
         <v>2022</v>
@@ -22583,13 +22588,13 @@
         <v>44834</v>
       </c>
       <c r="F68" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G68" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H68" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I68" s="79" t="n">
         <v>11021.725</v>
@@ -22622,7 +22627,7 @@
         <v>16</v>
       </c>
       <c r="S68" s="66" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22630,7 +22635,7 @@
         <v>171</v>
       </c>
       <c r="B69" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C69" s="77" t="n">
         <v>2022</v>
@@ -22642,13 +22647,13 @@
         <v>44742</v>
       </c>
       <c r="F69" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G69" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H69" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I69" s="79" t="n">
         <v>18030.672</v>
@@ -22681,7 +22686,7 @@
         <v>17</v>
       </c>
       <c r="S69" s="66" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22689,7 +22694,7 @@
         <v>171</v>
       </c>
       <c r="B70" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C70" s="77" t="n">
         <v>2022</v>
@@ -22701,13 +22706,13 @@
         <v>44651</v>
       </c>
       <c r="F70" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G70" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H70" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I70" s="79" t="n">
         <v>19946.325</v>
@@ -22740,7 +22745,7 @@
         <v>18</v>
       </c>
       <c r="S70" s="66" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22748,7 +22753,7 @@
         <v>171</v>
       </c>
       <c r="B71" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C71" s="77" t="n">
         <v>2021</v>
@@ -22760,13 +22765,13 @@
         <v>44561</v>
       </c>
       <c r="F71" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G71" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H71" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I71" s="79" t="n">
         <v>21398.949</v>
@@ -22799,7 +22804,7 @@
         <v>19</v>
       </c>
       <c r="S71" s="66" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22807,7 +22812,7 @@
         <v>171</v>
       </c>
       <c r="B72" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C72" s="77" t="n">
         <v>2021</v>
@@ -22819,13 +22824,13 @@
         <v>44469</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G72" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H72" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I72" s="79" t="n">
         <v>23837.128</v>
@@ -22858,7 +22863,7 @@
         <v>20</v>
       </c>
       <c r="S72" s="66" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22866,7 +22871,7 @@
         <v>171</v>
       </c>
       <c r="B73" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C73" s="77" t="n">
         <v>2021</v>
@@ -22878,13 +22883,13 @@
         <v>44377</v>
       </c>
       <c r="F73" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G73" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H73" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I73" s="79" t="n">
         <v>22637.468</v>
@@ -22917,7 +22922,7 @@
         <v>21</v>
       </c>
       <c r="S73" s="66" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22925,7 +22930,7 @@
         <v>171</v>
       </c>
       <c r="B74" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C74" s="77" t="n">
         <v>2021</v>
@@ -22937,13 +22942,13 @@
         <v>44286</v>
       </c>
       <c r="F74" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G74" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H74" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I74" s="79" t="n">
         <v>17730.613</v>
@@ -22976,7 +22981,7 @@
         <v>22</v>
       </c>
       <c r="S74" s="66" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22984,7 +22989,7 @@
         <v>171</v>
       </c>
       <c r="B75" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C75" s="77" t="n">
         <v>2020</v>
@@ -22996,13 +23001,13 @@
         <v>44196</v>
       </c>
       <c r="F75" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G75" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H75" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I75" s="79" t="n">
         <v>14773.42</v>
@@ -23035,7 +23040,7 @@
         <v>23</v>
       </c>
       <c r="S75" s="66" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23043,7 +23048,7 @@
         <v>171</v>
       </c>
       <c r="B76" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C76" s="77" t="n">
         <v>2020</v>
@@ -23055,13 +23060,13 @@
         <v>44104</v>
       </c>
       <c r="F76" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G76" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H76" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I76" s="79" t="n">
         <v>15323.867</v>
@@ -23092,7 +23097,7 @@
         <v>24</v>
       </c>
       <c r="S76" s="66" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23100,7 +23105,7 @@
         <v>179</v>
       </c>
       <c r="B77" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C77" s="77" t="n">
         <v>2026</v>
@@ -23112,13 +23117,13 @@
         <v>46295</v>
       </c>
       <c r="F77" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G77" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H77" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I77" s="79"/>
       <c r="J77" s="79"/>
@@ -23135,7 +23140,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="66" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23143,7 +23148,7 @@
         <v>179</v>
       </c>
       <c r="B78" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C78" s="77" t="n">
         <v>2026</v>
@@ -23155,13 +23160,13 @@
         <v>46203</v>
       </c>
       <c r="F78" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G78" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H78" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I78" s="79" t="n">
         <v>965.373</v>
@@ -23194,7 +23199,7 @@
         <v>1</v>
       </c>
       <c r="S78" s="66" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23202,7 +23207,7 @@
         <v>179</v>
       </c>
       <c r="B79" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C79" s="77" t="n">
         <v>2026</v>
@@ -23214,13 +23219,13 @@
         <v>46112</v>
       </c>
       <c r="F79" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G79" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H79" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I79" s="79" t="n">
         <v>959.31</v>
@@ -23253,7 +23258,7 @@
         <v>2</v>
       </c>
       <c r="S79" s="66" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23261,7 +23266,7 @@
         <v>179</v>
       </c>
       <c r="B80" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C80" s="77" t="n">
         <v>2025</v>
@@ -23273,13 +23278,13 @@
         <v>46022</v>
       </c>
       <c r="F80" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G80" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H80" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I80" s="79" t="n">
         <v>959.589</v>
@@ -23312,7 +23317,7 @@
         <v>3</v>
       </c>
       <c r="S80" s="66" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23320,7 +23325,7 @@
         <v>179</v>
       </c>
       <c r="B81" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C81" s="77" t="n">
         <v>2025</v>
@@ -23332,13 +23337,13 @@
         <v>45930</v>
       </c>
       <c r="F81" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G81" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H81" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I81" s="79" t="n">
         <v>912.804</v>
@@ -23371,7 +23376,7 @@
         <v>4</v>
       </c>
       <c r="S81" s="66" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23379,7 +23384,7 @@
         <v>179</v>
       </c>
       <c r="B82" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C82" s="77" t="n">
         <v>2025</v>
@@ -23391,13 +23396,13 @@
         <v>45838</v>
       </c>
       <c r="F82" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G82" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H82" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I82" s="79" t="n">
         <v>714.087</v>
@@ -23430,7 +23435,7 @@
         <v>5</v>
       </c>
       <c r="S82" s="66" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23438,7 +23443,7 @@
         <v>179</v>
       </c>
       <c r="B83" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C83" s="77" t="n">
         <v>2025</v>
@@ -23450,13 +23455,13 @@
         <v>45747</v>
       </c>
       <c r="F83" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G83" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H83" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I83" s="79" t="n">
         <v>793.663</v>
@@ -23489,7 +23494,7 @@
         <v>6</v>
       </c>
       <c r="S83" s="66" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23497,7 +23502,7 @@
         <v>179</v>
       </c>
       <c r="B84" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C84" s="77" t="n">
         <v>2024</v>
@@ -23509,13 +23514,13 @@
         <v>45657</v>
       </c>
       <c r="F84" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G84" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H84" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I84" s="79" t="n">
         <v>722.474</v>
@@ -23548,7 +23553,7 @@
         <v>7</v>
       </c>
       <c r="S84" s="66" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23556,7 +23561,7 @@
         <v>179</v>
       </c>
       <c r="B85" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C85" s="77" t="n">
         <v>2024</v>
@@ -23568,13 +23573,13 @@
         <v>45565</v>
       </c>
       <c r="F85" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G85" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H85" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I85" s="79" t="n">
         <v>805.747</v>
@@ -23607,7 +23612,7 @@
         <v>8</v>
       </c>
       <c r="S85" s="66" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23615,7 +23620,7 @@
         <v>179</v>
       </c>
       <c r="B86" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C86" s="77" t="n">
         <v>2024</v>
@@ -23627,13 +23632,13 @@
         <v>45473</v>
       </c>
       <c r="F86" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G86" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H86" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I86" s="79" t="n">
         <v>875.601</v>
@@ -23666,7 +23671,7 @@
         <v>9</v>
       </c>
       <c r="S86" s="66" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23674,7 +23679,7 @@
         <v>179</v>
       </c>
       <c r="B87" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C87" s="77" t="n">
         <v>2024</v>
@@ -23686,13 +23691,13 @@
         <v>45382</v>
       </c>
       <c r="F87" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G87" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H87" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I87" s="79" t="n">
         <v>837.395</v>
@@ -23725,7 +23730,7 @@
         <v>10</v>
       </c>
       <c r="S87" s="66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23733,7 +23738,7 @@
         <v>179</v>
       </c>
       <c r="B88" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C88" s="77" t="n">
         <v>2023</v>
@@ -23745,13 +23750,13 @@
         <v>45291</v>
       </c>
       <c r="F88" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G88" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H88" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I88" s="79" t="n">
         <v>936.937</v>
@@ -23784,7 +23789,7 @@
         <v>11</v>
       </c>
       <c r="S88" s="66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23792,7 +23797,7 @@
         <v>179</v>
       </c>
       <c r="B89" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C89" s="77" t="n">
         <v>2023</v>
@@ -23804,13 +23809,13 @@
         <v>45199</v>
       </c>
       <c r="F89" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G89" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H89" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I89" s="79" t="n">
         <v>768.427</v>
@@ -23843,7 +23848,7 @@
         <v>12</v>
       </c>
       <c r="S89" s="66" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23851,7 +23856,7 @@
         <v>179</v>
       </c>
       <c r="B90" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C90" s="77" t="n">
         <v>2023</v>
@@ -23863,13 +23868,13 @@
         <v>45107</v>
       </c>
       <c r="F90" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G90" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H90" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I90" s="79" t="n">
         <v>594.323</v>
@@ -23902,7 +23907,7 @@
         <v>13</v>
       </c>
       <c r="S90" s="66" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23910,7 +23915,7 @@
         <v>179</v>
       </c>
       <c r="B91" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C91" s="77" t="n">
         <v>2023</v>
@@ -23922,13 +23927,13 @@
         <v>45016</v>
       </c>
       <c r="F91" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G91" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H91" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I91" s="79" t="n">
         <v>394.417</v>
@@ -23961,7 +23966,7 @@
         <v>14</v>
       </c>
       <c r="S91" s="66" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23969,7 +23974,7 @@
         <v>179</v>
       </c>
       <c r="B92" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C92" s="77" t="n">
         <v>2022</v>
@@ -23981,13 +23986,13 @@
         <v>44926</v>
       </c>
       <c r="F92" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G92" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H92" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I92" s="79" t="n">
         <v>506.067</v>
@@ -24020,7 +24025,7 @@
         <v>15</v>
       </c>
       <c r="S92" s="66" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24028,7 +24033,7 @@
         <v>179</v>
       </c>
       <c r="B93" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C93" s="77" t="n">
         <v>2022</v>
@@ -24040,13 +24045,13 @@
         <v>44834</v>
       </c>
       <c r="F93" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G93" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H93" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I93" s="79" t="n">
         <v>522.089</v>
@@ -24079,7 +24084,7 @@
         <v>16</v>
       </c>
       <c r="S93" s="66" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24087,7 +24092,7 @@
         <v>179</v>
       </c>
       <c r="B94" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C94" s="77" t="n">
         <v>2022</v>
@@ -24099,13 +24104,13 @@
         <v>44742</v>
       </c>
       <c r="F94" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G94" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H94" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I94" s="79" t="n">
         <v>736.276</v>
@@ -24138,7 +24143,7 @@
         <v>17</v>
       </c>
       <c r="S94" s="66" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24146,7 +24151,7 @@
         <v>179</v>
       </c>
       <c r="B95" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C95" s="77" t="n">
         <v>2022</v>
@@ -24158,13 +24163,13 @@
         <v>44651</v>
       </c>
       <c r="F95" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G95" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H95" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I95" s="79" t="n">
         <v>839.197</v>
@@ -24197,7 +24202,7 @@
         <v>18</v>
       </c>
       <c r="S95" s="66" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24205,7 +24210,7 @@
         <v>179</v>
       </c>
       <c r="B96" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C96" s="77" t="n">
         <v>2021</v>
@@ -24217,13 +24222,13 @@
         <v>44561</v>
       </c>
       <c r="F96" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G96" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H96" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I96" s="79" t="n">
         <v>875.843</v>
@@ -24256,7 +24261,7 @@
         <v>19</v>
       </c>
       <c r="S96" s="66" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24264,7 +24269,7 @@
         <v>179</v>
       </c>
       <c r="B97" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C97" s="77" t="n">
         <v>2021</v>
@@ -24276,13 +24281,13 @@
         <v>44469</v>
       </c>
       <c r="F97" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G97" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H97" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I97" s="79" t="n">
         <v>947.399</v>
@@ -24315,7 +24320,7 @@
         <v>20</v>
       </c>
       <c r="S97" s="66" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24323,7 +24328,7 @@
         <v>179</v>
       </c>
       <c r="B98" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C98" s="77" t="n">
         <v>2021</v>
@@ -24335,13 +24340,13 @@
         <v>44377</v>
       </c>
       <c r="F98" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G98" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H98" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I98" s="79" t="n">
         <v>896.062</v>
@@ -24374,7 +24379,7 @@
         <v>21</v>
       </c>
       <c r="S98" s="66" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24382,7 +24387,7 @@
         <v>179</v>
       </c>
       <c r="B99" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C99" s="77" t="n">
         <v>2021</v>
@@ -24394,13 +24399,13 @@
         <v>44286</v>
       </c>
       <c r="F99" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G99" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H99" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I99" s="79" t="n">
         <v>889.217</v>
@@ -24433,7 +24438,7 @@
         <v>22</v>
       </c>
       <c r="S99" s="66" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24441,7 +24446,7 @@
         <v>179</v>
       </c>
       <c r="B100" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C100" s="77" t="n">
         <v>2020</v>
@@ -24453,13 +24458,13 @@
         <v>44196</v>
       </c>
       <c r="F100" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G100" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H100" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I100" s="79" t="n">
         <v>757.232</v>
@@ -24492,7 +24497,7 @@
         <v>23</v>
       </c>
       <c r="S100" s="66" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24500,7 +24505,7 @@
         <v>179</v>
       </c>
       <c r="B101" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C101" s="77" t="n">
         <v>2020</v>
@@ -24512,13 +24517,13 @@
         <v>44104</v>
       </c>
       <c r="F101" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G101" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H101" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I101" s="79" t="n">
         <v>644.391</v>
@@ -24549,15 +24554,15 @@
         <v>24</v>
       </c>
       <c r="S101" s="66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B102" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C102" s="77" t="n">
         <v>2026</v>
@@ -24569,13 +24574,13 @@
         <v>46295</v>
       </c>
       <c r="F102" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G102" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H102" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I102" s="79"/>
       <c r="J102" s="79"/>
@@ -24592,15 +24597,15 @@
         <v>0</v>
       </c>
       <c r="S102" s="66" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B103" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C103" s="77" t="n">
         <v>2026</v>
@@ -24612,13 +24617,13 @@
         <v>46203</v>
       </c>
       <c r="F103" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G103" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H103" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I103" s="79" t="n">
         <v>28660.098</v>
@@ -24651,15 +24656,15 @@
         <v>1</v>
       </c>
       <c r="S103" s="66" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B104" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C104" s="77" t="n">
         <v>2026</v>
@@ -24671,13 +24676,13 @@
         <v>46112</v>
       </c>
       <c r="F104" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G104" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H104" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I104" s="79" t="n">
         <v>23145.303</v>
@@ -24710,15 +24715,15 @@
         <v>2</v>
       </c>
       <c r="S104" s="66" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C105" s="77" t="n">
         <v>2025</v>
@@ -24730,13 +24735,13 @@
         <v>46022</v>
       </c>
       <c r="F105" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G105" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H105" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I105" s="79" t="n">
         <v>22817.209</v>
@@ -24769,15 +24774,15 @@
         <v>3</v>
       </c>
       <c r="S105" s="66" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B106" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C106" s="77" t="n">
         <v>2025</v>
@@ -24789,13 +24794,13 @@
         <v>45930</v>
       </c>
       <c r="F106" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G106" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H106" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I106" s="79" t="n">
         <v>24573.67</v>
@@ -24828,15 +24833,15 @@
         <v>4</v>
       </c>
       <c r="S106" s="66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B107" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C107" s="77" t="n">
         <v>2025</v>
@@ -24848,13 +24853,13 @@
         <v>45838</v>
       </c>
       <c r="F107" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G107" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H107" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I107" s="79" t="n">
         <v>26152.063</v>
@@ -24887,15 +24892,15 @@
         <v>5</v>
       </c>
       <c r="S107" s="66" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B108" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C108" s="77" t="n">
         <v>2025</v>
@@ -24907,13 +24912,13 @@
         <v>45747</v>
       </c>
       <c r="F108" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G108" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H108" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I108" s="79" t="n">
         <v>27120.202</v>
@@ -24946,15 +24951,15 @@
         <v>6</v>
       </c>
       <c r="S108" s="66" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B109" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C109" s="77" t="n">
         <v>2024</v>
@@ -24966,13 +24971,13 @@
         <v>45657</v>
       </c>
       <c r="F109" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G109" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H109" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I109" s="79" t="n">
         <v>25262.519</v>
@@ -25005,15 +25010,15 @@
         <v>7</v>
       </c>
       <c r="S109" s="66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B110" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C110" s="77" t="n">
         <v>2024</v>
@@ -25025,13 +25030,13 @@
         <v>45565</v>
       </c>
       <c r="F110" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G110" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H110" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I110" s="79" t="n">
         <v>27866.328</v>
@@ -25064,15 +25069,15 @@
         <v>8</v>
       </c>
       <c r="S110" s="66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B111" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C111" s="77" t="n">
         <v>2024</v>
@@ -25084,13 +25089,13 @@
         <v>45473</v>
       </c>
       <c r="F111" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G111" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H111" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I111" s="79" t="n">
         <v>25231.019</v>
@@ -25123,15 +25128,15 @@
         <v>9</v>
       </c>
       <c r="S111" s="66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B112" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C112" s="77" t="n">
         <v>2024</v>
@@ -25143,13 +25148,13 @@
         <v>45382</v>
       </c>
       <c r="F112" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G112" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H112" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I112" s="79" t="n">
         <v>24427.885</v>
@@ -25182,15 +25187,15 @@
         <v>10</v>
       </c>
       <c r="S112" s="66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B113" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C113" s="77" t="n">
         <v>2023</v>
@@ -25202,13 +25207,13 @@
         <v>45291</v>
       </c>
       <c r="F113" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G113" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H113" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I113" s="79" t="n">
         <v>27153.825</v>
@@ -25241,15 +25246,15 @@
         <v>11</v>
       </c>
       <c r="S113" s="66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B114" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C114" s="77" t="n">
         <v>2023</v>
@@ -25261,13 +25266,13 @@
         <v>45199</v>
       </c>
       <c r="F114" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G114" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H114" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I114" s="79" t="n">
         <v>28929.962</v>
@@ -25300,15 +25305,15 @@
         <v>12</v>
       </c>
       <c r="S114" s="66" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B115" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C115" s="77" t="n">
         <v>2023</v>
@@ -25320,13 +25325,13 @@
         <v>45107</v>
       </c>
       <c r="F115" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G115" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H115" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I115" s="79" t="n">
         <v>30299.029</v>
@@ -25359,15 +25364,15 @@
         <v>13</v>
       </c>
       <c r="S115" s="66" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B116" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C116" s="77" t="n">
         <v>2023</v>
@@ -25379,13 +25384,13 @@
         <v>45016</v>
       </c>
       <c r="F116" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G116" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H116" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I116" s="79" t="n">
         <v>24045.882</v>
@@ -25418,15 +25423,15 @@
         <v>14</v>
       </c>
       <c r="S116" s="66" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B117" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C117" s="77" t="n">
         <v>2022</v>
@@ -25438,13 +25443,13 @@
         <v>44926</v>
       </c>
       <c r="F117" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G117" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H117" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I117" s="79" t="n">
         <v>22420.161</v>
@@ -25477,15 +25482,15 @@
         <v>15</v>
       </c>
       <c r="S117" s="66" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B118" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C118" s="77" t="n">
         <v>2022</v>
@@ -25497,13 +25502,13 @@
         <v>44834</v>
       </c>
       <c r="F118" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G118" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H118" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I118" s="79" t="n">
         <v>19563.686</v>
@@ -25536,15 +25541,15 @@
         <v>16</v>
       </c>
       <c r="S118" s="66" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B119" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C119" s="77" t="n">
         <v>2022</v>
@@ -25556,13 +25561,13 @@
         <v>44742</v>
       </c>
       <c r="F119" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G119" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H119" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I119" s="79" t="n">
         <v>31461.142</v>
@@ -25595,15 +25600,15 @@
         <v>17</v>
       </c>
       <c r="S119" s="66" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B120" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C120" s="77" t="n">
         <v>2022</v>
@@ -25615,13 +25620,13 @@
         <v>44651</v>
       </c>
       <c r="F120" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G120" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H120" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I120" s="79" t="n">
         <v>36511.685</v>
@@ -25654,15 +25659,15 @@
         <v>18</v>
       </c>
       <c r="S120" s="66" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B121" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C121" s="77" t="n">
         <v>2021</v>
@@ -25674,13 +25679,13 @@
         <v>44561</v>
       </c>
       <c r="F121" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G121" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H121" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I121" s="79" t="n">
         <v>36542.106</v>
@@ -25713,15 +25718,15 @@
         <v>19</v>
       </c>
       <c r="S121" s="66" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B122" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C122" s="77" t="n">
         <v>2021</v>
@@ -25733,13 +25738,13 @@
         <v>44469</v>
       </c>
       <c r="F122" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G122" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H122" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I122" s="79" t="n">
         <v>38345.587</v>
@@ -25772,15 +25777,15 @@
         <v>20</v>
       </c>
       <c r="S122" s="66" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B123" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C123" s="77" t="n">
         <v>2021</v>
@@ -25792,13 +25797,13 @@
         <v>44377</v>
       </c>
       <c r="F123" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G123" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H123" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I123" s="79" t="n">
         <v>34111.302</v>
@@ -25831,15 +25836,15 @@
         <v>21</v>
       </c>
       <c r="S123" s="66" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B124" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C124" s="77" t="n">
         <v>2021</v>
@@ -25851,13 +25856,13 @@
         <v>44286</v>
       </c>
       <c r="F124" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G124" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H124" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I124" s="79" t="n">
         <v>26366.515</v>
@@ -25890,15 +25895,15 @@
         <v>22</v>
       </c>
       <c r="S124" s="66" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B125" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C125" s="77" t="n">
         <v>2020</v>
@@ -25910,13 +25915,13 @@
         <v>44196</v>
       </c>
       <c r="F125" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G125" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H125" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I125" s="79" t="n">
         <v>22452.842</v>
@@ -25949,15 +25954,15 @@
         <v>23</v>
       </c>
       <c r="S125" s="66" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B126" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C126" s="77" t="n">
         <v>2020</v>
@@ -25969,13 +25974,13 @@
         <v>44104</v>
       </c>
       <c r="F126" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G126" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H126" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I126" s="79" t="n">
         <v>22001.236</v>
@@ -26006,15 +26011,15 @@
         <v>24</v>
       </c>
       <c r="S126" s="66" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B127" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C127" s="77" t="n">
         <v>2026</v>
@@ -26026,13 +26031,13 @@
         <v>46295</v>
       </c>
       <c r="F127" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G127" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H127" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I127" s="79"/>
       <c r="J127" s="79"/>
@@ -26049,15 +26054,15 @@
         <v>0</v>
       </c>
       <c r="S127" s="66" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B128" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C128" s="77" t="n">
         <v>2026</v>
@@ -26069,13 +26074,13 @@
         <v>46203</v>
       </c>
       <c r="F128" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G128" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H128" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I128" s="79" t="n">
         <v>23281.188</v>
@@ -26108,15 +26113,15 @@
         <v>1</v>
       </c>
       <c r="S128" s="66" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B129" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C129" s="77" t="n">
         <v>2026</v>
@@ -26128,13 +26133,13 @@
         <v>46112</v>
       </c>
       <c r="F129" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G129" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H129" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I129" s="79" t="n">
         <v>20863.649</v>
@@ -26167,15 +26172,15 @@
         <v>2</v>
       </c>
       <c r="S129" s="66" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B130" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C130" s="77" t="n">
         <v>2025</v>
@@ -26187,13 +26192,13 @@
         <v>46022</v>
       </c>
       <c r="F130" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G130" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H130" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I130" s="79" t="n">
         <v>19779.964</v>
@@ -26226,15 +26231,15 @@
         <v>3</v>
       </c>
       <c r="S130" s="66" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B131" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C131" s="77" t="n">
         <v>2025</v>
@@ -26246,13 +26251,13 @@
         <v>45930</v>
       </c>
       <c r="F131" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G131" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H131" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I131" s="79" t="n">
         <v>18413.195</v>
@@ -26285,15 +26290,15 @@
         <v>4</v>
       </c>
       <c r="S131" s="66" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B132" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C132" s="77" t="n">
         <v>2025</v>
@@ -26305,13 +26310,13 @@
         <v>45838</v>
       </c>
       <c r="F132" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G132" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H132" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I132" s="79" t="n">
         <v>16933.328</v>
@@ -26344,15 +26349,15 @@
         <v>5</v>
       </c>
       <c r="S132" s="66" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B133" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C133" s="77" t="n">
         <v>2025</v>
@@ -26364,13 +26369,13 @@
         <v>45747</v>
       </c>
       <c r="F133" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G133" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H133" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I133" s="79" t="n">
         <v>16120.785</v>
@@ -26403,15 +26408,15 @@
         <v>6</v>
       </c>
       <c r="S133" s="66" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B134" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C134" s="77" t="n">
         <v>2024</v>
@@ -26423,13 +26428,13 @@
         <v>45657</v>
       </c>
       <c r="F134" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G134" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H134" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I134" s="79" t="n">
         <v>14411.637</v>
@@ -26462,15 +26467,15 @@
         <v>7</v>
       </c>
       <c r="S134" s="66" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B135" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C135" s="77" t="n">
         <v>2024</v>
@@ -26482,13 +26487,13 @@
         <v>45565</v>
       </c>
       <c r="F135" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G135" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H135" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I135" s="79" t="n">
         <v>14259.287</v>
@@ -26521,15 +26526,15 @@
         <v>8</v>
       </c>
       <c r="S135" s="66" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B136" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C136" s="77" t="n">
         <v>2024</v>
@@ -26541,13 +26546,13 @@
         <v>45473</v>
       </c>
       <c r="F136" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G136" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H136" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I136" s="79" t="n">
         <v>12983.996</v>
@@ -26580,15 +26585,15 @@
         <v>9</v>
       </c>
       <c r="S136" s="66" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B137" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C137" s="77" t="n">
         <v>2024</v>
@@ -26600,13 +26605,13 @@
         <v>45382</v>
       </c>
       <c r="F137" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G137" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H137" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I137" s="79" t="n">
         <v>12425.561</v>
@@ -26639,15 +26644,15 @@
         <v>10</v>
       </c>
       <c r="S137" s="66" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B138" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C138" s="77" t="n">
         <v>2023</v>
@@ -26659,13 +26664,13 @@
         <v>45291</v>
       </c>
       <c r="F138" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G138" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H138" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I138" s="79" t="n">
         <v>12195.595</v>
@@ -26698,15 +26703,15 @@
         <v>11</v>
       </c>
       <c r="S138" s="66" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B139" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C139" s="77" t="n">
         <v>2023</v>
@@ -26718,13 +26723,13 @@
         <v>45199</v>
       </c>
       <c r="F139" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G139" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H139" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I139" s="79" t="n">
         <v>13150.145</v>
@@ -26757,15 +26762,15 @@
         <v>12</v>
       </c>
       <c r="S139" s="66" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B140" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C140" s="77" t="n">
         <v>2023</v>
@@ -26777,13 +26782,13 @@
         <v>45107</v>
       </c>
       <c r="F140" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G140" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H140" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I140" s="79" t="n">
         <v>13004.395</v>
@@ -26816,15 +26821,15 @@
         <v>13</v>
       </c>
       <c r="S140" s="66" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B141" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C141" s="77" t="n">
         <v>2023</v>
@@ -26836,13 +26841,13 @@
         <v>45016</v>
       </c>
       <c r="F141" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G141" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H141" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I141" s="79" t="n">
         <v>12701.656</v>
@@ -26875,15 +26880,15 @@
         <v>14</v>
       </c>
       <c r="S141" s="66" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B142" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C142" s="77" t="n">
         <v>2022</v>
@@ -26895,13 +26900,13 @@
         <v>44926</v>
       </c>
       <c r="F142" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G142" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H142" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I142" s="79" t="n">
         <v>13600.543</v>
@@ -26934,15 +26939,15 @@
         <v>15</v>
       </c>
       <c r="S142" s="66" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B143" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C143" s="77" t="n">
         <v>2022</v>
@@ -26954,13 +26959,13 @@
         <v>44834</v>
       </c>
       <c r="F143" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G143" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H143" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I143" s="79" t="n">
         <v>14526.402</v>
@@ -26993,15 +26998,15 @@
         <v>16</v>
       </c>
       <c r="S143" s="66" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B144" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C144" s="77" t="n">
         <v>2022</v>
@@ -27013,13 +27018,13 @@
         <v>44742</v>
       </c>
       <c r="F144" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G144" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H144" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I144" s="79" t="n">
         <v>13963.028</v>
@@ -27052,15 +27057,15 @@
         <v>17</v>
       </c>
       <c r="S144" s="66" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B145" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C145" s="77" t="n">
         <v>2022</v>
@@ -27072,13 +27077,13 @@
         <v>44651</v>
       </c>
       <c r="F145" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G145" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H145" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I145" s="79" t="n">
         <v>11667.198</v>
@@ -27111,15 +27116,15 @@
         <v>18</v>
       </c>
       <c r="S145" s="66" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B146" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C146" s="77" t="n">
         <v>2021</v>
@@ -27131,13 +27136,13 @@
         <v>44561</v>
       </c>
       <c r="F146" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G146" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H146" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I146" s="79" t="n">
         <v>7998.723</v>
@@ -27170,15 +27175,15 @@
         <v>19</v>
       </c>
       <c r="S146" s="66" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B147" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C147" s="77" t="n">
         <v>2021</v>
@@ -27190,13 +27195,13 @@
         <v>44469</v>
       </c>
       <c r="F147" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G147" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H147" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I147" s="79" t="n">
         <v>7415.446</v>
@@ -27229,15 +27234,15 @@
         <v>20</v>
       </c>
       <c r="S147" s="66" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B148" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C148" s="77" t="n">
         <v>2021</v>
@@ -27249,13 +27254,13 @@
         <v>44377</v>
       </c>
       <c r="F148" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G148" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H148" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I148" s="79" t="n">
         <v>7015.992</v>
@@ -27288,15 +27293,15 @@
         <v>21</v>
       </c>
       <c r="S148" s="66" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B149" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C149" s="77" t="n">
         <v>2021</v>
@@ -27308,13 +27313,13 @@
         <v>44286</v>
       </c>
       <c r="F149" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G149" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H149" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I149" s="79" t="n">
         <v>6134.214</v>
@@ -27347,15 +27352,15 @@
         <v>22</v>
       </c>
       <c r="S149" s="66" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B150" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C150" s="77" t="n">
         <v>2020</v>
@@ -27367,13 +27372,13 @@
         <v>44196</v>
       </c>
       <c r="F150" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G150" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H150" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I150" s="79" t="n">
         <v>6266.652</v>
@@ -27406,15 +27411,15 @@
         <v>23</v>
       </c>
       <c r="S150" s="66" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B151" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C151" s="77" t="n">
         <v>2020</v>
@@ -27426,13 +27431,13 @@
         <v>44104</v>
       </c>
       <c r="F151" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G151" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H151" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I151" s="79" t="n">
         <v>6049.454</v>
@@ -27463,7 +27468,7 @@
         <v>24</v>
       </c>
       <c r="S151" s="66" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27471,7 +27476,7 @@
         <v>176</v>
       </c>
       <c r="B152" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C152" s="77" t="n">
         <v>2026</v>
@@ -27483,13 +27488,13 @@
         <v>46295</v>
       </c>
       <c r="F152" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G152" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H152" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I152" s="79"/>
       <c r="J152" s="79"/>
@@ -27506,7 +27511,7 @@
         <v>0</v>
       </c>
       <c r="S152" s="66" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27514,7 +27519,7 @@
         <v>176</v>
       </c>
       <c r="B153" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C153" s="77" t="n">
         <v>2026</v>
@@ -27526,13 +27531,13 @@
         <v>46203</v>
       </c>
       <c r="F153" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G153" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H153" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I153" s="79" t="n">
         <v>22443.411</v>
@@ -27565,7 +27570,7 @@
         <v>1</v>
       </c>
       <c r="S153" s="66" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27573,7 +27578,7 @@
         <v>176</v>
       </c>
       <c r="B154" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C154" s="77" t="n">
         <v>2026</v>
@@ -27585,13 +27590,13 @@
         <v>46112</v>
       </c>
       <c r="F154" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G154" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H154" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I154" s="79" t="n">
         <v>13182.608</v>
@@ -27624,7 +27629,7 @@
         <v>2</v>
       </c>
       <c r="S154" s="66" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27632,7 +27637,7 @@
         <v>176</v>
       </c>
       <c r="B155" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C155" s="77" t="n">
         <v>2025</v>
@@ -27644,13 +27649,13 @@
         <v>46022</v>
       </c>
       <c r="F155" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G155" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H155" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I155" s="79" t="n">
         <v>4806.69</v>
@@ -27683,7 +27688,7 @@
         <v>3</v>
       </c>
       <c r="S155" s="66" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27691,7 +27696,7 @@
         <v>176</v>
       </c>
       <c r="B156" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C156" s="77" t="n">
         <v>2025</v>
@@ -27703,13 +27708,13 @@
         <v>45930</v>
       </c>
       <c r="F156" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G156" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H156" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I156" s="79" t="n">
         <v>3807.401</v>
@@ -27742,7 +27747,7 @@
         <v>4</v>
       </c>
       <c r="S156" s="66" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27750,7 +27755,7 @@
         <v>176</v>
       </c>
       <c r="B157" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C157" s="77" t="n">
         <v>2025</v>
@@ -27762,13 +27767,13 @@
         <v>45838</v>
       </c>
       <c r="F157" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G157" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H157" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I157" s="79" t="n">
         <v>3028.429</v>
@@ -27801,7 +27806,7 @@
         <v>5</v>
       </c>
       <c r="S157" s="66" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27809,7 +27814,7 @@
         <v>176</v>
       </c>
       <c r="B158" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C158" s="77" t="n">
         <v>2025</v>
@@ -27821,13 +27826,13 @@
         <v>45747</v>
       </c>
       <c r="F158" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G158" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H158" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I158" s="79" t="n">
         <v>2618.742</v>
@@ -27860,7 +27865,7 @@
         <v>6</v>
       </c>
       <c r="S158" s="66" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27868,7 +27873,7 @@
         <v>176</v>
       </c>
       <c r="B159" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C159" s="77" t="n">
         <v>2024</v>
@@ -27880,13 +27885,13 @@
         <v>45657</v>
       </c>
       <c r="F159" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G159" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H159" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I159" s="79" t="n">
         <v>2228.005</v>
@@ -27919,7 +27924,7 @@
         <v>7</v>
       </c>
       <c r="S159" s="66" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27927,7 +27932,7 @@
         <v>176</v>
       </c>
       <c r="B160" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C160" s="77" t="n">
         <v>2024</v>
@@ -27939,13 +27944,13 @@
         <v>45565</v>
       </c>
       <c r="F160" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G160" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H160" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I160" s="79" t="n">
         <v>2321.419</v>
@@ -27978,7 +27983,7 @@
         <v>8</v>
       </c>
       <c r="S160" s="66" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27986,7 +27991,7 @@
         <v>176</v>
       </c>
       <c r="B161" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C161" s="77" t="n">
         <v>2024</v>
@@ -27998,13 +28003,13 @@
         <v>45473</v>
       </c>
       <c r="F161" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G161" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H161" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I161" s="79" t="n">
         <v>2190.229</v>
@@ -28037,7 +28042,7 @@
         <v>9</v>
       </c>
       <c r="S161" s="66" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28045,7 +28050,7 @@
         <v>176</v>
       </c>
       <c r="B162" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C162" s="77" t="n">
         <v>2024</v>
@@ -28057,13 +28062,13 @@
         <v>45382</v>
       </c>
       <c r="F162" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G162" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H162" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I162" s="79" t="n">
         <v>2175.989</v>
@@ -28096,7 +28101,7 @@
         <v>10</v>
       </c>
       <c r="S162" s="66" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28104,7 +28109,7 @@
         <v>176</v>
       </c>
       <c r="B163" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C163" s="77" t="n">
         <v>2023</v>
@@ -28116,13 +28121,13 @@
         <v>45291</v>
       </c>
       <c r="F163" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G163" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H163" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I163" s="79" t="n">
         <v>2130.049</v>
@@ -28155,7 +28160,7 @@
         <v>11</v>
       </c>
       <c r="S163" s="66" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28163,7 +28168,7 @@
         <v>176</v>
       </c>
       <c r="B164" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C164" s="77" t="n">
         <v>2023</v>
@@ -28175,13 +28180,13 @@
         <v>45199</v>
       </c>
       <c r="F164" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G164" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H164" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I164" s="79" t="n">
         <v>1993.007</v>
@@ -28214,7 +28219,7 @@
         <v>12</v>
       </c>
       <c r="S164" s="66" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28222,7 +28227,7 @@
         <v>176</v>
       </c>
       <c r="B165" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C165" s="77" t="n">
         <v>2023</v>
@@ -28234,13 +28239,13 @@
         <v>45107</v>
       </c>
       <c r="F165" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G165" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H165" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I165" s="79" t="n">
         <v>1930.516</v>
@@ -28273,7 +28278,7 @@
         <v>13</v>
       </c>
       <c r="S165" s="66" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28281,7 +28286,7 @@
         <v>176</v>
       </c>
       <c r="B166" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C166" s="77" t="n">
         <v>2023</v>
@@ -28293,13 +28298,13 @@
         <v>45016</v>
       </c>
       <c r="F166" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G166" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H166" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I166" s="79" t="n">
         <v>2260.206</v>
@@ -28332,7 +28337,7 @@
         <v>14</v>
       </c>
       <c r="S166" s="66" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28340,7 +28345,7 @@
         <v>176</v>
       </c>
       <c r="B167" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C167" s="77" t="n">
         <v>2022</v>
@@ -28352,13 +28357,13 @@
         <v>44926</v>
       </c>
       <c r="F167" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G167" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H167" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I167" s="79" t="n">
         <v>2286.572</v>
@@ -28391,7 +28396,7 @@
         <v>15</v>
       </c>
       <c r="S167" s="66" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28399,7 +28404,7 @@
         <v>176</v>
       </c>
       <c r="B168" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C168" s="77" t="n">
         <v>2022</v>
@@ -28411,13 +28416,13 @@
         <v>44834</v>
       </c>
       <c r="F168" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G168" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H168" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I168" s="79" t="n">
         <v>2560.341</v>
@@ -28450,7 +28455,7 @@
         <v>16</v>
       </c>
       <c r="S168" s="66" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28458,7 +28463,7 @@
         <v>176</v>
       </c>
       <c r="B169" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C169" s="77" t="n">
         <v>2022</v>
@@ -28470,13 +28475,13 @@
         <v>44742</v>
       </c>
       <c r="F169" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G169" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H169" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I169" s="79" t="n">
         <v>2866.579</v>
@@ -28509,7 +28514,7 @@
         <v>17</v>
       </c>
       <c r="S169" s="66" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28517,7 +28522,7 @@
         <v>176</v>
       </c>
       <c r="B170" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C170" s="77" t="n">
         <v>2022</v>
@@ -28529,13 +28534,13 @@
         <v>44651</v>
       </c>
       <c r="F170" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G170" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H170" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I170" s="79" t="n">
         <v>2589.737</v>
@@ -28568,7 +28573,7 @@
         <v>18</v>
       </c>
       <c r="S170" s="66" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28576,7 +28581,7 @@
         <v>176</v>
       </c>
       <c r="B171" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C171" s="77" t="n">
         <v>2021</v>
@@ -28588,13 +28593,13 @@
         <v>44561</v>
       </c>
       <c r="F171" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G171" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H171" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I171" s="79" t="n">
         <v>2396.847</v>
@@ -28627,7 +28632,7 @@
         <v>19</v>
       </c>
       <c r="S171" s="66" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28635,7 +28640,7 @@
         <v>176</v>
       </c>
       <c r="B172" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C172" s="77" t="n">
         <v>2021</v>
@@ -28647,13 +28652,13 @@
         <v>44469</v>
       </c>
       <c r="F172" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G172" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H172" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I172" s="79" t="n">
         <v>2973.845</v>
@@ -28686,7 +28691,7 @@
         <v>20</v>
       </c>
       <c r="S172" s="66" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28694,7 +28699,7 @@
         <v>176</v>
       </c>
       <c r="B173" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C173" s="77" t="n">
         <v>2021</v>
@@ -28706,13 +28711,13 @@
         <v>44377</v>
       </c>
       <c r="F173" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G173" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H173" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I173" s="79" t="n">
         <v>2885.046</v>
@@ -28745,7 +28750,7 @@
         <v>21</v>
       </c>
       <c r="S173" s="66" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28753,7 +28758,7 @@
         <v>176</v>
       </c>
       <c r="B174" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C174" s="77" t="n">
         <v>2021</v>
@@ -28765,13 +28770,13 @@
         <v>44286</v>
       </c>
       <c r="F174" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G174" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H174" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I174" s="79" t="n">
         <v>1939.92</v>
@@ -28804,7 +28809,7 @@
         <v>22</v>
       </c>
       <c r="S174" s="66" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28812,7 +28817,7 @@
         <v>176</v>
       </c>
       <c r="B175" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C175" s="77" t="n">
         <v>2020</v>
@@ -28824,13 +28829,13 @@
         <v>44196</v>
       </c>
       <c r="F175" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G175" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H175" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I175" s="79" t="n">
         <v>1575.49</v>
@@ -28863,7 +28868,7 @@
         <v>23</v>
       </c>
       <c r="S175" s="66" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28871,7 +28876,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C176" s="77" t="n">
         <v>2020</v>
@@ -28883,13 +28888,13 @@
         <v>44104</v>
       </c>
       <c r="F176" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G176" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H176" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I176" s="79" t="n">
         <v>1627.205</v>
@@ -28920,15 +28925,15 @@
         <v>24</v>
       </c>
       <c r="S176" s="66" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B177" s="76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C177" s="77" t="n">
         <v>2026</v>
@@ -28940,13 +28945,13 @@
         <v>46295</v>
       </c>
       <c r="F177" s="76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G177" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H177" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I177" s="79"/>
       <c r="J177" s="79"/>
@@ -28963,15 +28968,15 @@
         <v>0</v>
       </c>
       <c r="S177" s="66" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B178" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C178" s="77" t="n">
         <v>2026</v>
@@ -28983,13 +28988,13 @@
         <v>46203</v>
       </c>
       <c r="F178" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G178" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H178" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I178" s="79" t="n">
         <v>20825.411</v>
@@ -29022,15 +29027,15 @@
         <v>1</v>
       </c>
       <c r="S178" s="66" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B179" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C179" s="77" t="n">
         <v>2026</v>
@@ -29042,13 +29047,13 @@
         <v>46112</v>
       </c>
       <c r="F179" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G179" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H179" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I179" s="79" t="n">
         <v>18536.692</v>
@@ -29081,15 +29086,15 @@
         <v>2</v>
       </c>
       <c r="S179" s="66" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B180" s="76" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C180" s="77" t="n">
         <v>2025</v>
@@ -29101,13 +29106,13 @@
         <v>46022</v>
       </c>
       <c r="F180" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G180" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H180" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I180" s="79" t="n">
         <v>17298.641</v>
@@ -29140,15 +29145,15 @@
         <v>3</v>
       </c>
       <c r="S180" s="66" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B181" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C181" s="77" t="n">
         <v>2025</v>
@@ -29160,13 +29165,13 @@
         <v>45930</v>
       </c>
       <c r="F181" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G181" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H181" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I181" s="79" t="n">
         <v>17538.579</v>
@@ -29199,15 +29204,15 @@
         <v>4</v>
       </c>
       <c r="S181" s="66" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B182" s="76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C182" s="77" t="n">
         <v>2025</v>
@@ -29219,13 +29224,13 @@
         <v>45838</v>
       </c>
       <c r="F182" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G182" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H182" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I182" s="79" t="n">
         <v>16986.85</v>
@@ -29258,15 +29263,15 @@
         <v>5</v>
       </c>
       <c r="S182" s="66" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B183" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C183" s="77" t="n">
         <v>2025</v>
@@ -29278,13 +29283,13 @@
         <v>45747</v>
       </c>
       <c r="F183" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G183" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H183" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I183" s="79" t="n">
         <v>15759.461</v>
@@ -29317,15 +29322,15 @@
         <v>6</v>
       </c>
       <c r="S183" s="66" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B184" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C184" s="77" t="n">
         <v>2024</v>
@@ -29337,13 +29342,13 @@
         <v>45657</v>
       </c>
       <c r="F184" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G184" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H184" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I184" s="79" t="n">
         <v>15907.231</v>
@@ -29376,15 +29381,15 @@
         <v>7</v>
       </c>
       <c r="S184" s="66" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B185" s="76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C185" s="77" t="n">
         <v>2024</v>
@@ -29396,13 +29401,13 @@
         <v>45565</v>
       </c>
       <c r="F185" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G185" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H185" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I185" s="79" t="n">
         <v>15366.525</v>
@@ -29435,15 +29440,15 @@
         <v>8</v>
       </c>
       <c r="S185" s="66" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B186" s="76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C186" s="77" t="n">
         <v>2024</v>
@@ -29455,13 +29460,13 @@
         <v>45473</v>
       </c>
       <c r="F186" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G186" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H186" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I186" s="79" t="n">
         <v>13791.78</v>
@@ -29494,15 +29499,15 @@
         <v>9</v>
       </c>
       <c r="S186" s="66" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B187" s="76" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C187" s="77" t="n">
         <v>2024</v>
@@ -29514,13 +29519,13 @@
         <v>45382</v>
       </c>
       <c r="F187" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G187" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H187" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I187" s="79" t="n">
         <v>11931.577</v>
@@ -29553,15 +29558,15 @@
         <v>10</v>
       </c>
       <c r="S187" s="66" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B188" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C188" s="77" t="n">
         <v>2023</v>
@@ -29573,13 +29578,13 @@
         <v>45291</v>
       </c>
       <c r="F188" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G188" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H188" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I188" s="79" t="n">
         <v>12233.421</v>
@@ -29612,15 +29617,15 @@
         <v>11</v>
       </c>
       <c r="S188" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B189" s="76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C189" s="77" t="n">
         <v>2023</v>
@@ -29632,13 +29637,13 @@
         <v>45199</v>
       </c>
       <c r="F189" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G189" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H189" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I189" s="79" t="n">
         <v>12492.338</v>
@@ -29671,15 +29676,15 @@
         <v>12</v>
       </c>
       <c r="S189" s="66" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B190" s="76" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C190" s="77" t="n">
         <v>2023</v>
@@ -29691,13 +29696,13 @@
         <v>45107</v>
       </c>
       <c r="F190" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G190" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H190" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I190" s="79" t="n">
         <v>12055.351</v>
@@ -29730,15 +29735,15 @@
         <v>13</v>
       </c>
       <c r="S190" s="66" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B191" s="76" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C191" s="77" t="n">
         <v>2023</v>
@@ -29750,13 +29755,13 @@
         <v>45016</v>
       </c>
       <c r="F191" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G191" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H191" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I191" s="79" t="n">
         <v>12492.345</v>
@@ -29789,15 +29794,15 @@
         <v>14</v>
       </c>
       <c r="S191" s="66" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B192" s="76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C192" s="77" t="n">
         <v>2022</v>
@@ -29809,13 +29814,13 @@
         <v>44926</v>
       </c>
       <c r="F192" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G192" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H192" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I192" s="79" t="n">
         <v>13377.459</v>
@@ -29848,15 +29853,15 @@
         <v>15</v>
       </c>
       <c r="S192" s="66" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B193" s="76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C193" s="77" t="n">
         <v>2022</v>
@@ -29868,13 +29873,13 @@
         <v>44834</v>
       </c>
       <c r="F193" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G193" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H193" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I193" s="79" t="n">
         <v>13792.845</v>
@@ -29907,15 +29912,15 @@
         <v>16</v>
       </c>
       <c r="S193" s="66" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B194" s="76" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C194" s="77" t="n">
         <v>2022</v>
@@ -29927,13 +29932,13 @@
         <v>44742</v>
       </c>
       <c r="F194" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G194" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H194" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I194" s="79" t="n">
         <v>13225.334</v>
@@ -29966,15 +29971,15 @@
         <v>17</v>
       </c>
       <c r="S194" s="66" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B195" s="76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C195" s="77" t="n">
         <v>2022</v>
@@ -29986,13 +29991,13 @@
         <v>44651</v>
       </c>
       <c r="F195" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G195" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H195" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I195" s="79" t="n">
         <v>12582.577</v>
@@ -30025,15 +30030,15 @@
         <v>18</v>
       </c>
       <c r="S195" s="66" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B196" s="76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C196" s="77" t="n">
         <v>2021</v>
@@ -30045,13 +30050,13 @@
         <v>44561</v>
       </c>
       <c r="F196" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G196" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H196" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I196" s="79" t="n">
         <v>11766.16</v>
@@ -30084,15 +30089,15 @@
         <v>19</v>
       </c>
       <c r="S196" s="66" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B197" s="76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C197" s="77" t="n">
         <v>2021</v>
@@ -30104,13 +30109,13 @@
         <v>44469</v>
       </c>
       <c r="F197" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G197" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H197" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I197" s="79" t="n">
         <v>10988.763</v>
@@ -30143,15 +30148,15 @@
         <v>20</v>
       </c>
       <c r="S197" s="66" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B198" s="76" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C198" s="77" t="n">
         <v>2021</v>
@@ -30163,13 +30168,13 @@
         <v>44377</v>
       </c>
       <c r="F198" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G198" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H198" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I198" s="79" t="n">
         <v>10381.154</v>
@@ -30202,15 +30207,15 @@
         <v>21</v>
       </c>
       <c r="S198" s="66" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B199" s="76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C199" s="77" t="n">
         <v>2021</v>
@@ -30222,13 +30227,13 @@
         <v>44286</v>
       </c>
       <c r="F199" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G199" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H199" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I199" s="79" t="n">
         <v>9532.889</v>
@@ -30261,15 +30266,15 @@
         <v>22</v>
       </c>
       <c r="S199" s="66" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B200" s="76" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C200" s="77" t="n">
         <v>2020</v>
@@ -30281,13 +30286,13 @@
         <v>44196</v>
       </c>
       <c r="F200" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G200" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H200" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I200" s="79" t="n">
         <v>8938.602</v>
@@ -30320,15 +30325,15 @@
         <v>23</v>
       </c>
       <c r="S200" s="66" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B201" s="76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C201" s="77" t="n">
         <v>2020</v>
@@ -30340,13 +30345,13 @@
         <v>44104</v>
       </c>
       <c r="F201" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G201" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H201" s="76" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I201" s="79" t="n">
         <v>9067.715</v>
@@ -30377,142 +30382,142 @@
         <v>24</v>
       </c>
       <c r="S201" s="66" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="81" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="42" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="82" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C205" s="24" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="82" t="s">
+        <v>448</v>
+      </c>
+      <c r="C206" s="24" t="s">
         <v>447</v>
-      </c>
-      <c r="C206" s="24" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="82" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C207" s="24" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="82" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C208" s="24" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="82" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C209" s="24" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="82" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C210" s="24" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="82" t="s">
+        <v>454</v>
+      </c>
+      <c r="C211" s="24" t="s">
         <v>453</v>
-      </c>
-      <c r="C211" s="24" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="82" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C212" s="25" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="82" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C213" s="24" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="82" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C214" s="24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="82" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C215" s="25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="82" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C216" s="25" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="82" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C217" s="24" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="82" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C218" s="24" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="82" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C219" s="25" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="82" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C220" s="24" t="s">
         <v>47</v>
@@ -30520,15 +30525,15 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="82" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C221" s="24" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="24" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -30564,19 +30569,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30601,7 +30606,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B3" s="80" t="n">
         <v>33.85612</v>
@@ -30661,7 +30666,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" s="80" t="n">
         <v>33.70448</v>
@@ -30681,7 +30686,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="80" t="n">
         <v>65.61145</v>
@@ -30721,7 +30726,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="76" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" s="80" t="n">
         <v>30.55</v>
@@ -30741,7 +30746,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -7295,7 +7295,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB6E1C1"/>
+          <fgColor rgb="FFB5E0C0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7303,7 +7303,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC8E8D0"/>
+          <fgColor rgb="FFC7E8CF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7311,7 +7311,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF2FAF4"/>
+          <fgColor rgb="FFF3FAF5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7319,7 +7319,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF9FDFA"/>
+          <fgColor rgb="FFFAFDFB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7487,6 +7487,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF9FDFA"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFAFDFA"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7552,14 +7560,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4FBF6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFAFDFB"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8286,7 +8286,7 @@
         <v>167</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>2410</v>
+        <v>2460</v>
       </c>
       <c r="C2" s="78" t="n">
         <v>46272</v>
@@ -8301,7 +8301,7 @@
         <v>192</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>361</v>
+        <v>364.5</v>
       </c>
       <c r="C3" s="78" t="n">
         <v>46272</v>
@@ -8316,7 +8316,7 @@
         <v>171</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="C4" s="78" t="n">
         <v>46272</v>
@@ -8331,7 +8331,7 @@
         <v>179</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="C5" s="78" t="n">
         <v>46272</v>
@@ -8346,7 +8346,7 @@
         <v>184</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="C6" s="78" t="n">
         <v>46272</v>
@@ -8361,7 +8361,7 @@
         <v>186</v>
       </c>
       <c r="B7" s="80" t="n">
-        <v>2145</v>
+        <v>2070</v>
       </c>
       <c r="C7" s="78" t="n">
         <v>46272</v>
@@ -8376,7 +8376,7 @@
         <v>176</v>
       </c>
       <c r="B8" s="80" t="n">
-        <v>1360</v>
+        <v>1405</v>
       </c>
       <c r="C8" s="78" t="n">
         <v>46272</v>
@@ -8391,7 +8391,7 @@
         <v>189</v>
       </c>
       <c r="B9" s="80" t="n">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C9" s="78" t="n">
         <v>46272</v>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2410</v>
+        <v>2460</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8628,15 +8628,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>27.9323133982383</v>
+        <v>28.5118219749652</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>24.8373027843441</v>
+        <v>25.3525995226085</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.3599833471309</v>
+        <v>18.7408958647062</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8644,11 +8644,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>0.524814336821755</v>
+        <v>0.535702601071169</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.573087280964525</v>
+        <v>0.584977058577897</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00912867227385892</v>
+        <v>0.00894313015447155</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8810,15 +8810,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>18.268876611418</v>
+        <v>19.0423572744015</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>10.4425779272114</v>
+        <v>10.8847032023555</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>5.58682336722819</v>
+        <v>5.82336225979229</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.115249781648616</v>
+        <v>0.120129308694223</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1360</v>
+        <v>1405</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8992,15 +8992,15 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>7.45001369487812</v>
+        <v>7.69652150095864</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>4.95103571298555</v>
+        <v>5.11485674760639</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>5.55718706810999</v>
+        <v>5.74106458139305</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.00466167911641093</v>
+        <v>0.00481592585188041</v>
       </c>
       <c r="O4" s="51" t="str">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00689502775</v>
+        <v>0.00667419056227758</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9174,15 +9174,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>128.155339805825</v>
+        <v>121.359223300971</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>112.477073210219</v>
+        <v>106.51237993392</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>68.1486005128649</v>
+        <v>64.5346595765766</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9190,11 +9190,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>2.08150392678251</v>
+        <v>1.97112114278647</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>1.02828911817767</v>
+        <v>0.973758634637944</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00496317524621212</v>
+        <v>0.00524111306</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9356,15 +9356,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>18.2769445413324</v>
+        <v>18.8350191838158</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>16.2567675775524</v>
+        <v>16.7531574272486</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>15.0514898909209</v>
+        <v>15.5110773685063</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Q6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(P6=0,"不配息",P6/D6),""))</f>
-        <v>0.0534351145038168</v>
+        <v>0.0518518518518519</v>
       </c>
       <c r="R6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9514,7 +9514,7 @@
       </c>
       <c r="D7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2145</v>
+        <v>2070</v>
       </c>
       <c r="E7" s="48" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9538,15 +9538,15 @@
       </c>
       <c r="J7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(F7&lt;=0,"N/M",D7/F7),"N/M"))</f>
-        <v>39.3361452411517</v>
+        <v>37.9607555474051</v>
       </c>
       <c r="K7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(G7&lt;=0,"N/M",D7/G7),"N/M"))</f>
-        <v>35.8913220806927</v>
+        <v>34.6363807492</v>
       </c>
       <c r="L7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(H7&lt;=0,"N/M",D7/H7),"N/M"))</f>
-        <v>21.6023666707785</v>
+        <v>20.8470391648073</v>
       </c>
       <c r="M7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9554,11 +9554,11 @@
       </c>
       <c r="N7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(J7)),I7&lt;Config!$B$6),"N/M",J7/(I7*100)),"N/M"))</f>
-        <v>0.684527994824664</v>
+        <v>0.660593449551075</v>
       </c>
       <c r="O7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(L7)),M7&lt;Config!$B$6),"N/M",L7/(M7*100)),"N/M"))</f>
-        <v>0.288213575819811</v>
+        <v>0.278136178063874</v>
       </c>
       <c r="P7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="Q7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(P7=0,"不配息",P7/D7),""))</f>
-        <v>0.00489766083449883</v>
+        <v>0.00507511231400966</v>
       </c>
       <c r="R7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="D8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E8" s="48" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9720,15 +9720,15 @@
       </c>
       <c r="J8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(F8&lt;=0,"N/M",D8/F8),"N/M"))</f>
-        <v>20.0074377091856</v>
+        <v>20.1190033469691</v>
       </c>
       <c r="K8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(G8&lt;=0,"N/M",D8/G8),"N/M"))</f>
-        <v>18.5240466571843</v>
+        <v>18.6273405976519</v>
       </c>
       <c r="L8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(H8&lt;=0,"N/M",D8/H8),"N/M"))</f>
-        <v>16.2078286527867</v>
+        <v>16.2982068794751</v>
       </c>
       <c r="M8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9736,11 +9736,11 @@
       </c>
       <c r="N8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(J8)),I8&lt;Config!$B$6),"N/M",J8/(I8*100)),"N/M"))</f>
-        <v>0.524017143769517</v>
+        <v>0.526939172452247</v>
       </c>
       <c r="O8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(L8)),M8&lt;Config!$B$6),"N/M",L8/(M8*100)),"N/M"))</f>
-        <v>1.2827698584006</v>
+        <v>1.28992285017607</v>
       </c>
       <c r="P8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Q8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(P8=0,"不配息",P8/D8),""))</f>
-        <v>0.0222780073605948</v>
+        <v>0.0221544694269871</v>
       </c>
       <c r="R8" s="49" t="str">
         <f aca="false">IF($A8="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="D9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>361</v>
+        <v>364.5</v>
       </c>
       <c r="E9" s="48" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9902,15 +9902,15 @@
       </c>
       <c r="J9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(F9&lt;=0,"N/M",D9/F9),"N/M"))</f>
-        <v>13.5155372519656</v>
+        <v>13.6465743167353</v>
       </c>
       <c r="K9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(G9&lt;=0,"N/M",D9/G9),"N/M"))</f>
-        <v>11.8880377361224</v>
+        <v>12.0032957197137</v>
       </c>
       <c r="L9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(H9&lt;=0,"N/M",D9/H9),"N/M"))</f>
-        <v>9.97690709262425</v>
+        <v>10.0736361087577</v>
       </c>
       <c r="M9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9918,11 +9918,11 @@
       </c>
       <c r="N9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(OR(NOT(ISNUMBER(J9)),I9&lt;Config!$B$6),"N/M",J9/(I9*100)),"N/M"))</f>
-        <v>0.21567067218394</v>
+        <v>0.21776166208046</v>
       </c>
       <c r="O9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(OR(NOT(ISNUMBER(L9)),M9&lt;Config!$B$6),"N/M",L9/(M9*100)),"N/M"))</f>
-        <v>0.994035902122793</v>
+        <v>1.00367336931789</v>
       </c>
       <c r="P9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="Q9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(P9=0,"不配息",P9/D9),""))</f>
-        <v>0.0277008310249307</v>
+        <v>0.0274348422496571</v>
       </c>
       <c r="R9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -12511,27 +12511,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>2410</v>
+        <v>2460</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>27.9323133982383</v>
+        <v>28.5118219749652</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.3599833471309</v>
+        <v>18.7408958647062</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>0.524814336821755</v>
+        <v>0.535702601071169</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.573087280964525</v>
+        <v>0.584977058577897</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00912867227385892</v>
+        <v>0.00894313015447155</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -12629,15 +12629,15 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>18.268876611418</v>
+        <v>19.0423572744015</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>5.58682336722819</v>
+        <v>5.82336225979229</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.115249781648616</v>
+        <v>0.120129308694223</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -12747,19 +12747,19 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>1360</v>
+        <v>1405</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>7.45001369487812</v>
+        <v>7.69652150095864</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>5.55718706810999</v>
+        <v>5.74106458139305</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.00466167911641093</v>
+        <v>0.00481592585188041</v>
       </c>
       <c r="H5" s="17" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00689502775</v>
+        <v>0.00667419056227758</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12865,27 +12865,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>528</v>
+        <v>500</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>128.155339805825</v>
+        <v>121.359223300971</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>68.1486005128649</v>
+        <v>64.5346595765766</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>2.08150392678251</v>
+        <v>1.97112114278647</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>1.02828911817767</v>
+        <v>0.973758634637944</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00496317524621212</v>
+        <v>0.00524111306</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12983,15 +12983,15 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>18.2769445413324</v>
+        <v>18.8350191838158</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>15.0514898909209</v>
+        <v>15.5110773685063</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
-        <v>0.0534351145038168</v>
+        <v>0.0518518518518519</v>
       </c>
       <c r="J7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!R$6)</f>
@@ -13101,27 +13101,27 @@
       </c>
       <c r="D8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!D$7)</f>
-        <v>2145</v>
+        <v>2070</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!J$7)</f>
-        <v>39.3361452411517</v>
+        <v>37.9607555474051</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!L$7)</f>
-        <v>21.6023666707785</v>
+        <v>20.8470391648073</v>
       </c>
       <c r="G8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!N$7)</f>
-        <v>0.684527994824664</v>
+        <v>0.660593449551075</v>
       </c>
       <c r="H8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!O$7)</f>
-        <v>0.288213575819811</v>
+        <v>0.278136178063874</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!Q$7)</f>
-        <v>0.00489766083449883</v>
+        <v>0.00507511231400966</v>
       </c>
       <c r="J8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!R$7)</f>
@@ -13219,27 +13219,27 @@
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!D$8)</f>
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!J$8)</f>
-        <v>20.0074377091856</v>
+        <v>20.1190033469691</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!L$8)</f>
-        <v>16.2078286527867</v>
+        <v>16.2982068794751</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!N$8)</f>
-        <v>0.524017143769517</v>
+        <v>0.526939172452247</v>
       </c>
       <c r="H9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!O$8)</f>
-        <v>1.2827698584006</v>
+        <v>1.28992285017607</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!Q$8)</f>
-        <v>0.0222780073605948</v>
+        <v>0.0221544694269871</v>
       </c>
       <c r="J9" s="19" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!R$8)</f>
@@ -13337,27 +13337,27 @@
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!D$9)</f>
-        <v>361</v>
+        <v>364.5</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!J$9)</f>
-        <v>13.5155372519656</v>
+        <v>13.6465743167353</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!L$9)</f>
-        <v>9.97690709262425</v>
+        <v>10.0736361087577</v>
       </c>
       <c r="G10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!N$9)</f>
-        <v>0.21567067218394</v>
+        <v>0.21776166208046</v>
       </c>
       <c r="H10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!O$9)</f>
-        <v>0.994035902122793</v>
+        <v>1.00367336931789</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!Q$9)</f>
-        <v>0.0277008310249307</v>
+        <v>0.0274348422496571</v>
       </c>
       <c r="J10" s="19" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!R$9)</f>
@@ -17255,7 +17255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8FCA1B15-646A-405F-B145-97E4842CD03E}</x14:id>
+          <x14:id>{DCFC243E-73AD-44F4-8853-5C377225CB29}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17386,7 +17386,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8FCA1B15-646A-405F-B145-97E4842CD03E}">
+          <x14:cfRule type="dataBar" id="{DCFC243E-73AD-44F4-8853-5C377225CB29}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -7228,7 +7228,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="55">
+  <dxfs count="56">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7295,7 +7295,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB5E0C0"/>
+          <fgColor rgb="FFB4E0C0"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7303,7 +7303,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFC7E8CF"/>
+          <fgColor rgb="FFC6E8CF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7320,6 +7320,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFAFDFB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEFFFF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8286,14 +8294,14 @@
         <v>167</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>2460</v>
+        <v>2470</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D2" s="78"/>
       <c r="E2" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8301,14 +8309,14 @@
         <v>192</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>364.5</v>
+        <v>357</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D3" s="78"/>
       <c r="E3" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8316,14 +8324,14 @@
         <v>171</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8331,14 +8339,14 @@
         <v>179</v>
       </c>
       <c r="B5" s="80" t="n">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="C5" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D5" s="78"/>
       <c r="E5" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8346,14 +8354,14 @@
         <v>184</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8361,14 +8369,14 @@
         <v>186</v>
       </c>
       <c r="B7" s="80" t="n">
-        <v>2070</v>
+        <v>1935</v>
       </c>
       <c r="C7" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D7" s="78"/>
       <c r="E7" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8376,14 +8384,14 @@
         <v>176</v>
       </c>
       <c r="B8" s="80" t="n">
-        <v>1405</v>
+        <v>1370</v>
       </c>
       <c r="C8" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D8" s="78"/>
       <c r="E8" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8391,14 +8399,14 @@
         <v>189</v>
       </c>
       <c r="B9" s="80" t="n">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="C9" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="D9" s="78"/>
       <c r="E9" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
   </sheetData>
@@ -8604,7 +8612,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2460</v>
+        <v>2470</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8620,7 +8628,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>131.263735616438</v>
+        <v>131.358216958904</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8628,15 +8636,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>28.5118219749652</v>
+        <v>28.6277236903106</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>25.3525995226085</v>
+        <v>25.4556588702614</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.7408958647062</v>
+        <v>18.8035439059952</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8644,11 +8652,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>0.535702601071169</v>
+        <v>0.537880253921051</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.584977058577897</v>
+        <v>0.586932550310174</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8656,7 +8664,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00894313015447155</v>
+        <v>0.00890692314979757</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -8748,7 +8756,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8786,7 +8794,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8802,7 +8810,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>88.7803260273973</v>
+        <v>88.8688449315068</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8810,15 +8818,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>19.0423572744015</v>
+        <v>19.5580110497238</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>10.8847032023555</v>
+        <v>11.1794533857848</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>5.82336225979229</v>
+        <v>5.97509735171255</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -8830,7 +8838,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.120129308694223</v>
+        <v>0.123259430243227</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8930,7 +8938,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -8968,7 +8976,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1405</v>
+        <v>1370</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -8984,7 +8992,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>244.728130136986</v>
+        <v>244.294182657534</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -8992,15 +9000,15 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>7.69652150095864</v>
+        <v>7.50479320734045</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>5.11485674760639</v>
+        <v>4.98744038734574</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>5.74106458139305</v>
+        <v>5.60799272867068</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9008,7 +9016,7 @@
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.00481592585188041</v>
+        <v>0.00469595616873748</v>
       </c>
       <c r="O4" s="51" t="str">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
@@ -9020,7 +9028,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00667419056227758</v>
+        <v>0.00684469908029197</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9112,7 +9120,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -9150,7 +9158,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9166,7 +9174,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.74777465753425</v>
+        <v>7.75745035616438</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -9174,15 +9182,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>121.359223300971</v>
+        <v>125</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>106.51237993392</v>
+        <v>109.707751331937</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>64.5346595765766</v>
+        <v>66.3877919103614</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9190,11 +9198,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>1.97112114278647</v>
+        <v>2.03025477707006</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>0.973758634637944</v>
+        <v>1.00172040933373</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9202,7 +9210,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00524111306</v>
+        <v>0.0050884592815534</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9294,7 +9302,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -9332,7 +9340,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9348,7 +9356,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>34.8138293150685</v>
+        <v>34.8182667123288</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -9356,15 +9364,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>18.8350191838158</v>
+        <v>18.6257411928845</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>16.7531574272486</v>
+        <v>16.5670112336125</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>15.5110773685063</v>
+        <v>15.3367772270788</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9384,7 +9392,7 @@
       </c>
       <c r="Q6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(P6=0,"不配息",P6/D6),""))</f>
-        <v>0.0518518518518519</v>
+        <v>0.052434456928839</v>
       </c>
       <c r="R6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9476,7 +9484,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -9514,7 +9522,7 @@
       </c>
       <c r="D7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2070</v>
+        <v>1935</v>
       </c>
       <c r="E7" s="48" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9530,7 +9538,7 @@
       </c>
       <c r="H7" s="51" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>99.2946760273973</v>
+        <v>99.4294089315068</v>
       </c>
       <c r="I7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -9538,15 +9546,15 @@
       </c>
       <c r="J7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(F7&lt;=0,"N/M",D7/F7),"N/M"))</f>
-        <v>37.9607555474051</v>
+        <v>35.4850540986613</v>
       </c>
       <c r="K7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(G7&lt;=0,"N/M",D7/G7),"N/M"))</f>
-        <v>34.6363807492</v>
+        <v>32.377486352513</v>
       </c>
       <c r="L7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(H7&lt;=0,"N/M",D7/H7),"N/M"))</f>
-        <v>20.8470391648073</v>
+        <v>19.4610429730398</v>
       </c>
       <c r="M7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9554,11 +9562,11 @@
       </c>
       <c r="N7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(J7)),I7&lt;Config!$B$6),"N/M",J7/(I7*100)),"N/M"))</f>
-        <v>0.660593449551075</v>
+        <v>0.617511268058613</v>
       </c>
       <c r="O7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(L7)),M7&lt;Config!$B$6),"N/M",L7/(M7*100)),"N/M"))</f>
-        <v>0.278136178063874</v>
+        <v>0.259644550521865</v>
       </c>
       <c r="P7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9566,7 +9574,7 @@
       </c>
       <c r="Q7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(P7=0,"不配息",P7/D7),""))</f>
-        <v>0.00507511231400966</v>
+        <v>0.00542918991731266</v>
       </c>
       <c r="R7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9658,7 +9666,7 @@
       </c>
       <c r="AN7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -9696,7 +9704,7 @@
       </c>
       <c r="D8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E8" s="48" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9712,7 +9720,7 @@
       </c>
       <c r="H8" s="51" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>33.1938356164384</v>
+        <v>33.2044109589041</v>
       </c>
       <c r="I8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -9720,15 +9728,15 @@
       </c>
       <c r="J8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(F8&lt;=0,"N/M",D8/F8),"N/M"))</f>
-        <v>20.1190033469691</v>
+        <v>19.7843064336184</v>
       </c>
       <c r="K8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(G8&lt;=0,"N/M",D8/G8),"N/M"))</f>
-        <v>18.6273405976519</v>
+        <v>18.3174587762491</v>
       </c>
       <c r="L8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(H8&lt;=0,"N/M",D8/H8),"N/M"))</f>
-        <v>16.2982068794751</v>
+        <v>16.0219677035812</v>
       </c>
       <c r="M8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9736,11 +9744,11 @@
       </c>
       <c r="N8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(J8)),I8&lt;Config!$B$6),"N/M",J8/(I8*100)),"N/M"))</f>
-        <v>0.526939172452247</v>
+        <v>0.518173086404058</v>
       </c>
       <c r="O8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(L8)),M8&lt;Config!$B$6),"N/M",L8/(M8*100)),"N/M"))</f>
-        <v>1.28992285017607</v>
+        <v>1.26805987913059</v>
       </c>
       <c r="P8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9748,7 +9756,7 @@
       </c>
       <c r="Q8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(P8=0,"不配息",P8/D8),""))</f>
-        <v>0.0221544694269871</v>
+        <v>0.0225292630827068</v>
       </c>
       <c r="R8" s="49" t="str">
         <f aca="false">IF($A8="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -9840,7 +9848,7 @@
       </c>
       <c r="AN8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -9878,7 +9886,7 @@
       </c>
       <c r="D9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>364.5</v>
+        <v>357</v>
       </c>
       <c r="E9" s="48" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9894,7 +9902,7 @@
       </c>
       <c r="H9" s="51" t="n">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>36.1835583561644</v>
+        <v>36.192868109589</v>
       </c>
       <c r="I9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -9902,15 +9910,15 @@
       </c>
       <c r="J9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(F9&lt;=0,"N/M",D9/F9),"N/M"))</f>
-        <v>13.6465743167353</v>
+        <v>13.3657806065144</v>
       </c>
       <c r="K9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(G9&lt;=0,"N/M",D9/G9),"N/M"))</f>
-        <v>12.0032957197137</v>
+        <v>11.7563143263039</v>
       </c>
       <c r="L9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(H9&lt;=0,"N/M",D9/H9),"N/M"))</f>
-        <v>10.0736361087577</v>
+        <v>9.86382175955311</v>
       </c>
       <c r="M9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9918,11 +9926,11 @@
       </c>
       <c r="N9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(OR(NOT(ISNUMBER(J9)),I9&lt;Config!$B$6),"N/M",J9/(I9*100)),"N/M"))</f>
-        <v>0.21776166208046</v>
+        <v>0.21328096944506</v>
       </c>
       <c r="O9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(OR(NOT(ISNUMBER(L9)),M9&lt;Config!$B$6),"N/M",L9/(M9*100)),"N/M"))</f>
-        <v>1.00367336931789</v>
+        <v>0.982768794989026</v>
       </c>
       <c r="P9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9930,7 +9938,7 @@
       </c>
       <c r="Q9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(P9=0,"不配息",P9/D9),""))</f>
-        <v>0.0274348422496571</v>
+        <v>0.0280112044817927</v>
       </c>
       <c r="R9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -10022,7 +10030,7 @@
       </c>
       <c r="AN9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="AO9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A9)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12511,27 +12519,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>2460</v>
+        <v>2470</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>28.5118219749652</v>
+        <v>28.6277236903106</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.7408958647062</v>
+        <v>18.8035439059952</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>0.535702601071169</v>
+        <v>0.537880253921051</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.584977058577897</v>
+        <v>0.586932550310174</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00894313015447155</v>
+        <v>0.00890692314979757</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -12629,15 +12637,15 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>19.0423572744015</v>
+        <v>19.5580110497238</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>5.82336225979229</v>
+        <v>5.97509735171255</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -12645,7 +12653,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.120129308694223</v>
+        <v>0.123259430243227</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -12747,19 +12755,19 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>1405</v>
+        <v>1370</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>7.69652150095864</v>
+        <v>7.50479320734045</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>5.74106458139305</v>
+        <v>5.60799272867068</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.00481592585188041</v>
+        <v>0.00469595616873748</v>
       </c>
       <c r="H5" s="17" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
@@ -12767,7 +12775,7 @@
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00667419056227758</v>
+        <v>0.00684469908029197</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -12865,27 +12873,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>121.359223300971</v>
+        <v>125</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>64.5346595765766</v>
+        <v>66.3877919103614</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>1.97112114278647</v>
+        <v>2.03025477707006</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>0.973758634637944</v>
+        <v>1.00172040933373</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00524111306</v>
+        <v>0.0050884592815534</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -12983,15 +12991,15 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>18.8350191838158</v>
+        <v>18.6257411928845</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>15.5110773685063</v>
+        <v>15.3367772270788</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
@@ -13003,7 +13011,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
-        <v>0.0518518518518519</v>
+        <v>0.052434456928839</v>
       </c>
       <c r="J7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!R$6)</f>
@@ -13101,27 +13109,27 @@
       </c>
       <c r="D8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!D$7)</f>
-        <v>2070</v>
+        <v>1935</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!J$7)</f>
-        <v>37.9607555474051</v>
+        <v>35.4850540986613</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!L$7)</f>
-        <v>20.8470391648073</v>
+        <v>19.4610429730398</v>
       </c>
       <c r="G8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!N$7)</f>
-        <v>0.660593449551075</v>
+        <v>0.617511268058613</v>
       </c>
       <c r="H8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!O$7)</f>
-        <v>0.278136178063874</v>
+        <v>0.259644550521865</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!Q$7)</f>
-        <v>0.00507511231400966</v>
+        <v>0.00542918991731266</v>
       </c>
       <c r="J8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!R$7)</f>
@@ -13219,27 +13227,27 @@
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!D$8)</f>
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!J$8)</f>
-        <v>20.1190033469691</v>
+        <v>19.7843064336184</v>
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!L$8)</f>
-        <v>16.2982068794751</v>
+        <v>16.0219677035812</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!N$8)</f>
-        <v>0.526939172452247</v>
+        <v>0.518173086404058</v>
       </c>
       <c r="H9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!O$8)</f>
-        <v>1.28992285017607</v>
+        <v>1.26805987913059</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!Q$8)</f>
-        <v>0.0221544694269871</v>
+        <v>0.0225292630827068</v>
       </c>
       <c r="J9" s="19" t="str">
         <f aca="false">IF(Calc!$A$8="","",Calc!R$8)</f>
@@ -13337,27 +13345,27 @@
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!D$9)</f>
-        <v>364.5</v>
+        <v>357</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!J$9)</f>
-        <v>13.6465743167353</v>
+        <v>13.3657806065144</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!L$9)</f>
-        <v>10.0736361087577</v>
+        <v>9.86382175955311</v>
       </c>
       <c r="G10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!N$9)</f>
-        <v>0.21776166208046</v>
+        <v>0.21328096944506</v>
       </c>
       <c r="H10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!O$9)</f>
-        <v>1.00367336931789</v>
+        <v>0.982768794989026</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!Q$9)</f>
-        <v>0.0274348422496571</v>
+        <v>0.0280112044817927</v>
       </c>
       <c r="J10" s="19" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!R$9)</f>
@@ -14969,36 +14977,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="43">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="46">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="46">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="46">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="47">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="47">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17255,7 +17263,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{DCFC243E-73AD-44F4-8853-5C377225CB29}</x14:id>
+          <x14:id>{3D629F2C-F672-4D24-B2C4-9E8247D3EC58}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17271,16 +17279,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="44">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="46">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="45">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="46">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="46">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="47">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17321,47 +17329,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="48">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17386,7 +17394,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{DCFC243E-73AD-44F4-8853-5C377225CB29}">
+          <x14:cfRule type="dataBar" id="{3D629F2C-F672-4D24-B2C4-9E8247D3EC58}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -17489,11 +17497,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J4" s="72" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -17531,11 +17539,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J5" s="72" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -17573,11 +17581,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J6" s="72" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -17615,11 +17623,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J7" s="72" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -17657,11 +17665,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J8" s="72" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -17699,11 +17707,11 @@
       </c>
       <c r="H9" s="47" t="n">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A9,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J9" s="72" t="str">
         <f aca="true">IF($A9="","",IF($B9=0,"未抓取",IF($B9&lt;$C9,"需補歷史 ("&amp;($C9-$B9)&amp;" 季)",IF(TODAY()&gt;$G9,"待更新財報","OK"))))</f>
@@ -17741,11 +17749,11 @@
       </c>
       <c r="H10" s="47" t="n">
         <f aca="true">IF($A10="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A10,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A10,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J10" s="72" t="str">
         <f aca="true">IF($A10="","",IF($B10=0,"未抓取",IF($B10&lt;$C10,"需補歷史 ("&amp;($C10-$B10)&amp;" 季)",IF(TODAY()&gt;$G10,"待更新財報","OK"))))</f>
@@ -17783,11 +17791,11 @@
       </c>
       <c r="H11" s="47" t="n">
         <f aca="true">IF($A11="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A11,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46272</v>
+        <v>-46273</v>
       </c>
       <c r="I11" s="67" t="n">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A11,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="J11" s="72" t="str">
         <f aca="true">IF($A11="","",IF($B11=0,"未抓取",IF($B11&lt;$C11,"需補歷史 ("&amp;($C11-$B11)&amp;" 季)",IF(TODAY()&gt;$G11,"待更新財報","OK"))))</f>
@@ -18305,18 +18313,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="49">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="50">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="50">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="51">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="51">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="52">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="52">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="53">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30601,7 +30609,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30621,7 +30629,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30641,7 +30649,7 @@
         <v>6</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30661,7 +30669,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30681,7 +30689,7 @@
         <v>14</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30701,7 +30709,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30721,7 +30729,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30741,7 +30749,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="78" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2208" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2207" uniqueCount="633">
   <si>
     <r>
       <rPr>
@@ -3935,7 +3935,25 @@
     <t xml:space="preserve">波若威</t>
   </si>
   <si>
-    <t xml:space="preserve">基本面普普</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="DejaVu Sans"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基本面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">not good</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">3189</t>
@@ -4904,79 +4922,82 @@
     <t xml:space="preserve">3163|24</t>
   </si>
   <si>
-    <t xml:space="preserve">3189|0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3189|24</t>
+    <t xml:space="preserve">3363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3363|24</t>
   </si>
   <si>
     <t xml:space="preserve">3665|0</t>
@@ -7552,7 +7573,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="69">
+  <dxfs count="65">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7675,14 +7696,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCFEFD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FF8CD09E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7723,14 +7736,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDFF2E4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFE0F2E5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7763,14 +7768,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFCCEAD4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFE5F4E9"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7796,6 +7793,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFBB3B4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCFEFD"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -7907,14 +7912,6 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFBFDFB"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FFE4F4E8"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -7947,47 +7944,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFB0DEBC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD0ECD7"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD5EEDB"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE3F4E8"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4F4E9"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE7F5EB"/>
+          <fgColor rgb="FFE2F3E7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8003,7 +7960,39 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE9F6EC"/>
+          <fgColor rgb="FFF4FBF6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFAFDFB"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDFFFE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEFFFE"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF808080"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8705,16 +8694,16 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8839,10 +8828,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B10" s="80" t="n">
-        <v>800</v>
+        <v>711</v>
       </c>
       <c r="C10" s="78" t="n">
         <v>46274</v>
@@ -8962,16 +8951,16 @@
         <v>55</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>68</v>
@@ -8980,13 +8969,13 @@
         <v>56</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N1" s="14" t="s">
         <v>58</v>
@@ -8995,7 +8984,7 @@
         <v>59</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Q1" s="15" t="s">
         <v>47</v>
@@ -9004,16 +8993,16 @@
         <v>60</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="V1" s="15" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="W1" s="15" t="s">
         <v>64</v>
@@ -9022,16 +9011,16 @@
         <v>65</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="Z1" s="15" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AB1" s="14" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AC1" s="14" t="s">
         <v>71</v>
@@ -9040,7 +9029,7 @@
         <v>106</v>
       </c>
       <c r="AE1" s="15" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AF1" s="14" t="s">
         <v>72</v>
@@ -9049,7 +9038,7 @@
         <v>73</v>
       </c>
       <c r="AH1" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AI1" s="15" t="s">
         <v>75</v>
@@ -9058,7 +9047,7 @@
         <v>76</v>
       </c>
       <c r="AK1" s="15" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AL1" s="15" t="s">
         <v>86</v>
@@ -9070,19 +9059,19 @@
         <v>88</v>
       </c>
       <c r="AO1" s="14" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AP1" s="14" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AQ1" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AR1" s="14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AS1" s="14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10916,7 +10905,7 @@
       </c>
       <c r="C12" s="66" t="str">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A12,Tickers!$A$2:$A$100,0)),""))</f>
-        <v>池子</v>
+        <v>基本面not good</v>
       </c>
       <c r="D12" s="51" t="n">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A12,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -11100,173 +11089,173 @@
         <f aca="false">IF($A13="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A13,Tickers!$A$2:$A$100,0)),""))</f>
         <v>池子</v>
       </c>
-      <c r="D13" s="51" t="n">
+      <c r="D13" s="51" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A13,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>800</v>
+        <v/>
       </c>
       <c r="E13" s="48" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v>44768.845</v>
+        <v>0</v>
       </c>
       <c r="F13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="G13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=0",Raw_Q!$R$2:$R$600,"&lt;=3"),""))</f>
-        <v>8.33425</v>
-      </c>
-      <c r="H13" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="51" t="str">
         <f aca="true">IF($A13="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>21.5507000273973</v>
-      </c>
-      <c r="I13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="I13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
-        <v>3.87603305785124</v>
-      </c>
-      <c r="J13" s="52" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="52" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(F13&lt;=0,"N/M",D13/F13),"N/M"))</f>
-        <v>135.593220338983</v>
-      </c>
-      <c r="K13" s="52" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="K13" s="52" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(G13&lt;=0,"N/M",D13/G13),"N/M"))</f>
-        <v>95.9894411614722</v>
-      </c>
-      <c r="L13" s="52" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="L13" s="52" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(H13&lt;=0,"N/M",D13/H13),"N/M"))</f>
-        <v>37.1217639790339</v>
-      </c>
-      <c r="M13" s="49" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="M13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-1,""))</f>
-        <v>1.50009682169788</v>
-      </c>
-      <c r="N13" s="51" t="n">
+        <v/>
+      </c>
+      <c r="N13" s="51" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(OR(NOT(ISNUMBER(J13)),I13&lt;Config!$B$6),"N/M",J13/(I13*100)),"N/M"))</f>
-        <v>0.349824726247696</v>
-      </c>
-      <c r="O13" s="51" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="O13" s="51" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(OR(NOT(ISNUMBER(L13)),M13&lt;Config!$B$6),"N/M",L13/(M13*100)),"N/M"))</f>
-        <v>0.247462453370294</v>
+        <v>N/M</v>
       </c>
       <c r="P13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
-        <v>1.00017193</v>
-      </c>
-      <c r="Q13" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(P13=0,"不配息",P13/D13),""))</f>
-        <v>0.0012502149125</v>
-      </c>
-      <c r="R13" s="49" t="n">
+        <v>不配息</v>
+      </c>
+      <c r="R13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
-        <v>6.40830892795208E-005</v>
-      </c>
-      <c r="S13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v>0.306630281963327</v>
-      </c>
-      <c r="T13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="T13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,2)-1,""))</f>
-        <v>0.125285311570095</v>
-      </c>
-      <c r="U13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,2)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,3)-1,""))</f>
-        <v>0.027149672411755</v>
-      </c>
-      <c r="V13" s="68" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="68" t="str">
         <f aca="false">IF($A13="","",IFERROR((T13-U13)*100,""))</f>
-        <v>9.81356391583401</v>
+        <v/>
       </c>
       <c r="W13" s="66" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(NOT(ISNUMBER(T13)),"",IF(T13&gt;0,IF(V13&gt;0,"成長且加速","成長但減速"),IF(V13&gt;0,"衰退但收斂","衰退且惡化"))),""))</f>
-        <v>成長且加速</v>
-      </c>
-      <c r="X13" s="68" t="n">
+        <v/>
+      </c>
+      <c r="X13" s="68" t="str">
         <f aca="false">IF($A13="","",IFERROR((T13-(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,6)-1))*100,""))</f>
-        <v>1.5771386330552</v>
-      </c>
-      <c r="Y13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="Y13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5)-1,""))</f>
-        <v>2.47297297297297</v>
-      </c>
-      <c r="Z13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="Z13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/E13,""))</f>
-        <v>0.222641906441857</v>
-      </c>
-      <c r="AA13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AA13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;="&amp;Config!$B$5),""))</f>
-        <v>0.285033485013648</v>
-      </c>
-      <c r="AB13" s="50" t="n">
+        <v/>
+      </c>
+      <c r="AB13" s="50" t="str">
         <f aca="false">IF($A13="","",IFERROR((Z13-AA13)*10000,""))</f>
-        <v>-623.915785717906</v>
-      </c>
-      <c r="AC13" s="50" t="n">
+        <v/>
+      </c>
+      <c r="AC13" s="50" t="str">
         <f aca="false">IF($A13="","",IFERROR((SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)-SUMIFS(Raw_Q!$J$2:$J$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5)/SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5))*10000,""))</f>
-        <v>501.715545944687</v>
-      </c>
-      <c r="AD13" s="51" t="n">
+        <v/>
+      </c>
+      <c r="AD13" s="51" t="str">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)/SUMIFS(Raw_Q!$M$2:$M$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v>84.3913765983742</v>
+        <v/>
       </c>
       <c r="AE13" s="48" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMPRODUCT((Raw_Q!$A$2:$A$600=$A13)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600),""))</f>
-        <v>2957.337459</v>
-      </c>
-      <c r="AF13" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5))&lt;=0,"N/M",AE13/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5))/2)),"N/M"))</f>
-        <v>0.0778103242070686</v>
-      </c>
-      <c r="AG13" s="49" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="AG13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(AVERAGE(AO13:AS13),""))</f>
-        <v>0.0864176589454461</v>
-      </c>
-      <c r="AH13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AH13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(AD13&lt;=0,"N/M",INDEX(Raw_Est!$B$2:$B$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))/AD13),"N/M"))</f>
-        <v>0.125444926089806</v>
+        <v>N/M</v>
       </c>
       <c r="AI13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,0),""))</f>
-        <v>3.18425</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="66" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A13&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v>FY2026Q3E</v>
+        <v/>
       </c>
       <c r="AK13" s="66" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Q!$G$2:$G$600,MATCH($A13&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v>consensus</v>
-      </c>
-      <c r="AL13" s="47" t="n">
+        <v/>
+      </c>
+      <c r="AL13" s="47" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Est!$E$2:$E$100,MATCH($A13,Raw_Est!$A$2:$A$100,0)),""))</f>
-        <v>11</v>
-      </c>
-      <c r="AM13" s="67" t="n">
+        <v/>
+      </c>
+      <c r="AM13" s="67" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A13,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="AN13" s="67" t="n">
+        <v/>
+      </c>
+      <c r="AN13" s="67" t="str">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A13,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46274</v>
-      </c>
-      <c r="AO13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AO13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A13)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
-        <v>0.0778103242070686</v>
-      </c>
-      <c r="AP13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AP13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,9))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A13)*(Raw_Q!$R$2:$R$600&gt;=5)*(Raw_Q!$R$2:$R$600&lt;=8)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,9))/2)),""))</f>
-        <v>0.0175261878892471</v>
-      </c>
-      <c r="AQ13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AQ13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,9),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,13))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A13)*(Raw_Q!$R$2:$R$600&gt;=9)*(Raw_Q!$R$2:$R$600&lt;=12)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,9)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,13))/2)),""))</f>
-        <v>0.00432562031280168</v>
-      </c>
-      <c r="AR13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AR13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,13),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,17))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A13)*(Raw_Q!$R$2:$R$600&gt;=13)*(Raw_Q!$R$2:$R$600&lt;=16)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,13)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,17))/2)),""))</f>
-        <v>0.108983567807926</v>
-      </c>
-      <c r="AS13" s="49" t="n">
+        <v/>
+      </c>
+      <c r="AS13" s="49" t="str">
         <f aca="false">IF($A13="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,17),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,21))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A13)*(Raw_Q!$R$2:$R$600&gt;=17)*(Raw_Q!$R$2:$R$600&lt;=20)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,17)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,21))/2)),""))</f>
-        <v>0.223442594510187</v>
+        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12727,7 +12716,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>
@@ -12756,78 +12745,78 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B4" s="83" t="n">
         <v>24</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B5" s="83" t="n">
         <v>20</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B6" s="84" t="n">
         <v>0.05</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B7" s="83" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B8" s="83" t="n">
         <v>365</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -14183,7 +14172,7 @@
       </c>
       <c r="C13" s="16" t="str">
         <f aca="false">IF(Calc!$A$12="","",Calc!C$12)</f>
-        <v>池子</v>
+        <v>基本面not good</v>
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">IF(Calc!$A$12="","",Calc!D$12)</f>
@@ -14303,109 +14292,109 @@
         <f aca="false">IF(Calc!$A$13="","",Calc!C$13)</f>
         <v>池子</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="17" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!D$13)</f>
-        <v>800</v>
-      </c>
-      <c r="E14" s="18" t="n">
+        <v/>
+      </c>
+      <c r="E14" s="18" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!J$13)</f>
-        <v>135.593220338983</v>
-      </c>
-      <c r="F14" s="18" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="F14" s="18" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!L$13)</f>
-        <v>37.1217639790339</v>
-      </c>
-      <c r="G14" s="17" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="G14" s="17" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!N$13)</f>
-        <v>0.349824726247696</v>
-      </c>
-      <c r="H14" s="17" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="H14" s="17" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!O$13)</f>
-        <v>0.247462453370294</v>
-      </c>
-      <c r="I14" s="19" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="I14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!Q$13)</f>
-        <v>0.0012502149125</v>
-      </c>
-      <c r="J14" s="19" t="n">
+        <v>不配息</v>
+      </c>
+      <c r="J14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!R$13)</f>
-        <v>6.40830892795208E-005</v>
-      </c>
-      <c r="K14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="K14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!T$13)</f>
-        <v>0.125285311570095</v>
-      </c>
-      <c r="L14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="L14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!U$13)</f>
-        <v>0.027149672411755</v>
-      </c>
-      <c r="M14" s="20" t="n">
+        <v/>
+      </c>
+      <c r="M14" s="20" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!V$13)</f>
-        <v>9.81356391583401</v>
+        <v/>
       </c>
       <c r="N14" s="21" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!W$13)</f>
-        <v>成長且加速</v>
-      </c>
-      <c r="O14" s="20" t="n">
+        <v/>
+      </c>
+      <c r="O14" s="20" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!X$13)</f>
-        <v>1.5771386330552</v>
-      </c>
-      <c r="P14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="P14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!S$13)</f>
-        <v>0.306630281963327</v>
-      </c>
-      <c r="Q14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!Y$13)</f>
-        <v>2.47297297297297</v>
-      </c>
-      <c r="R14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!I$13)</f>
-        <v>3.87603305785124</v>
-      </c>
-      <c r="S14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!Z$13)</f>
-        <v>0.222641906441857</v>
-      </c>
-      <c r="T14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="T14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AA$13)</f>
-        <v>0.285033485013648</v>
-      </c>
-      <c r="U14" s="22" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="22" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AB$13)</f>
-        <v>-623.915785717906</v>
-      </c>
-      <c r="V14" s="22" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="22" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AC$13)</f>
-        <v>501.715545944687</v>
-      </c>
-      <c r="W14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AF$13)</f>
-        <v>0.0778103242070686</v>
-      </c>
-      <c r="X14" s="19" t="n">
+        <v>N/M</v>
+      </c>
+      <c r="X14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AG$13)</f>
-        <v>0.0864176589454461</v>
-      </c>
-      <c r="Y14" s="19" t="n">
+        <v/>
+      </c>
+      <c r="Y14" s="19" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AH$13)</f>
-        <v>0.125444926089806</v>
+        <v>N/M</v>
       </c>
       <c r="Z14" s="17" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!AI$13)</f>
-        <v>3.18425</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="16" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AJ$13)</f>
-        <v>FY2026Q3E</v>
+        <v/>
       </c>
       <c r="AB14" s="16" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AK$13)</f>
-        <v>consensus</v>
-      </c>
-      <c r="AC14" s="23" t="n">
+        <v/>
+      </c>
+      <c r="AC14" s="23" t="str">
         <f aca="false">IF(Calc!$A$13="","",Calc!AM$13)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15465,36 +15454,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="57">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="53">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G22">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="54">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H22">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="54">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N22">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="54">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="59">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="55">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="59">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="55">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="60">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="56">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC22">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="61">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="57">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17751,7 +17740,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2631EAEF-C1A0-46DA-B455-5EE14F56B84E}</x14:id>
+          <x14:id>{B1FE44B1-3661-41B7-9110-E080C0919635}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -17767,16 +17756,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="54">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="59">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="55">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="59">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="55">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="60">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="56">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17817,47 +17806,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="58">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17882,7 +17871,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2631EAEF-C1A0-46DA-B455-5EE14F56B84E}">
+          <x14:cfRule type="dataBar" id="{B1FE44B1-3661-41B7-9110-E080C0919635}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18423,7 +18412,7 @@
       </c>
       <c r="B15" s="47" t="n">
         <f aca="false">IF($A15="","",COUNTIFS(Raw_Q!$A$2:$A$600,$A15,Raw_Q!$F$2:$F$600,"N"))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C15" s="47" t="n">
         <f aca="false">IF($A15="","",Config!$B$4)</f>
@@ -18431,31 +18420,31 @@
       </c>
       <c r="D15" s="67" t="n">
         <f aca="false">IF($A15="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,$B15),""))</f>
-        <v>44104</v>
+        <v>0</v>
       </c>
       <c r="E15" s="67" t="n">
         <f aca="false">IF($A15="","",IFERROR(SUMIFS(Raw_Q!$E$2:$E$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,1),""))</f>
-        <v>46203</v>
+        <v>0</v>
       </c>
       <c r="F15" s="66" t="str">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Q!$B$2:$B$600,MATCH($A15&amp;"|"&amp;0,Raw_Q!$S$2:$S$600,0)),""))</f>
-        <v>FY2026Q3E</v>
-      </c>
-      <c r="G15" s="67" t="n">
+        <v/>
+      </c>
+      <c r="G15" s="67" t="str">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A15,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="47" t="n">
+        <v/>
+      </c>
+      <c r="H15" s="47" t="str">
         <f aca="true">IF($A15="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A15,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
-      </c>
-      <c r="I15" s="67" t="n">
+        <v/>
+      </c>
+      <c r="I15" s="67" t="str">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A15,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46274</v>
+        <v/>
       </c>
       <c r="J15" s="72" t="str">
         <f aca="true">IF($A15="","",IF($B15=0,"未抓取",IF($B15&lt;$C15,"需補歷史 ("&amp;($C15-$B15)&amp;" 季)",IF(TODAY()&gt;$G15,"待更新財報","OK"))))</f>
-        <v>待更新財報</v>
+        <v>未抓取</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18801,18 +18790,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J23">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="63">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="59">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="64">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="60">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="65">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="61">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="66">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="62">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19073,15 +19062,13 @@
         <v>181</v>
       </c>
       <c r="D12" s="74" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="E12" s="73"/>
       <c r="F12" s="75" t="n">
         <v>46274</v>
       </c>
-      <c r="G12" s="74" t="s">
-        <v>201</v>
-      </c>
+      <c r="G12" s="73"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="73" t="s">
@@ -30882,7 +30869,7 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B201" s="76" t="s">
         <v>223</v>
@@ -30909,7 +30896,7 @@
       <c r="J201" s="79"/>
       <c r="K201" s="79"/>
       <c r="L201" s="80" t="n">
-        <v>3.18425</v>
+        <v>0.19</v>
       </c>
       <c r="M201" s="79"/>
       <c r="N201" s="79"/>
@@ -30920,12 +30907,12 @@
         <v>0</v>
       </c>
       <c r="S201" s="66" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B202" s="76" t="s">
         <v>228</v>
@@ -30949,42 +30936,42 @@
         <v>226</v>
       </c>
       <c r="I202" s="79" t="n">
-        <v>12496.254</v>
+        <v>429.188</v>
       </c>
       <c r="J202" s="79" t="n">
-        <v>3260.82</v>
+        <v>0.979</v>
       </c>
       <c r="K202" s="79" t="n">
-        <v>1310553000</v>
+        <v>-24861000</v>
       </c>
       <c r="L202" s="80" t="n">
-        <v>2.57</v>
+        <v>-0.22</v>
       </c>
       <c r="M202" s="79" t="n">
-        <v>526.9104</v>
+        <v>113.6406</v>
       </c>
       <c r="N202" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O202" s="79" t="n">
-        <v>44466.694</v>
+        <v>5717.152</v>
       </c>
       <c r="P202" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q202" s="80" t="n">
-        <v>891</v>
+        <v>578</v>
       </c>
       <c r="R202" s="47" t="n">
         <v>1</v>
       </c>
       <c r="S202" s="66" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B203" s="76" t="s">
         <v>232</v>
@@ -31008,42 +30995,42 @@
         <v>226</v>
       </c>
       <c r="I203" s="79" t="n">
-        <v>11104.965</v>
+        <v>381.969</v>
       </c>
       <c r="J203" s="79" t="n">
-        <v>2349.499</v>
+        <v>7.197</v>
       </c>
       <c r="K203" s="79" t="n">
-        <v>549232000</v>
+        <v>-107036000</v>
       </c>
       <c r="L203" s="80" t="n">
-        <v>1.17</v>
+        <v>-0.98</v>
       </c>
       <c r="M203" s="79" t="n">
-        <v>526.9158</v>
+        <v>113.6406</v>
       </c>
       <c r="N203" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O203" s="79" t="n">
-        <v>43152.823</v>
+        <v>5734.096</v>
       </c>
       <c r="P203" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q203" s="80" t="n">
-        <v>313</v>
+        <v>550</v>
       </c>
       <c r="R203" s="47" t="n">
         <v>2</v>
       </c>
       <c r="S203" s="66" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B204" s="76" t="s">
         <v>234</v>
@@ -31067,42 +31054,42 @@
         <v>226</v>
       </c>
       <c r="I204" s="79" t="n">
-        <v>10811.438</v>
+        <v>390.774</v>
       </c>
       <c r="J204" s="79" t="n">
-        <v>2393.395</v>
+        <v>48.559</v>
       </c>
       <c r="K204" s="79" t="n">
-        <v>642333000</v>
+        <v>-22365000</v>
       </c>
       <c r="L204" s="80" t="n">
-        <v>1.41</v>
+        <v>-0.21</v>
       </c>
       <c r="M204" s="79" t="n">
-        <v>456.792</v>
+        <v>103.6406</v>
       </c>
       <c r="N204" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O204" s="79" t="n">
-        <v>32731.765</v>
+        <v>2549.092</v>
       </c>
       <c r="P204" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q204" s="80" t="n">
-        <v>159</v>
+        <v>457.5</v>
       </c>
       <c r="R204" s="47" t="n">
         <v>3</v>
       </c>
       <c r="S204" s="66" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B205" s="76" t="s">
         <v>236</v>
@@ -31126,42 +31113,42 @@
         <v>226</v>
       </c>
       <c r="I205" s="79" t="n">
-        <v>10356.188</v>
+        <v>507.741</v>
       </c>
       <c r="J205" s="79" t="n">
-        <v>1963.707</v>
+        <v>120.893</v>
       </c>
       <c r="K205" s="79" t="n">
-        <v>339339000</v>
+        <v>20579000</v>
       </c>
       <c r="L205" s="80" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
       <c r="M205" s="79" t="n">
-        <v>456.8127</v>
+        <v>103.6406</v>
       </c>
       <c r="N205" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O205" s="79" t="n">
-        <v>32008.425</v>
+        <v>2562.064</v>
       </c>
       <c r="P205" s="80" t="n">
-        <v>1.00017193</v>
+        <v>0</v>
       </c>
       <c r="Q205" s="80" t="n">
-        <v>107.5</v>
+        <v>354.5</v>
       </c>
       <c r="R205" s="47" t="n">
         <v>4</v>
       </c>
       <c r="S205" s="66" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B206" s="76" t="s">
         <v>238</v>
@@ -31185,42 +31172,42 @@
         <v>226</v>
       </c>
       <c r="I206" s="79" t="n">
-        <v>9563.726</v>
+        <v>582.076</v>
       </c>
       <c r="J206" s="79" t="n">
-        <v>2015.768</v>
+        <v>114.919</v>
       </c>
       <c r="K206" s="79" t="n">
-        <v>338192000</v>
+        <v>16870000</v>
       </c>
       <c r="L206" s="80" t="n">
-        <v>0.74</v>
+        <v>0.16</v>
       </c>
       <c r="M206" s="79" t="n">
-        <v>456.5709</v>
+        <v>103.6406</v>
       </c>
       <c r="N206" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O206" s="79" t="n">
-        <v>31547.318</v>
+        <v>2522.912</v>
       </c>
       <c r="P206" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q206" s="80" t="n">
-        <v>83.7</v>
+        <v>273.5</v>
       </c>
       <c r="R206" s="47" t="n">
         <v>5</v>
       </c>
       <c r="S206" s="66" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B207" s="76" t="s">
         <v>240</v>
@@ -31244,42 +31231,42 @@
         <v>226</v>
       </c>
       <c r="I207" s="79" t="n">
-        <v>8619.744</v>
+        <v>411.403</v>
       </c>
       <c r="J207" s="79" t="n">
-        <v>1941.539</v>
+        <v>70.544</v>
       </c>
       <c r="K207" s="79" t="n">
-        <v>276072000</v>
+        <v>1110000</v>
       </c>
       <c r="L207" s="80" t="n">
-        <v>0.61</v>
+        <v>0.01</v>
       </c>
       <c r="M207" s="79" t="n">
-        <v>456.6072</v>
+        <v>103.6406</v>
       </c>
       <c r="N207" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O207" s="79" t="n">
-        <v>31519.108</v>
+        <v>2522.837</v>
       </c>
       <c r="P207" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q207" s="80" t="n">
-        <v>81</v>
+        <v>246.5</v>
       </c>
       <c r="R207" s="47" t="n">
         <v>6</v>
       </c>
       <c r="S207" s="66" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B208" s="76" t="s">
         <v>242</v>
@@ -31303,42 +31290,42 @@
         <v>226</v>
       </c>
       <c r="I208" s="79" t="n">
-        <v>8042.993</v>
+        <v>359.876</v>
       </c>
       <c r="J208" s="79" t="n">
-        <v>2246.342</v>
+        <v>33.397</v>
       </c>
       <c r="K208" s="79" t="n">
-        <v>-249438000</v>
+        <v>-30788000</v>
       </c>
       <c r="L208" s="80" t="n">
-        <v>-0.55</v>
+        <v>-0.31</v>
       </c>
       <c r="M208" s="79" t="n">
-        <v>456.6494</v>
+        <v>103.6406</v>
       </c>
       <c r="N208" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O208" s="79" t="n">
-        <v>31652.295</v>
+        <v>2530.636</v>
       </c>
       <c r="P208" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q208" s="80" t="n">
-        <v>101</v>
+        <v>247.5</v>
       </c>
       <c r="R208" s="47" t="n">
         <v>7</v>
       </c>
       <c r="S208" s="66" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B209" s="76" t="s">
         <v>244</v>
@@ -31362,42 +31349,42 @@
         <v>226</v>
       </c>
       <c r="I209" s="79" t="n">
-        <v>8197.12</v>
+        <v>382.698</v>
       </c>
       <c r="J209" s="79" t="n">
-        <v>2407.521</v>
+        <v>54.205</v>
       </c>
       <c r="K209" s="79" t="n">
-        <v>185268000</v>
+        <v>-14773000</v>
       </c>
       <c r="L209" s="80" t="n">
-        <v>0.41</v>
+        <v>-0.14</v>
       </c>
       <c r="M209" s="79" t="n">
-        <v>456.6591</v>
+        <v>103.6406</v>
       </c>
       <c r="N209" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O209" s="79" t="n">
-        <v>31844.519</v>
+        <v>2606.362</v>
       </c>
       <c r="P209" s="80" t="n">
-        <v>1.00010784</v>
+        <v>0</v>
       </c>
       <c r="Q209" s="80" t="n">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="R209" s="47" t="n">
         <v>8</v>
       </c>
       <c r="S209" s="66" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B210" s="76" t="s">
         <v>246</v>
@@ -31421,42 +31408,42 @@
         <v>226</v>
       </c>
       <c r="I210" s="79" t="n">
-        <v>7300.482</v>
+        <v>352.765</v>
       </c>
       <c r="J210" s="79" t="n">
-        <v>2123.917</v>
+        <v>70.385</v>
       </c>
       <c r="K210" s="79" t="n">
-        <v>88558000</v>
+        <v>25562000</v>
       </c>
       <c r="L210" s="80" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="M210" s="79" t="n">
-        <v>454.3741</v>
+        <v>103.6406</v>
       </c>
       <c r="N210" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O210" s="79" t="n">
-        <v>31497.301</v>
+        <v>2623.963</v>
       </c>
       <c r="P210" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q210" s="80" t="n">
-        <v>92.4</v>
+        <v>157</v>
       </c>
       <c r="R210" s="47" t="n">
         <v>9</v>
       </c>
       <c r="S210" s="66" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B211" s="76" t="s">
         <v>248</v>
@@ -31480,42 +31467,42 @@
         <v>226</v>
       </c>
       <c r="I211" s="79" t="n">
-        <v>6994.384</v>
+        <v>268.538</v>
       </c>
       <c r="J211" s="79" t="n">
-        <v>1889.945</v>
+        <v>21.169</v>
       </c>
       <c r="K211" s="79" t="n">
-        <v>24501000</v>
+        <v>-28273000</v>
       </c>
       <c r="L211" s="80" t="n">
-        <v>0.05</v>
+        <v>-0.29</v>
       </c>
       <c r="M211" s="79" t="n">
-        <v>454.4231</v>
+        <v>98.6406</v>
       </c>
       <c r="N211" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O211" s="79" t="n">
-        <v>31386.065</v>
+        <v>2060.341</v>
       </c>
       <c r="P211" s="80" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q211" s="80" t="n">
-        <v>98.7</v>
+        <v>96.2</v>
       </c>
       <c r="R211" s="47" t="n">
         <v>10</v>
       </c>
       <c r="S211" s="66" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B212" s="76" t="s">
         <v>250</v>
@@ -31539,42 +31526,42 @@
         <v>226</v>
       </c>
       <c r="I212" s="79" t="n">
-        <v>7489.463</v>
+        <v>337.273</v>
       </c>
       <c r="J212" s="79" t="n">
-        <v>2311.784</v>
+        <v>46.849</v>
       </c>
       <c r="K212" s="79" t="n">
-        <v>363384000</v>
+        <v>-7518000</v>
       </c>
       <c r="L212" s="80" t="n">
-        <v>0.81</v>
+        <v>-0.09</v>
       </c>
       <c r="M212" s="79" t="n">
-        <v>454.4231</v>
+        <v>98.6406</v>
       </c>
       <c r="N212" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O212" s="79" t="n">
-        <v>31694.889</v>
+        <v>2138.249</v>
       </c>
       <c r="P212" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q212" s="80" t="n">
-        <v>99.7</v>
+        <v>69.3</v>
       </c>
       <c r="R212" s="47" t="n">
         <v>11</v>
       </c>
       <c r="S212" s="66" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B213" s="76" t="s">
         <v>252</v>
@@ -31598,42 +31585,42 @@
         <v>226</v>
       </c>
       <c r="I213" s="79" t="n">
-        <v>6045.775</v>
+        <v>328.229</v>
       </c>
       <c r="J213" s="79" t="n">
-        <v>1364.149</v>
+        <v>63.443</v>
       </c>
       <c r="K213" s="79" t="n">
-        <v>-343033000</v>
+        <v>292000</v>
       </c>
       <c r="L213" s="80" t="n">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="M213" s="79" t="n">
-        <v>454.4671</v>
+        <v>88.6406</v>
       </c>
       <c r="N213" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O213" s="79" t="n">
-        <v>31453.101</v>
+        <v>1618.138</v>
       </c>
       <c r="P213" s="80" t="n">
-        <v>6.47563615</v>
+        <v>0</v>
       </c>
       <c r="Q213" s="80" t="n">
-        <v>108.5</v>
+        <v>73.9</v>
       </c>
       <c r="R213" s="47" t="n">
         <v>12</v>
       </c>
       <c r="S213" s="66" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B214" s="76" t="s">
         <v>254</v>
@@ -31657,42 +31644,42 @@
         <v>226</v>
       </c>
       <c r="I214" s="79" t="n">
-        <v>6462.205</v>
+        <v>284.079</v>
       </c>
       <c r="J214" s="79" t="n">
-        <v>1480.509</v>
+        <v>20.57</v>
       </c>
       <c r="K214" s="79" t="n">
-        <v>19151000</v>
+        <v>-14707000</v>
       </c>
       <c r="L214" s="80" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="M214" s="79" t="n">
-        <v>454.4991</v>
+        <v>88.6274</v>
       </c>
       <c r="N214" s="79" t="n">
-        <v>24500</v>
+        <v>0</v>
       </c>
       <c r="O214" s="79" t="n">
-        <v>31515.021</v>
+        <v>1608.276</v>
       </c>
       <c r="P214" s="80" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q214" s="80" t="n">
-        <v>116.5</v>
+        <v>41.6</v>
       </c>
       <c r="R214" s="47" t="n">
         <v>13</v>
       </c>
       <c r="S214" s="66" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B215" s="76" t="s">
         <v>256</v>
@@ -31716,42 +31703,42 @@
         <v>226</v>
       </c>
       <c r="I215" s="79" t="n">
-        <v>6834.744</v>
+        <v>322.164</v>
       </c>
       <c r="J215" s="79" t="n">
-        <v>1601.064</v>
+        <v>46.955</v>
       </c>
       <c r="K215" s="79" t="n">
-        <v>8014000</v>
+        <v>33991000</v>
       </c>
       <c r="L215" s="80" t="n">
-        <v>0.02</v>
+        <v>0.38</v>
       </c>
       <c r="M215" s="79" t="n">
-        <v>454.2191</v>
+        <v>88.3366</v>
       </c>
       <c r="N215" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O215" s="79" t="n">
-        <v>31541.256</v>
+        <v>1648.698</v>
       </c>
       <c r="P215" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q215" s="80" t="n">
-        <v>116</v>
+        <v>25.95</v>
       </c>
       <c r="R215" s="47" t="n">
         <v>14</v>
       </c>
       <c r="S215" s="66" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B216" s="76" t="s">
         <v>258</v>
@@ -31775,42 +31762,42 @@
         <v>226</v>
       </c>
       <c r="I216" s="79" t="n">
-        <v>8614.195</v>
+        <v>328.101</v>
       </c>
       <c r="J216" s="79" t="n">
-        <v>3598.905</v>
+        <v>59.018</v>
       </c>
       <c r="K216" s="79" t="n">
-        <v>1191084000</v>
+        <v>20197000</v>
       </c>
       <c r="L216" s="80" t="n">
-        <v>2.64</v>
+        <v>0.23</v>
       </c>
       <c r="M216" s="79" t="n">
-        <v>452.7761</v>
+        <v>88.3366</v>
       </c>
       <c r="N216" s="79" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="O216" s="79" t="n">
-        <v>34321.7</v>
+        <v>1660.503</v>
       </c>
       <c r="P216" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q216" s="80" t="n">
-        <v>104.5</v>
+        <v>22.7</v>
       </c>
       <c r="R216" s="47" t="n">
         <v>15</v>
       </c>
       <c r="S216" s="66" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B217" s="76" t="s">
         <v>260</v>
@@ -31834,42 +31821,42 @@
         <v>226</v>
       </c>
       <c r="I217" s="79" t="n">
-        <v>11544.421</v>
+        <v>432.414</v>
       </c>
       <c r="J217" s="79" t="n">
-        <v>4497.867</v>
+        <v>71.477</v>
       </c>
       <c r="K217" s="79" t="n">
-        <v>2160635000</v>
+        <v>22679000</v>
       </c>
       <c r="L217" s="80" t="n">
-        <v>4.79</v>
+        <v>0.26</v>
       </c>
       <c r="M217" s="79" t="n">
-        <v>452.7761</v>
+        <v>88.3366</v>
       </c>
       <c r="N217" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O217" s="79" t="n">
-        <v>33123.402</v>
+        <v>1631.994</v>
       </c>
       <c r="P217" s="80" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q217" s="80" t="n">
-        <v>93</v>
+        <v>23.3</v>
       </c>
       <c r="R217" s="47" t="n">
         <v>16</v>
       </c>
       <c r="S217" s="66" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B218" s="76" t="s">
         <v>262</v>
@@ -31893,42 +31880,42 @@
         <v>226</v>
       </c>
       <c r="I218" s="79" t="n">
-        <v>11453.611</v>
+        <v>421.858</v>
       </c>
       <c r="J218" s="79" t="n">
-        <v>4249.263</v>
+        <v>72.099</v>
       </c>
       <c r="K218" s="79" t="n">
-        <v>2095669000</v>
+        <v>7273000</v>
       </c>
       <c r="L218" s="80" t="n">
-        <v>4.65</v>
+        <v>0.08</v>
       </c>
       <c r="M218" s="79" t="n">
-        <v>450.8441</v>
+        <v>88.3146</v>
       </c>
       <c r="N218" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O218" s="79" t="n">
-        <v>30721.715</v>
+        <v>1607.118</v>
       </c>
       <c r="P218" s="80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q218" s="80" t="n">
-        <v>142.5</v>
+        <v>23.55</v>
       </c>
       <c r="R218" s="47" t="n">
         <v>17</v>
       </c>
       <c r="S218" s="66" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B219" s="76" t="s">
         <v>264</v>
@@ -31952,42 +31939,42 @@
         <v>226</v>
       </c>
       <c r="I219" s="79" t="n">
-        <v>10014.259</v>
+        <v>438.286</v>
       </c>
       <c r="J219" s="79" t="n">
-        <v>3522.28</v>
+        <v>94.536</v>
       </c>
       <c r="K219" s="79" t="n">
-        <v>1529404000</v>
+        <v>-3128000</v>
       </c>
       <c r="L219" s="80" t="n">
-        <v>3.39</v>
+        <v>-0.04</v>
       </c>
       <c r="M219" s="79" t="n">
-        <v>450.8441</v>
+        <v>88.3146</v>
       </c>
       <c r="N219" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O219" s="79" t="n">
-        <v>28671.921</v>
+        <v>1617.177</v>
       </c>
       <c r="P219" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q219" s="80" t="n">
-        <v>194.5</v>
+        <v>30.6</v>
       </c>
       <c r="R219" s="47" t="n">
         <v>18</v>
       </c>
       <c r="S219" s="66" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B220" s="76" t="s">
         <v>266</v>
@@ -32011,42 +31998,42 @@
         <v>226</v>
       </c>
       <c r="I220" s="79" t="n">
-        <v>9953.739</v>
+        <v>553.177</v>
       </c>
       <c r="J220" s="79" t="n">
-        <v>3341.276</v>
+        <v>149.828</v>
       </c>
       <c r="K220" s="79" t="n">
-        <v>1363132000</v>
+        <v>41027000</v>
       </c>
       <c r="L220" s="80" t="n">
-        <v>3.02</v>
+        <v>0.47</v>
       </c>
       <c r="M220" s="79" t="n">
-        <v>450.8441</v>
+        <v>88.2731</v>
       </c>
       <c r="N220" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O220" s="79" t="n">
-        <v>29069.332</v>
+        <v>1750.967</v>
       </c>
       <c r="P220" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q220" s="80" t="n">
-        <v>233</v>
+        <v>33.4</v>
       </c>
       <c r="R220" s="47" t="n">
         <v>19</v>
       </c>
       <c r="S220" s="66" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B221" s="76" t="s">
         <v>268</v>
@@ -32070,42 +32057,42 @@
         <v>226</v>
       </c>
       <c r="I221" s="79" t="n">
-        <v>9767.683</v>
+        <v>652.042</v>
       </c>
       <c r="J221" s="79" t="n">
-        <v>3221.739</v>
+        <v>191.472</v>
       </c>
       <c r="K221" s="79" t="n">
-        <v>1384821000</v>
+        <v>130574000</v>
       </c>
       <c r="L221" s="80" t="n">
-        <v>3.07</v>
+        <v>1.5</v>
       </c>
       <c r="M221" s="79" t="n">
-        <v>450.8441</v>
+        <v>87.1279</v>
       </c>
       <c r="N221" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O221" s="79" t="n">
-        <v>27674.388</v>
+        <v>1717.167</v>
       </c>
       <c r="P221" s="80" t="n">
-        <v>1.00000735</v>
+        <v>0</v>
       </c>
       <c r="Q221" s="80" t="n">
-        <v>202</v>
+        <v>27.65</v>
       </c>
       <c r="R221" s="47" t="n">
         <v>20</v>
       </c>
       <c r="S221" s="66" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B222" s="76" t="s">
         <v>270</v>
@@ -32129,42 +32116,42 @@
         <v>226</v>
       </c>
       <c r="I222" s="79" t="n">
-        <v>8725.355</v>
+        <v>416.845</v>
       </c>
       <c r="J222" s="79" t="n">
-        <v>2364.625</v>
+        <v>70.15</v>
       </c>
       <c r="K222" s="79" t="n">
-        <v>852908000</v>
+        <v>28098000</v>
       </c>
       <c r="L222" s="80" t="n">
-        <v>1.89</v>
+        <v>0.32</v>
       </c>
       <c r="M222" s="79" t="n">
-        <v>450.8441</v>
+        <v>87.0739</v>
       </c>
       <c r="N222" s="79" t="n">
         <v>0</v>
       </c>
       <c r="O222" s="79" t="n">
-        <v>26298.99</v>
+        <v>1594.253</v>
       </c>
       <c r="P222" s="80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q222" s="80" t="n">
-        <v>135</v>
+        <v>25.15</v>
       </c>
       <c r="R222" s="47" t="n">
         <v>21</v>
       </c>
       <c r="S222" s="66" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B223" s="76" t="s">
         <v>272</v>
@@ -32188,42 +32175,42 @@
         <v>226</v>
       </c>
       <c r="I223" s="79" t="n">
-        <v>7225.986</v>
+        <v>366.205</v>
       </c>
       <c r="J223" s="79" t="n">
-        <v>1598.205</v>
+        <v>43.196</v>
       </c>
       <c r="K223" s="79" t="n">
-        <v>258123000</v>
+        <v>1945000</v>
       </c>
       <c r="L223" s="80" t="n">
-        <v>0.57</v>
+        <v>0.02</v>
       </c>
       <c r="M223" s="79" t="n">
-        <v>450.8473</v>
+        <v>87.0739</v>
       </c>
       <c r="N223" s="79" t="n">
-        <v>3315</v>
+        <v>0</v>
       </c>
       <c r="O223" s="79" t="n">
-        <v>25467.585</v>
+        <v>1571.599</v>
       </c>
       <c r="P223" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q223" s="80" t="n">
-        <v>112</v>
+        <v>27.1</v>
       </c>
       <c r="R223" s="47" t="n">
         <v>22</v>
       </c>
       <c r="S223" s="66" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B224" s="76" t="s">
         <v>274</v>
@@ -32247,42 +32234,42 @@
         <v>226</v>
       </c>
       <c r="I224" s="79" t="n">
-        <v>7548.022</v>
+        <v>407.008</v>
       </c>
       <c r="J224" s="79" t="n">
-        <v>1814.825</v>
+        <v>72.485</v>
       </c>
       <c r="K224" s="79" t="n">
-        <v>169978000</v>
+        <v>-33792000</v>
       </c>
       <c r="L224" s="80" t="n">
-        <v>0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="M224" s="79" t="n">
-        <v>450.8625</v>
+        <v>91.0739</v>
       </c>
       <c r="N224" s="79" t="n">
-        <v>14265</v>
+        <v>4000000</v>
       </c>
       <c r="O224" s="79" t="n">
-        <v>25669.652</v>
+        <v>1655.427</v>
       </c>
       <c r="P224" s="80" t="n">
         <v>0</v>
       </c>
       <c r="Q224" s="80" t="n">
-        <v>80.9</v>
+        <v>28.45</v>
       </c>
       <c r="R224" s="47" t="n">
         <v>23</v>
       </c>
       <c r="S224" s="66" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B225" s="76" t="s">
         <v>276</v>
@@ -32306,35 +32293,35 @@
         <v>226</v>
       </c>
       <c r="I225" s="79" t="n">
-        <v>6871.934</v>
+        <v>410.473</v>
       </c>
       <c r="J225" s="79" t="n">
-        <v>1435.581</v>
+        <v>63.59</v>
       </c>
       <c r="K225" s="79" t="n">
-        <v>59154000</v>
+        <v>46660000</v>
       </c>
       <c r="L225" s="80" t="n">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
       <c r="M225" s="79" t="n">
-        <v>450.8753</v>
+        <v>90.7432</v>
       </c>
       <c r="N225" s="79" t="n">
-        <v>11670</v>
+        <v>4000000</v>
       </c>
       <c r="O225" s="79" t="n">
-        <v>25481.078</v>
+        <v>1702.503</v>
       </c>
       <c r="P225" s="80"/>
       <c r="Q225" s="80" t="n">
-        <v>65.9</v>
+        <v>26.15</v>
       </c>
       <c r="R225" s="47" t="n">
         <v>24</v>
       </c>
       <c r="S225" s="66" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32377,7 +32364,7 @@
         <v>0</v>
       </c>
       <c r="S226" s="66" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32436,7 +32423,7 @@
         <v>1</v>
       </c>
       <c r="S227" s="66" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32495,7 +32482,7 @@
         <v>2</v>
       </c>
       <c r="S228" s="66" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32554,7 +32541,7 @@
         <v>3</v>
       </c>
       <c r="S229" s="66" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32613,7 +32600,7 @@
         <v>4</v>
       </c>
       <c r="S230" s="66" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32672,7 +32659,7 @@
         <v>5</v>
       </c>
       <c r="S231" s="66" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32731,7 +32718,7 @@
         <v>6</v>
       </c>
       <c r="S232" s="66" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32790,7 +32777,7 @@
         <v>7</v>
       </c>
       <c r="S233" s="66" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32849,7 +32836,7 @@
         <v>8</v>
       </c>
       <c r="S234" s="66" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32908,7 +32895,7 @@
         <v>9</v>
       </c>
       <c r="S235" s="66" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32967,7 +32954,7 @@
         <v>10</v>
       </c>
       <c r="S236" s="66" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33026,7 +33013,7 @@
         <v>11</v>
       </c>
       <c r="S237" s="66" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33085,7 +33072,7 @@
         <v>12</v>
       </c>
       <c r="S238" s="66" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33144,7 +33131,7 @@
         <v>13</v>
       </c>
       <c r="S239" s="66" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33203,7 +33190,7 @@
         <v>14</v>
       </c>
       <c r="S240" s="66" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33262,7 +33249,7 @@
         <v>15</v>
       </c>
       <c r="S241" s="66" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33321,7 +33308,7 @@
         <v>16</v>
       </c>
       <c r="S242" s="66" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33380,7 +33367,7 @@
         <v>17</v>
       </c>
       <c r="S243" s="66" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33439,7 +33426,7 @@
         <v>18</v>
       </c>
       <c r="S244" s="66" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33498,7 +33485,7 @@
         <v>19</v>
       </c>
       <c r="S245" s="66" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33557,7 +33544,7 @@
         <v>20</v>
       </c>
       <c r="S246" s="66" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33616,7 +33603,7 @@
         <v>21</v>
       </c>
       <c r="S247" s="66" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33675,7 +33662,7 @@
         <v>22</v>
       </c>
       <c r="S248" s="66" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33734,7 +33721,7 @@
         <v>23</v>
       </c>
       <c r="S249" s="66" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33791,7 +33778,7 @@
         <v>24</v>
       </c>
       <c r="S250" s="66" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33834,7 +33821,7 @@
         <v>0</v>
       </c>
       <c r="S251" s="66" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33893,7 +33880,7 @@
         <v>1</v>
       </c>
       <c r="S252" s="66" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33952,7 +33939,7 @@
         <v>2</v>
       </c>
       <c r="S253" s="66" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34011,7 +33998,7 @@
         <v>3</v>
       </c>
       <c r="S254" s="66" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34070,7 +34057,7 @@
         <v>4</v>
       </c>
       <c r="S255" s="66" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34129,7 +34116,7 @@
         <v>5</v>
       </c>
       <c r="S256" s="66" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34188,7 +34175,7 @@
         <v>6</v>
       </c>
       <c r="S257" s="66" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34247,7 +34234,7 @@
         <v>7</v>
       </c>
       <c r="S258" s="66" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34306,7 +34293,7 @@
         <v>8</v>
       </c>
       <c r="S259" s="66" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34365,7 +34352,7 @@
         <v>9</v>
       </c>
       <c r="S260" s="66" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34424,7 +34411,7 @@
         <v>10</v>
       </c>
       <c r="S261" s="66" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34483,7 +34470,7 @@
         <v>11</v>
       </c>
       <c r="S262" s="66" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34542,7 +34529,7 @@
         <v>12</v>
       </c>
       <c r="S263" s="66" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34601,7 +34588,7 @@
         <v>13</v>
       </c>
       <c r="S264" s="66" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34660,7 +34647,7 @@
         <v>14</v>
       </c>
       <c r="S265" s="66" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34719,7 +34706,7 @@
         <v>15</v>
       </c>
       <c r="S266" s="66" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34778,7 +34765,7 @@
         <v>16</v>
       </c>
       <c r="S267" s="66" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34837,7 +34824,7 @@
         <v>17</v>
       </c>
       <c r="S268" s="66" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34896,7 +34883,7 @@
         <v>18</v>
       </c>
       <c r="S269" s="66" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34955,7 +34942,7 @@
         <v>19</v>
       </c>
       <c r="S270" s="66" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35014,7 +35001,7 @@
         <v>20</v>
       </c>
       <c r="S271" s="66" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35073,7 +35060,7 @@
         <v>21</v>
       </c>
       <c r="S272" s="66" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35132,7 +35119,7 @@
         <v>22</v>
       </c>
       <c r="S273" s="66" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35191,7 +35178,7 @@
         <v>23</v>
       </c>
       <c r="S274" s="66" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35248,7 +35235,7 @@
         <v>24</v>
       </c>
       <c r="S275" s="66" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35291,7 +35278,7 @@
         <v>0</v>
       </c>
       <c r="S276" s="66" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35350,7 +35337,7 @@
         <v>1</v>
       </c>
       <c r="S277" s="66" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35409,7 +35396,7 @@
         <v>2</v>
       </c>
       <c r="S278" s="66" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35468,7 +35455,7 @@
         <v>3</v>
       </c>
       <c r="S279" s="66" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35527,7 +35514,7 @@
         <v>4</v>
       </c>
       <c r="S280" s="66" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35586,7 +35573,7 @@
         <v>5</v>
       </c>
       <c r="S281" s="66" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35645,7 +35632,7 @@
         <v>6</v>
       </c>
       <c r="S282" s="66" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35704,7 +35691,7 @@
         <v>7</v>
       </c>
       <c r="S283" s="66" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35763,7 +35750,7 @@
         <v>8</v>
       </c>
       <c r="S284" s="66" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35822,7 +35809,7 @@
         <v>9</v>
       </c>
       <c r="S285" s="66" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35881,7 +35868,7 @@
         <v>10</v>
       </c>
       <c r="S286" s="66" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35940,7 +35927,7 @@
         <v>11</v>
       </c>
       <c r="S287" s="66" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35999,7 +35986,7 @@
         <v>12</v>
       </c>
       <c r="S288" s="66" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36058,7 +36045,7 @@
         <v>13</v>
       </c>
       <c r="S289" s="66" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36117,7 +36104,7 @@
         <v>14</v>
       </c>
       <c r="S290" s="66" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36176,7 +36163,7 @@
         <v>15</v>
       </c>
       <c r="S291" s="66" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36235,7 +36222,7 @@
         <v>16</v>
       </c>
       <c r="S292" s="66" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36294,7 +36281,7 @@
         <v>17</v>
       </c>
       <c r="S293" s="66" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36353,7 +36340,7 @@
         <v>18</v>
       </c>
       <c r="S294" s="66" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36412,7 +36399,7 @@
         <v>19</v>
       </c>
       <c r="S295" s="66" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36471,7 +36458,7 @@
         <v>20</v>
       </c>
       <c r="S296" s="66" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36530,7 +36517,7 @@
         <v>21</v>
       </c>
       <c r="S297" s="66" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36589,7 +36576,7 @@
         <v>22</v>
       </c>
       <c r="S298" s="66" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36648,7 +36635,7 @@
         <v>23</v>
       </c>
       <c r="S299" s="66" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36705,142 +36692,142 @@
         <v>24</v>
       </c>
       <c r="S300" s="66" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="81" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="42" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="82" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C304" s="24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="82" t="s">
+        <v>557</v>
+      </c>
+      <c r="C305" s="24" t="s">
         <v>556</v>
-      </c>
-      <c r="C305" s="24" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="82" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C306" s="24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="82" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C307" s="24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="82" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C308" s="24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="82" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C309" s="24" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="82" t="s">
+        <v>563</v>
+      </c>
+      <c r="C310" s="24" t="s">
         <v>562</v>
-      </c>
-      <c r="C310" s="24" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="82" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C311" s="25" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="82" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C312" s="24" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="82" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C313" s="24" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="82" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C314" s="25" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="82" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C315" s="25" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="82" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C316" s="24" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="82" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C317" s="24" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="82" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C318" s="25" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="82" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C319" s="24" t="s">
         <v>47</v>
@@ -36848,15 +36835,15 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="82" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C320" s="24" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="24" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -36892,19 +36879,19 @@
         <v>155</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37061,19 +37048,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="76" t="s">
-        <v>202</v>
+        <v>452</v>
       </c>
       <c r="B10" s="80" t="n">
-        <v>10.58647</v>
+        <v>0.205</v>
       </c>
       <c r="C10" s="80" t="n">
-        <v>26.4672</v>
+        <v>16.925</v>
       </c>
       <c r="D10" s="78" t="n">
         <v>46387</v>
       </c>
       <c r="E10" s="77" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F10" s="78" t="n">
         <v>46274</v>
@@ -37141,7 +37128,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -3796,9 +3796,6 @@
     <t xml:space="preserve">南亞科</t>
   </si>
   <si>
-    <t xml:space="preserve">觀察</t>
-  </si>
-  <si>
     <t xml:space="preserve">DRAM</t>
   </si>
   <si>
@@ -3849,6 +3846,9 @@
   </si>
   <si>
     <t xml:space="preserve">電腦及週邊設備業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">觀察</t>
   </si>
   <si>
     <t xml:space="preserve">2455</t>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B15" s="80" t="n">
         <v>1355</v>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>131.507088876712</v>
+        <v>131.601786054795</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.7442366875822</v>
+        <v>18.7307488286949</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9666,7 +9666,7 @@
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.583747810238688</v>
+        <v>0.583327760693781</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C3" s="66" t="str">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Tickers!$D$2:$D$100,MATCH($A3,Tickers!$A$2:$A$100,0)),""))</f>
-        <v>觀察</v>
+        <v>核心</v>
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>88.9573638356164</v>
+        <v>89.045882739726</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>5.87922098238486</v>
+        <v>5.87337655496871</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.121281610308003</v>
+        <v>0.121161046449206</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>243.860235178082</v>
+        <v>243.42628769863</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>5.55646146658758</v>
+        <v>5.56636677497023</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.76712605479452</v>
+        <v>7.77680175342466</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>68.6225505083682</v>
+        <v>68.5371720791627</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>1.03544051408703</v>
+        <v>1.03415224537691</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>34.822704109589</v>
+        <v>34.8271415068493</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>15.5932749590942</v>
+        <v>15.5912881880705</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="H7" s="51" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>99.5641418356164</v>
+        <v>99.698874739726</v>
       </c>
       <c r="I7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="L7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(H7&lt;=0,"N/M",D7/H7),"N/M"))</f>
-        <v>19.8364588253147</v>
+        <v>19.8096518657401</v>
       </c>
       <c r="M7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="O7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(L7)),M7&lt;Config!$B$6),"N/M",L7/(M7*100)),"N/M"))</f>
-        <v>0.264653258449685</v>
+        <v>0.264295606448235</v>
       </c>
       <c r="P7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="H8" s="51" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>33.2149863013699</v>
+        <v>33.2255616438356</v>
       </c>
       <c r="I8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10746,7 +10746,7 @@
       </c>
       <c r="L8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(H8&lt;=0,"N/M",D8/H8),"N/M"))</f>
-        <v>16.1071871337167</v>
+        <v>16.1020603875709</v>
       </c>
       <c r="M8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="O8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(L8)),M8&lt;Config!$B$6),"N/M",L8/(M8*100)),"N/M"))</f>
-        <v>1.27480457755193</v>
+        <v>1.27439882082977</v>
       </c>
       <c r="P8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="H9" s="51" t="n">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>36.2021778630137</v>
+        <v>36.2114876164384</v>
       </c>
       <c r="I9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="L9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(H9&lt;=0,"N/M",D9/H9),"N/M"))</f>
-        <v>9.65411532208039</v>
+        <v>9.65163330769496</v>
       </c>
       <c r="M9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="O9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(OR(NOT(ISNUMBER(L9)),M9&lt;Config!$B$6),"N/M",L9/(M9*100)),"N/M"))</f>
-        <v>0.961874972302409</v>
+        <v>0.961627680091927</v>
       </c>
       <c r="P9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="H10" s="51" t="n">
         <f aca="true">IF($A10="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>452.720771945205</v>
+        <v>453.119410246575</v>
       </c>
       <c r="I10" s="49" t="n">
         <f aca="false">IF($A10="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L10" s="52" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(H10&lt;=0,"N/M",D10/H10),"N/M"))</f>
-        <v>27.3899515295508</v>
+        <v>27.3658548267713</v>
       </c>
       <c r="M10" s="49" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="O10" s="51" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(OR(NOT(ISNUMBER(L10)),M10&lt;Config!$B$6),"N/M",L10/(M10*100)),"N/M"))</f>
-        <v>0.663112995652017</v>
+        <v>0.662529612481433</v>
       </c>
       <c r="P10" s="51" t="n">
         <f aca="false">IF($A10="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="H11" s="51" t="n">
         <f aca="true">IF($A11="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>33.2809751780822</v>
+        <v>33.3346376986301</v>
       </c>
       <c r="I11" s="49" t="n">
         <f aca="false">IF($A11="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="L11" s="52" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(H11&lt;=0,"N/M",D11/H11),"N/M"))</f>
-        <v>85.634509949003</v>
+        <v>85.4966544339289</v>
       </c>
       <c r="M11" s="49" t="n">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="O11" s="51" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(OR(NOT(ISNUMBER(L11)),M11&lt;Config!$B$6),"N/M",L11/(M11*100)),"N/M"))</f>
-        <v>0.863830045031608</v>
+        <v>0.862439440521053</v>
       </c>
       <c r="P11" s="51" t="n">
         <f aca="false">IF($A11="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="H13" s="51" t="n">
         <f aca="true">IF($A13="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>21.5507000273973</v>
+        <v>21.5942088767123</v>
       </c>
       <c r="I13" s="49" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="L13" s="52" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(H13&lt;=0,"N/M",D13/H13),"N/M"))</f>
-        <v>37.6785904387194</v>
+        <v>37.602674153795</v>
       </c>
       <c r="M13" s="49" t="n">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="O13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(OR(NOT(ISNUMBER(L13)),M13&lt;Config!$B$6),"N/M",L13/(M13*100)),"N/M"))</f>
-        <v>0.251174390170848</v>
+        <v>0.250668314270771</v>
       </c>
       <c r="P13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="H14" s="51" t="n">
         <f aca="true">IF($A14="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>108.95104109589</v>
+        <v>109.137315068493</v>
       </c>
       <c r="I14" s="49" t="n">
         <f aca="false">IF($A14="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11838,7 +11838,7 @@
       </c>
       <c r="L14" s="52" t="n">
         <f aca="false">IF($A14="","",IFERROR(IF(H14&lt;=0,"N/M",D14/H14),"N/M"))</f>
-        <v>15.6033387372938</v>
+        <v>15.5767071870249</v>
       </c>
       <c r="M14" s="49" t="n">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="O14" s="51" t="n">
         <f aca="false">IF($A14="","",IFERROR(IF(OR(NOT(ISNUMBER(L14)),M14&lt;Config!$B$6),"N/M",L14/(M14*100)),"N/M"))</f>
-        <v>0.142309609516045</v>
+        <v>0.142066717556614</v>
       </c>
       <c r="P14" s="51" t="n">
         <f aca="false">IF($A14="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="H15" s="51" t="n">
         <f aca="true">IF($A15="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.13764506849315</v>
+        <v>7.13825219178082</v>
       </c>
       <c r="I15" s="49" t="n">
         <f aca="false">IF($A15="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="L15" s="52" t="n">
         <f aca="false">IF($A15="","",IFERROR(IF(H15&lt;=0,"N/M",D15/H15),"N/M"))</f>
-        <v>19.8244657225401</v>
+        <v>19.8227796102423</v>
       </c>
       <c r="M15" s="49" t="n">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.7442366875822</v>
+        <v>18.7307488286949</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.583747810238688</v>
+        <v>0.583327760693781</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="C4" s="16" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!C$3)</f>
-        <v>觀察</v>
+        <v>核心</v>
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>5.87922098238486</v>
+        <v>5.87337655496871</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.121281610308003</v>
+        <v>0.121161046449206</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>5.55646146658758</v>
+        <v>5.56636677497023</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>68.6225505083682</v>
+        <v>68.5371720791627</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>1.03544051408703</v>
+        <v>1.03415224537691</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>15.5932749590942</v>
+        <v>15.5912881880705</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
@@ -14127,7 +14127,7 @@
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!L$7)</f>
-        <v>19.8364588253147</v>
+        <v>19.8096518657401</v>
       </c>
       <c r="G8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!N$7)</f>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="H8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!O$7)</f>
-        <v>0.264653258449685</v>
+        <v>0.264295606448235</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!Q$7)</f>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!L$8)</f>
-        <v>16.1071871337167</v>
+        <v>16.1020603875709</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!N$8)</f>
@@ -14253,7 +14253,7 @@
       </c>
       <c r="H9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!O$8)</f>
-        <v>1.27480457755193</v>
+        <v>1.27439882082977</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!Q$8)</f>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!L$9)</f>
-        <v>9.65411532208039</v>
+        <v>9.65163330769496</v>
       </c>
       <c r="G10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!N$9)</f>
@@ -14371,7 +14371,7 @@
       </c>
       <c r="H10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!O$9)</f>
-        <v>0.961874972302409</v>
+        <v>0.961627680091927</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!Q$9)</f>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!L$10)</f>
-        <v>27.3899515295508</v>
+        <v>27.3658548267713</v>
       </c>
       <c r="G11" s="17" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!N$10)</f>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="H11" s="17" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!O$10)</f>
-        <v>0.663112995652017</v>
+        <v>0.662529612481433</v>
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!Q$10)</f>
@@ -14599,7 +14599,7 @@
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!L$11)</f>
-        <v>85.634509949003</v>
+        <v>85.4966544339289</v>
       </c>
       <c r="G12" s="17" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!N$11)</f>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="H12" s="17" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!O$11)</f>
-        <v>0.863830045031608</v>
+        <v>0.862439440521053</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!Q$11)</f>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!L$13)</f>
-        <v>37.6785904387194</v>
+        <v>37.602674153795</v>
       </c>
       <c r="G14" s="17" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!N$13)</f>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="H14" s="17" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!O$13)</f>
-        <v>0.251174390170848</v>
+        <v>0.250668314270771</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!Q$13)</f>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="F15" s="18" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!L$14)</f>
-        <v>15.6033387372938</v>
+        <v>15.5767071870249</v>
       </c>
       <c r="G15" s="17" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!N$14)</f>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="H15" s="17" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!O$14)</f>
-        <v>0.142309609516045</v>
+        <v>0.142066717556614</v>
       </c>
       <c r="I15" s="19" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!Q$14)</f>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">IF(Calc!$A$15="","",Calc!L$15)</f>
-        <v>19.8244657225401</v>
+        <v>19.8227796102423</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">IF(Calc!$A$15="","",Calc!N$15)</f>
@@ -18273,7 +18273,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6156C2F6-5FFD-4894-923B-61822BEB4198}</x14:id>
+          <x14:id>{F8F96085-6094-4B96-858A-A91F901CA14C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -18404,7 +18404,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6156C2F6-5FFD-4894-923B-61822BEB4198}">
+          <x14:cfRule type="dataBar" id="{F8F96085-6094-4B96-858A-A91F901CA14C}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18591,7 +18591,7 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18675,7 +18675,7 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18717,7 +18717,7 @@
       </c>
       <c r="H9" s="47" t="n">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A9,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18759,7 +18759,7 @@
       </c>
       <c r="H10" s="47" t="n">
         <f aca="true">IF($A10="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A10,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A10,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18801,7 +18801,7 @@
       </c>
       <c r="H11" s="47" t="n">
         <f aca="true">IF($A11="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A11,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I11" s="67" t="n">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A11,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="H12" s="47" t="n">
         <f aca="true">IF($A12="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A12,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I12" s="67" t="n">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A12,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18885,7 +18885,7 @@
       </c>
       <c r="H13" s="47" t="n">
         <f aca="true">IF($A13="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A13,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I13" s="67" t="n">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A13,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18927,7 +18927,7 @@
       </c>
       <c r="H14" s="47" t="n">
         <f aca="true">IF($A14="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A14,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I14" s="67" t="n">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A14,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="H15" s="47" t="n">
         <f aca="true">IF($A15="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A15,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I15" s="67" t="n">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A15,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -19011,7 +19011,7 @@
       </c>
       <c r="H16" s="47" t="n">
         <f aca="true">IF($A16="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A16,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I16" s="67" t="n">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A16,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -19053,7 +19053,7 @@
       </c>
       <c r="H17" s="47" t="n">
         <f aca="true">IF($A17="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A17,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46274</v>
+        <v>-46275</v>
       </c>
       <c r="I17" s="67" t="n">
         <f aca="false">IF($A17="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A17,Raw_Price!$A$2:$A$100,0)),""))</f>
@@ -19418,30 +19418,30 @@
         <v>169</v>
       </c>
       <c r="D3" s="74" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="73" t="s">
         <v>173</v>
-      </c>
-      <c r="E3" s="73" t="s">
-        <v>174</v>
       </c>
       <c r="F3" s="75" t="n">
         <v>46264</v>
       </c>
       <c r="G3" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="C4" s="74" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="D4" s="74" t="s">
         <v>178</v>
-      </c>
-      <c r="D4" s="74" t="s">
-        <v>173</v>
       </c>
       <c r="E4" s="73"/>
       <c r="F4" s="75" t="n">
@@ -40123,7 +40123,7 @@
     </row>
     <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B350" s="76" t="s">
         <v>228</v>
@@ -40166,7 +40166,7 @@
     </row>
     <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B351" s="76" t="s">
         <v>233</v>
@@ -40225,7 +40225,7 @@
     </row>
     <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B352" s="76" t="s">
         <v>237</v>
@@ -40284,7 +40284,7 @@
     </row>
     <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B353" s="76" t="s">
         <v>239</v>
@@ -40343,7 +40343,7 @@
     </row>
     <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B354" s="76" t="s">
         <v>241</v>
@@ -40402,7 +40402,7 @@
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B355" s="76" t="s">
         <v>243</v>
@@ -40461,7 +40461,7 @@
     </row>
     <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B356" s="76" t="s">
         <v>245</v>
@@ -40520,7 +40520,7 @@
     </row>
     <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B357" s="76" t="s">
         <v>247</v>
@@ -40579,7 +40579,7 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B358" s="76" t="s">
         <v>249</v>
@@ -40638,7 +40638,7 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B359" s="76" t="s">
         <v>251</v>
@@ -40697,7 +40697,7 @@
     </row>
     <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B360" s="76" t="s">
         <v>253</v>
@@ -40756,7 +40756,7 @@
     </row>
     <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B361" s="76" t="s">
         <v>255</v>
@@ -40815,7 +40815,7 @@
     </row>
     <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B362" s="76" t="s">
         <v>257</v>
@@ -40874,7 +40874,7 @@
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B363" s="76" t="s">
         <v>259</v>
@@ -40933,7 +40933,7 @@
     </row>
     <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B364" s="76" t="s">
         <v>261</v>
@@ -40992,7 +40992,7 @@
     </row>
     <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B365" s="76" t="s">
         <v>263</v>
@@ -41051,7 +41051,7 @@
     </row>
     <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B366" s="76" t="s">
         <v>265</v>
@@ -41110,7 +41110,7 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B367" s="76" t="s">
         <v>267</v>
@@ -41169,7 +41169,7 @@
     </row>
     <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B368" s="76" t="s">
         <v>269</v>
@@ -41228,7 +41228,7 @@
     </row>
     <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B369" s="76" t="s">
         <v>271</v>
@@ -41287,7 +41287,7 @@
     </row>
     <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B370" s="76" t="s">
         <v>273</v>
@@ -41346,7 +41346,7 @@
     </row>
     <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B371" s="76" t="s">
         <v>275</v>
@@ -41405,7 +41405,7 @@
     </row>
     <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B372" s="76" t="s">
         <v>277</v>
@@ -41464,7 +41464,7 @@
     </row>
     <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B373" s="76" t="s">
         <v>279</v>
@@ -41523,7 +41523,7 @@
     </row>
     <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B374" s="76" t="s">
         <v>281</v>
@@ -44963,7 +44963,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="76" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B16" s="80" t="n">
         <v>353.215</v>

--- a/台股觀察表.xlsx
+++ b/台股觀察表.xlsx
@@ -8683,7 +8683,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="87">
+  <dxfs count="89">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -8750,7 +8750,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FF7AC88E"/>
+          <fgColor rgb="FF79C88E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8758,7 +8758,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFA9DCB7"/>
+          <fgColor rgb="FFA8DBB6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8766,7 +8766,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFBBE3C5"/>
+          <fgColor rgb="FFBAE3C5"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8774,7 +8774,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDDF1E2"/>
+          <fgColor rgb="FFDCF1E1"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8782,7 +8782,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFE5F4E9"/>
+          <fgColor rgb="FFE4F4E8"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8798,7 +8798,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFEFF9F2"/>
+          <fgColor rgb="FFEFF9F1"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8806,7 +8806,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF1F9F3"/>
+          <fgColor rgb="FFF0F9F3"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8814,7 +8814,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF3FAF5"/>
+          <fgColor rgb="FFF2FAF4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -8886,6 +8886,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFDDF1E2"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFDFF2E4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -8926,6 +8934,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF1F9F3"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF8BCF9D"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -8959,6 +8975,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFCCEAD4"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE5F4E9"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -9095,14 +9119,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDCF1E2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE4F4E8"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -9997,14 +10013,14 @@
         <v>196</v>
       </c>
       <c r="B2" s="80" t="n">
-        <v>12600</v>
+        <v>12080</v>
       </c>
       <c r="C2" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D2" s="78"/>
       <c r="E2" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10012,14 +10028,14 @@
         <v>208</v>
       </c>
       <c r="B3" s="80" t="n">
-        <v>142.5</v>
+        <v>140.5</v>
       </c>
       <c r="C3" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D3" s="78"/>
       <c r="E3" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10027,14 +10043,14 @@
         <v>167</v>
       </c>
       <c r="B4" s="80" t="n">
-        <v>2450</v>
+        <v>2410</v>
       </c>
       <c r="C4" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D4" s="78"/>
       <c r="E4" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10057,14 +10073,14 @@
         <v>193</v>
       </c>
       <c r="B6" s="80" t="n">
-        <v>351.5</v>
+        <v>349</v>
       </c>
       <c r="C6" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D6" s="78"/>
       <c r="E6" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10072,14 +10088,14 @@
         <v>171</v>
       </c>
       <c r="B7" s="80" t="n">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="C7" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D7" s="78"/>
       <c r="E7" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10102,14 +10118,14 @@
         <v>210</v>
       </c>
       <c r="B9" s="80" t="n">
-        <v>4720</v>
+        <v>4585</v>
       </c>
       <c r="C9" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D9" s="78"/>
       <c r="E9" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10117,14 +10133,14 @@
         <v>179</v>
       </c>
       <c r="B10" s="80" t="n">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="C10" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D10" s="78"/>
       <c r="E10" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10132,14 +10148,14 @@
         <v>212</v>
       </c>
       <c r="B11" s="80" t="n">
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="C11" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D11" s="78"/>
       <c r="E11" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10147,14 +10163,14 @@
         <v>184</v>
       </c>
       <c r="B12" s="80" t="n">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C12" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D12" s="78"/>
       <c r="E12" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10162,14 +10178,14 @@
         <v>198</v>
       </c>
       <c r="B13" s="80" t="n">
-        <v>2830</v>
+        <v>2810</v>
       </c>
       <c r="C13" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D13" s="78"/>
       <c r="E13" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10177,14 +10193,14 @@
         <v>218</v>
       </c>
       <c r="B14" s="80" t="n">
-        <v>461.5</v>
+        <v>437.5</v>
       </c>
       <c r="C14" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D14" s="78"/>
       <c r="E14" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10192,14 +10208,14 @@
         <v>200</v>
       </c>
       <c r="B15" s="80" t="n">
-        <v>707</v>
+        <v>670</v>
       </c>
       <c r="C15" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D15" s="78"/>
       <c r="E15" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10207,14 +10223,14 @@
         <v>204</v>
       </c>
       <c r="B16" s="80" t="n">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C16" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D16" s="78"/>
       <c r="E16" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10252,14 +10268,14 @@
         <v>186</v>
       </c>
       <c r="B19" s="80" t="n">
-        <v>1930</v>
+        <v>1875</v>
       </c>
       <c r="C19" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D19" s="78"/>
       <c r="E19" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10285,11 +10301,11 @@
         <v>91</v>
       </c>
       <c r="C21" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D21" s="78"/>
       <c r="E21" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10312,14 +10328,14 @@
         <v>175</v>
       </c>
       <c r="B23" s="80" t="n">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="C23" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D23" s="78"/>
       <c r="E23" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10330,11 +10346,11 @@
         <v>527</v>
       </c>
       <c r="C24" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D24" s="78"/>
       <c r="E24" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10342,14 +10358,14 @@
         <v>206</v>
       </c>
       <c r="B25" s="80" t="n">
-        <v>1800</v>
+        <v>1670</v>
       </c>
       <c r="C25" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D25" s="78"/>
       <c r="E25" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10357,14 +10373,14 @@
         <v>216</v>
       </c>
       <c r="B26" s="80" t="n">
-        <v>2065</v>
+        <v>1990</v>
       </c>
       <c r="C26" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D26" s="78"/>
       <c r="E26" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
   </sheetData>
@@ -10570,7 +10586,7 @@
       </c>
       <c r="D2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2450</v>
+        <v>2410</v>
       </c>
       <c r="E2" s="48" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10586,7 +10602,7 @@
       </c>
       <c r="H2" s="51" t="n">
         <f aca="true">IF($A2="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>131.601786054795</v>
+        <v>131.696483232877</v>
       </c>
       <c r="I2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10594,15 +10610,15 @@
       </c>
       <c r="J2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(F2&lt;=0,"N/M",D2/F2),"N/M"))</f>
-        <v>28.3959202596198</v>
+        <v>27.9323133982383</v>
       </c>
       <c r="K2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(G2&lt;=0,"N/M",D2/G2),"N/M"))</f>
-        <v>25.2495401749556</v>
+        <v>24.8373027843441</v>
       </c>
       <c r="L2" s="52" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(H2&lt;=0,"N/M",D2/H2),"N/M"))</f>
-        <v>18.6167686126988</v>
+        <v>18.2996534215605</v>
       </c>
       <c r="M2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A2,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10610,11 +10626,11 @@
       </c>
       <c r="N2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(J2)),I2&lt;Config!$B$6),"N/M",J2/(I2*100)),"N/M"))</f>
-        <v>0.533524948221286</v>
+        <v>0.524814336821755</v>
       </c>
       <c r="O2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(OR(NOT(ISNUMBER(L2)),M2&lt;Config!$B$6),"N/M",L2/(M2*100)),"N/M"))</f>
-        <v>0.579778098864001</v>
+        <v>0.569902247341969</v>
       </c>
       <c r="P2" s="51" t="n">
         <f aca="false">IF($A2="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10622,7 +10638,7 @@
       </c>
       <c r="Q2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(P2=0,"不配息",P2/D2),""))</f>
-        <v>0.00897963272653061</v>
+        <v>0.00912867227385892</v>
       </c>
       <c r="R2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -10714,7 +10730,7 @@
       </c>
       <c r="AN2" s="67" t="n">
         <f aca="false">IF($A2="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A2,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO2" s="49" t="n">
         <f aca="false">IF($A2="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A2)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A2,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -10752,7 +10768,7 @@
       </c>
       <c r="D3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="E3" s="48" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10768,7 +10784,7 @@
       </c>
       <c r="H3" s="51" t="n">
         <f aca="true">IF($A3="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>89.045882739726</v>
+        <v>89.1344016438356</v>
       </c>
       <c r="I3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10776,15 +10792,15 @@
       </c>
       <c r="J3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(F3&lt;=0,"N/M",D3/F3),"N/M"))</f>
-        <v>18.9686924493554</v>
+        <v>18.158379373849</v>
       </c>
       <c r="K3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(G3&lt;=0,"N/M",D3/G3),"N/M"))</f>
-        <v>10.8425960332941</v>
+        <v>10.3794171736194</v>
       </c>
       <c r="L3" s="52" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(H3&lt;=0,"N/M",D3/H3),"N/M"))</f>
-        <v>5.78353523099214</v>
+        <v>5.53097334932404</v>
       </c>
       <c r="M3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A3,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10796,7 +10812,7 @@
       </c>
       <c r="O3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(OR(NOT(ISNUMBER(L3)),M3&lt;Config!$B$6),"N/M",L3/(M3*100)),"N/M"))</f>
-        <v>0.119307722602947</v>
+        <v>0.11409765960261</v>
       </c>
       <c r="P3" s="51" t="n">
         <f aca="false">IF($A3="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10896,7 +10912,7 @@
       </c>
       <c r="AN3" s="67" t="n">
         <f aca="false">IF($A3="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A3,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO3" s="49" t="n">
         <f aca="false">IF($A3="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A3)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A3,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -10934,7 +10950,7 @@
       </c>
       <c r="D4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="E4" s="48" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -10950,7 +10966,7 @@
       </c>
       <c r="H4" s="51" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>243.42628769863</v>
+        <v>242.992340219178</v>
       </c>
       <c r="I4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -10958,15 +10974,15 @@
       </c>
       <c r="J4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(F4&lt;=0,"N/M",D4/F4),"N/M"))</f>
-        <v>7.06655710764174</v>
+        <v>7.09394686387291</v>
       </c>
       <c r="K4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(G4&lt;=0,"N/M",D4/G4),"N/M"))</f>
-        <v>4.69620299246423</v>
+        <v>4.71440532964433</v>
       </c>
       <c r="L4" s="52" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(H4&lt;=0,"N/M",D4/H4),"N/M"))</f>
-        <v>5.29934549056207</v>
+        <v>5.32938609847502</v>
       </c>
       <c r="M4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A4,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -10974,7 +10990,7 @@
       </c>
       <c r="N4" s="51" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(J4)),I4&lt;Config!$B$6),"N/M",J4/(I4*100)),"N/M"))</f>
-        <v>0.00442173975012507</v>
+        <v>0.00443887827628835</v>
       </c>
       <c r="O4" s="51" t="str">
         <f aca="false">IF($A4="","",IFERROR(IF(OR(NOT(ISNUMBER(L4)),M4&lt;Config!$B$6),"N/M",L4/(M4*100)),"N/M"))</f>
@@ -10986,7 +11002,7 @@
       </c>
       <c r="Q4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(P4=0,"不配息",P4/D4),""))</f>
-        <v>0.00726917654263566</v>
+        <v>0.00724111022393822</v>
       </c>
       <c r="R4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -11078,7 +11094,7 @@
       </c>
       <c r="AN4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO4" s="49" t="n">
         <f aca="false">IF($A4="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A4)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A4,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -11116,7 +11132,7 @@
       </c>
       <c r="D5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="E5" s="48" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11132,7 +11148,7 @@
       </c>
       <c r="H5" s="51" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.9668864109589</v>
+        <v>7.97711224657534</v>
       </c>
       <c r="I5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11140,15 +11156,15 @@
       </c>
       <c r="J5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(F5&lt;=0,"N/M",D5/F5),"N/M"))</f>
-        <v>129.126213592233</v>
+        <v>125</v>
       </c>
       <c r="K5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(G5&lt;=0,"N/M",D5/G5),"N/M"))</f>
-        <v>113.329172249691</v>
+        <v>109.707751331937</v>
       </c>
       <c r="L5" s="52" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(H5&lt;=0,"N/M",D5/H5),"N/M"))</f>
-        <v>66.7764007866616</v>
+        <v>64.5597033213485</v>
       </c>
       <c r="M5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A5,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11156,11 +11172,11 @@
       </c>
       <c r="N5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(J5)),I5&lt;Config!$B$6),"N/M",J5/(I5*100)),"N/M"))</f>
-        <v>2.0972728959248</v>
+        <v>2.03025477707006</v>
       </c>
       <c r="O5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(OR(NOT(ISNUMBER(L5)),M5&lt;Config!$B$6),"N/M",L5/(M5*100)),"N/M"))</f>
-        <v>0.962483803131051</v>
+        <v>0.930533362830715</v>
       </c>
       <c r="P5" s="51" t="n">
         <f aca="false">IF($A5="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11168,7 +11184,7 @@
       </c>
       <c r="Q5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(P5=0,"不配息",P5/D5),""))</f>
-        <v>0.00492585813909775</v>
+        <v>0.0050884592815534</v>
       </c>
       <c r="R5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -11260,7 +11276,7 @@
       </c>
       <c r="AN5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO5" s="49" t="n">
         <f aca="false">IF($A5="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A5)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A5,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -11298,7 +11314,7 @@
       </c>
       <c r="D6" s="51" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E6" s="48" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11314,7 +11330,7 @@
       </c>
       <c r="H6" s="51" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>34.8271415068493</v>
+        <v>34.8315789041096</v>
       </c>
       <c r="I6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11322,15 +11338,15 @@
       </c>
       <c r="J6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(F6&lt;=0,"N/M",D6/F6),"N/M"))</f>
-        <v>19.0094175095919</v>
+        <v>19.0791768399023</v>
       </c>
       <c r="K6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(G6&lt;=0,"N/M",D6/G6),"N/M"))</f>
-        <v>16.9082792552787</v>
+        <v>16.9703279864907</v>
       </c>
       <c r="L6" s="52" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(H6&lt;=0,"N/M",D6/H6),"N/M"))</f>
-        <v>15.6487146639013</v>
+        <v>15.7041402431362</v>
       </c>
       <c r="M6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A6,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11350,7 +11366,7 @@
       </c>
       <c r="Q6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(P6=0,"不配息",P6/D6),""))</f>
-        <v>0.0513761467889908</v>
+        <v>0.0511882998171846</v>
       </c>
       <c r="R6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -11442,7 +11458,7 @@
       </c>
       <c r="AN6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO6" s="49" t="n">
         <f aca="false">IF($A6="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A6)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A6,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -11480,7 +11496,7 @@
       </c>
       <c r="D7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1930</v>
+        <v>1875</v>
       </c>
       <c r="E7" s="48" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11496,7 +11512,7 @@
       </c>
       <c r="H7" s="51" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>99.698874739726</v>
+        <v>99.8336076438356</v>
       </c>
       <c r="I7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11504,15 +11520,15 @@
       </c>
       <c r="J7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(F7&lt;=0,"N/M",D7/F7),"N/M"))</f>
-        <v>35.3933614524115</v>
+        <v>34.384742343664</v>
       </c>
       <c r="K7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(G7&lt;=0,"N/M",D7/G7),"N/M"))</f>
-        <v>32.2938235970802</v>
+        <v>31.3735332873188</v>
       </c>
       <c r="L7" s="52" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(H7&lt;=0,"N/M",D7/H7),"N/M"))</f>
-        <v>19.3582927093055</v>
+        <v>18.7812505653328</v>
       </c>
       <c r="M7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A7,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11520,11 +11536,11 @@
       </c>
       <c r="N7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(J7)),I7&lt;Config!$B$6),"N/M",J7/(I7*100)),"N/M"))</f>
-        <v>0.61591563170704</v>
+        <v>0.598363631839741</v>
       </c>
       <c r="O7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(OR(NOT(ISNUMBER(L7)),M7&lt;Config!$B$6),"N/M",L7/(M7*100)),"N/M"))</f>
-        <v>0.258273681238022</v>
+        <v>0.250574923863531</v>
       </c>
       <c r="P7" s="51" t="n">
         <f aca="false">IF($A7="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11532,7 +11548,7 @@
       </c>
       <c r="Q7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(P7=0,"不配息",P7/D7),""))</f>
-        <v>0.0054432551761658</v>
+        <v>0.00560292399466667</v>
       </c>
       <c r="R7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -11624,7 +11640,7 @@
       </c>
       <c r="AN7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO7" s="49" t="n">
         <f aca="false">IF($A7="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A7)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A7,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -11678,7 +11694,7 @@
       </c>
       <c r="H8" s="51" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>33.2255616438356</v>
+        <v>33.2361369863014</v>
       </c>
       <c r="I8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11694,7 +11710,7 @@
       </c>
       <c r="L8" s="52" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(H8&lt;=0,"N/M",D8/H8),"N/M"))</f>
-        <v>15.8612819144857</v>
+        <v>15.8562350437179</v>
       </c>
       <c r="M8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A8,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11706,7 +11722,7 @@
       </c>
       <c r="O8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(OR(NOT(ISNUMBER(L8)),M8&lt;Config!$B$6),"N/M",L8/(M8*100)),"N/M"))</f>
-        <v>1.25534238986409</v>
+        <v>1.25494295488493</v>
       </c>
       <c r="P8" s="51" t="n">
         <f aca="false">IF($A8="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11806,7 +11822,7 @@
       </c>
       <c r="AN8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO8" s="49" t="n">
         <f aca="false">IF($A8="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A8)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A8,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -11844,7 +11860,7 @@
       </c>
       <c r="D9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>351.5</v>
+        <v>349</v>
       </c>
       <c r="E9" s="48" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11860,7 +11876,7 @@
       </c>
       <c r="H9" s="51" t="n">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>36.2114876164384</v>
+        <v>36.220797369863</v>
       </c>
       <c r="I9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -11868,15 +11884,15 @@
       </c>
       <c r="J9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(F9&lt;=0,"N/M",D9/F9),"N/M"))</f>
-        <v>13.1598652190191</v>
+        <v>13.0662673156121</v>
       </c>
       <c r="K9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(G9&lt;=0,"N/M",D9/G9),"N/M"))</f>
-        <v>11.5751946378034</v>
+        <v>11.4928675066669</v>
       </c>
       <c r="L9" s="52" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(H9&lt;=0,"N/M",D9/H9),"N/M"))</f>
-        <v>9.70686439958449</v>
+        <v>9.63534834521286</v>
       </c>
       <c r="M9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A9,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -11884,11 +11900,11 @@
       </c>
       <c r="N9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(OR(NOT(ISNUMBER(J9)),I9&lt;Config!$B$6),"N/M",J9/(I9*100)),"N/M"))</f>
-        <v>0.2099951281791</v>
+        <v>0.2085015639673</v>
       </c>
       <c r="O9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(OR(NOT(ISNUMBER(L9)),M9&lt;Config!$B$6),"N/M",L9/(M9*100)),"N/M"))</f>
-        <v>0.967130556658977</v>
+        <v>0.960005149459774</v>
       </c>
       <c r="P9" s="51" t="n">
         <f aca="false">IF($A9="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -11896,7 +11912,7 @@
       </c>
       <c r="Q9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(P9=0,"不配息",P9/D9),""))</f>
-        <v>0.0284495021337127</v>
+        <v>0.0286532951289398</v>
       </c>
       <c r="R9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -11988,7 +12004,7 @@
       </c>
       <c r="AN9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO9" s="49" t="n">
         <f aca="false">IF($A9="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A9)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A9,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12026,7 +12042,7 @@
       </c>
       <c r="D10" s="51" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A10,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>12600</v>
+        <v>12080</v>
       </c>
       <c r="E10" s="48" t="n">
         <f aca="false">IF($A10="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12042,7 +12058,7 @@
       </c>
       <c r="H10" s="51" t="n">
         <f aca="true">IF($A10="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>453.119410246575</v>
+        <v>453.518048547945</v>
       </c>
       <c r="I10" s="49" t="n">
         <f aca="false">IF($A10="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -12050,15 +12066,15 @@
       </c>
       <c r="J10" s="52" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(F10&lt;=0,"N/M",D10/F10),"N/M"))</f>
-        <v>69.4635867467887</v>
+        <v>66.5968355477149</v>
       </c>
       <c r="K10" s="52" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(G10&lt;=0,"N/M",D10/G10),"N/M"))</f>
-        <v>47.3255878373239</v>
+        <v>45.3724683392756</v>
       </c>
       <c r="L10" s="52" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(H10&lt;=0,"N/M",D10/H10),"N/M"))</f>
-        <v>27.8072395820418</v>
+        <v>26.6362056343231</v>
       </c>
       <c r="M10" s="49" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A10,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -12066,11 +12082,11 @@
       </c>
       <c r="N10" s="51" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(OR(NOT(ISNUMBER(J10)),I10&lt;Config!$B$6),"N/M",J10/(I10*100)),"N/M"))</f>
-        <v>0.412180717212366</v>
+        <v>0.395170084438523</v>
       </c>
       <c r="O10" s="51" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(OR(NOT(ISNUMBER(L10)),M10&lt;Config!$B$6),"N/M",L10/(M10*100)),"N/M"))</f>
-        <v>0.673215573973069</v>
+        <v>0.644864745084447</v>
       </c>
       <c r="P10" s="51" t="n">
         <f aca="false">IF($A10="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12078,7 +12094,7 @@
       </c>
       <c r="Q10" s="49" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(P10=0,"不配息",P10/D10),""))</f>
-        <v>0.00255555555555556</v>
+        <v>0.00266556291390729</v>
       </c>
       <c r="R10" s="49" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -12170,7 +12186,7 @@
       </c>
       <c r="AN10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A10,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO10" s="49" t="n">
         <f aca="false">IF($A10="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A10)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A10,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12208,7 +12224,7 @@
       </c>
       <c r="D11" s="51" t="n">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A11,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2830</v>
+        <v>2810</v>
       </c>
       <c r="E11" s="48" t="n">
         <f aca="false">IF($A11="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12224,7 +12240,7 @@
       </c>
       <c r="H11" s="51" t="n">
         <f aca="true">IF($A11="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>33.3346376986301</v>
+        <v>33.3883002191781</v>
       </c>
       <c r="I11" s="49" t="n">
         <f aca="false">IF($A11="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -12232,15 +12248,15 @@
       </c>
       <c r="J11" s="52" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(F11&lt;=0,"N/M",D11/F11),"N/M"))</f>
-        <v>252.453166815343</v>
+        <v>250.669045495094</v>
       </c>
       <c r="K11" s="52" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(G11&lt;=0,"N/M",D11/G11),"N/M"))</f>
-        <v>177.763819095477</v>
+        <v>176.507537688442</v>
       </c>
       <c r="L11" s="52" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(H11&lt;=0,"N/M",D11/H11),"N/M"))</f>
-        <v>84.8966779115856</v>
+        <v>84.1612175987908</v>
       </c>
       <c r="M11" s="49" t="n">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A11,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -12248,11 +12264,11 @@
       </c>
       <c r="N11" s="51" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(OR(NOT(ISNUMBER(J11)),I11&lt;Config!$B$6),"N/M",J11/(I11*100)),"N/M"))</f>
-        <v>0.448157407476818</v>
+        <v>0.444990217317971</v>
       </c>
       <c r="O11" s="51" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(OR(NOT(ISNUMBER(L11)),M11&lt;Config!$B$6),"N/M",L11/(M11*100)),"N/M"))</f>
-        <v>0.856387233920905</v>
+        <v>0.848968347358714</v>
       </c>
       <c r="P11" s="51" t="n">
         <f aca="false">IF($A11="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12260,7 +12276,7 @@
       </c>
       <c r="Q11" s="49" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(P11=0,"不配息",P11/D11),""))</f>
-        <v>0.000176686272084806</v>
+        <v>0.000177943825622776</v>
       </c>
       <c r="R11" s="49" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -12352,7 +12368,7 @@
       </c>
       <c r="AN11" s="67" t="n">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A11,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO11" s="49" t="n">
         <f aca="false">IF($A11="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A11)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A11,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12390,7 +12406,7 @@
       </c>
       <c r="D12" s="51" t="n">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A12,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>707</v>
+        <v>670</v>
       </c>
       <c r="E12" s="48" t="n">
         <f aca="false">IF($A12="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A12,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12414,11 +12430,11 @@
       </c>
       <c r="J12" s="52" t="n">
         <f aca="false">IF($A12="","",IFERROR(IF(F12&lt;=0,"N/M",D12/F12),"N/M"))</f>
-        <v>73.3402489626556</v>
+        <v>69.5020746887967</v>
       </c>
       <c r="K12" s="52" t="n">
         <f aca="false">IF($A12="","",IFERROR(IF(G12&lt;=0,"N/M",D12/G12),"N/M"))</f>
-        <v>103.061224489796</v>
+        <v>97.667638483965</v>
       </c>
       <c r="L12" s="52" t="str">
         <f aca="false">IF($A12="","",IFERROR(IF(H12&lt;=0,"N/M",D12/H12),"N/M"))</f>
@@ -12430,7 +12446,7 @@
       </c>
       <c r="N12" s="51" t="n">
         <f aca="false">IF($A12="","",IFERROR(IF(OR(NOT(ISNUMBER(J12)),I12&lt;Config!$B$6),"N/M",J12/(I12*100)),"N/M"))</f>
-        <v>0.275156711514671</v>
+        <v>0.260756713882361</v>
       </c>
       <c r="O12" s="51" t="str">
         <f aca="false">IF($A12="","",IFERROR(IF(OR(NOT(ISNUMBER(L12)),M12&lt;Config!$B$6),"N/M",L12/(M12*100)),"N/M"))</f>
@@ -12534,7 +12550,7 @@
       </c>
       <c r="AN12" s="67" t="n">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A12,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO12" s="49" t="n">
         <f aca="false">IF($A12="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A12,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A12,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A12)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A12,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A12,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12572,7 +12588,7 @@
       </c>
       <c r="D13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A13,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="E13" s="48" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12588,7 +12604,7 @@
       </c>
       <c r="H13" s="51" t="n">
         <f aca="true">IF($A13="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>21.5424096438356</v>
+        <v>21.5863809863014</v>
       </c>
       <c r="I13" s="49" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -12596,15 +12612,15 @@
       </c>
       <c r="J13" s="52" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(F13&lt;=0,"N/M",D13/F13),"N/M"))</f>
-        <v>140.169491525424</v>
+        <v>139.322033898305</v>
       </c>
       <c r="K13" s="52" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(G13&lt;=0,"N/M",D13/G13),"N/M"))</f>
-        <v>99.2290848006719</v>
+        <v>98.6291507934127</v>
       </c>
       <c r="L13" s="52" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(H13&lt;=0,"N/M",D13/H13),"N/M"))</f>
-        <v>38.3893916081318</v>
+        <v>38.0795650980884</v>
       </c>
       <c r="M13" s="49" t="n">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A13,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -12612,11 +12628,11 @@
       </c>
       <c r="N13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(OR(NOT(ISNUMBER(J13)),I13&lt;Config!$B$6),"N/M",J13/(I13*100)),"N/M"))</f>
-        <v>0.361631310758556</v>
+        <v>0.359444906219508</v>
       </c>
       <c r="O13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(OR(NOT(ISNUMBER(L13)),M13&lt;Config!$B$6),"N/M",L13/(M13*100)),"N/M"))</f>
-        <v>0.249183234772068</v>
+        <v>0.247172169507507</v>
       </c>
       <c r="P13" s="51" t="n">
         <f aca="false">IF($A13="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12624,7 +12640,7 @@
       </c>
       <c r="Q13" s="49" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(P13=0,"不配息",P13/D13),""))</f>
-        <v>0.00120939773881499</v>
+        <v>0.00121675417274939</v>
       </c>
       <c r="R13" s="49" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -12716,7 +12732,7 @@
       </c>
       <c r="AN13" s="67" t="n">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A13,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO13" s="49" t="n">
         <f aca="false">IF($A13="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A13)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A13,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12754,7 +12770,7 @@
       </c>
       <c r="D14" s="51" t="n">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A14,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>1800</v>
+        <v>1670</v>
       </c>
       <c r="E14" s="48" t="n">
         <f aca="false">IF($A14="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12770,7 +12786,7 @@
       </c>
       <c r="H14" s="51" t="n">
         <f aca="true">IF($A14="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>109.137315068493</v>
+        <v>109.323589041096</v>
       </c>
       <c r="I14" s="49" t="str">
         <f aca="false">IF($A14="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -12778,15 +12794,15 @@
       </c>
       <c r="J14" s="52" t="n">
         <f aca="false">IF($A14="","",IFERROR(IF(F14&lt;=0,"N/M",D14/F14),"N/M"))</f>
-        <v>160.57091882248</v>
+        <v>148.974130240856</v>
       </c>
       <c r="K14" s="52" t="n">
         <f aca="false">IF($A14="","",IFERROR(IF(G14&lt;=0,"N/M",D14/G14),"N/M"))</f>
-        <v>72.8744939271255</v>
+        <v>67.6113360323887</v>
       </c>
       <c r="L14" s="52" t="n">
         <f aca="false">IF($A14="","",IFERROR(IF(H14&lt;=0,"N/M",D14/H14),"N/M"))</f>
-        <v>16.4929840803793</v>
+        <v>15.27575168953</v>
       </c>
       <c r="M14" s="49" t="n">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A14,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -12798,7 +12814,7 @@
       </c>
       <c r="O14" s="51" t="n">
         <f aca="false">IF($A14="","",IFERROR(IF(OR(NOT(ISNUMBER(L14)),M14&lt;Config!$B$6),"N/M",L14/(M14*100)),"N/M"))</f>
-        <v>0.150423583295238</v>
+        <v>0.139321865313686</v>
       </c>
       <c r="P14" s="51" t="n">
         <f aca="false">IF($A14="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12898,7 +12914,7 @@
       </c>
       <c r="AN14" s="67" t="n">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A14,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO14" s="49" t="str">
         <f aca="false">IF($A14="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A14)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A14,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -12936,7 +12952,7 @@
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A15,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>142.5</v>
+        <v>140.5</v>
       </c>
       <c r="E15" s="48" t="n">
         <f aca="false">IF($A15="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -12952,7 +12968,7 @@
       </c>
       <c r="H15" s="51" t="n">
         <f aca="true">IF($A15="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>7.13825219178082</v>
+        <v>7.13885931506849</v>
       </c>
       <c r="I15" s="49" t="n">
         <f aca="false">IF($A15="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -12960,15 +12976,15 @@
       </c>
       <c r="J15" s="52" t="n">
         <f aca="false">IF($A15="","",IFERROR(IF(F15&lt;=0,"N/M",D15/F15),"N/M"))</f>
-        <v>21.3323353293413</v>
+        <v>21.0329341317365</v>
       </c>
       <c r="K15" s="52" t="n">
         <f aca="false">IF($A15="","",IFERROR(IF(G15&lt;=0,"N/M",D15/G15),"N/M"))</f>
-        <v>20.6779464259802</v>
+        <v>20.3877296340366</v>
       </c>
       <c r="L15" s="52" t="n">
         <f aca="false">IF($A15="","",IFERROR(IF(H15&lt;=0,"N/M",D15/H15),"N/M"))</f>
-        <v>19.962869925509</v>
+        <v>19.6810153834292</v>
       </c>
       <c r="M15" s="49" t="n">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A15,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -12976,7 +12992,7 @@
       </c>
       <c r="N15" s="51" t="n">
         <f aca="false">IF($A15="","",IFERROR(IF(OR(NOT(ISNUMBER(J15)),I15&lt;Config!$B$6),"N/M",J15/(I15*100)),"N/M"))</f>
-        <v>0.192659552689493</v>
+        <v>0.189955558967535</v>
       </c>
       <c r="O15" s="51" t="str">
         <f aca="false">IF($A15="","",IFERROR(IF(OR(NOT(ISNUMBER(L15)),M15&lt;Config!$B$6),"N/M",L15/(M15*100)),"N/M"))</f>
@@ -13080,7 +13096,7 @@
       </c>
       <c r="AN15" s="67" t="n">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A15,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO15" s="49" t="n">
         <f aca="false">IF($A15="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A15)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A15,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -13118,7 +13134,7 @@
       </c>
       <c r="D16" s="51" t="n">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A16,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>4720</v>
+        <v>4585</v>
       </c>
       <c r="E16" s="48" t="n">
         <f aca="false">IF($A16="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -13134,7 +13150,7 @@
       </c>
       <c r="H16" s="51" t="n">
         <f aca="true">IF($A16="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A16,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A16,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A16,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A16,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>121.793973506849</v>
+        <v>122.00638490411</v>
       </c>
       <c r="I16" s="49" t="n">
         <f aca="false">IF($A16="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -13142,15 +13158,15 @@
       </c>
       <c r="J16" s="52" t="n">
         <f aca="false">IF($A16="","",IFERROR(IF(F16&lt;=0,"N/M",D16/F16),"N/M"))</f>
-        <v>77.7722853847421</v>
+        <v>75.5478662053057</v>
       </c>
       <c r="K16" s="52" t="n">
         <f aca="false">IF($A16="","",IFERROR(IF(G16&lt;=0,"N/M",D16/G16),"N/M"))</f>
-        <v>78.2956237059243</v>
+        <v>76.0562361634879</v>
       </c>
       <c r="L16" s="52" t="n">
         <f aca="false">IF($A16="","",IFERROR(IF(H16&lt;=0,"N/M",D16/H16),"N/M"))</f>
-        <v>38.7539700372331</v>
+        <v>37.5800004532842</v>
       </c>
       <c r="M16" s="49" t="n">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A16,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A16,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -13162,7 +13178,7 @@
       </c>
       <c r="O16" s="51" t="n">
         <f aca="false">IF($A16="","",IFERROR(IF(OR(NOT(ISNUMBER(L16)),M16&lt;Config!$B$6),"N/M",L16/(M16*100)),"N/M"))</f>
-        <v>0.340171929733817</v>
+        <v>0.329867140355153</v>
       </c>
       <c r="P16" s="51" t="n">
         <f aca="false">IF($A16="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -13170,7 +13186,7 @@
       </c>
       <c r="Q16" s="49" t="n">
         <f aca="false">IF($A16="","",IFERROR(IF(P16=0,"不配息",P16/D16),""))</f>
-        <v>0.0114407240402542</v>
+        <v>0.01177758287241</v>
       </c>
       <c r="R16" s="49" t="n">
         <f aca="false">IF($A16="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -13262,7 +13278,7 @@
       </c>
       <c r="AN16" s="67" t="n">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A16,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO16" s="49" t="n">
         <f aca="false">IF($A16="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A16)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A16,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -13300,7 +13316,7 @@
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">IF($A17="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A17,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="E17" s="48" t="n">
         <f aca="false">IF($A17="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A17,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -13324,11 +13340,11 @@
       </c>
       <c r="J17" s="52" t="n">
         <f aca="false">IF($A17="","",IFERROR(IF(F17&lt;=0,"N/M",D17/F17),"N/M"))</f>
-        <v>33.962962962963</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="K17" s="52" t="n">
         <f aca="false">IF($A17="","",IFERROR(IF(G17&lt;=0,"N/M",D17/G17),"N/M"))</f>
-        <v>29.297124600639</v>
+        <v>28.7539936102236</v>
       </c>
       <c r="L17" s="52" t="str">
         <f aca="false">IF($A17="","",IFERROR(IF(H17&lt;=0,"N/M",D17/H17),"N/M"))</f>
@@ -13444,7 +13460,7 @@
       </c>
       <c r="AN17" s="67" t="n">
         <f aca="false">IF($A17="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A17,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO17" s="49" t="n">
         <f aca="false">IF($A17="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A17,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A17,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A17)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A17,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A17,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -13498,7 +13514,7 @@
       </c>
       <c r="H18" s="51" t="n">
         <f aca="true">IF($A18="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A18,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A18,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A18,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A18,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>6.7392818630137</v>
+        <v>6.74357791780822</v>
       </c>
       <c r="I18" s="49" t="n">
         <f aca="false">IF($A18="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A18,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A18,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -13514,7 +13530,7 @@
       </c>
       <c r="L18" s="52" t="n">
         <f aca="false">IF($A18="","",IFERROR(IF(H18&lt;=0,"N/M",D18/H18),"N/M"))</f>
-        <v>13.502922395845</v>
+        <v>13.4943202420321</v>
       </c>
       <c r="M18" s="49" t="n">
         <f aca="false">IF($A18="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A18,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A18,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -13526,7 +13542,7 @@
       </c>
       <c r="O18" s="51" t="n">
         <f aca="false">IF($A18="","",IFERROR(IF(OR(NOT(ISNUMBER(L18)),M18&lt;Config!$B$6),"N/M",L18/(M18*100)),"N/M"))</f>
-        <v>0.486739337090587</v>
+        <v>0.486429255574769</v>
       </c>
       <c r="P18" s="51" t="n">
         <f aca="false">IF($A18="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A18,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -13626,7 +13642,7 @@
       </c>
       <c r="AN18" s="67" t="n">
         <f aca="false">IF($A18="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A18,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO18" s="49" t="n">
         <f aca="false">IF($A18="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A18,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A18,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A18)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A18,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A18,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -13664,7 +13680,7 @@
       </c>
       <c r="D19" s="51" t="n">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A19,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>2065</v>
+        <v>1990</v>
       </c>
       <c r="E19" s="48" t="n">
         <f aca="false">IF($A19="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A19,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -13680,7 +13696,7 @@
       </c>
       <c r="H19" s="51" t="n">
         <f aca="true">IF($A19="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A19,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A19,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A19,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A19,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>287.429802136986</v>
+        <v>287.146854082192</v>
       </c>
       <c r="I19" s="49" t="str">
         <f aca="false">IF($A19="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A19,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A19,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -13696,7 +13712,7 @@
       </c>
       <c r="L19" s="52" t="n">
         <f aca="false">IF($A19="","",IFERROR(IF(H19&lt;=0,"N/M",D19/H19),"N/M"))</f>
-        <v>7.18436287624705</v>
+        <v>6.93025179175527</v>
       </c>
       <c r="M19" s="49" t="n">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A19,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A19,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -13808,7 +13824,7 @@
       </c>
       <c r="AN19" s="67" t="n">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A19,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO19" s="49" t="str">
         <f aca="false">IF($A19="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A19,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A19,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A19)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A19,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A19,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -13846,7 +13862,7 @@
       </c>
       <c r="D20" s="51" t="n">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Raw_Price!$B$2:$B$100,MATCH($A20,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>461.5</v>
+        <v>437.5</v>
       </c>
       <c r="E20" s="48" t="n">
         <f aca="false">IF($A20="","",IFERROR(SUMIFS(Raw_Q!$I$2:$I$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -13862,7 +13878,7 @@
       </c>
       <c r="H20" s="51" t="n">
         <f aca="true">IF($A20="","",IFERROR(INDEX(Raw_Est!$B$2:$B$100,MATCH($A20,Raw_Est!$A$2:$A$100,0))*MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A20,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))+INDEX(Raw_Est!$C$2:$C$100,MATCH($A20,Raw_Est!$A$2:$A$100,0))*(1-MIN(1,MAX(0,(INDEX(Raw_Est!$D$2:$D$100,MATCH($A20,Raw_Est!$A$2:$A$100,0))-TODAY())/Config!$B$8))),""))</f>
-        <v>9.24343646575342</v>
+        <v>9.24959747945206</v>
       </c>
       <c r="I20" s="49" t="n">
         <f aca="false">IF($A20="","",IFERROR(SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$L$2:$L$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1,""))</f>
@@ -13870,15 +13886,15 @@
       </c>
       <c r="J20" s="52" t="n">
         <f aca="false">IF($A20="","",IFERROR(IF(F20&lt;=0,"N/M",D20/F20),"N/M"))</f>
-        <v>54.2303172737955</v>
+        <v>51.4101057579318</v>
       </c>
       <c r="K20" s="52" t="n">
         <f aca="false">IF($A20="","",IFERROR(IF(G20&lt;=0,"N/M",D20/G20),"N/M"))</f>
-        <v>56.9209175429898</v>
+        <v>53.9607831528885</v>
       </c>
       <c r="L20" s="52" t="n">
         <f aca="false">IF($A20="","",IFERROR(IF(H20&lt;=0,"N/M",D20/H20),"N/M"))</f>
-        <v>49.9273188829544</v>
+        <v>47.2993555635156</v>
       </c>
       <c r="M20" s="49" t="n">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Raw_Est!$C$2:$C$100,MATCH($A20,Raw_Est!$A$2:$A$100,0))/INDEX(Raw_Est!$B$2:$B$100,MATCH($A20,Raw_Est!$A$2:$A$100,0))-1,""))</f>
@@ -13890,7 +13906,7 @@
       </c>
       <c r="O20" s="51" t="n">
         <f aca="false">IF($A20="","",IFERROR(IF(OR(NOT(ISNUMBER(L20)),M20&lt;Config!$B$6),"N/M",L20/(M20*100)),"N/M"))</f>
-        <v>1.70616144567848</v>
+        <v>1.6163563089998</v>
       </c>
       <c r="P20" s="51" t="n">
         <f aca="false">IF($A20="","",IFERROR(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4"),""))</f>
@@ -13898,7 +13914,7 @@
       </c>
       <c r="Q20" s="49" t="n">
         <f aca="false">IF($A20="","",IFERROR(IF(P20=0,"不配息",P20/D20),""))</f>
-        <v>0.00433369447453955</v>
+        <v>0.00457142857142857</v>
       </c>
       <c r="R20" s="49" t="n">
         <f aca="false">IF($A20="","",IFERROR(IF(SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")=0,"",SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,"&gt;=1",Raw_Q!$R$2:$R$600,"&lt;=4")/SUMIFS(Raw_Q!$P$2:$P$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,"&gt;=5",Raw_Q!$R$2:$R$600,"&lt;=8")-1),""))</f>
@@ -13990,7 +14006,7 @@
       </c>
       <c r="AN20" s="67" t="n">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A20,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="AO20" s="49" t="n">
         <f aca="false">IF($A20="","",IFERROR(IF(MIN(SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,1),SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,5))&lt;=0,"",SUMPRODUCT((Raw_Q!$A$2:$A$600=$A20)*(Raw_Q!$R$2:$R$600&gt;=1)*(Raw_Q!$R$2:$R$600&lt;=4)*Raw_Q!$L$2:$L$600*Raw_Q!$M$2:$M$600)/((SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,1)+SUMIFS(Raw_Q!$O$2:$O$600,Raw_Q!$A$2:$A$600,$A20,Raw_Q!$R$2:$R$600,5))/2)),""))</f>
@@ -15205,27 +15221,27 @@
       </c>
       <c r="D3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!D$2)</f>
-        <v>2450</v>
+        <v>2410</v>
       </c>
       <c r="E3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!J$2)</f>
-        <v>28.3959202596198</v>
+        <v>27.9323133982383</v>
       </c>
       <c r="F3" s="18" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!L$2)</f>
-        <v>18.6167686126988</v>
+        <v>18.2996534215605</v>
       </c>
       <c r="G3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!N$2)</f>
-        <v>0.533524948221286</v>
+        <v>0.524814336821755</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!O$2)</f>
-        <v>0.579778098864001</v>
+        <v>0.569902247341969</v>
       </c>
       <c r="I3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!Q$2)</f>
-        <v>0.00897963272653061</v>
+        <v>0.00912867227385892</v>
       </c>
       <c r="J3" s="19" t="n">
         <f aca="false">IF(Calc!$A$2="","",Calc!R$2)</f>
@@ -15323,15 +15339,15 @@
       </c>
       <c r="D4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!D$3)</f>
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="E4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!J$3)</f>
-        <v>18.9686924493554</v>
+        <v>18.158379373849</v>
       </c>
       <c r="F4" s="18" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!L$3)</f>
-        <v>5.78353523099214</v>
+        <v>5.53097334932404</v>
       </c>
       <c r="G4" s="17" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!N$3)</f>
@@ -15339,7 +15355,7 @@
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IF(Calc!$A$3="","",Calc!O$3)</f>
-        <v>0.119307722602947</v>
+        <v>0.11409765960261</v>
       </c>
       <c r="I4" s="19" t="str">
         <f aca="false">IF(Calc!$A$3="","",Calc!Q$3)</f>
@@ -15441,19 +15457,19 @@
       </c>
       <c r="D5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!D$4)</f>
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!J$4)</f>
-        <v>7.06655710764174</v>
+        <v>7.09394686387291</v>
       </c>
       <c r="F5" s="18" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!L$4)</f>
-        <v>5.29934549056207</v>
+        <v>5.32938609847502</v>
       </c>
       <c r="G5" s="17" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!N$4)</f>
-        <v>0.00442173975012507</v>
+        <v>0.00443887827628835</v>
       </c>
       <c r="H5" s="17" t="str">
         <f aca="false">IF(Calc!$A$4="","",Calc!O$4)</f>
@@ -15461,7 +15477,7 @@
       </c>
       <c r="I5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!Q$4)</f>
-        <v>0.00726917654263566</v>
+        <v>0.00724111022393822</v>
       </c>
       <c r="J5" s="19" t="n">
         <f aca="false">IF(Calc!$A$4="","",Calc!R$4)</f>
@@ -15559,27 +15575,27 @@
       </c>
       <c r="D6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!D$5)</f>
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="E6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!J$5)</f>
-        <v>129.126213592233</v>
+        <v>125</v>
       </c>
       <c r="F6" s="18" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!L$5)</f>
-        <v>66.7764007866616</v>
+        <v>64.5597033213485</v>
       </c>
       <c r="G6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!N$5)</f>
-        <v>2.0972728959248</v>
+        <v>2.03025477707006</v>
       </c>
       <c r="H6" s="17" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!O$5)</f>
-        <v>0.962483803131051</v>
+        <v>0.930533362830715</v>
       </c>
       <c r="I6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!Q$5)</f>
-        <v>0.00492585813909775</v>
+        <v>0.0050884592815534</v>
       </c>
       <c r="J6" s="19" t="n">
         <f aca="false">IF(Calc!$A$5="","",Calc!R$5)</f>
@@ -15677,15 +15693,15 @@
       </c>
       <c r="D7" s="17" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!D$6)</f>
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!J$6)</f>
-        <v>19.0094175095919</v>
+        <v>19.0791768399023</v>
       </c>
       <c r="F7" s="18" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!L$6)</f>
-        <v>15.6487146639013</v>
+        <v>15.7041402431362</v>
       </c>
       <c r="G7" s="17" t="str">
         <f aca="false">IF(Calc!$A$6="","",Calc!N$6)</f>
@@ -15697,7 +15713,7 @@
       </c>
       <c r="I7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!Q$6)</f>
-        <v>0.0513761467889908</v>
+        <v>0.0511882998171846</v>
       </c>
       <c r="J7" s="19" t="n">
         <f aca="false">IF(Calc!$A$6="","",Calc!R$6)</f>
@@ -15795,27 +15811,27 @@
       </c>
       <c r="D8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!D$7)</f>
-        <v>1930</v>
+        <v>1875</v>
       </c>
       <c r="E8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!J$7)</f>
-        <v>35.3933614524115</v>
+        <v>34.384742343664</v>
       </c>
       <c r="F8" s="18" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!L$7)</f>
-        <v>19.3582927093055</v>
+        <v>18.7812505653328</v>
       </c>
       <c r="G8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!N$7)</f>
-        <v>0.61591563170704</v>
+        <v>0.598363631839741</v>
       </c>
       <c r="H8" s="17" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!O$7)</f>
-        <v>0.258273681238022</v>
+        <v>0.250574923863531</v>
       </c>
       <c r="I8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!Q$7)</f>
-        <v>0.0054432551761658</v>
+        <v>0.00560292399466667</v>
       </c>
       <c r="J8" s="19" t="n">
         <f aca="false">IF(Calc!$A$7="","",Calc!R$7)</f>
@@ -15921,7 +15937,7 @@
       </c>
       <c r="F9" s="18" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!L$8)</f>
-        <v>15.8612819144857</v>
+        <v>15.8562350437179</v>
       </c>
       <c r="G9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!N$8)</f>
@@ -15929,7 +15945,7 @@
       </c>
       <c r="H9" s="17" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!O$8)</f>
-        <v>1.25534238986409</v>
+        <v>1.25494295488493</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">IF(Calc!$A$8="","",Calc!Q$8)</f>
@@ -16031,27 +16047,27 @@
       </c>
       <c r="D10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!D$9)</f>
-        <v>351.5</v>
+        <v>349</v>
       </c>
       <c r="E10" s="18" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!J$9)</f>
-        <v>13.1598652190191</v>
+        <v>13.0662673156121</v>
       </c>
       <c r="F10" s="18" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!L$9)</f>
-        <v>9.70686439958449</v>
+        <v>9.63534834521286</v>
       </c>
       <c r="G10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!N$9)</f>
-        <v>0.2099951281791</v>
+        <v>0.2085015639673</v>
       </c>
       <c r="H10" s="17" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!O$9)</f>
-        <v>0.967130556658977</v>
+        <v>0.960005149459774</v>
       </c>
       <c r="I10" s="19" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!Q$9)</f>
-        <v>0.0284495021337127</v>
+        <v>0.0286532951289398</v>
       </c>
       <c r="J10" s="19" t="n">
         <f aca="false">IF(Calc!$A$9="","",Calc!R$9)</f>
@@ -16149,27 +16165,27 @@
       </c>
       <c r="D11" s="17" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!D$10)</f>
-        <v>12600</v>
+        <v>12080</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!J$10)</f>
-        <v>69.4635867467887</v>
+        <v>66.5968355477149</v>
       </c>
       <c r="F11" s="18" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!L$10)</f>
-        <v>27.8072395820418</v>
+        <v>26.6362056343231</v>
       </c>
       <c r="G11" s="17" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!N$10)</f>
-        <v>0.412180717212366</v>
+        <v>0.395170084438523</v>
       </c>
       <c r="H11" s="17" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!O$10)</f>
-        <v>0.673215573973069</v>
+        <v>0.644864745084447</v>
       </c>
       <c r="I11" s="19" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!Q$10)</f>
-        <v>0.00255555555555556</v>
+        <v>0.00266556291390729</v>
       </c>
       <c r="J11" s="19" t="n">
         <f aca="false">IF(Calc!$A$10="","",Calc!R$10)</f>
@@ -16267,27 +16283,27 @@
       </c>
       <c r="D12" s="17" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!D$11)</f>
-        <v>2830</v>
+        <v>2810</v>
       </c>
       <c r="E12" s="18" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!J$11)</f>
-        <v>252.453166815343</v>
+        <v>250.669045495094</v>
       </c>
       <c r="F12" s="18" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!L$11)</f>
-        <v>84.8966779115856</v>
+        <v>84.1612175987908</v>
       </c>
       <c r="G12" s="17" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!N$11)</f>
-        <v>0.448157407476818</v>
+        <v>0.444990217317971</v>
       </c>
       <c r="H12" s="17" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!O$11)</f>
-        <v>0.856387233920905</v>
+        <v>0.848968347358714</v>
       </c>
       <c r="I12" s="19" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!Q$11)</f>
-        <v>0.000176686272084806</v>
+        <v>0.000177943825622776</v>
       </c>
       <c r="J12" s="19" t="n">
         <f aca="false">IF(Calc!$A$11="","",Calc!R$11)</f>
@@ -16385,11 +16401,11 @@
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">IF(Calc!$A$12="","",Calc!D$12)</f>
-        <v>707</v>
+        <v>670</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">IF(Calc!$A$12="","",Calc!J$12)</f>
-        <v>73.3402489626556</v>
+        <v>69.5020746887967</v>
       </c>
       <c r="F13" s="18" t="str">
         <f aca="false">IF(Calc!$A$12="","",Calc!L$12)</f>
@@ -16397,7 +16413,7 @@
       </c>
       <c r="G13" s="17" t="n">
         <f aca="false">IF(Calc!$A$12="","",Calc!N$12)</f>
-        <v>0.275156711514671</v>
+        <v>0.260756713882361</v>
       </c>
       <c r="H13" s="17" t="str">
         <f aca="false">IF(Calc!$A$12="","",Calc!O$12)</f>
@@ -16503,27 +16519,27 @@
       </c>
       <c r="D14" s="17" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!D$13)</f>
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="E14" s="18" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!J$13)</f>
-        <v>140.169491525424</v>
+        <v>139.322033898305</v>
       </c>
       <c r="F14" s="18" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!L$13)</f>
-        <v>38.3893916081318</v>
+        <v>38.0795650980884</v>
       </c>
       <c r="G14" s="17" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!N$13)</f>
-        <v>0.361631310758556</v>
+        <v>0.359444906219508</v>
       </c>
       <c r="H14" s="17" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!O$13)</f>
-        <v>0.249183234772068</v>
+        <v>0.247172169507507</v>
       </c>
       <c r="I14" s="19" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!Q$13)</f>
-        <v>0.00120939773881499</v>
+        <v>0.00121675417274939</v>
       </c>
       <c r="J14" s="19" t="n">
         <f aca="false">IF(Calc!$A$13="","",Calc!R$13)</f>
@@ -16621,15 +16637,15 @@
       </c>
       <c r="D15" s="17" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!D$14)</f>
-        <v>1800</v>
+        <v>1670</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!J$14)</f>
-        <v>160.57091882248</v>
+        <v>148.974130240856</v>
       </c>
       <c r="F15" s="18" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!L$14)</f>
-        <v>16.4929840803793</v>
+        <v>15.27575168953</v>
       </c>
       <c r="G15" s="17" t="str">
         <f aca="false">IF(Calc!$A$14="","",Calc!N$14)</f>
@@ -16637,7 +16653,7 @@
       </c>
       <c r="H15" s="17" t="n">
         <f aca="false">IF(Calc!$A$14="","",Calc!O$14)</f>
-        <v>0.150423583295238</v>
+        <v>0.139321865313686</v>
       </c>
       <c r="I15" s="19" t="str">
         <f aca="false">IF(Calc!$A$14="","",Calc!Q$14)</f>
@@ -16739,19 +16755,19 @@
       </c>
       <c r="D16" s="17" t="n">
         <f aca="false">IF(Calc!$A$15="","",Calc!D$15)</f>
-        <v>142.5</v>
+        <v>140.5</v>
       </c>
       <c r="E16" s="18" t="n">
         <f aca="false">IF(Calc!$A$15="","",Calc!J$15)</f>
-        <v>21.3323353293413</v>
+        <v>21.0329341317365</v>
       </c>
       <c r="F16" s="18" t="n">
         <f aca="false">IF(Calc!$A$15="","",Calc!L$15)</f>
-        <v>19.962869925509</v>
+        <v>19.6810153834292</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">IF(Calc!$A$15="","",Calc!N$15)</f>
-        <v>0.192659552689493</v>
+        <v>0.189955558967535</v>
       </c>
       <c r="H16" s="17" t="str">
         <f aca="false">IF(Calc!$A$15="","",Calc!O$15)</f>
@@ -16857,15 +16873,15 @@
       </c>
       <c r="D17" s="17" t="n">
         <f aca="false">IF(Calc!$A$16="","",Calc!D$16)</f>
-        <v>4720</v>
+        <v>4585</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">IF(Calc!$A$16="","",Calc!J$16)</f>
-        <v>77.7722853847421</v>
+        <v>75.5478662053057</v>
       </c>
       <c r="F17" s="18" t="n">
         <f aca="false">IF(Calc!$A$16="","",Calc!L$16)</f>
-        <v>38.7539700372331</v>
+        <v>37.5800004532842</v>
       </c>
       <c r="G17" s="17" t="str">
         <f aca="false">IF(Calc!$A$16="","",Calc!N$16)</f>
@@ -16873,11 +16889,11 @@
       </c>
       <c r="H17" s="17" t="n">
         <f aca="false">IF(Calc!$A$16="","",Calc!O$16)</f>
-        <v>0.340171929733817</v>
+        <v>0.329867140355153</v>
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">IF(Calc!$A$16="","",Calc!Q$16)</f>
-        <v>0.0114407240402542</v>
+        <v>0.01177758287241</v>
       </c>
       <c r="J17" s="19" t="n">
         <f aca="false">IF(Calc!$A$16="","",Calc!R$16)</f>
@@ -16975,11 +16991,11 @@
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">IF(Calc!$A$17="","",Calc!D$17)</f>
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="E18" s="18" t="n">
         <f aca="false">IF(Calc!$A$17="","",Calc!J$17)</f>
-        <v>33.962962962963</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="F18" s="18" t="str">
         <f aca="false">IF(Calc!$A$17="","",Calc!L$17)</f>
@@ -17101,7 +17117,7 @@
       </c>
       <c r="F19" s="18" t="n">
         <f aca="false">IF(Calc!$A$18="","",Calc!L$18)</f>
-        <v>13.502922395845</v>
+        <v>13.4943202420321</v>
       </c>
       <c r="G19" s="17" t="n">
         <f aca="false">IF(Calc!$A$18="","",Calc!N$18)</f>
@@ -17109,7 +17125,7 @@
       </c>
       <c r="H19" s="17" t="n">
         <f aca="false">IF(Calc!$A$18="","",Calc!O$18)</f>
-        <v>0.486739337090587</v>
+        <v>0.486429255574769</v>
       </c>
       <c r="I19" s="19" t="n">
         <f aca="false">IF(Calc!$A$18="","",Calc!Q$18)</f>
@@ -17211,7 +17227,7 @@
       </c>
       <c r="D20" s="17" t="n">
         <f aca="false">IF(Calc!$A$19="","",Calc!D$19)</f>
-        <v>2065</v>
+        <v>1990</v>
       </c>
       <c r="E20" s="18" t="str">
         <f aca="false">IF(Calc!$A$19="","",Calc!J$19)</f>
@@ -17219,7 +17235,7 @@
       </c>
       <c r="F20" s="18" t="n">
         <f aca="false">IF(Calc!$A$19="","",Calc!L$19)</f>
-        <v>7.18436287624705</v>
+        <v>6.93025179175527</v>
       </c>
       <c r="G20" s="17" t="str">
         <f aca="false">IF(Calc!$A$19="","",Calc!N$19)</f>
@@ -17329,15 +17345,15 @@
       </c>
       <c r="D21" s="17" t="n">
         <f aca="false">IF(Calc!$A$20="","",Calc!D$20)</f>
-        <v>461.5</v>
+        <v>437.5</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">IF(Calc!$A$20="","",Calc!J$20)</f>
-        <v>54.2303172737955</v>
+        <v>51.4101057579318</v>
       </c>
       <c r="F21" s="18" t="n">
         <f aca="false">IF(Calc!$A$20="","",Calc!L$20)</f>
-        <v>49.9273188829544</v>
+        <v>47.2993555635156</v>
       </c>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(Calc!$A$20="","",Calc!N$20)</f>
@@ -17345,11 +17361,11 @@
       </c>
       <c r="H21" s="17" t="n">
         <f aca="false">IF(Calc!$A$20="","",Calc!O$20)</f>
-        <v>1.70616144567848</v>
+        <v>1.6163563089998</v>
       </c>
       <c r="I21" s="19" t="n">
         <f aca="false">IF(Calc!$A$20="","",Calc!Q$20)</f>
-        <v>0.00433369447453955</v>
+        <v>0.00457142857142857</v>
       </c>
       <c r="J21" s="19" t="n">
         <f aca="false">IF(Calc!$A$20="","",Calc!R$20)</f>
@@ -18135,36 +18151,36 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="75">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="77">
       <formula>"N/M"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3:G26">
-    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="76">
+    <cfRule type="cellIs" priority="11" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="78">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H26">
-    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="76">
+    <cfRule type="cellIs" priority="12" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="78">
       <formula>1.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N26">
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="76">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="78">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="77">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="79">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="77">
+    <cfRule type="cellIs" priority="15" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="79">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="78">
+    <cfRule type="cellIs" priority="16" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:AC26">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="79">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="81">
       <formula>$C3="池子"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20421,7 +20437,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EFAD4A61-AADA-40E2-8DD4-B0F140EBA020}</x14:id>
+          <x14:id>{209866BD-5753-46E5-8C55-1A304C848A22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -20437,16 +20453,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G17">
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="76">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="78">
       <formula>"成長且加速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="77">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="79">
       <formula>"成長但減速"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="77">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="79">
       <formula>"衰退但收斂"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="78">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
       <formula>"衰退且惡化"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20487,47 +20503,47 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5:O17">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>$O5="預估"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:B28">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C24:C28">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D24:D28">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:E28">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A24,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:B37">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,1,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C33:C37">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,2,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D33:D37">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,3,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33:E37">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="80">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
       <formula>COUNTIFS(Raw_Q!$A$2:$A$600,Stock_Card!$B$2,Raw_Q!$C$2:$C$600,$A33,Raw_Q!$D$2:$D$600,4,Raw_Q!$F$2:$F$600,"Y")&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20552,7 +20568,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EFAD4A61-AADA-40E2-8DD4-B0F140EBA020}">
+          <x14:cfRule type="dataBar" id="{209866BD-5753-46E5-8C55-1A304C848A22}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -20655,11 +20671,11 @@
       </c>
       <c r="H4" s="47" t="n">
         <f aca="true">IF($A4="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A4,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I4" s="67" t="n">
         <f aca="false">IF($A4="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A4,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J4" s="72" t="str">
         <f aca="true">IF($A4="","",IF($B4=0,"未抓取",IF($B4&lt;$C4,"需補歷史 ("&amp;($C4-$B4)&amp;" 季)",IF(TODAY()&gt;$G4,"待更新財報","OK"))))</f>
@@ -20697,11 +20713,11 @@
       </c>
       <c r="H5" s="47" t="n">
         <f aca="true">IF($A5="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A5,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I5" s="67" t="n">
         <f aca="false">IF($A5="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A5,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J5" s="72" t="str">
         <f aca="true">IF($A5="","",IF($B5=0,"未抓取",IF($B5&lt;$C5,"需補歷史 ("&amp;($C5-$B5)&amp;" 季)",IF(TODAY()&gt;$G5,"待更新財報","OK"))))</f>
@@ -20739,11 +20755,11 @@
       </c>
       <c r="H6" s="47" t="n">
         <f aca="true">IF($A6="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A6,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I6" s="67" t="n">
         <f aca="false">IF($A6="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A6,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J6" s="72" t="str">
         <f aca="true">IF($A6="","",IF($B6=0,"未抓取",IF($B6&lt;$C6,"需補歷史 ("&amp;($C6-$B6)&amp;" 季)",IF(TODAY()&gt;$G6,"待更新財報","OK"))))</f>
@@ -20781,11 +20797,11 @@
       </c>
       <c r="H7" s="47" t="n">
         <f aca="true">IF($A7="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A7,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I7" s="67" t="n">
         <f aca="false">IF($A7="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A7,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J7" s="72" t="str">
         <f aca="true">IF($A7="","",IF($B7=0,"未抓取",IF($B7&lt;$C7,"需補歷史 ("&amp;($C7-$B7)&amp;" 季)",IF(TODAY()&gt;$G7,"待更新財報","OK"))))</f>
@@ -20823,11 +20839,11 @@
       </c>
       <c r="H8" s="47" t="n">
         <f aca="true">IF($A8="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A8,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I8" s="67" t="n">
         <f aca="false">IF($A8="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A8,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J8" s="72" t="str">
         <f aca="true">IF($A8="","",IF($B8=0,"未抓取",IF($B8&lt;$C8,"需補歷史 ("&amp;($C8-$B8)&amp;" 季)",IF(TODAY()&gt;$G8,"待更新財報","OK"))))</f>
@@ -20865,11 +20881,11 @@
       </c>
       <c r="H9" s="47" t="n">
         <f aca="true">IF($A9="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A9,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I9" s="67" t="n">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A9,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J9" s="72" t="str">
         <f aca="true">IF($A9="","",IF($B9=0,"未抓取",IF($B9&lt;$C9,"需補歷史 ("&amp;($C9-$B9)&amp;" 季)",IF(TODAY()&gt;$G9,"待更新財報","OK"))))</f>
@@ -20907,11 +20923,11 @@
       </c>
       <c r="H10" s="47" t="n">
         <f aca="true">IF($A10="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A10,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I10" s="67" t="n">
         <f aca="false">IF($A10="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A10,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J10" s="72" t="str">
         <f aca="true">IF($A10="","",IF($B10=0,"未抓取",IF($B10&lt;$C10,"需補歷史 ("&amp;($C10-$B10)&amp;" 季)",IF(TODAY()&gt;$G10,"待更新財報","OK"))))</f>
@@ -20949,11 +20965,11 @@
       </c>
       <c r="H11" s="47" t="n">
         <f aca="true">IF($A11="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A11,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I11" s="67" t="n">
         <f aca="false">IF($A11="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A11,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J11" s="72" t="str">
         <f aca="true">IF($A11="","",IF($B11=0,"未抓取",IF($B11&lt;$C11,"需補歷史 ("&amp;($C11-$B11)&amp;" 季)",IF(TODAY()&gt;$G11,"待更新財報","OK"))))</f>
@@ -20991,11 +21007,11 @@
       </c>
       <c r="H12" s="47" t="n">
         <f aca="true">IF($A12="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A12,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I12" s="67" t="n">
         <f aca="false">IF($A12="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A12,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J12" s="72" t="str">
         <f aca="true">IF($A12="","",IF($B12=0,"未抓取",IF($B12&lt;$C12,"需補歷史 ("&amp;($C12-$B12)&amp;" 季)",IF(TODAY()&gt;$G12,"待更新財報","OK"))))</f>
@@ -21033,11 +21049,11 @@
       </c>
       <c r="H13" s="47" t="n">
         <f aca="true">IF($A13="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A13,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I13" s="67" t="n">
         <f aca="false">IF($A13="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A13,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J13" s="72" t="str">
         <f aca="true">IF($A13="","",IF($B13=0,"未抓取",IF($B13&lt;$C13,"需補歷史 ("&amp;($C13-$B13)&amp;" 季)",IF(TODAY()&gt;$G13,"待更新財報","OK"))))</f>
@@ -21075,11 +21091,11 @@
       </c>
       <c r="H14" s="47" t="n">
         <f aca="true">IF($A14="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A14,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I14" s="67" t="n">
         <f aca="false">IF($A14="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A14,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J14" s="72" t="str">
         <f aca="true">IF($A14="","",IF($B14=0,"未抓取",IF($B14&lt;$C14,"需補歷史 ("&amp;($C14-$B14)&amp;" 季)",IF(TODAY()&gt;$G14,"待更新財報","OK"))))</f>
@@ -21117,11 +21133,11 @@
       </c>
       <c r="H15" s="47" t="n">
         <f aca="true">IF($A15="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A15,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I15" s="67" t="n">
         <f aca="false">IF($A15="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A15,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J15" s="72" t="str">
         <f aca="true">IF($A15="","",IF($B15=0,"未抓取",IF($B15&lt;$C15,"需補歷史 ("&amp;($C15-$B15)&amp;" 季)",IF(TODAY()&gt;$G15,"待更新財報","OK"))))</f>
@@ -21159,11 +21175,11 @@
       </c>
       <c r="H16" s="47" t="n">
         <f aca="true">IF($A16="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A16,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I16" s="67" t="n">
         <f aca="false">IF($A16="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A16,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J16" s="72" t="str">
         <f aca="true">IF($A16="","",IF($B16=0,"未抓取",IF($B16&lt;$C16,"需補歷史 ("&amp;($C16-$B16)&amp;" 季)",IF(TODAY()&gt;$G16,"待更新財報","OK"))))</f>
@@ -21201,11 +21217,11 @@
       </c>
       <c r="H17" s="47" t="n">
         <f aca="true">IF($A17="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A17,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I17" s="67" t="n">
         <f aca="false">IF($A17="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A17,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J17" s="72" t="str">
         <f aca="true">IF($A17="","",IF($B17=0,"未抓取",IF($B17&lt;$C17,"需補歷史 ("&amp;($C17-$B17)&amp;" 季)",IF(TODAY()&gt;$G17,"待更新財報","OK"))))</f>
@@ -21243,11 +21259,11 @@
       </c>
       <c r="H18" s="47" t="n">
         <f aca="true">IF($A18="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A18,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I18" s="67" t="n">
         <f aca="false">IF($A18="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A18,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J18" s="72" t="str">
         <f aca="true">IF($A18="","",IF($B18=0,"未抓取",IF($B18&lt;$C18,"需補歷史 ("&amp;($C18-$B18)&amp;" 季)",IF(TODAY()&gt;$G18,"待更新財報","OK"))))</f>
@@ -21285,11 +21301,11 @@
       </c>
       <c r="H19" s="47" t="n">
         <f aca="true">IF($A19="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A19,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I19" s="67" t="n">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A19,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J19" s="72" t="str">
         <f aca="true">IF($A19="","",IF($B19=0,"未抓取",IF($B19&lt;$C19,"需補歷史 ("&amp;($C19-$B19)&amp;" 季)",IF(TODAY()&gt;$G19,"待更新財報","OK"))))</f>
@@ -21327,11 +21343,11 @@
       </c>
       <c r="H20" s="47" t="n">
         <f aca="true">IF($A20="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A20,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I20" s="67" t="n">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A20,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J20" s="72" t="str">
         <f aca="true">IF($A20="","",IF($B20=0,"未抓取",IF($B20&lt;$C20,"需補歷史 ("&amp;($C20-$B20)&amp;" 季)",IF(TODAY()&gt;$G20,"待更新財報","OK"))))</f>
@@ -21369,11 +21385,11 @@
       </c>
       <c r="H21" s="47" t="n">
         <f aca="true">IF($A21="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A21,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I21" s="67" t="n">
         <f aca="false">IF($A21="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A21,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J21" s="72" t="str">
         <f aca="true">IF($A21="","",IF($B21=0,"未抓取",IF($B21&lt;$C21,"需補歷史 ("&amp;($C21-$B21)&amp;" 季)",IF(TODAY()&gt;$G21,"待更新財報","OK"))))</f>
@@ -21411,11 +21427,11 @@
       </c>
       <c r="H22" s="47" t="n">
         <f aca="true">IF($A22="","",IFERROR(INDEX(Raw_Price!$D$2:$D$100,MATCH($A22,Raw_Price!$A$2:$A$100,0))-TODAY(),""))</f>
-        <v>-46275</v>
+        <v>-46276</v>
       </c>
       <c r="I22" s="67" t="n">
         <f aca="false">IF($A22="","",IFERROR(INDEX(Raw_Price!$E$2:$E$100,MATCH($A22,Raw_Price!$A$2:$A$100,0)),""))</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="J22" s="72" t="str">
         <f aca="true">IF($A22="","",IF($B22=0,"未抓取",IF($B22&lt;$C22,"需補歷史 ("&amp;($C22-$B22)&amp;" 季)",IF(TODAY()&gt;$G22,"待更新財報","OK"))))</f>
@@ -21639,18 +21655,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J4:J27">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="81">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="83">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="82">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="84">
       <formula>"待更新財報"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="83">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="85">
       <formula>ISNUMBER(SEARCH("補歷史",$J4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H27">
-    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="84">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="86">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -60148,7 +60164,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60168,7 +60184,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60188,7 +60204,7 @@
         <v>23</v>
       </c>
       <c r="F4" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60228,7 +60244,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60248,7 +60264,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60288,7 +60304,7 @@
         <v>16</v>
       </c>
       <c r="F9" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60308,7 +60324,7 @@
         <v>9</v>
       </c>
       <c r="F10" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60320,7 +60336,7 @@
       <c r="D11" s="78"/>
       <c r="E11" s="77"/>
       <c r="F11" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60340,7 +60356,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60360,7 +60376,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60380,7 +60396,7 @@
         <v>9</v>
       </c>
       <c r="F14" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60392,7 +60408,7 @@
       <c r="D15" s="78"/>
       <c r="E15" s="77"/>
       <c r="F15" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60412,7 +60428,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60490,7 +60506,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60530,7 +60546,7 @@
         <v>6</v>
       </c>
       <c r="F22" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60570,7 +60586,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60590,7 +60606,7 @@
         <v>3</v>
       </c>
       <c r="F25" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60610,7 +60626,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60630,7 +60646,7 @@
         <v>7</v>
       </c>
       <c r="F27" s="78" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
